--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -494,7 +494,7 @@
     <tabColor rgb="70AD47"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4207,24 +4207,456 @@
         </is>
       </c>
     </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-034</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurement</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بالا</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پس از Init یا شکست ADC، snapshot.valid=false</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0V / 0V</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همه LED و بوق خاموش؛ آلارم باتری false</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">safe-off و بدون BatteryRun</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-035</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurement</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بالا</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snapshot.valid=true؛ input_present=false؛ vbat=28000mV</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0V / 28V</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BatteryRun؛ آلارم کم‌باتری false</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ورودی قطع و باتری فول معتبر</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-036</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputOk</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بالا</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snapshot.valid=true؛ input_present=true؛ vbat=28000mV</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24V / 28V</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سبز دائم؛ زرد/قرمز/بوق خاموش</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">منبع متصل و باتری فول</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-037</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charging</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">متوسط</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snapshot.valid=true؛ input_present=true؛ vbat=25000mV</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24V / 25V</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سبز دائم؛ زرد چشمک؛ بوق خاموش</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">باتری در حال شارژ</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-038</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OverVoltage</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بالا</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snapshot.valid=true؛ v_in&gt;28000mV</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29V / 25V</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قرمز چشمک و بوق طبق جدول</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آستانه از v_in معتبر</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-039</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LowBattery flag</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بالا</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snapshot.valid=true؛ input_present=false؛ vbat&lt;21000mV</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0V / 20.9V</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low Battery Alarm فعال؛ UiBatteryAlarmIssued=true</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فلگ سطحی برای مصرف Changeover</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:S44"/>
+  <autoFilter ref="A4:S50"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="C5:C44">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="C5:C50">
       <formula1>بالا,متوسط,پایین</formula1>
       <promptTitle>اولویت</promptTitle>
       <prompt>اولویت تست را انتخاب کن.</prompt>
       <errorTitle>مقدار نامعتبر</errorTitle>
       <error>یکی از گزینه‌های فهرست را انتخاب کن.</error>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="N5:N44">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="N5:N50">
       <formula1>در انتظار,قبول,رد,مسدود,نیاز به تکرار</formula1>
       <promptTitle>وضعیت تست</promptTitle>
       <prompt>بعد از مشاهدهٔ نتیجه انتخاب کن.</prompt>
       <errorTitle>مقدار نامعتبر</errorTitle>
       <error>وضعیت را از فهرست انتخاب کن.</error>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="S5:S44">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" sqref="S5:S50">
       <formula1>در انتظار,تأیید شد,تأیید نشد,نیاز به بررسی</formula1>
       <promptTitle>تأیید تست</promptTitle>
       <prompt>پس از ثبت نتیجه تصمیم بگیر.</prompt>
@@ -4232,32 +4664,32 @@
       <error>وضعیت تأیید را از فهرست انتخاب کن.</error>
     </dataValidation>
   </dataValidations>
-  <conditionalFormatting sqref="N5:N44">
+  <conditionalFormatting sqref="N5:N50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>N5="قبول"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N44">
+  <conditionalFormatting sqref="N5:N50">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>N5="رد"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N44">
+  <conditionalFormatting sqref="N5:N50">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>N5="مسدود"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N44">
+  <conditionalFormatting sqref="N5:N50">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>N5="در انتظار"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S44">
+  <conditionalFormatting sqref="S5:S50">
     <cfRule type="expression" dxfId="0" priority="5">
       <formula>S5="تأیید شد"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S44">
+  <conditionalFormatting sqref="S5:S50">
     <cfRule type="expression" dxfId="1" priority="6">
       <formula>S5="تأیید نشد"</formula>
     </cfRule>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
@@ -4656,8 +4656,8 @@
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -4679,8 +4679,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -4702,8 +4702,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -4725,8 +4725,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -4744,8 +4744,8 @@
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -4763,8 +4763,8 @@
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
+          <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -15,7 +15,7 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,11 +107,6 @@
     </font>
     <font>
       <color rgb="009C0006"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00404040"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="12">
@@ -252,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -322,7 +317,6 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -697,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -721,14 +715,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>برگه تست و اعتبارسنجی عملی ماژول UI — LED/BUZZER با هیسترزیس 2% + فاز-حفاظ 25V</t>
+          <t>برگه تست و اعتبارسنجی عملی ماژول UI — BatteryRun 2%+0/1, Charging 5%, InputOk 100/95</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PA3/ADC1_IN3/raw[2]/v_bat24_mv → BatteryRun | PA2/ADC1_IN2/raw[1]/v_in_mv → ورودی/McuPowerPath | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
+          <t>PA3/ADC1_IN3/raw2/v_bat24 → BatteryRun/Charging | PA2/ADC1_IN2/raw1/v_in → ورودی | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
         </is>
       </c>
     </row>
@@ -757,7 +751,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>ولیدیشن UI با snapshot واقعی: هیسترزیس درصد باتری 2% + رفتار خاص 0/1، حفظ فاز چشمک سبز، InputOk/Charging non-blocking فاز-محور، و بررسی RTOS/Stack.دامنه فقط LED/BUZZER؛ ADC فعال و snapshot از Measurement.</t>
+          <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -779,7 +773,7 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>منبع و mapping (نباید تغییر کند)</t>
+          <t>منبع و mapping</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -798,10 +792,10 @@
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT → raw[2] → snapshot.v_bat24_mv → UI BatteryRun (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → BSP_ADC_CHANNEL_24V_IN → raw[1] → snapshot.v_in_mv → ورودی/McuPowerPath (PA2 فقط v_in). PB4 MCU_INT_24_IN EXTI وصل/قطع، PB5 Q1 فقط McuPowerPath، PB11 Q17 فقط Changeover.</t>
+          <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
@@ -823,7 +817,7 @@
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>هیسترزیس درصد باتری (BatteryRun-only)</t>
+          <t>BatteryRun 2%+0/1</t>
         </is>
       </c>
       <c r="B7" s="4" t="n"/>
@@ -845,7 +839,7 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>stable 57, raw 56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable 0 تا raw&gt;=2 روی 0 سپس →1، stable 1: raw0→0، &gt;=3→2، else 1. ثابت‌ها: UI_BATTERY_PERCENT_HYSTERESIS_PERCENT=2, ZERO_EXIT=2, ONE_EXIT=3 در ui_led.h (بدون عدد جادویی).</t>
+          <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -867,7 +861,7 @@
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>رفتار 0% و 1% جدا</t>
+          <t>Charging 5%</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -889,7 +883,7 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>0%: raw0 → بحرانی، یک بوق 10s سپس همه LED خاموش تا خروج از 0% (stable0→1 با raw&gt;=2). 1%: سه‌بوق هر 20s با چشمک سبز، stable1→0 با raw0، →2 با raw&gt;=3. نویز 0↔1 باعث restart بحرانی نمی‌شود.</t>
+          <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -911,7 +905,7 @@
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>حفظ فاز چشمک سبز</t>
+          <t>فول InputOk/Charging 100/95</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -930,10 +924,10 @@
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>تغییر stable نباید BOOL__G__UiBatteryGreenOn و phaseStartTick را reset کند؛ زمان جدید از مرز فاز بعدی اعمال شود. فقط ورود/خروج BatteryRun، snapshot invalid/NULL یا Ui_Init ریست فاز مجاز است. فرمول: greenOff=(100-stable)*period/100 (min10), greenOn=1000-greenOff.</t>
+          <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -955,7 +949,7 @@
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>InputOk/Charging non-blocking</t>
+          <t>حفظ فاز</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -977,7 +971,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>InputOk (سبز ثابت) و Charging (زرد چشمک) قبلاً delay 500ms/1000ms مسدودکننده داشتند که واکنش UI را کند می‌کرد. اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick هر 10ms سریع برمی‌گردد و حلقه task_ui (10ms) polling را می‌دهد. ظاهر سناریوها بدون تغییر.</t>
+          <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -999,7 +993,7 @@
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>RTOS و حافظه</t>
+          <t>غیرمسدودکننده</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1018,10 +1012,10 @@
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>همه taskهای فعال از حافظه static (cb_mem/stack_mem)، SUPPORT_DYNAMIC_ALLOCATION=0، stack mapping words/bytes صحیح، high-water via osThreadGetStackSpace, بدون queue/timer/mutex جدید برای هیسترزیس, task_ui بدون delay طولانی و بدون starvation, Measurement_GetSnapshot قفل/کپی ایمن.</t>
+          <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -1040,15 +1034,61 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="n"/>
     </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>RTOS و حافظه</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="A13:P13"/>
     <mergeCell ref="A14:P14"/>
     <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A17:P17"/>
     <mergeCell ref="A9:P9"/>
+    <mergeCell ref="A18:P18"/>
     <mergeCell ref="A8:P8"/>
     <mergeCell ref="A6:P6"/>
     <mergeCell ref="A12:P12"/>
@@ -1070,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1095,21 +1135,21 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>برنامهٔ تست عملی — ماژول UI (هیسترزیس 2% + فاز BatteryRun 25V, 0/1, InputOk/Charging non-blocking)</t>
+          <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>ورودی‌ها mV، درصد 0-100، زمان ms. BatteryRun از PA3/v_bat24 با stablePercent، ورودی از PA2/v_in. PB5/Q1 و PB11/Q17 بدون تغییر.</t>
+          <t>ورودی mV، درصد 0-100، زمان ms. BatteryRun PA3 stable2%، Charging PA3 stable5% و زرد، Full 100/95 با raw.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable percent, ورودی present/overvoltage, و فاز LED/بوق را با اسکوپ/تایمر 10ms بسنج. InputOk/Charging باید non-blocking و سریع برگردند.</t>
+          <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable, ورودی present/overvoltage, فاز LED/بوق با اسکوپ 10ms. InputOk/Charging سریع برگردد.</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1258,12 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>برد روشن, Measurement valid</t>
+          <t>برد روشن, valid</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>PA3 با 2.0V pin (counts 2482) را اعمال کن؛ raw[2] و snapshot.v_bat24_mv را خوانده و درصد BatteryVoltageToPercent را حساب کن.</t>
+          <t>PA3 2.0V pin (counts 2482) اعمال؛ raw2 و v_bat24_mv خوانده و percent حساب.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -1238,7 +1278,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>v_bat24_mv≈22352, raw→percent ~17% (21000=0,28000=100). PA3 فقط v_bat, PA2 فقط v_in</t>
+          <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1248,7 +1288,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>PASS: v_bat از PA3/raw[2] و فرمول 21000-28000. FAIL: استفاده از v_in برای BatteryRun</t>
+          <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr"/>
@@ -1271,7 +1311,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>BatteryRun hysteresis 25V 56/57/58</t>
+          <t>BatteryRun 2% 56/57/58</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1286,12 +1326,12 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>باتری 25V (raw≈57%): v_bat 25000→ raw57. سپس نویز 56 و 58 را هر 100ms اعمال کن (ADC jitter). سبز را با اسکوپ بسنج.</t>
+          <t>باتری 25V raw57: v_bat25000→57. نویز 56 و 58 هر 100ms، سبز با اسکوپ.</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>v_bat 25000 (raw57) → 56/58 jitter</t>
+          <t>v_bat25000 raw57 →56/58 jitter</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -1301,17 +1341,17 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>stable 57 حفظ, green Off 430ms On 570ms ثابت, فاز reset نشود (GreenOn و startTick حفظ)</t>
+          <t>stable57 حفظ, green Off430 On570 ثابت, فاز reset نشود</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>فاز حفظ، On/Off ثابت</t>
+          <t>فاز حفظ On/Off ثابت</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>PASS: stable 57, فاز حفظ, Off430 On570. FAIL: stable 56/58 یا فاز restart و Off طولانی</t>
+          <t>PASS: stable57 فاز حفظ. FAIL: stable56/58 یا reset</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr"/>
@@ -1334,7 +1374,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>BatteryRun hysteresis 57→55</t>
+          <t>BatteryRun 57→55</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1344,17 +1384,17 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>stable 57</t>
+          <t>stable57</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>raw را به 55 (v_bat≈24850) کاهش ده.</t>
+          <t>raw به 55 (v_bat≈24850) کاهش.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>raw 55</t>
+          <t>raw55</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1364,7 +1404,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>stable →55, green Off 450ms On 550ms از مرز فاز بعدی, فاز فعلی تا پایان حفظ</t>
+          <t>stable→55, green Off450 On550 از مرز بعدی, فاز حفظ</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1374,7 +1414,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>PASS: stable 55 و فاز از مرز بعدی. FAIL: حفظ 57 یا reset فوری</t>
+          <t>PASS: stable55. FAIL: 57 حفظ</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr"/>
@@ -1397,7 +1437,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>BatteryRun hysteresis 57→59</t>
+          <t>BatteryRun 57→59</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1407,17 +1447,17 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>stable 57</t>
+          <t>stable57</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>raw به 59 (v_bat≈25130) افزایش.</t>
+          <t>raw به 59 (25130) افزایش.</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>raw 59</t>
+          <t>raw59</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1427,17 +1467,17 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>stable 59, Off 410 On 590, فاز حفظ</t>
+          <t>stable59 Off410 On590 فاز حفظ</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>حفظ فاز</t>
+          <t>حفظ</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>PASS: stable 59. FAIL: 57 حفظ</t>
+          <t>PASS: stable59. FAIL: 57 حفظ</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr"/>
@@ -1460,7 +1500,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>0% critical — raw0</t>
+          <t>0% critical raw0</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1470,17 +1510,17 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>BatteryRun, باتری 21V یا کمتر</t>
+          <t>BatteryRun 21V یا کمتر</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>v_bat 21000 (0%) را اعمال کن؛ LED و بوق را مانیتور.</t>
+          <t>v_bat21000 (0%) اعمال؛ LED و بوق مانیتور.</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>v_bat 21000 raw0 stable0</t>
+          <t>v_bat21000 raw0 stable0</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -1490,7 +1530,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>همه LED خاموش، یک بوق 10s سپس بوق خاموش و LED خاموش بماند تا خروج از 0%</t>
+          <t>همه LED خاموش، یک بوق 10s سپس خاموش تا خروج از 0%</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1500,7 +1540,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>PASS: یک 10s سپس خاموش مانده. FAIL: بوق مکرر یا LED روشن</t>
+          <t>PASS: یک 10s سپس خاموش. FAIL: مکرر/LED روشن</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr"/>
@@ -1523,7 +1563,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>0↔1 نویز — no restart</t>
+          <t>0↔1 نویز</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1533,17 +1573,17 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>stable 0 Critical 10s در حال پخش</t>
+          <t>stable0 Critical 10s</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>نویز raw 0→1→0→1 هر 200ms (ADC jitter نزدیک 0).</t>
+          <t>نویز raw0→1→0→1 هر 200ms</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>raw 0/1 jitter</t>
+          <t>raw0/1 jitter</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -1553,7 +1593,7 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>stable 0 حفظ (چون raw1 &lt;2), بوق بحرانی restart نشود, LED خاموش بماند</t>
+          <t>stable0 حفظ (&lt;2) بوق restart نشود LED خاموش</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
@@ -1563,7 +1603,7 @@
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>PASS: بوق یک بار, stable 0. FAIL: restart بوق یا stable 1</t>
+          <t>PASS: یک بار. FAIL: restart</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr"/>
@@ -1586,7 +1626,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>1% independent — raw1</t>
+          <t>1% مستقل raw1</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1596,12 +1636,12 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Stable 0, خروج به 1</t>
+          <t>Stable0 خروج به1</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>raw را از 0 به 1 سپس به 1 نگه دار (v_bat 21070).</t>
+          <t>raw 0→1 سپس نگه (v_bat21070).</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1616,7 +1656,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>stable 1, سه‌بوق هر 20s (2000ms هر بوق) + سبز چشمک (remaining 99% Off990 On10)</t>
+          <t>stable1 سه‌بوق هر20s + سبز Off990 On10</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1626,7 +1666,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>PASS: stable1, سه‌بوق. FAIL: بحرانی 0% یا stable 0</t>
+          <t>PASS: stable1 سه‌بوق. FAIL: بحرانی</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr"/>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>raw1→2 (21000+2%≈21140) را 1s نگه دار.</t>
+          <t>raw1→2 (21140) 1s نگه.</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -1679,7 +1719,7 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>stable1 حفظ (raw2&lt;3), همچنان سه‌بوق</t>
+          <t>stable1 حفظ (raw2&lt;3) همچنان سه‌بوق</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1689,7 +1729,7 @@
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>PASS: stable1 حفظ. FAIL: stable 2</t>
+          <t>PASS: stable1. FAIL: 2</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr"/>
@@ -1712,7 +1752,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>1% →2 خروج با 3</t>
+          <t>1% →2 خروج با3</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1727,7 +1767,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>raw3 (v_bat≈21210) را اعمال.</t>
+          <t>raw3 (21210) اعمال.</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1742,12 +1782,12 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>stable 2, دو بوق هر 60s یا یک بوق؟ (10%&lt;stable&lt;20% → دو بوق)</t>
+          <t>stable2 دو بوق 60s یا یک بوق</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>حفظ فاز</t>
+          <t>حفظ</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
@@ -1775,7 +1815,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>BoardTest — 0% تا 2%</t>
+          <t>BoardTest 0→2</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -1790,7 +1830,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>raw0→2 (21140) را اعمال.</t>
+          <t>raw0→2 (21140) اعمال.</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -1805,7 +1845,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>stable0→1 (ابتدا 1, نه 2)</t>
+          <t>stable0→1 ابتدا 1 نه 2</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1815,7 +1855,7 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>PASS: stable1 نه 2. FAIL: مستقیم 2</t>
+          <t>PASS: 1 نه 2. FAIL: مستقیم 2</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr"/>
@@ -1838,7 +1878,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>InputOk non-blocking</t>
+          <t>Charging 5% 56/57/58</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1848,37 +1888,37 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Input 24V, Battery 28V</t>
+          <t>Charging Input24V Battery25V</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>InputOk را صدا بزن؛ Ui_Tick را 10ms لوپ کن و با اسکوپ زمان بازگشت را بسنج.</t>
+          <t>Charging 25V raw57: نویز 56/57/58 هر 100ms، زرد با اسکوپ.</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>v_in 24000 valid, v_bat 28000</t>
+          <t>v_in24000 v_bat25000 raw57→56/58</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>1s</t>
+          <t>5s</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>سبز ثابت, زرد/قرمز خاموش, بوق خاموش, Ui_Tick &lt;1ms برگردد (نه 500ms delay)</t>
+          <t>chargingStable57 حفظ, yellow On430 Off570 ثابت, فاز reset نشود</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>زرد فاز حفظ</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>PASS: بدون delay 500ms, سریع. FAIL: delay 500ms داخل سناریو</t>
+          <t>PASS: stable57 فاز حفظ. FAIL: 56/58 یا reset</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr"/>
@@ -1901,7 +1941,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Charging non-blocking</t>
+          <t>Charging 5% 53..61</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1911,37 +1951,37 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Input 24V, Battery 25V</t>
+          <t>stable57</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Charging_Tick با battery 25V (57% raw) را هر 10ms صدا بزن؛ زرد چشمک remaining 43% → On 430 Off 570 را با اسکوپ بسنج؛ Ui_Tick باید سریع برگردد.</t>
+          <t>raw به 53 (diff4) سپس 61 (diff4) هر 500ms.</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>v_in 24000, v_bat 25000 raw57</t>
+          <t>raw53 raw61</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>1s each</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>سبز ثابت, زرد چشمک فاز-محور (On430 Off570), بدون delay 1s, فاز حفظ روی تغییر درصد</t>
+          <t>57 حفظ، زرد ثابت</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>زرد فاز حفظ</t>
+          <t>حفظ</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>PASS: زرد non-blocking فاز-محور. FAIL: blocking delay 1s</t>
+          <t>PASS: 57 حفظ. FAIL: تغییر</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr"/>
@@ -1964,7 +2004,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>BatteryRun phase preserve</t>
+          <t>Charging 5% خروج</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1974,37 +2014,37 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>BatteryRun 25V stable57, سبز ON</t>
+          <t>stable57</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>سبز ON در حال 570ms؛ پس از 100ms raw 56 (jitter) → stable 57 حفظ، فاز ON باید تا 570ms ادامه یابد نه restart.</t>
+          <t>raw52 (diff5) و 62 (diff5)</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>On570, jitter 56</t>
+          <t>raw52→62</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>700ms</t>
+          <t>100ms</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>فاز ON تا 570ms حفظ، سپس OFF 430ms</t>
+          <t>stable→52 سپس 62, yellow زمان جدید از مرز بعدی فاز حفظ</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>ON حفظ 570</t>
+          <t>از مرز بعدی</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>PASS: restart نشد. FAIL: فاز از 100ms restart و On طولانی</t>
+          <t>PASS: stable52/62. FAIL: 57 حفظ</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr"/>
@@ -2027,7 +2067,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>InputOverVoltage</t>
+          <t>Charging yellow phase</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -2037,37 +2077,37 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>v_in 28.5V</t>
+          <t>Charging 25V On430</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>v_in 28500 (&gt;28000) را اعمال؛ سپس 27.5V و 26V.</t>
+          <t>زرد ON 430ms؛ پس از 100ms jitter 56 (stable57 حفظ) فاز ON تا 430 حفظ.</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>v_in 28500→27500→26000</t>
+          <t>On430 jitter56</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>سبز ثابت, زرد خاموش, قرمز 50% 1s, بوق 1s هر10s؛ 27.5V حفظ، 27V پاک</t>
+          <t>ON تا 430 حفظ سپس OFF</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>قرمز 50%</t>
+          <t>ON حفظ</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>PASS: hysteresis 27/28. FAIL: خاموش زود</t>
+          <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr"/>
@@ -2090,7 +2130,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Snapshot invalid</t>
+          <t>Full 100/95 enter</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2100,37 +2140,37 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>هر سناریو</t>
+          <t>Charging valid</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>snapshot.valid=false یا NULL را تزریق.</t>
+          <t>v_bat خام 99→100 اعمال؛ InputOk/Charging تشخیص.</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>valid false</t>
+          <t>raw99→100</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>500ms</t>
+          <t>500ms each</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>safe-off همه LED/بوق خاموش, flag false, فازها reset (stable برای 0/1 حفظ)</t>
+          <t>99→Charging، 100→InputOk سبز ثابت زرد خاموش</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>PASS: safe-off. FAIL: LED روشن یا flag true</t>
+          <t>PASS: ورود 100. FAIL: 99 InputOk</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr"/>
@@ -2153,7 +2193,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Low Battery Alarm hysteresis</t>
+          <t>Full 100/95 stay</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -2163,27 +2203,27 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>valid</t>
+          <t>InputOk active</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>v_bat 20900 (&lt;21000) → flag true؛ سپس 21100 (21000-21200) → flag حفظ؛ 21200 → false.</t>
+          <t>از InputOk خام 99/96/95 نگه.</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>v_bat 20900/21100/21200</t>
+          <t>raw99 96 95</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>1s each</t>
+          <t>500ms each</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>flag true, حفظ, false</t>
+          <t>همچنان InputOk سبز ثابت</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -2193,7 +2233,7 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>PASS: hysteresis 21000/21200. FAIL: فوری false</t>
+          <t>PASS: ماندن. FAIL: Charging</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr"/>
@@ -2216,7 +2256,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Input switch present↔disconnected</t>
+          <t>Full 95 exit</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2226,37 +2266,37 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>BatteryRun ↔Charging</t>
+          <t>InputOk active</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>v_in 19V→22V→19V با هیسترزیس 20/21V.</t>
+          <t>خام94 (&lt;95) اعمال.</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>v_in 19V/22V</t>
+          <t>raw94</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>2s each</t>
+          <t>100ms</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>19V BatteryRun, 22V Charging/InputOk, بدون فلیکر 20.5V</t>
+          <t>Charging دوباره: سبز ثابت زرد چشمک 5%</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>حفظ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>PASS: hysteresis 20/21. FAIL: فلیکر</t>
+          <t>PASS: 94→Charging. FAIL: InputOk ماند</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr"/>
@@ -2279,7 +2319,7 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Mapping PA3/PA2</t>
+          <t>BatteryRun phase preserve</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2289,37 +2329,37 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>BatteryRun 25V stable57 ON570</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>PA3 1.0V pin → v_bat ~11176mV, PA2 1.0V → v_in ~11176mV; raw[1]=v_in, raw[2]=v_bat را چک.</t>
+          <t>ON 570؛ پس از100ms jitter56 stable57 حفظ تا 570 ادامه.</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>PA2/PA3 1V</t>
+          <t>On570 jitter56</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>700ms</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>v_bat از PA3/raw[2], v_in از PA2/raw[1], UI BatteryRun فقط v_bat</t>
+          <t>ON تا 570 حفظ سپس OFF430</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ON حفظ570</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>PASS: mapping صحیح. FAIL: جابجایی</t>
+          <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr"/>
@@ -2342,7 +2382,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>RTOS static + stack high-water</t>
+          <t>InputOk non-blocking</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2352,37 +2392,37 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>همه taskها</t>
+          <t>Input 24V Battery28V</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>FreeRTOSConfig SUPPORT_DYNAMIC=0, هر osThreadNew cb/stack معتبر, stack words/bytes mapping (128/192/256 words), osThreadGetStackSpace یا highWaterMark را بخوان.</t>
+          <t>InputOk هر10ms؛ Ui_Tick &lt;1ms برگردد.</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
+          <t>v_in24000 v_bat28000</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>1s</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>سبز ثابت بوق خاموش Ui_Tick سریع</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>همه static, UI 128w (512B), Meas 192w, Ctrl 256w, no overflow, حافظه باقی‌مانده &gt;20%</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>PASS: static و no overflow. FAIL: dynamic یا overflow</t>
+          <t>PASS: بدون 500ms. FAIL: delay</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr"/>
@@ -2405,7 +2445,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>No extra RTOS objects</t>
+          <t>Charging non-blocking</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2415,37 +2455,37 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>هیسترزیس UI</t>
+          <t>Input24V Battery25V</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>کد را grep برای queue/timer/mutex/heap جدید برای hysteresis.</t>
+          <t>Charging هر10ms؛ زرد On430 Off570 با اسکوپ؛ Ui_Tick سریع.</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>v_in24000 v_bat25000 raw57</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3s</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>هیچ queue/timer/mutex جدید برای hysteresis ایجاد نشده</t>
+          <t>سبز ثابت زرد فاز-محور بدون delay1s</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>زرد فاز حفظ</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>PASS: بدون شئ جدید. FAIL: شئ جدید</t>
+          <t>PASS: non-blocking. FAIL: blocking</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr"/>
@@ -2468,7 +2508,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Task starvation</t>
+          <t>InputOverVoltage</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2478,37 +2518,37 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>همه سناریوها</t>
+          <t>v_in28.5V</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>InputOk/Charging/BatteryRun هر 10ms؛ task_ui بدون delay طولانی و سایر taskها اجرا شوند.</t>
+          <t>v_in28500→27500→26000</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28500→27500→26000</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>5s run</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>ui 10ms, measurement 10ms, control 10ms, همه اجرا</t>
+          <t>سبز ثابت زرد خاموش قرمز50%1s بوق1s/10s؛ 27500 حفظ 27000 پاک</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>قرمز50%</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>PASS: بدون starvation. FAIL: ui delay 500ms/1000ms</t>
+          <t>PASS: 27/28 hysteresis. FAIL: زود پاک</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr"/>
@@ -2523,15 +2563,456 @@
       <c r="P25" s="10" t="inlineStr"/>
       <c r="Q25" s="10" t="inlineStr"/>
     </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>UI-022</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Snapshot invalid</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>هر سناریو</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>valid false/NULL تزریق</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>valid false</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>safe-off همه خاموش flag false فاز reset stable حفظ</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>reset</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>PASS: safe-off. FAIL: LED(flag)true</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr"/>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
+      <c r="N26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr"/>
+      <c r="P26" s="13" t="inlineStr"/>
+      <c r="Q26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>UI-023</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Low Alarm 21/21.2</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>v_bat20900→21100→21200</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>20900/21100/21200</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>1s each</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>flag true حفظ false</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>PASS: 21/21.2 hysteresis. FAIL: فوری</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" s="10" t="inlineStr"/>
+      <c r="Q27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>UI-024</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Input switch 20/21</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>BatteryRun↔Charging</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>v_in19V→22V→19V</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>19V/22V</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>19V BatteryRun 22V Charging/InputOk بدون فلیکر20.5V</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>حفظ</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>PASS: 20/21. FAIL: فلیکر</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
+      <c r="N28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
+      <c r="P28" s="13" t="inlineStr"/>
+      <c r="Q28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>UI-025</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Mapping PA3/PA2</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>PA3 1V→v_bat~11176 PA2 1V→v_in~11176 raw1=v_in raw2=v_bat چک</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PA2/PA3 1V</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>PASS: mapping. FAIL: جابجایی</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>UI-026</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>RTOS static + stack</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>همه taskها</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>SUPPORT_DYNAMIC0 cb/stack valid word/byte (128/192/256) highWater</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>همه static UI512 Meas768 Ctrl1024 high-water&gt;20%</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>PASS: static no overflow. FAIL: dynamic/overflow</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr"/>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr"/>
+      <c r="N30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr"/>
+      <c r="P30" s="13" t="inlineStr"/>
+      <c r="Q30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>UI-027</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>No extra RTOS</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>hysteresis UI</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>grep queue/timer/mutex/heap جدید برای hysteresis</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>هیچ شئ جدید برای hysteresis</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>PASS: بدون شئ. FAIL: شئ جدید</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>UI-028</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Task starvation</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>همه سناریوها</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>InputOk/Charging/BatteryRun هر10ms task_ui بدون delay طولانی</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>PASS: بدون starvation. FAIL: delay500/1000</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr"/>
+      <c r="N32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr"/>
+      <c r="P32" s="13" t="inlineStr"/>
+      <c r="Q32" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q25"/>
+  <autoFilter ref="A4:Q32"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2541,7 +3022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2555,14 +3036,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>مرجع سریع سناریوهای UI — هیسترزیس، فاز و نگاشت</t>
+          <t>مرجع سریع UI — هیسترزیس 2%/5%/100.95 و نگاشت</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>هیسترزیس‌ها: ورودی 20/21V (1000mV), باتری BatteryRun 2% + 0/1، Low Alarm 21000/21200، Overvoltage 27/28V</t>
+          <t>هیسترزیس: ورودی 20/21 (1000mV), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
         </is>
       </c>
     </row>
@@ -2584,7 +3065,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>ثابت / محل کد</t>
+          <t>ثابت / محل</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -2606,7 +3087,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>PA3 pin13 ADC1_IN3 → raw[2] → v_bat24_mv → BatteryRun</t>
+          <t>PA3 pin13 ADC1_IN3 → raw2 → v_bat24_mv → BatteryRun/Charging</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2626,7 +3107,7 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>UI-001,018</t>
+          <t>UI-001,025</t>
         </is>
       </c>
     </row>
@@ -2638,7 +3119,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PA2 pin12 ADC1_IN2 → raw[1] → v_in_mv → ورودی</t>
+          <t>PA2 pin12 ADC1_IN2 → raw1 → v_in_mv → ورودی</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -2648,7 +3129,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>board_pins.h:PIN_ADC_24_IN</t>
+          <t>PIN_ADC_24_IN</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -2658,7 +3139,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>UI-001,018</t>
+          <t>UI-001,025</t>
         </is>
       </c>
     </row>
@@ -2690,7 +3171,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>UI-017</t>
+          <t>UI-024</t>
         </is>
       </c>
     </row>
@@ -2722,19 +3203,19 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>UI-019</t>
+          <t>UI-026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Battery hysteresis</t>
+          <t>Battery 2%+0/1</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>stable0→ raw&gt;=2→1, stable1: 0→0, &gt;=3→2</t>
+          <t>stable0→raw&gt;=2→1, stable1:0→0 &gt;=3→2 else1</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -2744,7 +3225,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>UI_BATTERY_*_EXIT</t>
+          <t>RUN_HYSTERESIS 2 ZERO2 ONE3</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -2754,14 +3235,14 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>UI-005-010</t>
+          <t>UI-002-010</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Battery hysteresis</t>
+          <t>Battery diff</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -2776,7 +3257,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>UI_BATTERY_PERCENT_HYSTERESIS 2</t>
+          <t>RUN_HYSTERESIS 2</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -2793,320 +3274,384 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Green phase</t>
+          <t>Charging 5%</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>تغییر stable فاز reset نکند، از مرز بعدی</t>
+          <t>|raw-stable|&gt;=5 → update else keep, 53..61 حفظ</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>پایدار</t>
+          <t>پایدار زرد</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>UpdateBatteryRunGreenBlink</t>
+          <t>CHARGING_HYSTERESIS 5</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>500mV hysteresis</t>
+          <t>فقط Charging</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>UI-002,013</t>
+          <t>UI-011-013</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>InputOk</t>
+          <t>Charging yellow</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>سبز ثابت, بدون delay</t>
+          <t>remaining=100-stable5, On=remaining*10(min10)</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>non-blocking</t>
+          <t>پایدار</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>ScenarioInputOk</t>
+          <t>ChargingStable</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>10ms loop</t>
+          <t>Off=1000-On</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>UI-011</t>
+          <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Charging</t>
+          <t>Full 100/95</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>زرد باقی‌مانده, فاز-محور</t>
+          <t>&gt;=100 InputOk, &lt;95 Charging, else hold</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>non-blocking</t>
+          <t>جلوگیری 28V پرش</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>UpdateChargingYellowBlink</t>
+          <t>FULL_ENTER 100 FULL_EXIT95</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>On430 Off570</t>
+          <t>stateful</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>UI-012</t>
+          <t>UI-015-017</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Input present</t>
+          <t>Green phase</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>&gt;=21000 وصل, &lt;=20000 قطع</t>
+          <t>stable تغییر فاز reset نه، از مرز بعدی</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>هیسترزیس 20/21</t>
+          <t>پایدار</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>UI_INPUT_CONNECTED</t>
+          <t>UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>1000mV</t>
+          <t>500m hysteresis</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>UI-017</t>
+          <t>UI-002,018</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Overvoltage</t>
+          <t>Yellow phase</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>&gt;28000 خطا, &lt;=27000 پاک</t>
+          <t>stable5 تغییر فاز reset نه</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>قرمز 50% + بوق 10s</t>
+          <t>پایدار</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>OVERVOLTAGE_THRESHOLD</t>
+          <t>UpdateChargingYellowBlink</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>UI-014</t>
+          <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Low Alarm</t>
+          <t>Input present</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>&lt;21000 set, &gt;=21200 clear</t>
+          <t>&gt;=21000 وصل &lt;=20000 قطع</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>پیوسته, flag</t>
+          <t>هیسترزیس20/21</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>LOW_BATTERY_ALARM</t>
+          <t>INPUT_CONNECTED</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>21000/21200</t>
+          <t>1000mV</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>UI-016</t>
+          <t>UI-024</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>0% critical</t>
+          <t>Overvoltage</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>&lt;1% یک 10s سپس خاموش</t>
+          <t>&gt;28000 خطا &lt;=27000 پاک</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>تا خروج از 0% تکرار نه</t>
+          <t>قرمز50%+بوق10s</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>CRITICAL_PERCENT 1</t>
+          <t>OVERVOLTAGE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>stable 0</t>
+          <t>27/28</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>UI-005,006</t>
+          <t>UI-021</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Snapshot invalid</t>
+          <t>Low Alarm</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>valid false/NULL → safe-off</t>
+          <t>&lt;21000 set &gt;=21200 clear</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>flag false, فاز reset</t>
+          <t>پیوسته flag</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Ui_Tick</t>
+          <t>LOW_BATTERY</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>no stale</t>
+          <t>21000/21200</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>UI-015</t>
+          <t>UI-023</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>RTOS static</t>
+          <t>0% critical</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>SUPPORT_DYNAMIC=0, cb/stack</t>
+          <t>&lt;1% 10s یک بار سپس خاموش</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>همه static</t>
+          <t>تا خروج 0 تکرار نه</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>FreeRTOSConfig</t>
+          <t>CRITICAL 1</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>words/bytes</t>
+          <t>stable0</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>UI-019</t>
+          <t>UI-005,006</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>Snapshot invalid</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>valid false/NULL→safe-off</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>flag false phase reset</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Ui_Tick</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>no stale</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>UI-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>RTOS static</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>DYNAMIC 0 cb/stack</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>همه static</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>FreeRTOSConfig</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>word/byte</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>UI-026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
           <t>Stack</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>UI 128w, Meas 192w, Ctrl 256w</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>high-water &gt;20%</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>rtos_config.h</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>UI128 Meas192 Ctrl256</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>high-water&gt;20%</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>rtos_config</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>512/768/1024B</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>UI-019</t>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>UI-026</t>
         </is>
       </c>
     </row>
@@ -3146,14 +3691,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس و فاز</t>
+          <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس 2%/5%/100.95 و فاز</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>برای هر «رد» یک ردیف پر کن؛ فاز چشمک و هیسترزیس 0/1 را با اسکوپ ثبت کن.</t>
+          <t>برای هر «رد» یک ردیف؛ فاز چشمک و هیسترزیس 0/1 را با اسکوپ ثبت.</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3725,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>شرح کوتاه ایراد</t>
+          <t>شرح کوتاه</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -3200,12 +3745,12 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>مدرک/عکس یا scope</t>
+          <t>مدرک/عکس</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>commit</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
@@ -3215,7 +3760,7 @@
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>وضعیت ایراد</t>
+          <t>وضعیت</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -3403,7 +3948,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تأیید نهایی اعتبارسنجی روی برد — UI — هیسترزیس و فاز</t>
+          <t>تأیید نهایی اعتبارسنجی روی برد — UI — 2%/5%/100.95</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3989,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>UI — BatteryRun/LED</t>
+          <t>UI — BatteryRun/Charging</t>
         </is>
       </c>
     </row>
@@ -3456,7 +4001,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17 (2.1 — هیسترزیس 2% + فاز)</t>
+          <t>2026-09-17 (2.2 — 2%+5%+100/95)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -3466,7 +4011,7 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>2.1 — 2% + 0/1 + non-blocking</t>
+          <t>2.2 — 2%+5%+ فول+فاز</t>
         </is>
       </c>
     </row>
@@ -3511,12 +4056,12 @@
       <c r="B8" s="15" t="inlineStr"/>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>ابزار اندازه‌گیری</t>
+          <t>ابزار</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>منبع آزمایشگاهی + DMM + اسکوپ + تایمر 10ms</t>
+          <t>منبع آزمایشگاهی + DMM + اسکوپ + تایمر10ms</t>
         </is>
       </c>
     </row>
@@ -3550,7 +4095,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>هیسترزیس باتری 2% (0→1→2), ورودی 20/21V, Low 21/21.2V</t>
+          <t>BatteryRun2%+0/1, Charging5%, Full100/95, Low21/21.2</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -3560,7 +4105,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>سبز Off (100-stable)*10ms</t>
+          <t>سبزOff(100-stable)*10 زردOn(100-stable5)*10</t>
         </is>
       </c>
     </row>
@@ -3608,12 +4153,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>UI-001 تا UI-021</t>
+          <t>UI-001 تا UI-028</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr"/>
@@ -3658,7 +4203,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr"/>
@@ -3704,7 +4249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3723,35 +4268,30 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
-        <is>
-          <t>لیست‌ها برای DataValidation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
@@ -3765,21 +4305,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -3793,28 +4333,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$32</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +109,29 @@
     <font>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -176,8 +198,13 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -243,11 +270,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -325,6 +366,20 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,21 +787,21 @@
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="28" t="n"/>
+      <c r="J3" s="28" t="n"/>
+      <c r="K3" s="28" t="n"/>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="28" t="n"/>
+      <c r="N3" s="28" t="n"/>
+      <c r="O3" s="28" t="n"/>
+      <c r="P3" s="29" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -754,21 +809,21 @@
           <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="28" t="n"/>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="28" t="n"/>
+      <c r="N4" s="28" t="n"/>
+      <c r="O4" s="28" t="n"/>
+      <c r="P4" s="29" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -776,21 +831,21 @@
           <t>منبع و mapping</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="29" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -798,21 +853,21 @@
           <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="28" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="28" t="n"/>
+      <c r="O6" s="28" t="n"/>
+      <c r="P6" s="29" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -820,21 +875,21 @@
           <t>BatteryRun 2%+0/1</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="28" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="29" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -842,21 +897,21 @@
           <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="28" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+      <c r="O8" s="28" t="n"/>
+      <c r="P8" s="29" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -864,21 +919,21 @@
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
+      <c r="P9" s="29" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -886,21 +941,21 @@
           <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="29" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -908,21 +963,21 @@
           <t>فول InputOk/Charging 100/95</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="29" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -930,21 +985,21 @@
           <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="29" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -952,21 +1007,21 @@
           <t>حفظ فاز</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="28" t="n"/>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="28" t="n"/>
+      <c r="P13" s="29" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -974,21 +1029,21 @@
           <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
+      <c r="P14" s="29" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -996,21 +1051,21 @@
           <t>غیرمسدودکننده</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="29" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1018,21 +1073,21 @@
           <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="28" t="n"/>
+      <c r="P16" s="29" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1040,21 +1095,21 @@
           <t>RTOS و حافظه</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="29" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1062,21 +1117,21 @@
           <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="28" t="n"/>
+      <c r="P18" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3965,11 +4020,11 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="21" t="n"/>
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="29" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
@@ -4121,11 +4176,11 @@
           <t>خلاصه وضعیت تست‌ها</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="29" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
@@ -4363,4 +4418,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول نمایش و بوق (UI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>Ui_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1165,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3058,6 +3058,146 @@
       <c r="O32" s="13" t="inlineStr"/>
       <c r="P32" s="13" t="inlineStr"/>
       <c r="Q32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UI-029</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_ui</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>task_ui با snapshot صفرشده اجرا شود</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>safe-off</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>LED خاموش بدون درصد کاذب</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UI-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ مستقل</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>پنل وصل</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>دیالوگ‌های پنل نباید UI برد را تحت تأثیر قرار دهد</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>UI مستقل از پنل؛ دیالوگ‌ها فقط در مرورگر</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>بدون تداخل</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q32"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1318,7 +1318,10 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>PA3 2.0V pin (counts 2482) اعمال؛ raw2 و v_bat24_mv خوانده و percent حساب.</t>
+          <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
+گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
+گام ۳: 100 میلی‌ثانیه صبر کن و raw2 و v_bat24_mv را بخوان.
+گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -1381,7 +1384,10 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>باتری 25V raw57: v_bat25000→57. نویز 56 و 58 هر 100ms، سبز با اسکوپ.</t>
+          <t>گام ۱: برد در BatteryRun با snapshot معتبر و ورودی قطع باشد و درصد پایدار (stable) روی 57 نشسته باشد (باتری 25 ولت، raw=57).
+گام ۲: اسیلوسکوپ را روی LED سبز بگذار.
+گام ۳: درصدی را که می‌آید بین 56 و 58 نویز بده (هر 100 میلی‌ثانیه یکی) و 5 ثانیه نگاه کن.
+گام ۴: درصد پایدار باید همان 57 بماند و چشمک سبز ثابت باشد: خاموشی 430 و روشنی 570 میلی‌ثانیه، بدون اینکه فاز از نو شروع شود.</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -1444,7 +1450,10 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>raw به 55 (v_bat≈24850) کاهش.</t>
+          <t>گام ۱: از stable=57 شروع کن (پایان UI-002).
+گام ۲: درصد خام را به 55 پایین بیاور (v_bat حدود 24850 میلی‌ولت).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: درصد پایدار باید 55 شده باشد و چشمک سبز از مرز بعدی با خاموشی 450 و روشنی 550 ادامه پیدا کند، بدون ریست شدن فاز؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -1507,7 +1516,10 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>raw به 59 (25130) افزایش.</t>
+          <t>گام ۱: از stable=57 شروع کن.
+گام ۲: درصد خام را به 59 بالا ببر (v_bat حدود 25130 میلی‌ولت).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: درصد پایدار باید 59 شده باشد و چشمک سبز از مرز بعدی با خاموشی 410 و روشنی 590 ادامه پیدا کند، بدون ریست شدن فاز.</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
@@ -1570,7 +1582,10 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>v_bat21000 (0%) اعمال؛ LED و بوق مانیتور.</t>
+          <t>گام ۱: برد در BatteryRun باشد و ولتاژ باتری را دقیقاً روی 21 ولت (21000 میلی‌ولت) بگذار تا درصد خام و پایدار هر دو صفر شوند.
+گام ۲: هر سه LED و بوق را 12 ثانیه زیر نظر بگیر.
+گام ۳: همهٔ LEDها باید خاموش بمانند.
+گام ۴: بوق باید فقط یک بار و 10 ثانیه باشد و بعد تا وقتی درصد از صفر بیرون نیامده ساکت بماند؛ بوق تکراری یا LED روشن یعنی رد تست.</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -1633,7 +1648,10 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>نویز raw0→1→0→1 هر 200ms</t>
+          <t>گام ۱: از وضعیت بحرانی صفر درصد شروع کن و بگذار بوق یک‌بارهٔ 10 ثانیه‌ای شروع شود (پایان UI-005).
+گام ۲: درصد خام را بین 0 و 1 نویز بده: 0، بعد 1، بعد 0، بعد 1، هر کدام 200 میلی‌ثانیه.
+گام ۳: 12 ثانیه نگاه کن.
+گام ۴: درصد پایدار باید صفر بماند (تغییر کمتر از 2 شمرده نمی‌شود)، بوق نباید از نو شروع شود و LEDها خاموش می‌مانند.</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -1696,7 +1714,10 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>raw 0→1 سپس نگه (v_bat21070).</t>
+          <t>گام ۱: از درصد پایدار صفر شروع کن.
+گام ۲: درصد خام را از 0 به 1 ببر (v_bat حدود 21070 میلی‌ولت) و همان‌جا نگه دار.
+گام ۳: 3 ثانیه نگاه کن.
+گام ۴: درصد پایدار باید 1 شود؛ علامتش سه‌بوق هر 20 ثانیه و چشمک سبز با خاموشی 990 و روشنی فقط 10 میلی‌ثانیه است؛ رفتار بحرانی (UI-005) یعنی رد تست.</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1759,7 +1780,9 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>raw1→2 (21140) 1s نگه.</t>
+          <t>گام ۱: از درصد پایدار 1 شروع کن (پایان UI-007).
+گام ۲: درصد خام را به 2 ببر (v_bat حدود 21140 میلی‌ولت) و 1 ثانیه نگه دار.
+گام ۳: درصد پایدار باید همان 1 بماند (چون رسیدن به 3 لازم است تا از 1 بیرون بیاید) و همان سه‌بوق ادامه داشته باشد؛ رفتن به 2 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -1822,7 +1845,10 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>raw3 (21210) اعمال.</t>
+          <t>گام ۱: از درصد پایدار 1 شروع کن.
+گام ۲: درصد خام را مستقیم روی 3 بگذار (v_bat حدود 21210 میلی‌ولت).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: درصد پایدار باید 2 شده باشد و الگوی بوق به الگوی درصد 2 عوض شود؛ ماندن روی 1 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1885,7 +1911,10 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>raw0→2 (21140) اعمال.</t>
+          <t>گام ۱: از درصد پایدار صفر شروع کن.
+گام ۲: درصد خام را از 0 به 2 ببر (v_bat حدود 21140 میلی‌ولت).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: درصد پایدار باید اول 1 شود، نه مستقیم 2؛ پریدن مستقیم به 2 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -1948,7 +1977,10 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Charging 25V raw57: نویز 56/57/58 هر 100ms، زرد با اسکوپ.</t>
+          <t>گام ۱: ورودی 24 ولت و باتری 25 ولت وصل باشد تا وضعیت Charging شود و درصد پایدار شارژ روی 57 نشسته باشد.
+گام ۲: اسیلوسکوپ را روی LED زرد بگذار.
+گام ۳: درصد خام را بین 56 و 58 نویز بده (هر 100 میلی‌ثانیه) و 5 ثانیه نگاه کن.
+گام ۴: درصد پایدار همان 57 می‌ماند و چشمک زرد ثابت است: روشنی 430 و خاموشی 570 میلی‌ثانیه، بدون ریست شدن فاز.</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -2011,7 +2043,9 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>raw به 53 (diff4) سپس 61 (diff4) هر 500ms.</t>
+          <t>گام ۱: از stable=57 در Charging شروع کن.
+گام ۲: درصد خام را اول به 53 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار؛ بعد به 61 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار.
+گام ۳: چون اختلاف کمتر از 5 است، درصد پایدار باید همان 57 بماند و چشمک زرد هیچ تغییری نکند؛ هر تغییری یعنی رد تست.</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -2074,7 +2108,9 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>raw52 (diff5) و 62 (diff5)</t>
+          <t>گام ۱: از stable=57 در Charging شروع کن.
+گام ۲: درصد خام را به 52 ببر (اختلاف 5) و بعد به 62 ببر (اختلاف 5)؛ هر کدام را ببین.
+گام ۳: این بار درصد پایدار باید اول 52 و بعد 62 شود، و زمان‌های چشمک زرد از مرز بعدی اعمال شوند، بدون اینکه فاز ریست شود؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -2137,7 +2173,10 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>زرد ON 430ms؛ پس از 100ms jitter 56 (stable57 حفظ) فاز ON تا 430 حفظ.</t>
+          <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
+گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
+گام ۳: تا 600 میلی‌ثانیه نگاه کن: روشنی باید تا 430 کامل ادامه پیدا کند و بعد خاموش شود.
+گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -2200,7 +2239,10 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>v_bat خام 99→100 اعمال؛ InputOk/Charging تشخیص.</t>
+          <t>گام ۱: وضعیت Charging با snapshot معتبر باشد.
+گام ۲: درصد خام باتری را روی 99 بگذار و 500 میلی‌ثانیه نگه دار؛ بعد روی 100 بگذار و 500 میلی‌ثانیه نگه دار.
+گام ۳: روی 99 باید Charging باشد؛ روی 100 باید InputOk شود: سبز ثابت و زرد خاموش.
+گام ۴: اگر روی 99 هم InputOk شد، تست رد است.</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2263,7 +2305,10 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>از InputOk خام 99/96/95 نگه.</t>
+          <t>گام ۱: وضعیت InputOk فعال باشد (درصد 100).
+گام ۲: درصد خام را این‌طوری نگه دار: 99، بعد 96، بعد 95؛ هر کدام 500 میلی‌ثانیه.
+گام ۳: در هر سه حالت باید همان InputOk بماند و سبز ثابت باشد.
+گام ۴: افتادن به Charging در این بازه یعنی رد تست (خروج فقط زیر 95 است).</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -2326,7 +2371,10 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>خام94 (&lt;95) اعمال.</t>
+          <t>گام ۱: وضعیت InputOk فعال باشد.
+گام ۲: درصد خام را روی 94 بگذار (زیر 95).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: باید برگردد به Charging: سبز ثابت و زرد با هیسترزیس 5 درصدی چشمک بزند؛ ماندن در InputOk یعنی رد تست.</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -2389,7 +2437,10 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>ON 570؛ پس از100ms jitter56 stable57 حفظ تا 570 ادامه.</t>
+          <t>گام ۱: BatteryRun با باتری 25 ولت و درصد پایدار 57 باشد تا سبز در فاز روشنی 570 میلی‌ثانیه‌ای باشد.
+گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (پایدار همان 57 می‌ماند).
+گام ۳: تا 700 میلی‌ثانیه نگاه کن: روشنی باید تا 570 کامل ادامه پیدا کند و بعد 430 خاموشی بیاید.
+گام ۴: اگر روشنی وسطش از نو شروع شد، تست رد است.</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -2452,7 +2503,10 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>InputOk هر10ms؛ Ui_Tick &lt;1ms برگردد.</t>
+          <t>گام ۱: ورودی 24 ولت و باتری 28 ولت بده تا وضعیت InputOk شود.
+گام ۲: هر 10 میلی‌ثانیه Ui_Tick را صدا بزن و زمان برگشتنش را اندازه بگیر.
+گام ۳: یک ثانیه ادامه بده: سبز باید ثابت، بوق خاموش و هر تیک در کمتر از 1 میلی‌ثانیه برگردد.
+گام ۴: معیار: هیچ تأخیر (delay) بلندی مثل 500 میلی‌ثانیه نباید باشد؛ بودن delay یعنی رد تست.</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -2515,7 +2569,10 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Charging هر10ms؛ زرد On430 Off570 با اسکوپ؛ Ui_Tick سریع.</t>
+          <t>گام ۱: ورودی 24 ولت و باتری 25 ولت بده تا وضعیت Charging شود (درصد خام 57).
+گام ۲: اسیلوسکوپ را روی LED زرد بگذار و هر 10 میلی‌ثانیه Ui_Tick را صدا بزن.
+گام ۳: 3 ثانیه نگاه کن: سبز ثابت و زرد فاز‌محور با روشنی 430 و خاموشی 570 چشمک بزند.
+گام ۴: تیک باید سریع برگردد؛ هیچ blocking یا delay یک‌ثانیه‌ای نباید باشد.</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -2578,7 +2635,10 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>v_in28500→27500→26000</t>
+          <t>گام ۱: ولتاژ ورودی را روی 28.5 ولت (28500 میلی‌ولت) بگذار.
+گام ۲: باید چهرهٔ اضافه‌ولتاژ بیاید: سبز ثابت، زرد خاموش، قرمز با دورهٔ 1 ثانیه و 50 درصد روشنی، و بوق 1 ثانیه‌ای هر 10 ثانیه.
+گام ۳: ولتاژ را به 27500 پایین بیاور و نگه دار: چهره باید حفظ شود (هنوز زیر 27 پاک نمی‌شود).
+گام ۴: ولتاژ را به 26000 بیاور: حالا باید چهره پاک شود. کل تست 12 ثانیه؛ پاک شدن زودتر از 27000 یعنی رد تست.</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -2641,7 +2701,10 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>valid false/NULL تزریق</t>
+          <t>گام ۱: در هر سناریویی که هستی (فرقی نمی‌کند) snapshot را نامعتبر کن: valid=false یا اشاره‌گر NULL بده.
+گام ۲: 500 میلی‌ثانیه نگاه کن.
+گام ۳: همهٔ LEDها و بوق باید خاموش شوند (safe-off)، همهٔ پرچم‌ها false و فاز از نو شروع شود، ولی درصد پایدار حفظ شود.
+گام ۴: روشن ماندن هر LED یعنی رد تست.</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -2704,7 +2767,10 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>v_bat20900→21100→21200</t>
+          <t>گام ۱: snapshot معتبر باشد و ولتاژ باتری را این‌طوری حرکت بده: اول 20900، بعد 21100، بعد 21200 میلی‌ولت؛ هر کدام 1 ثانیه.
+گام ۲: پرچم «باتری کم» را نگاه کن.
+گام ۳: پرچم باید روی گذر از 21000 ست شود و تا وقتی زیر 21200 هستیم با همان منطق هیسترزیس حفظ شود و فوری بالا و پایین نپرد.
+گام ۴: معیار قبولی هیسترزیس 21 و 21.2 ولت است؛ تغییر فوری بدون هیسترزیس یعنی رد تست.</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -2767,7 +2833,10 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>v_in19V→22V→19V</t>
+          <t>گام ۱: ورودی را روی 19 ولت بگذار تا وضعیت BatteryRun باشد.
+گام ۲: ورودی را به 22 ولت بالا ببر: باید Charging یا InputOk شود.
+گام ۳: دوباره به 19 ولت برگردان: باید BatteryRun شود.
+گام ۴: کل رفت‌وبرگشت 2 ثانیه؛ اطراف 20.5 ولت هیچ فلیکری نباید دیده شود (هیسترزیس 20 و 21 ولت).</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -2830,7 +2899,10 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>PA3 1V→v_bat~11176 PA2 1V→v_in~11176 raw1=v_in raw2=v_bat چک</t>
+          <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
+گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
+گام ۳: چک کن v_bat از PA3 و raw2 می‌آید و v_in از PA2 و raw1.
+گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -2893,7 +2965,10 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>SUPPORT_DYNAMIC0 cb/stack valid word/byte (128/192/256) highWater</t>
+          <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
+گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
+گام ۳: مقدار high-water هر استک را بخوان: باید بیشتر از 20 درصد از استک آزاد مانده باشد.
+گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -2956,7 +3031,9 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>grep queue/timer/mutex/heap جدید برای hysteresis</t>
+          <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
+گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
+گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -3019,7 +3096,10 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>InputOk/Charging/BatteryRun هر10ms task_ui بدون delay طولانی</t>
+          <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
+گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
+گام ۳: task_ui، تسک اندازه‌گیری و تسک کنترل هر سه باید هر 10 میلی‌ثانیه اجرا شوند.
+گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -3082,7 +3162,9 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>task_ui با snapshot صفرشده اجرا شود</t>
+          <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
+گام ۲: 2 ثانیه نگاه کن.
+گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3115,14 +3197,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -3152,7 +3231,9 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>دیالوگ‌های پنل نباید UI برد را تحت تأثیر قرار دهد</t>
+          <t>گام ۱: پنل را وصل کن و چند دیالوگ پنل (تأیید و خطا) پشت سر هم بساز.
+گام ۲: هم‌زمان چراغ‌های روی برد را 3 ثانیه نگاه کن.
+گام ۳: UI برد باید کاملاً مستقل از پنل کار خودش را بکند؛ دیالوگ‌ها فقط داخل مرورگر هستند و نباید هیچ اثری روی LED یا بوق برد بگذارند.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3185,14 +3266,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -16,16 +16,19 @@
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,8 +133,132 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00262626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00404040"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00262626"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -203,8 +330,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -284,11 +431,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -381,6 +586,123 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -743,6 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -768,43 +1091,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول UI — BatteryRun 2%+0/1, Charging 5%, InputOk 100/95</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>PA3/ADC1_IN3/raw2/v_bat24 → BatteryRun/Charging | PA2/ADC1_IN2/raw1/v_in → ورودی | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
-      <c r="H3" s="28" t="n"/>
-      <c r="I3" s="28" t="n"/>
-      <c r="J3" s="28" t="n"/>
-      <c r="K3" s="28" t="n"/>
-      <c r="L3" s="28" t="n"/>
-      <c r="M3" s="28" t="n"/>
-      <c r="N3" s="28" t="n"/>
-      <c r="O3" s="28" t="n"/>
-      <c r="P3" s="29" t="n"/>
+      <c r="B3" s="73" t="n"/>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="73" t="n"/>
+      <c r="E3" s="73" t="n"/>
+      <c r="F3" s="73" t="n"/>
+      <c r="G3" s="73" t="n"/>
+      <c r="H3" s="73" t="n"/>
+      <c r="I3" s="73" t="n"/>
+      <c r="J3" s="73" t="n"/>
+      <c r="K3" s="73" t="n"/>
+      <c r="L3" s="73" t="n"/>
+      <c r="M3" s="73" t="n"/>
+      <c r="N3" s="73" t="n"/>
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="74" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
         </is>
@@ -826,7 +1149,7 @@
       <c r="P4" s="29" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>منبع و mapping</t>
         </is>
@@ -848,7 +1171,7 @@
       <c r="P5" s="29" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
         </is>
@@ -870,7 +1193,7 @@
       <c r="P6" s="29" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>BatteryRun 2%+0/1</t>
         </is>
@@ -892,7 +1215,7 @@
       <c r="P7" s="29" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
         </is>
@@ -914,7 +1237,7 @@
       <c r="P8" s="29" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
@@ -936,7 +1259,7 @@
       <c r="P9" s="29" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
         </is>
@@ -958,7 +1281,7 @@
       <c r="P10" s="29" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>فول InputOk/Charging 100/95</t>
         </is>
@@ -980,7 +1303,7 @@
       <c r="P11" s="29" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
         </is>
@@ -1002,7 +1325,7 @@
       <c r="P12" s="29" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>حفظ فاز</t>
         </is>
@@ -1024,7 +1347,7 @@
       <c r="P13" s="29" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
         </is>
@@ -1046,7 +1369,7 @@
       <c r="P14" s="29" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>غیرمسدودکننده</t>
         </is>
@@ -1068,7 +1391,7 @@
       <c r="P15" s="29" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
         </is>
@@ -1090,7 +1413,7 @@
       <c r="P16" s="29" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>RTOS و حافظه</t>
         </is>
@@ -1112,7 +1435,7 @@
       <c r="P17" s="29" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
         </is>
@@ -1162,161 +1485,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>ورودی mV، درصد 0-100، زمان ms. BatteryRun PA3 stable2%، Charging PA3 stable5% و زرد، Full 100/95 با raw.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable, ورودی present/overvoltage, فاز LED/بوق با اسکوپ 10ms. InputOk/Charging سریع برگردد.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>ورودی‌ها (v_bat/v_in/raw)</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="36" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="36" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="N4" s="36" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="36" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="9" t="inlineStr">
+      <c r="P4" s="36" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="36" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>UI-001</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Mapping PA3→v_bat</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>برد روشن, valid</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
 گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
@@ -1324,65 +1648,68 @@
 گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="45" t="inlineStr">
         <is>
           <t>PA3 2.0V pin → v_bat≈22352mV, v_in 24V</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
         <is>
           <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr"/>
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr"/>
+      <c r="N5" s="43" t="inlineStr"/>
+      <c r="O5" s="45" t="inlineStr"/>
+      <c r="P5" s="45" t="inlineStr"/>
+      <c r="Q5" s="47">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>UI-002</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>BatteryRun 2% 56/57/58</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>BatteryRun, valid, InputDisconnected</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در BatteryRun با snapshot معتبر و ورودی قطع باشد و درصد پایدار (stable) روی 57 نشسته باشد (باتری 25 ولت، raw=57).
 گام ۲: اسیلوسکوپ را روی LED سبز بگذار.
@@ -1390,65 +1717,68 @@
 گام ۴: درصد پایدار باید همان 57 بماند و چشمک سبز ثابت باشد: خاموشی 430 و روشنی 570 میلی‌ثانیه، بدون اینکه فاز از نو شروع شود.</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>v_bat25000 raw57 →56/58 jitter</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="50" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t>stable57 حفظ, green Off430 On570 ثابت, فاز reset نشود</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="48" t="inlineStr">
         <is>
           <t>فاز حفظ On/Off ثابت</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="48" t="inlineStr">
         <is>
           <t>PASS: stable57 فاز حفظ. FAIL: stable56/58 یا reset</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="K6" s="48" t="inlineStr"/>
+      <c r="L6" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr"/>
-      <c r="N6" s="13" t="inlineStr"/>
-      <c r="O6" s="13" t="inlineStr"/>
-      <c r="P6" s="13" t="inlineStr"/>
-      <c r="Q6" s="13" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="M6" s="48" t="inlineStr"/>
+      <c r="N6" s="48" t="inlineStr"/>
+      <c r="O6" s="50" t="inlineStr"/>
+      <c r="P6" s="50" t="inlineStr"/>
+      <c r="Q6" s="51">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>UI-003</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>BatteryRun 57→55</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="52" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 شروع کن (پایان UI-002).
 گام ۲: درصد خام را به 55 پایین بیاور (v_bat حدود 24850 میلی‌ولت).
@@ -1456,65 +1786,68 @@
 گام ۴: درصد پایدار باید 55 شده باشد و چشمک سبز از مرز بعدی با خاموشی 450 و روشنی 550 ادامه پیدا کند، بدون ریست شدن فاز؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="45" t="inlineStr">
         <is>
           <t>raw55</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="43" t="inlineStr">
         <is>
           <t>stable→55, green Off450 On550 از مرز بعدی, فاز حفظ</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="43" t="inlineStr">
         <is>
           <t>تغییر از مرز بعدی</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="43" t="inlineStr">
         <is>
           <t>PASS: stable55. FAIL: 57 حفظ</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="K7" s="43" t="inlineStr"/>
+      <c r="L7" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr"/>
-      <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="M7" s="43" t="inlineStr"/>
+      <c r="N7" s="43" t="inlineStr"/>
+      <c r="O7" s="45" t="inlineStr"/>
+      <c r="P7" s="45" t="inlineStr"/>
+      <c r="Q7" s="47">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>UI-004</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>BatteryRun 57→59</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 شروع کن.
 گام ۲: درصد خام را به 59 بالا ببر (v_bat حدود 25130 میلی‌ولت).
@@ -1522,65 +1855,68 @@
 گام ۴: درصد پایدار باید 59 شده باشد و چشمک سبز از مرز بعدی با خاموشی 410 و روشنی 590 ادامه پیدا کند، بدون ریست شدن فاز.</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>raw59</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="50" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="48" t="inlineStr">
         <is>
           <t>stable59 Off410 On590 فاز حفظ</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="48" t="inlineStr">
         <is>
           <t>PASS: stable59. FAIL: 57 حفظ</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="K8" s="48" t="inlineStr"/>
+      <c r="L8" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr"/>
-      <c r="N8" s="13" t="inlineStr"/>
-      <c r="O8" s="13" t="inlineStr"/>
-      <c r="P8" s="13" t="inlineStr"/>
-      <c r="Q8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="M8" s="48" t="inlineStr"/>
+      <c r="N8" s="48" t="inlineStr"/>
+      <c r="O8" s="50" t="inlineStr"/>
+      <c r="P8" s="50" t="inlineStr"/>
+      <c r="Q8" s="51">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>UI-005</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>0% critical raw0</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>BatteryRun 21V یا کمتر</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="43" t="inlineStr">
         <is>
           <t>گام ۱: برد در BatteryRun باشد و ولتاژ باتری را دقیقاً روی 21 ولت (21000 میلی‌ولت) بگذار تا درصد خام و پایدار هر دو صفر شوند.
 گام ۲: هر سه LED و بوق را 12 ثانیه زیر نظر بگیر.
@@ -1588,65 +1924,68 @@
 گام ۴: بوق باید فقط یک بار و 10 ثانیه باشد و بعد تا وقتی درصد از صفر بیرون نیامده ساکت بماند؛ بوق تکراری یا LED روشن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="45" t="inlineStr">
         <is>
           <t>v_bat21000 raw0 stable0</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="45" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="43" t="inlineStr">
         <is>
           <t>همه LED خاموش، یک بوق 10s سپس خاموش تا خروج از 0%</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="43" t="inlineStr">
         <is>
           <t>PASS: یک 10s سپس خاموش. FAIL: مکرر/LED روشن</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="K9" s="43" t="inlineStr"/>
+      <c r="L9" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="M9" s="43" t="inlineStr"/>
+      <c r="N9" s="43" t="inlineStr"/>
+      <c r="O9" s="45" t="inlineStr"/>
+      <c r="P9" s="45" t="inlineStr"/>
+      <c r="Q9" s="47">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>UI-006</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>0↔1 نویز</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>stable0 Critical 10s</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>گام ۱: از وضعیت بحرانی صفر درصد شروع کن و بگذار بوق یک‌بارهٔ 10 ثانیه‌ای شروع شود (پایان UI-005).
 گام ۲: درصد خام را بین 0 و 1 نویز بده: 0، بعد 1، بعد 0، بعد 1، هر کدام 200 میلی‌ثانیه.
@@ -1654,65 +1993,68 @@
 گام ۴: درصد پایدار باید صفر بماند (تغییر کمتر از 2 شمرده نمی‌شود)، بوق نباید از نو شروع شود و LEDها خاموش می‌مانند.</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>raw0/1 jitter</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="50" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="48" t="inlineStr">
         <is>
           <t>stable0 حفظ (&lt;2) بوق restart نشود LED خاموش</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="48" t="inlineStr">
         <is>
           <t>PASS: یک بار. FAIL: restart</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr"/>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="K10" s="48" t="inlineStr"/>
+      <c r="L10" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr"/>
-      <c r="N10" s="13" t="inlineStr"/>
-      <c r="O10" s="13" t="inlineStr"/>
-      <c r="P10" s="13" t="inlineStr"/>
-      <c r="Q10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="M10" s="48" t="inlineStr"/>
+      <c r="N10" s="48" t="inlineStr"/>
+      <c r="O10" s="50" t="inlineStr"/>
+      <c r="P10" s="50" t="inlineStr"/>
+      <c r="Q10" s="51">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>UI-007</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>1% مستقل raw1</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Stable0 خروج به1</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="52" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار صفر شروع کن.
 گام ۲: درصد خام را از 0 به 1 ببر (v_bat حدود 21070 میلی‌ولت) و همان‌جا نگه دار.
@@ -1720,130 +2062,136 @@
 گام ۴: درصد پایدار باید 1 شود؛ علامتش سه‌بوق هر 20 ثانیه و چشمک سبز با خاموشی 990 و روشنی فقط 10 میلی‌ثانیه است؛ رفتار بحرانی (UI-005) یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="45" t="inlineStr">
         <is>
           <t>raw1 stable1</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="45" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="43" t="inlineStr">
         <is>
           <t>stable1 سه‌بوق هر20s + سبز Off990 On10</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="43" t="inlineStr">
         <is>
           <t>سه‌بوق</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="43" t="inlineStr">
         <is>
           <t>PASS: stable1 سه‌بوق. FAIL: بحرانی</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="K11" s="43" t="inlineStr"/>
+      <c r="L11" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr"/>
-      <c r="P11" s="10" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="M11" s="43" t="inlineStr"/>
+      <c r="N11" s="43" t="inlineStr"/>
+      <c r="O11" s="45" t="inlineStr"/>
+      <c r="P11" s="45" t="inlineStr"/>
+      <c r="Q11" s="47">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>UI-008</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>1% →2 حفظ/خروج</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>stable1</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار 1 شروع کن (پایان UI-007).
 گام ۲: درصد خام را به 2 ببر (v_bat حدود 21140 میلی‌ولت) و 1 ثانیه نگه دار.
 گام ۳: درصد پایدار باید همان 1 بماند (چون رسیدن به 3 لازم است تا از 1 بیرون بیاید) و همان سه‌بوق ادامه داشته باشد؛ رفتن به 2 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>raw2</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="50" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="48" t="inlineStr">
         <is>
           <t>stable1 حفظ (raw2&lt;3) همچنان سه‌بوق</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="48" t="inlineStr">
         <is>
           <t>PASS: stable1. FAIL: 2</t>
         </is>
       </c>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="K12" s="48" t="inlineStr"/>
+      <c r="L12" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr"/>
-      <c r="N12" s="13" t="inlineStr"/>
-      <c r="O12" s="13" t="inlineStr"/>
-      <c r="P12" s="13" t="inlineStr"/>
-      <c r="Q12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="M12" s="48" t="inlineStr"/>
+      <c r="N12" s="48" t="inlineStr"/>
+      <c r="O12" s="50" t="inlineStr"/>
+      <c r="P12" s="50" t="inlineStr"/>
+      <c r="Q12" s="51">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>UI-009</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>1% →2 خروج با3</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>stable1</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="43" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار 1 شروع کن.
 گام ۲: درصد خام را مستقیم روی 3 بگذار (v_bat حدود 21210 میلی‌ولت).
@@ -1851,65 +2199,68 @@
 گام ۴: درصد پایدار باید 2 شده باشد و الگوی بوق به الگوی درصد 2 عوض شود؛ ماندن روی 1 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="45" t="inlineStr">
         <is>
           <t>raw3</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="43" t="inlineStr">
         <is>
           <t>stable2 دو بوق 60s یا یک بوق</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="43" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J13" s="43" t="inlineStr">
         <is>
           <t>PASS: stable2. FAIL: 1 حفظ</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="K13" s="43" t="inlineStr"/>
+      <c r="L13" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr"/>
-      <c r="P13" s="10" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="M13" s="43" t="inlineStr"/>
+      <c r="N13" s="43" t="inlineStr"/>
+      <c r="O13" s="45" t="inlineStr"/>
+      <c r="P13" s="45" t="inlineStr"/>
+      <c r="Q13" s="47">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>UI-010</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="48" t="inlineStr">
         <is>
           <t>BoardTest 0→2</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>stable0</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار صفر شروع کن.
 گام ۲: درصد خام را از 0 به 2 ببر (v_bat حدود 21140 میلی‌ولت).
@@ -1917,65 +2268,68 @@
 گام ۴: درصد پایدار باید اول 1 شود، نه مستقیم 2؛ پریدن مستقیم به 2 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>raw2</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="50" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="48" t="inlineStr">
         <is>
           <t>stable0→1 ابتدا 1 نه 2</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="48" t="inlineStr">
         <is>
           <t>PASS: 1 نه 2. FAIL: مستقیم 2</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="K14" s="48" t="inlineStr"/>
+      <c r="L14" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr"/>
-      <c r="N14" s="13" t="inlineStr"/>
-      <c r="O14" s="13" t="inlineStr"/>
-      <c r="P14" s="13" t="inlineStr"/>
-      <c r="Q14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="M14" s="48" t="inlineStr"/>
+      <c r="N14" s="48" t="inlineStr"/>
+      <c r="O14" s="50" t="inlineStr"/>
+      <c r="P14" s="50" t="inlineStr"/>
+      <c r="Q14" s="51">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>UI-011</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>Charging 5% 56/57/58</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Charging Input24V Battery25V</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 25 ولت وصل باشد تا وضعیت Charging شود و درصد پایدار شارژ روی 57 نشسته باشد.
 گام ۲: اسیلوسکوپ را روی LED زرد بگذار.
@@ -1983,195 +2337,204 @@
 گام ۴: درصد پایدار همان 57 می‌ماند و چشمک زرد ثابت است: روشنی 430 و خاموشی 570 میلی‌ثانیه، بدون ریست شدن فاز.</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="45" t="inlineStr">
         <is>
           <t>v_in24000 v_bat25000 raw57→56/58</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="45" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>chargingStable57 حفظ, yellow On430 Off570 ثابت, فاز reset نشود</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="43" t="inlineStr">
         <is>
           <t>زرد فاز حفظ</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="43" t="inlineStr">
         <is>
           <t>PASS: stable57 فاز حفظ. FAIL: 56/58 یا reset</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="K15" s="43" t="inlineStr"/>
+      <c r="L15" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="10" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="M15" s="43" t="inlineStr"/>
+      <c r="N15" s="43" t="inlineStr"/>
+      <c r="O15" s="45" t="inlineStr"/>
+      <c r="P15" s="45" t="inlineStr"/>
+      <c r="Q15" s="47">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>UI-012</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>Charging 5% 53..61</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 در Charging شروع کن.
 گام ۲: درصد خام را اول به 53 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار؛ بعد به 61 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار.
 گام ۳: چون اختلاف کمتر از 5 است، درصد پایدار باید همان 57 بماند و چشمک زرد هیچ تغییری نکند؛ هر تغییری یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="50" t="inlineStr">
         <is>
           <t>raw53 raw61</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="50" t="inlineStr">
         <is>
           <t>1s each</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="48" t="inlineStr">
         <is>
           <t>57 حفظ، زرد ثابت</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="48" t="inlineStr">
         <is>
           <t>PASS: 57 حفظ. FAIL: تغییر</t>
         </is>
       </c>
-      <c r="K16" s="13" t="inlineStr"/>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="K16" s="48" t="inlineStr"/>
+      <c r="L16" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="13" t="inlineStr"/>
-      <c r="N16" s="13" t="inlineStr"/>
-      <c r="O16" s="13" t="inlineStr"/>
-      <c r="P16" s="13" t="inlineStr"/>
-      <c r="Q16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="M16" s="48" t="inlineStr"/>
+      <c r="N16" s="48" t="inlineStr"/>
+      <c r="O16" s="50" t="inlineStr"/>
+      <c r="P16" s="50" t="inlineStr"/>
+      <c r="Q16" s="51">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>UI-013</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>Charging 5% خروج</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="43" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 در Charging شروع کن.
 گام ۲: درصد خام را به 52 ببر (اختلاف 5) و بعد به 62 ببر (اختلاف 5)؛ هر کدام را ببین.
 گام ۳: این بار درصد پایدار باید اول 52 و بعد 62 شود، و زمان‌های چشمک زرد از مرز بعدی اعمال شوند، بدون اینکه فاز ریست شود؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="45" t="inlineStr">
         <is>
           <t>raw52→62</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>stable→52 سپس 62, yellow زمان جدید از مرز بعدی فاز حفظ</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="43" t="inlineStr">
         <is>
           <t>از مرز بعدی</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="43" t="inlineStr">
         <is>
           <t>PASS: stable52/62. FAIL: 57 حفظ</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="K17" s="43" t="inlineStr"/>
+      <c r="L17" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr"/>
-      <c r="P17" s="10" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="M17" s="43" t="inlineStr"/>
+      <c r="N17" s="43" t="inlineStr"/>
+      <c r="O17" s="45" t="inlineStr"/>
+      <c r="P17" s="45" t="inlineStr"/>
+      <c r="Q17" s="47">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>UI-014</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
         <is>
           <t>Charging yellow phase</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Charging 25V On430</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
 گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
@@ -2179,65 +2542,68 @@
 گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>On430 jitter56</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="50" t="inlineStr">
         <is>
           <t>600ms</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="48" t="inlineStr">
         <is>
           <t>ON تا 430 حفظ سپس OFF</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="48" t="inlineStr">
         <is>
           <t>ON حفظ</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="48" t="inlineStr">
         <is>
           <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="K18" s="48" t="inlineStr"/>
+      <c r="L18" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="13" t="inlineStr"/>
-      <c r="O18" s="13" t="inlineStr"/>
-      <c r="P18" s="13" t="inlineStr"/>
-      <c r="Q18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="M18" s="48" t="inlineStr"/>
+      <c r="N18" s="48" t="inlineStr"/>
+      <c r="O18" s="50" t="inlineStr"/>
+      <c r="P18" s="50" t="inlineStr"/>
+      <c r="Q18" s="51">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>UI-015</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>Full 100/95 enter</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>Charging valid</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="43" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت Charging با snapshot معتبر باشد.
 گام ۲: درصد خام باتری را روی 99 بگذار و 500 میلی‌ثانیه نگه دار؛ بعد روی 100 بگذار و 500 میلی‌ثانیه نگه دار.
@@ -2245,65 +2611,68 @@
 گام ۴: اگر روی 99 هم InputOk شد، تست رد است.</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="45" t="inlineStr">
         <is>
           <t>raw99→100</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="45" t="inlineStr">
         <is>
           <t>500ms each</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
         <is>
           <t>99→Charging، 100→InputOk سبز ثابت زرد خاموش</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J19" s="43" t="inlineStr">
         <is>
           <t>PASS: ورود 100. FAIL: 99 InputOk</t>
         </is>
       </c>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="K19" s="43" t="inlineStr"/>
+      <c r="L19" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="10" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="M19" s="43" t="inlineStr"/>
+      <c r="N19" s="43" t="inlineStr"/>
+      <c r="O19" s="45" t="inlineStr"/>
+      <c r="P19" s="45" t="inlineStr"/>
+      <c r="Q19" s="47">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>UI-016</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="48" t="inlineStr">
         <is>
           <t>Full 100/95 stay</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>InputOk active</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="48" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت InputOk فعال باشد (درصد 100).
 گام ۲: درصد خام را این‌طوری نگه دار: 99، بعد 96، بعد 95؛ هر کدام 500 میلی‌ثانیه.
@@ -2311,65 +2680,68 @@
 گام ۴: افتادن به Charging در این بازه یعنی رد تست (خروج فقط زیر 95 است).</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>raw99 96 95</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="50" t="inlineStr">
         <is>
           <t>500ms each</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="48" t="inlineStr">
         <is>
           <t>همچنان InputOk سبز ثابت</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J20" s="48" t="inlineStr">
         <is>
           <t>PASS: ماندن. FAIL: Charging</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr"/>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="K20" s="48" t="inlineStr"/>
+      <c r="L20" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr"/>
-      <c r="N20" s="13" t="inlineStr"/>
-      <c r="O20" s="13" t="inlineStr"/>
-      <c r="P20" s="13" t="inlineStr"/>
-      <c r="Q20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="M20" s="48" t="inlineStr"/>
+      <c r="N20" s="48" t="inlineStr"/>
+      <c r="O20" s="50" t="inlineStr"/>
+      <c r="P20" s="50" t="inlineStr"/>
+      <c r="Q20" s="51">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>UI-017</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Full 95 exit</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>InputOk active</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت InputOk فعال باشد.
 گام ۲: درصد خام را روی 94 بگذار (زیر 95).
@@ -2377,65 +2749,68 @@
 گام ۴: باید برگردد به Charging: سبز ثابت و زرد با هیسترزیس 5 درصدی چشمک بزند؛ ماندن در InputOk یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="45" t="inlineStr">
         <is>
           <t>raw94</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>Charging دوباره: سبز ثابت زرد چشمک 5%</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="43" t="inlineStr">
         <is>
           <t>PASS: 94→Charging. FAIL: InputOk ماند</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="K21" s="43" t="inlineStr"/>
+      <c r="L21" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="10" t="inlineStr"/>
-      <c r="Q21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="M21" s="43" t="inlineStr"/>
+      <c r="N21" s="43" t="inlineStr"/>
+      <c r="O21" s="45" t="inlineStr"/>
+      <c r="P21" s="45" t="inlineStr"/>
+      <c r="Q21" s="47">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>UI-018</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="48" t="inlineStr">
         <is>
           <t>BatteryRun phase preserve</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>BatteryRun 25V stable57 ON570</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="48" t="inlineStr">
         <is>
           <t>گام ۱: BatteryRun با باتری 25 ولت و درصد پایدار 57 باشد تا سبز در فاز روشنی 570 میلی‌ثانیه‌ای باشد.
 گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (پایدار همان 57 می‌ماند).
@@ -2443,65 +2818,68 @@
 گام ۴: اگر روشنی وسطش از نو شروع شد، تست رد است.</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>On570 jitter56</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="50" t="inlineStr">
         <is>
           <t>700ms</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="48" t="inlineStr">
         <is>
           <t>ON تا 570 حفظ سپس OFF430</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="48" t="inlineStr">
         <is>
           <t>ON حفظ570</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J22" s="48" t="inlineStr">
         <is>
           <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
-      <c r="K22" s="13" t="inlineStr"/>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="K22" s="48" t="inlineStr"/>
+      <c r="L22" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="13" t="inlineStr"/>
-      <c r="N22" s="13" t="inlineStr"/>
-      <c r="O22" s="13" t="inlineStr"/>
-      <c r="P22" s="13" t="inlineStr"/>
-      <c r="Q22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="M22" s="48" t="inlineStr"/>
+      <c r="N22" s="48" t="inlineStr"/>
+      <c r="O22" s="50" t="inlineStr"/>
+      <c r="P22" s="50" t="inlineStr"/>
+      <c r="Q22" s="51">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>UI-019</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>InputOk non-blocking</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="43" t="inlineStr">
         <is>
           <t>Input 24V Battery28V</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 28 ولت بده تا وضعیت InputOk شود.
 گام ۲: هر 10 میلی‌ثانیه Ui_Tick را صدا بزن و زمان برگشتنش را اندازه بگیر.
@@ -2509,65 +2887,68 @@
 گام ۴: معیار: هیچ تأخیر (delay) بلندی مثل 500 میلی‌ثانیه نباید باشد؛ بودن delay یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="45" t="inlineStr">
         <is>
           <t>v_in24000 v_bat28000</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="45" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="43" t="inlineStr">
         <is>
           <t>سبز ثابت بوق خاموش Ui_Tick سریع</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I23" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="43" t="inlineStr">
         <is>
           <t>PASS: بدون 500ms. FAIL: delay</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="K23" s="43" t="inlineStr"/>
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="10" t="inlineStr"/>
-      <c r="Q23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="M23" s="43" t="inlineStr"/>
+      <c r="N23" s="43" t="inlineStr"/>
+      <c r="O23" s="45" t="inlineStr"/>
+      <c r="P23" s="45" t="inlineStr"/>
+      <c r="Q23" s="47">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>UI-020</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="48" t="inlineStr">
         <is>
           <t>Charging non-blocking</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Input24V Battery25V</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="48" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 25 ولت بده تا وضعیت Charging شود (درصد خام 57).
 گام ۲: اسیلوسکوپ را روی LED زرد بگذار و هر 10 میلی‌ثانیه Ui_Tick را صدا بزن.
@@ -2575,65 +2956,68 @@
 گام ۴: تیک باید سریع برگردد؛ هیچ blocking یا delay یک‌ثانیه‌ای نباید باشد.</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="50" t="inlineStr">
         <is>
           <t>v_in24000 v_bat25000 raw57</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="50" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="48" t="inlineStr">
         <is>
           <t>سبز ثابت زرد فاز-محور بدون delay1s</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="48" t="inlineStr">
         <is>
           <t>زرد فاز حفظ</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J24" s="48" t="inlineStr">
         <is>
           <t>PASS: non-blocking. FAIL: blocking</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="K24" s="48" t="inlineStr"/>
+      <c r="L24" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr"/>
-      <c r="N24" s="13" t="inlineStr"/>
-      <c r="O24" s="13" t="inlineStr"/>
-      <c r="P24" s="13" t="inlineStr"/>
-      <c r="Q24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="M24" s="48" t="inlineStr"/>
+      <c r="N24" s="48" t="inlineStr"/>
+      <c r="O24" s="50" t="inlineStr"/>
+      <c r="P24" s="50" t="inlineStr"/>
+      <c r="Q24" s="51">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>v_in28.5V</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را روی 28.5 ولت (28500 میلی‌ولت) بگذار.
 گام ۲: باید چهرهٔ اضافه‌ولتاژ بیاید: سبز ثابت، زرد خاموش، قرمز با دورهٔ 1 ثانیه و 50 درصد روشنی، و بوق 1 ثانیه‌ای هر 10 ثانیه.
@@ -2641,65 +3025,68 @@
 گام ۴: ولتاژ را به 26000 بیاور: حالا باید چهره پاک شود. کل تست 12 ثانیه؛ پاک شدن زودتر از 27000 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="45" t="inlineStr">
         <is>
           <t>28500→27500→26000</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="45" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="43" t="inlineStr">
         <is>
           <t>سبز ثابت زرد خاموش قرمز50%1s بوق1s/10s؛ 27500 حفظ 27000 پاک</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I25" s="43" t="inlineStr">
         <is>
           <t>قرمز50%</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J25" s="43" t="inlineStr">
         <is>
           <t>PASS: 27/28 hysteresis. FAIL: زود پاک</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="K25" s="43" t="inlineStr"/>
+      <c r="L25" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="10" t="inlineStr"/>
-      <c r="Q25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="M25" s="43" t="inlineStr"/>
+      <c r="N25" s="43" t="inlineStr"/>
+      <c r="O25" s="45" t="inlineStr"/>
+      <c r="P25" s="45" t="inlineStr"/>
+      <c r="Q25" s="47">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>UI-022</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
         <is>
           <t>Snapshot invalid</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>هر سناریو</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>گام ۱: در هر سناریویی که هستی (فرقی نمی‌کند) snapshot را نامعتبر کن: valid=false یا اشاره‌گر NULL بده.
 گام ۲: 500 میلی‌ثانیه نگاه کن.
@@ -2707,65 +3094,68 @@
 گام ۴: روشن ماندن هر LED یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="50" t="inlineStr">
         <is>
           <t>valid false</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="50" t="inlineStr">
         <is>
           <t>500ms</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="48" t="inlineStr">
         <is>
           <t>safe-off همه خاموش flag false فاز reset stable حفظ</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="48" t="inlineStr">
         <is>
           <t>reset</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J26" s="48" t="inlineStr">
         <is>
           <t>PASS: safe-off. FAIL: LED(flag)true</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr"/>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="K26" s="48" t="inlineStr"/>
+      <c r="L26" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr"/>
-      <c r="N26" s="13" t="inlineStr"/>
-      <c r="O26" s="13" t="inlineStr"/>
-      <c r="P26" s="13" t="inlineStr"/>
-      <c r="Q26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="M26" s="48" t="inlineStr"/>
+      <c r="N26" s="48" t="inlineStr"/>
+      <c r="O26" s="50" t="inlineStr"/>
+      <c r="P26" s="50" t="inlineStr"/>
+      <c r="Q26" s="51">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>UI-023</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>Low Alarm 21/21.2</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="43" t="inlineStr">
         <is>
           <t>گام ۱: snapshot معتبر باشد و ولتاژ باتری را این‌طوری حرکت بده: اول 20900، بعد 21100، بعد 21200 میلی‌ولت؛ هر کدام 1 ثانیه.
 گام ۲: پرچم «باتری کم» را نگاه کن.
@@ -2773,65 +3163,68 @@
 گام ۴: معیار قبولی هیسترزیس 21 و 21.2 ولت است؛ تغییر فوری بدون هیسترزیس یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="45" t="inlineStr">
         <is>
           <t>20900/21100/21200</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="45" t="inlineStr">
         <is>
           <t>1s each</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="43" t="inlineStr">
         <is>
           <t>flag true حفظ false</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="J27" s="43" t="inlineStr">
         <is>
           <t>PASS: 21/21.2 hysteresis. FAIL: فوری</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="K27" s="43" t="inlineStr"/>
+      <c r="L27" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" s="10" t="inlineStr"/>
-      <c r="O27" s="10" t="inlineStr"/>
-      <c r="P27" s="10" t="inlineStr"/>
-      <c r="Q27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="M27" s="43" t="inlineStr"/>
+      <c r="N27" s="43" t="inlineStr"/>
+      <c r="O27" s="45" t="inlineStr"/>
+      <c r="P27" s="45" t="inlineStr"/>
+      <c r="Q27" s="47">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="48" t="inlineStr">
         <is>
           <t>Input switch 20/21</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>BatteryRun↔Charging</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="48" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را روی 19 ولت بگذار تا وضعیت BatteryRun باشد.
 گام ۲: ورودی را به 22 ولت بالا ببر: باید Charging یا InputOk شود.
@@ -2839,65 +3232,68 @@
 گام ۴: کل رفت‌وبرگشت 2 ثانیه؛ اطراف 20.5 ولت هیچ فلیکری نباید دیده شود (هیسترزیس 20 و 21 ولت).</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="50" t="inlineStr">
         <is>
           <t>19V/22V</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="50" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="48" t="inlineStr">
         <is>
           <t>19V BatteryRun 22V Charging/InputOk بدون فلیکر20.5V</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J28" s="48" t="inlineStr">
         <is>
           <t>PASS: 20/21. FAIL: فلیکر</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr"/>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="K28" s="48" t="inlineStr"/>
+      <c r="L28" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M28" s="13" t="inlineStr"/>
-      <c r="N28" s="13" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
-      <c r="P28" s="13" t="inlineStr"/>
-      <c r="Q28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="M28" s="48" t="inlineStr"/>
+      <c r="N28" s="48" t="inlineStr"/>
+      <c r="O28" s="50" t="inlineStr"/>
+      <c r="P28" s="50" t="inlineStr"/>
+      <c r="Q28" s="51">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>UI-025</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>Mapping PA3/PA2</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
 گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
@@ -2905,65 +3301,68 @@
 گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="45" t="inlineStr">
         <is>
           <t>PA2/PA3 1V</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="45" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="43" t="inlineStr">
         <is>
           <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="J29" s="43" t="inlineStr">
         <is>
           <t>PASS: mapping. FAIL: جابجایی</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="K29" s="43" t="inlineStr"/>
+      <c r="L29" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="10" t="inlineStr"/>
-      <c r="Q29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="M29" s="43" t="inlineStr"/>
+      <c r="N29" s="43" t="inlineStr"/>
+      <c r="O29" s="45" t="inlineStr"/>
+      <c r="P29" s="45" t="inlineStr"/>
+      <c r="Q29" s="47">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="48" t="inlineStr">
         <is>
           <t>RTOS static + stack</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>همه taskها</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="48" t="inlineStr">
         <is>
           <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
 گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
@@ -2971,130 +3370,136 @@
 گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F30" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G30" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="48" t="inlineStr">
         <is>
           <t>همه static UI512 Meas768 Ctrl1024 high-water&gt;20%</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="J30" s="48" t="inlineStr">
         <is>
           <t>PASS: static no overflow. FAIL: dynamic/overflow</t>
         </is>
       </c>
-      <c r="K30" s="13" t="inlineStr"/>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="K30" s="48" t="inlineStr"/>
+      <c r="L30" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="13" t="inlineStr"/>
-      <c r="O30" s="13" t="inlineStr"/>
-      <c r="P30" s="13" t="inlineStr"/>
-      <c r="Q30" s="13" t="inlineStr"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="M30" s="48" t="inlineStr"/>
+      <c r="N30" s="48" t="inlineStr"/>
+      <c r="O30" s="50" t="inlineStr"/>
+      <c r="P30" s="50" t="inlineStr"/>
+      <c r="Q30" s="51">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="40.5" customHeight="1">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>UI-027</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>No extra RTOS</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>hysteresis UI</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="43" t="inlineStr">
         <is>
           <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
 گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
 گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="43" t="inlineStr">
         <is>
           <t>هیچ شئ جدید برای hysteresis</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J31" s="43" t="inlineStr">
         <is>
           <t>PASS: بدون شئ. FAIL: شئ جدید</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="K31" s="43" t="inlineStr"/>
+      <c r="L31" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" s="10" t="inlineStr"/>
-      <c r="Q31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="M31" s="43" t="inlineStr"/>
+      <c r="N31" s="43" t="inlineStr"/>
+      <c r="O31" s="45" t="inlineStr"/>
+      <c r="P31" s="45" t="inlineStr"/>
+      <c r="Q31" s="47">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>UI-028</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="48" t="inlineStr">
         <is>
           <t>Task starvation</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>همه سناریوها</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="48" t="inlineStr">
         <is>
           <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
 گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
@@ -3102,196 +3507,459 @@
 گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G32" s="50" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H32" s="48" t="inlineStr">
         <is>
           <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I32" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="J32" s="48" t="inlineStr">
         <is>
           <t>PASS: بدون starvation. FAIL: delay500/1000</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr"/>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="K32" s="48" t="inlineStr"/>
+      <c r="L32" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr"/>
-      <c r="N32" s="13" t="inlineStr"/>
-      <c r="O32" s="13" t="inlineStr"/>
-      <c r="P32" s="13" t="inlineStr"/>
-      <c r="Q32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="M32" s="48" t="inlineStr"/>
+      <c r="N32" s="48" t="inlineStr"/>
+      <c r="O32" s="50" t="inlineStr"/>
+      <c r="P32" s="50" t="inlineStr"/>
+      <c r="Q32" s="51">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="40.5" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>UI-029</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="54" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="43" t="inlineStr">
         <is>
           <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
 گام ۲: 2 ثانیه نگاه کن.
 گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="45" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="45" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="43" t="inlineStr">
         <is>
           <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="43" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="43" t="inlineStr">
         <is>
           <t>LED خاموش بدون درصد کاذب</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" s="43" t="n"/>
+      <c r="L33" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="M33" s="43" t="n"/>
+      <c r="N33" s="43" t="n"/>
+      <c r="O33" s="45" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="P33" s="45" t="n"/>
+      <c r="Q33" s="47" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="40.5" customHeight="1">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>UI-030</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="48" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="50" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="48" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و چند دیالوگ پنل (تأیید و خطا) پشت سر هم بساز.
 گام ۲: هم‌زمان چراغ‌های روی برد را 3 ثانیه نگاه کن.
 گام ۳: UI برد باید کاملاً مستقل از پنل کار خودش را بکند؛ دیالوگ‌ها فقط داخل مرورگر هستند و نباید هیچ اثری روی LED یا بوق برد بگذارند.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="50" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="48" t="inlineStr">
         <is>
           <t>UI مستقل از پنل؛ دیالوگ‌ها فقط در مرورگر</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="48" t="inlineStr">
         <is>
           <t>بدون تداخل</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" s="48" t="n"/>
+      <c r="L34" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="M34" s="48" t="n"/>
+      <c r="N34" s="48" t="n"/>
+      <c r="O34" s="50" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="P34" s="50" t="n"/>
+      <c r="Q34" s="51" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="Q35" s="56">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="56">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="56">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="56">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="56">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="56">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="56">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="56">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="56">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="56">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="56">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="56">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="56">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="56">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="56">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="56">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="56">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="56">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="56">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="56">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="56">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="Q56" s="56">
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="Q57" s="56">
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Q58" s="56">
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Q59" s="56">
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Q60" s="56">
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Q61" s="56">
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Q62" s="56">
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Q63" s="56">
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Q64" s="56">
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="Q65" s="56">
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="Q66" s="56">
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="Q67" s="56">
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="Q68" s="56">
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="Q69" s="56">
+        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="Q70" s="56">
+        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="Q71" s="56">
+        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="Q72" s="56">
+        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="Q73" s="56">
+        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="Q74" s="56">
+        <f>IF(OR(L74="",L74="در انتظار"),"",IF(Q74="",TODAY(),Q74))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q32"/>
+  <autoFilter ref="A4:Q34"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="L5:L114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3307,622 +3975,622 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>مرجع سریع UI — هیسترزیس 2%/5%/100.95 و نگاشت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>هیسترزیس: ورودی 20/21 (1000mV), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="57" t="inlineStr">
         <is>
           <t>رفتار</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>ثابت / محل</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="57" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="57" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>PA3 mapping</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>PA3 pin13 ADC1_IN3 → raw2 → v_bat24_mv → BatteryRun/Charging</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>فقط v_bat</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>board_pins.h:PIN_ADC_24_BAT</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>PA3→BatteryRun</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="59" t="inlineStr">
         <is>
           <t>UI-001,025</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>PA2 mapping</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>PA2 pin12 ADC1_IN2 → raw1 → v_in_mv → ورودی</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>فقط v_in</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>PIN_ADC_24_IN</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>PA2→Input</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>UI-001,025</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>PB4</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>MCU_INT_24_IN EXTI دو لبه</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>فقط ورودی</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>board_pins.h</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="58" t="inlineStr">
         <is>
           <t>PB4→ورودی</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>PB5/PB11</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>PB5 Q1 McuPowerPath, PB11 Q17 Changeover</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>بدون تغییر UI</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>board_pins.h</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>ممنوع UI</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>Battery 2%+0/1</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>stable0→raw&gt;=2→1, stable1:0→0 &gt;=3→2 else1</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>جلوگیری 0↔1</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>RUN_HYSTERESIS 2 ZERO2 ONE3</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="58" t="inlineStr">
         <is>
           <t>0/1 جدا</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>UI-002-010</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>Battery diff</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>|raw-stable|&gt;=2 → update else keep</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>56↔57 حفظ</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>RUN_HYSTERESIS 2</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>فقط BatteryRun</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>UI-002-004</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>|raw-stable|&gt;=5 → update else keep, 53..61 حفظ</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>پایدار زرد</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="58" t="inlineStr">
         <is>
           <t>CHARGING_HYSTERESIS 5</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="58" t="inlineStr">
         <is>
           <t>فقط Charging</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>UI-011-013</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>Charging yellow</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>remaining=100-stable5, On=remaining*10(min10)</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>ChargingStable</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>Off=1000-On</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Full 100/95</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>&gt;=100 InputOk, &lt;95 Charging, else hold</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>جلوگیری 28V پرش</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="58" t="inlineStr">
         <is>
           <t>FULL_ENTER 100 FULL_EXIT95</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="58" t="inlineStr">
         <is>
           <t>stateful</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>UI-015-017</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>Green phase</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>stable تغییر فاز reset نه، از مرز بعدی</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>500m hysteresis</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>UI-002,018</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>Yellow phase</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>stable5 تغییر فاز reset نه</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>UpdateChargingYellowBlink</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="58" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="59" t="inlineStr">
         <is>
           <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>Input present</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>&gt;=21000 وصل &lt;=20000 قطع</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>هیسترزیس20/21</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>INPUT_CONNECTED</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>1000mV</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="61" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Overvoltage</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>&gt;28000 خطا &lt;=27000 پاک</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="58" t="inlineStr">
         <is>
           <t>قرمز50%+بوق10s</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="58" t="inlineStr">
         <is>
           <t>OVERVOLTAGE</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="58" t="inlineStr">
         <is>
           <t>27/28</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="59" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>Low Alarm</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>&lt;21000 set &gt;=21200 clear</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>پیوسته flag</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>LOW_BATTERY</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>21000/21200</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="61" t="inlineStr">
         <is>
           <t>UI-023</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>0% critical</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>&lt;1% 10s یک بار سپس خاموش</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="58" t="inlineStr">
         <is>
           <t>تا خروج 0 تکرار نه</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="58" t="inlineStr">
         <is>
           <t>CRITICAL 1</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="58" t="inlineStr">
         <is>
           <t>stable0</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="59" t="inlineStr">
         <is>
           <t>UI-005,006</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>Snapshot invalid</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>valid false/NULL→safe-off</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>flag false phase reset</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t>Ui_Tick</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>no stale</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>UI-022</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>RTOS static</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>DYNAMIC 0 cb/stack</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="58" t="inlineStr">
         <is>
           <t>همه static</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="58" t="inlineStr">
         <is>
           <t>FreeRTOSConfig</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="58" t="inlineStr">
         <is>
           <t>word/byte</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="59" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>Stack</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>UI128 Meas192 Ctrl256</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>high-water&gt;20%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr">
         <is>
           <t>rtos_config</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>512/768/1024B</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="61" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
@@ -3933,6 +4601,29 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3940,6 +4631,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3962,81 +4654,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس 2%/5%/100.95 و فاز</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>برای هر «رد» یک ردیف؛ فاز چشمک و هیسترزیس 0/1 را با اسکوپ ثبت.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="36" t="inlineStr">
         <is>
           <t>شرح کوتاه</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="36" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="36" t="inlineStr">
         <is>
           <t>مدرک/عکس</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="36" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="36" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="36" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="36" t="inlineStr">
         <is>
           <t>تأیید رفع</t>
         </is>
@@ -4204,6 +4896,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4219,21 +4912,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — UI — 2%/5%/100.95</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>فقط پس از تکمیل تست‌ها و بستن ایرادهای بحرانی/بالا.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
@@ -4245,61 +4938,61 @@
       <c r="F3" s="29" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="63" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>UI — BatteryRun/Charging</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>2026-09-17 (2.2 — 2%+5%+100/95)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>2.2 — 2%+5%+ فول+فاز</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
@@ -4307,13 +5000,13 @@
       <c r="E6" s="15" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -4321,62 +5014,62 @@
       <c r="E7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسکوپ + تایمر10ms</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>1000Hz (osKernelGetTickFreq)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>دوره UI</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>BatteryRun2%+0/1, Charging5%, Full100/95, Low21/21.2</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>سبزOff(100-stable)*10 زردOn(100-stable5)*10</t>
         </is>
@@ -4389,7 +5082,7 @@
       <c r="E11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>خلاصه وضعیت تست‌ها</t>
         </is>
@@ -4401,17 +5094,17 @@
       <c r="F12" s="29" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="63" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
@@ -4419,17 +5112,17 @@
       <c r="E13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="63" t="inlineStr">
         <is>
           <t>UI-001 تا UI-028</t>
         </is>
@@ -4437,17 +5130,17 @@
       <c r="E14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="63" t="inlineStr">
         <is>
           <t>COUNTIF</t>
         </is>
@@ -4455,12 +5148,12 @@
       <c r="E15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4469,12 +5162,12 @@
       <c r="E16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -4483,12 +5176,12 @@
       <c r="E17" s="15" t="inlineStr"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="63" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4496,8 +5189,9 @@
       <c r="D18" s="22" t="inlineStr"/>
       <c r="E18" s="15" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>امضا: تست‌کننده ________________  سرپرست ________________  تاریخ ________________</t>
         </is>
@@ -4519,6 +5213,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4529,105 +5224,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -4641,7 +5344,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4653,55 +5356,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول نمایش و بوق (UI)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>Ui_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -4714,6 +5418,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -253,6 +256,20 @@
     </font>
     <font>
       <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
       <u val="single"/>
@@ -493,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -703,6 +720,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1489,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3344,12 +3371,12 @@
     <row r="30" ht="54" customHeight="1">
       <c r="A30" s="42" t="inlineStr">
         <is>
-          <t>UI-026</t>
+          <t>UI-028</t>
         </is>
       </c>
       <c r="B30" s="48" t="inlineStr">
         <is>
-          <t>RTOS static + stack</t>
+          <t>Task starvation</t>
         </is>
       </c>
       <c r="C30" s="49" t="inlineStr">
@@ -3359,15 +3386,15 @@
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>همه taskها</t>
+          <t>همه سناریوها</t>
         </is>
       </c>
       <c r="E30" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
-گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
-گام ۳: مقدار high-water هر استک را بخوان: باید بیشتر از 20 درصد از استک آزاد مانده باشد.
-گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
+          <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
+گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
+گام ۳: task_ui، تسک اندازه‌گیری و تسک کنترل هر سه باید هر 10 میلی‌ثانیه اجرا شوند.
+گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
       <c r="F30" s="50" t="inlineStr">
@@ -3377,22 +3404,22 @@
       </c>
       <c r="G30" s="50" t="inlineStr">
         <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H30" s="48" t="inlineStr">
+        <is>
+          <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
+        </is>
+      </c>
+      <c r="I30" s="48" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="48" t="inlineStr">
-        <is>
-          <t>همه static UI512 Meas768 Ctrl1024 high-water&gt;20%</t>
-        </is>
-      </c>
-      <c r="I30" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J30" s="48" t="inlineStr">
         <is>
-          <t>PASS: static no overflow. FAIL: dynamic/overflow</t>
+          <t>PASS: بدون starvation. FAIL: delay500/1000</t>
         </is>
       </c>
       <c r="K30" s="48" t="inlineStr"/>
@@ -3406,535 +3433,325 @@
       <c r="O30" s="50" t="inlineStr"/>
       <c r="P30" s="50" t="inlineStr"/>
       <c r="Q30" s="51">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="40.5" customHeight="1">
       <c r="A31" s="42" t="inlineStr">
         <is>
-          <t>UI-027</t>
-        </is>
-      </c>
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>No extra RTOS</t>
-        </is>
-      </c>
-      <c r="C31" s="44" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>hysteresis UI</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="inlineStr">
-        <is>
-          <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
-گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
-گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F31" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="43" t="inlineStr">
-        <is>
-          <t>هیچ شئ جدید برای hysteresis</t>
-        </is>
-      </c>
-      <c r="I31" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="43" t="inlineStr">
-        <is>
-          <t>PASS: بدون شئ. FAIL: شئ جدید</t>
-        </is>
-      </c>
-      <c r="K31" s="43" t="inlineStr"/>
-      <c r="L31" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M31" s="43" t="inlineStr"/>
-      <c r="N31" s="43" t="inlineStr"/>
-      <c r="O31" s="45" t="inlineStr"/>
-      <c r="P31" s="45" t="inlineStr"/>
-      <c r="Q31" s="47">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="42" t="inlineStr">
-        <is>
-          <t>UI-028</t>
-        </is>
-      </c>
-      <c r="B32" s="48" t="inlineStr">
-        <is>
-          <t>Task starvation</t>
-        </is>
-      </c>
-      <c r="C32" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D32" s="48" t="inlineStr">
-        <is>
-          <t>همه سناریوها</t>
-        </is>
-      </c>
-      <c r="E32" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
-گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
-گام ۳: task_ui، تسک اندازه‌گیری و تسک کنترل هر سه باید هر 10 میلی‌ثانیه اجرا شوند.
-گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F32" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="50" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H32" s="48" t="inlineStr">
-        <is>
-          <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
-        </is>
-      </c>
-      <c r="I32" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="48" t="inlineStr">
-        <is>
-          <t>PASS: بدون starvation. FAIL: delay500/1000</t>
-        </is>
-      </c>
-      <c r="K32" s="48" t="inlineStr"/>
-      <c r="L32" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M32" s="48" t="inlineStr"/>
-      <c r="N32" s="48" t="inlineStr"/>
-      <c r="O32" s="50" t="inlineStr"/>
-      <c r="P32" s="50" t="inlineStr"/>
-      <c r="Q32" s="51">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="40.5" customHeight="1">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>UI-029</t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_ui</t>
-        </is>
-      </c>
-      <c r="C33" s="54" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="inlineStr">
-        <is>
-          <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
-گام ۲: 2 ثانیه نگاه کن.
-گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F33" s="45" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G33" s="45" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H33" s="43" t="inlineStr">
-        <is>
-          <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
-        </is>
-      </c>
-      <c r="I33" s="43" t="inlineStr">
-        <is>
-          <t>safe-off</t>
-        </is>
-      </c>
-      <c r="J33" s="43" t="inlineStr">
-        <is>
-          <t>LED خاموش بدون درصد کاذب</t>
-        </is>
-      </c>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="55" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M33" s="43" t="n"/>
-      <c r="N33" s="43" t="n"/>
-      <c r="O33" s="45" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P33" s="45" t="n"/>
-      <c r="Q33" s="47" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="40.5" customHeight="1">
-      <c r="A34" s="42" t="inlineStr">
-        <is>
           <t>UI-030</t>
         </is>
       </c>
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B31" s="48" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C34" s="50" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D34" s="48" t="inlineStr">
+      <c r="D31" s="48" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E34" s="48" t="inlineStr">
+      <c r="E31" s="48" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و چند دیالوگ پنل (تأیید و خطا) پشت سر هم بساز.
 گام ۲: هم‌زمان چراغ‌های روی برد را 3 ثانیه نگاه کن.
 گام ۳: UI برد باید کاملاً مستقل از پنل کار خودش را بکند؛ دیالوگ‌ها فقط داخل مرورگر هستند و نباید هیچ اثری روی LED یا بوق برد بگذارند.</t>
         </is>
       </c>
-      <c r="F34" s="50" t="inlineStr">
+      <c r="F31" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="50" t="inlineStr">
+      <c r="G31" s="50" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H34" s="48" t="inlineStr">
+      <c r="H31" s="48" t="inlineStr">
         <is>
           <t>UI مستقل از پنل؛ دیالوگ‌ها فقط در مرورگر</t>
         </is>
       </c>
-      <c r="I34" s="48" t="inlineStr">
+      <c r="I31" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J34" s="48" t="inlineStr">
+      <c r="J31" s="48" t="inlineStr">
         <is>
           <t>بدون تداخل</t>
         </is>
       </c>
-      <c r="K34" s="48" t="n"/>
-      <c r="L34" s="55" t="inlineStr">
+      <c r="K31" s="48" t="n"/>
+      <c r="L31" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M34" s="48" t="n"/>
-      <c r="N34" s="48" t="n"/>
-      <c r="O34" s="50" t="inlineStr">
+      <c r="M31" s="48" t="n"/>
+      <c r="N31" s="48" t="n"/>
+      <c r="O31" s="50" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P34" s="50" t="n"/>
-      <c r="Q34" s="51" t="inlineStr">
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="51" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="Q32" s="56">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="40.5" customHeight="1">
+      <c r="Q33" s="56">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="40.5" customHeight="1">
+      <c r="Q34" s="56">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="56">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="56">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="56">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="56">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="56">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="56">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="56">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="56">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="56">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="56">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="56">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="56">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="56">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="56">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="56">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="56">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="56">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="56">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="56">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="56">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="56">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="56">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="56">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="56">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="56">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="56">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="56">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="56">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="Q63" s="56">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="Q64" s="56">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="Q65" s="56">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="Q66" s="56">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="Q67" s="56">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="Q68" s="56">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="Q69" s="56">
-        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
+        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="Q70" s="56">
-        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
+        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="Q71" s="56">
-        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="Q72" s="56">
-        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="Q73" s="56">
-        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="Q74" s="56">
         <f>IF(OR(L74="",L74="در انتظار"),"",IF(Q74="",TODAY(),Q74))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q34"/>
+  <autoFilter ref="A4:Q71"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -3946,10 +3763,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
+    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
+    <hyperlink ref="E11" location="'برنامه تست'!A9"/>
+    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3957,6 +3774,479 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="75" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="76" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>ورودی‌ها (v_bat/v_in/raw)</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>LED/بوق — انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>فاز چشمک — انتظار</t>
+        </is>
+      </c>
+      <c r="J4" s="36" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="L4" s="36" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="36" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="N4" s="36" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="O4" s="36" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="36" t="inlineStr">
+        <is>
+          <t>تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="36" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>UI-026</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>RTOS static + stack</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>همه taskها</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
+گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
+گام ۳: مقدار high-water هر استک را بخوان: باید بیشتر از 20 درصد از استک آزاد مانده باشد.
+گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F5" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>همه static UI512 Meas768 Ctrl1024 high-water&gt;20%</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="48" t="inlineStr">
+        <is>
+          <t>PASS: static no overflow. FAIL: dynamic/overflow</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="n"/>
+      <c r="L5" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="48" t="n"/>
+      <c r="N5" s="48" t="n"/>
+      <c r="O5" s="50" t="n"/>
+      <c r="P5" s="50" t="n"/>
+      <c r="Q5" s="51">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>UI-027</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>No extra RTOS</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>hysteresis UI</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
+گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
+گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F6" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>هیچ شئ جدید برای hysteresis</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>PASS: بدون شئ. FAIL: شئ جدید</t>
+        </is>
+      </c>
+      <c r="K6" s="43" t="n"/>
+      <c r="L6" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="43" t="n"/>
+      <c r="N6" s="43" t="n"/>
+      <c r="O6" s="45" t="n"/>
+      <c r="P6" s="45" t="n"/>
+      <c r="Q6" s="47">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>UI-029</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_ui</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
+گام ۲: 2 ثانیه نگاه کن.
+گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F7" s="45" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G7" s="45" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="inlineStr">
+        <is>
+          <t>safe-off</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>LED خاموش بدون درصد کاذب</t>
+        </is>
+      </c>
+      <c r="K7" s="43" t="n"/>
+      <c r="L7" s="55" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M7" s="43" t="n"/>
+      <c r="N7" s="43" t="n"/>
+      <c r="O7" s="45" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P7" s="45" t="n"/>
+      <c r="Q7" s="47" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="56">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="56">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="56">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="56">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="56">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="56">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="56">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="56">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="56">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="56">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="56">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="56">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="56">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="56">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="56">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="56">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="56">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="56">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="56">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="56">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q7"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -4603,32 +4893,32 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId21"/>
+    <hyperlink ref="F4" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F5" location="'برنامه تست'!A5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
+    <hyperlink ref="F7" location="'تست‌های برنامه‌نویسی'!A5"/>
+    <hyperlink ref="F8" location="'برنامه تست'!A6"/>
+    <hyperlink ref="F9" location="'برنامه تست'!A6"/>
+    <hyperlink ref="F10" location="'برنامه تست'!A15"/>
+    <hyperlink ref="F11" location="'برنامه تست'!A15"/>
+    <hyperlink ref="F12" location="'برنامه تست'!A19"/>
+    <hyperlink ref="F13" location="'برنامه تست'!A6"/>
+    <hyperlink ref="F14" location="'برنامه تست'!A15"/>
+    <hyperlink ref="F15" location="'برنامه تست'!A28"/>
+    <hyperlink ref="F16" location="'برنامه تست'!A25"/>
+    <hyperlink ref="F17" location="'برنامه تست'!A27"/>
+    <hyperlink ref="F18" location="'برنامه تست'!A9"/>
+    <hyperlink ref="F19" location="'برنامه تست'!A26"/>
+    <hyperlink ref="F20" location="'تست‌های برنامه‌نویسی'!A5"/>
+    <hyperlink ref="F21" location="'تست‌های برنامه‌نویسی'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4893,7 +5183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -5122,7 +5412,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="63" t="inlineStr">
+      <c r="D14" s="78" t="inlineStr">
         <is>
           <t>UI-001 تا UI-028</t>
         </is>
@@ -5205,12 +5495,15 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D14" location="'برنامه تست'!A5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -5341,7 +5634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -9,18 +9,21 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های آزمایشگاهی'!$A$4:$Q$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های آزمایشگاهی'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1516,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1649,94 +1652,25 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="42" t="inlineStr">
         <is>
-          <t>UI-001</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>Mapping PA3→v_bat</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="inlineStr">
+          <t>UI-002</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>BatteryRun 2% 56/57/58</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
-        <is>
-          <t>برد روشن, valid</t>
-        </is>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
-گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
-گام ۳: 100 میلی‌ثانیه صبر کن و raw2 و v_bat24_mv را بخوان.
-گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
-        </is>
-      </c>
-      <c r="F5" s="45" t="inlineStr">
-        <is>
-          <t>PA3 2.0V pin → v_bat≈22352mV, v_in 24V</t>
-        </is>
-      </c>
-      <c r="G5" s="45" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H5" s="43" t="inlineStr">
-        <is>
-          <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
-        </is>
-      </c>
-      <c r="I5" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="43" t="inlineStr">
-        <is>
-          <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
-        </is>
-      </c>
-      <c r="K5" s="43" t="inlineStr"/>
-      <c r="L5" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M5" s="43" t="inlineStr"/>
-      <c r="N5" s="43" t="inlineStr"/>
-      <c r="O5" s="45" t="inlineStr"/>
-      <c r="P5" s="45" t="inlineStr"/>
-      <c r="Q5" s="47">
-        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
-        <is>
-          <t>UI-002</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>BatteryRun 2% 56/57/58</t>
-        </is>
-      </c>
-      <c r="C6" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>BatteryRun, valid, InputDisconnected</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E5" s="48" t="inlineStr">
         <is>
           <t>گام ۱: برد در BatteryRun با snapshot معتبر و ورودی قطع باشد و درصد پایدار (stable) روی 57 نشسته باشد (باتری 25 ولت، raw=57).
 گام ۲: اسیلوسکوپ را روی LED سبز بگذار.
@@ -1744,68 +1678,68 @@
 گام ۴: درصد پایدار باید همان 57 بماند و چشمک سبز ثابت باشد: خاموشی 430 و روشنی 570 میلی‌ثانیه، بدون اینکه فاز از نو شروع شود.</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>v_bat25000 raw57 →56/58 jitter</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
-        <is>
-          <t>stable57 حفظ, green Off430 On570 ثابت, فاز reset نشود</t>
-        </is>
-      </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>درصد پایدار همان 57 می‌ماند و چشمک سبز منظم است؛ ریتم چشمک نه تکان می‌خورد نه از نو شروع می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
         <is>
           <t>فاز حفظ On/Off ثابت</t>
         </is>
       </c>
-      <c r="J6" s="48" t="inlineStr">
-        <is>
-          <t>PASS: stable57 فاز حفظ. FAIL: stable56/58 یا reset</t>
-        </is>
-      </c>
-      <c r="K6" s="48" t="inlineStr"/>
-      <c r="L6" s="46" t="inlineStr">
+      <c r="J5" s="48" t="inlineStr">
+        <is>
+          <t>درصد و ریتم ثابت بمانند؛ عوض شدن درصد با نویز یا پریدن ریتم = رد</t>
+        </is>
+      </c>
+      <c r="K5" s="48" t="inlineStr"/>
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="48" t="inlineStr"/>
-      <c r="N6" s="48" t="inlineStr"/>
-      <c r="O6" s="50" t="inlineStr"/>
-      <c r="P6" s="50" t="inlineStr"/>
-      <c r="Q6" s="51">
+      <c r="M5" s="48" t="inlineStr"/>
+      <c r="N5" s="48" t="inlineStr"/>
+      <c r="O5" s="50" t="inlineStr"/>
+      <c r="P5" s="50" t="inlineStr"/>
+      <c r="Q5" s="51">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>UI-003</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>BatteryRun 57→55</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 شروع کن (پایان UI-002).
 گام ۲: درصد خام را به 55 پایین بیاور (v_bat حدود 24850 میلی‌ولت).
@@ -1813,68 +1747,68 @@
 گام ۴: درصد پایدار باید 55 شده باشد و چشمک سبز از مرز بعدی با خاموشی 450 و روشنی 550 ادامه پیدا کند، بدون ریست شدن فاز؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="45" t="inlineStr">
+      <c r="F6" s="45" t="inlineStr">
         <is>
           <t>raw55</t>
         </is>
       </c>
-      <c r="G7" s="45" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H7" s="43" t="inlineStr">
-        <is>
-          <t>stable→55, green Off450 On550 از مرز بعدی, فاز حفظ</t>
-        </is>
-      </c>
-      <c r="I7" s="43" t="inlineStr">
+      <c r="G6" s="45" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>درصد پایدار به 55 می‌رسد و چشمک سبز کمی تندتر می‌شود (خاموشی بیشتر از قبل)، بدون پرش ناگهانی</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="inlineStr">
         <is>
           <t>تغییر از مرز بعدی</t>
         </is>
       </c>
-      <c r="J7" s="43" t="inlineStr">
-        <is>
-          <t>PASS: stable55. FAIL: 57 حفظ</t>
-        </is>
-      </c>
-      <c r="K7" s="43" t="inlineStr"/>
-      <c r="L7" s="46" t="inlineStr">
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>پایدار 55 شود؛ ماندن روی 57 = رد</t>
+        </is>
+      </c>
+      <c r="K6" s="43" t="inlineStr"/>
+      <c r="L6" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="43" t="inlineStr"/>
-      <c r="N7" s="43" t="inlineStr"/>
-      <c r="O7" s="45" t="inlineStr"/>
-      <c r="P7" s="45" t="inlineStr"/>
-      <c r="Q7" s="47">
+      <c r="M6" s="43" t="inlineStr"/>
+      <c r="N6" s="43" t="inlineStr"/>
+      <c r="O6" s="45" t="inlineStr"/>
+      <c r="P6" s="45" t="inlineStr"/>
+      <c r="Q6" s="47">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>UI-004</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>BatteryRun 57→59</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E8" s="48" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 شروع کن.
 گام ۲: درصد خام را به 59 بالا ببر (v_bat حدود 25130 میلی‌ولت).
@@ -1882,68 +1816,68 @@
 گام ۴: درصد پایدار باید 59 شده باشد و چشمک سبز از مرز بعدی با خاموشی 410 و روشنی 590 ادامه پیدا کند، بدون ریست شدن فاز.</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>raw59</t>
         </is>
       </c>
-      <c r="G8" s="50" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="inlineStr">
-        <is>
-          <t>stable59 Off410 On590 فاز حفظ</t>
-        </is>
-      </c>
-      <c r="I8" s="48" t="inlineStr">
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="inlineStr">
+        <is>
+          <t>درصد پایدار به 59 می‌رسد و چشمک سبز کمی کندتر می‌شود (روشنی بیشتر از قبل)، بدون پرش ناگهانی</t>
+        </is>
+      </c>
+      <c r="I7" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J8" s="48" t="inlineStr">
-        <is>
-          <t>PASS: stable59. FAIL: 57 حفظ</t>
-        </is>
-      </c>
-      <c r="K8" s="48" t="inlineStr"/>
-      <c r="L8" s="46" t="inlineStr">
+      <c r="J7" s="48" t="inlineStr">
+        <is>
+          <t>پایدار 59 شود؛ ماندن روی 57 = رد</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="inlineStr"/>
+      <c r="L7" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="48" t="inlineStr"/>
-      <c r="N8" s="48" t="inlineStr"/>
-      <c r="O8" s="50" t="inlineStr"/>
-      <c r="P8" s="50" t="inlineStr"/>
-      <c r="Q8" s="51">
+      <c r="M7" s="48" t="inlineStr"/>
+      <c r="N7" s="48" t="inlineStr"/>
+      <c r="O7" s="50" t="inlineStr"/>
+      <c r="P7" s="50" t="inlineStr"/>
+      <c r="Q7" s="51">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>UI-005</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>0% critical raw0</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>BatteryRun 21V یا کمتر</t>
         </is>
       </c>
-      <c r="E9" s="43" t="inlineStr">
+      <c r="E8" s="43" t="inlineStr">
         <is>
           <t>گام ۱: برد در BatteryRun باشد و ولتاژ باتری را دقیقاً روی 21 ولت (21000 میلی‌ولت) بگذار تا درصد خام و پایدار هر دو صفر شوند.
 گام ۲: هر سه LED و بوق را 12 ثانیه زیر نظر بگیر.
@@ -1951,68 +1885,68 @@
 گام ۴: بوق باید فقط یک بار و 10 ثانیه باشد و بعد تا وقتی درصد از صفر بیرون نیامده ساکت بماند؛ بوق تکراری یا LED روشن یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F9" s="45" t="inlineStr">
+      <c r="F8" s="45" t="inlineStr">
         <is>
           <t>v_bat21000 raw0 stable0</t>
         </is>
       </c>
-      <c r="G9" s="45" t="inlineStr">
+      <c r="G8" s="45" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="H8" s="43" t="inlineStr">
         <is>
           <t>همه LED خاموش، یک بوق 10s سپس خاموش تا خروج از 0%</t>
         </is>
       </c>
-      <c r="I9" s="43" t="inlineStr">
+      <c r="I8" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="43" t="inlineStr">
+      <c r="J8" s="43" t="inlineStr">
         <is>
           <t>PASS: یک 10s سپس خاموش. FAIL: مکرر/LED روشن</t>
         </is>
       </c>
-      <c r="K9" s="43" t="inlineStr"/>
-      <c r="L9" s="46" t="inlineStr">
+      <c r="K8" s="43" t="inlineStr"/>
+      <c r="L8" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="43" t="inlineStr"/>
-      <c r="N9" s="43" t="inlineStr"/>
-      <c r="O9" s="45" t="inlineStr"/>
-      <c r="P9" s="45" t="inlineStr"/>
-      <c r="Q9" s="47">
+      <c r="M8" s="43" t="inlineStr"/>
+      <c r="N8" s="43" t="inlineStr"/>
+      <c r="O8" s="45" t="inlineStr"/>
+      <c r="P8" s="45" t="inlineStr"/>
+      <c r="Q8" s="47">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>UI-006</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>0↔1 نویز</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="48" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>stable0 Critical 10s</t>
         </is>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>گام ۱: از وضعیت بحرانی صفر درصد شروع کن و بگذار بوق یک‌بارهٔ 10 ثانیه‌ای شروع شود (پایان UI-005).
 گام ۲: درصد خام را بین 0 و 1 نویز بده: 0، بعد 1، بعد 0، بعد 1، هر کدام 200 میلی‌ثانیه.
@@ -2020,68 +1954,68 @@
 گام ۴: درصد پایدار باید صفر بماند (تغییر کمتر از 2 شمرده نمی‌شود)، بوق نباید از نو شروع شود و LEDها خاموش می‌مانند.</t>
         </is>
       </c>
-      <c r="F10" s="50" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>raw0/1 jitter</t>
         </is>
       </c>
-      <c r="G10" s="50" t="inlineStr">
+      <c r="G9" s="50" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H10" s="48" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>stable0 حفظ (&lt;2) بوق restart نشود LED خاموش</t>
         </is>
       </c>
-      <c r="I10" s="48" t="inlineStr">
+      <c r="I9" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="48" t="inlineStr">
+      <c r="J9" s="48" t="inlineStr">
         <is>
           <t>PASS: یک بار. FAIL: restart</t>
         </is>
       </c>
-      <c r="K10" s="48" t="inlineStr"/>
-      <c r="L10" s="46" t="inlineStr">
+      <c r="K9" s="48" t="inlineStr"/>
+      <c r="L9" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="48" t="inlineStr"/>
-      <c r="N10" s="48" t="inlineStr"/>
-      <c r="O10" s="50" t="inlineStr"/>
-      <c r="P10" s="50" t="inlineStr"/>
-      <c r="Q10" s="51">
+      <c r="M9" s="48" t="inlineStr"/>
+      <c r="N9" s="48" t="inlineStr"/>
+      <c r="O9" s="50" t="inlineStr"/>
+      <c r="P9" s="50" t="inlineStr"/>
+      <c r="Q9" s="51">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>UI-007</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>1% مستقل raw1</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Stable0 خروج به1</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr">
+      <c r="E10" s="52" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار صفر شروع کن.
 گام ۲: درصد خام را از 0 به 1 ببر (v_bat حدود 21070 میلی‌ولت) و همان‌جا نگه دار.
@@ -2089,136 +2023,136 @@
 گام ۴: درصد پایدار باید 1 شود؛ علامتش سه‌بوق هر 20 ثانیه و چشمک سبز با خاموشی 990 و روشنی فقط 10 میلی‌ثانیه است؛ رفتار بحرانی (UI-005) یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F11" s="45" t="inlineStr">
+      <c r="F10" s="45" t="inlineStr">
         <is>
           <t>raw1 stable1</t>
         </is>
       </c>
-      <c r="G11" s="45" t="inlineStr">
+      <c r="G10" s="45" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H11" s="43" t="inlineStr">
-        <is>
-          <t>stable1 سه‌بوق هر20s + سبز Off990 On10</t>
-        </is>
-      </c>
-      <c r="I11" s="43" t="inlineStr">
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>درصد پایدار 1 می‌شود؛ سه‌بوق هر از چندی و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="inlineStr">
         <is>
           <t>سه‌بوق</t>
         </is>
       </c>
-      <c r="J11" s="43" t="inlineStr">
-        <is>
-          <t>PASS: stable1 سه‌بوق. FAIL: بحرانی</t>
-        </is>
-      </c>
-      <c r="K11" s="43" t="inlineStr"/>
-      <c r="L11" s="46" t="inlineStr">
+      <c r="J10" s="43" t="inlineStr">
+        <is>
+          <t>پایدار 1 با همان رفتار؛ رفتار بحرانی درصد صفر = رد</t>
+        </is>
+      </c>
+      <c r="K10" s="43" t="inlineStr"/>
+      <c r="L10" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="43" t="inlineStr"/>
-      <c r="N11" s="43" t="inlineStr"/>
-      <c r="O11" s="45" t="inlineStr"/>
-      <c r="P11" s="45" t="inlineStr"/>
-      <c r="Q11" s="47">
+      <c r="M10" s="43" t="inlineStr"/>
+      <c r="N10" s="43" t="inlineStr"/>
+      <c r="O10" s="45" t="inlineStr"/>
+      <c r="P10" s="45" t="inlineStr"/>
+      <c r="Q10" s="47">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>UI-008</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>1% →2 حفظ/خروج</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="48" t="inlineStr">
+      <c r="D11" s="48" t="inlineStr">
         <is>
           <t>stable1</t>
         </is>
       </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار 1 شروع کن (پایان UI-007).
 گام ۲: درصد خام را به 2 ببر (v_bat حدود 21140 میلی‌ولت) و 1 ثانیه نگه دار.
 گام ۳: درصد پایدار باید همان 1 بماند (چون رسیدن به 3 لازم است تا از 1 بیرون بیاید) و همان سه‌بوق ادامه داشته باشد؛ رفتن به 2 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F12" s="50" t="inlineStr">
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>raw2</t>
         </is>
       </c>
-      <c r="G12" s="50" t="inlineStr">
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>stable1 حفظ (raw2&lt;3) همچنان سه‌بوق</t>
-        </is>
-      </c>
-      <c r="I12" s="48" t="inlineStr">
+      <c r="H11" s="48" t="inlineStr">
+        <is>
+          <t>درصد پایدار همان 1 می‌ماند و همان سه‌بوق ادامه دارد</t>
+        </is>
+      </c>
+      <c r="I11" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J12" s="48" t="inlineStr">
-        <is>
-          <t>PASS: stable1. FAIL: 2</t>
-        </is>
-      </c>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="46" t="inlineStr">
+      <c r="J11" s="48" t="inlineStr">
+        <is>
+          <t>پایدار 1 بماند؛ رفتن به 2 = رد</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="inlineStr"/>
+      <c r="L11" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="48" t="inlineStr"/>
-      <c r="N12" s="48" t="inlineStr"/>
-      <c r="O12" s="50" t="inlineStr"/>
-      <c r="P12" s="50" t="inlineStr"/>
-      <c r="Q12" s="51">
+      <c r="M11" s="48" t="inlineStr"/>
+      <c r="N11" s="48" t="inlineStr"/>
+      <c r="O11" s="50" t="inlineStr"/>
+      <c r="P11" s="50" t="inlineStr"/>
+      <c r="Q11" s="51">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>UI-009</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>1% →2 خروج با3</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>stable1</t>
         </is>
       </c>
-      <c r="E13" s="43" t="inlineStr">
+      <c r="E12" s="43" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار 1 شروع کن.
 گام ۲: درصد خام را مستقیم روی 3 بگذار (v_bat حدود 21210 میلی‌ولت).
@@ -2226,68 +2160,68 @@
 گام ۴: درصد پایدار باید 2 شده باشد و الگوی بوق به الگوی درصد 2 عوض شود؛ ماندن روی 1 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F13" s="45" t="inlineStr">
+      <c r="F12" s="45" t="inlineStr">
         <is>
           <t>raw3</t>
         </is>
       </c>
-      <c r="G13" s="45" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H13" s="43" t="inlineStr">
-        <is>
-          <t>stable2 دو بوق 60s یا یک بوق</t>
-        </is>
-      </c>
-      <c r="I13" s="43" t="inlineStr">
+      <c r="G12" s="45" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>درصد پایدار 2 می‌شود و الگوی بوق به الگوی باند ۲ عوض می‌شود</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J13" s="43" t="inlineStr">
-        <is>
-          <t>PASS: stable2. FAIL: 1 حفظ</t>
-        </is>
-      </c>
-      <c r="K13" s="43" t="inlineStr"/>
-      <c r="L13" s="46" t="inlineStr">
+      <c r="J12" s="43" t="inlineStr">
+        <is>
+          <t>پایدار 2 شود؛ ماندن روی 1 = رد</t>
+        </is>
+      </c>
+      <c r="K12" s="43" t="inlineStr"/>
+      <c r="L12" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="43" t="inlineStr"/>
-      <c r="N13" s="43" t="inlineStr"/>
-      <c r="O13" s="45" t="inlineStr"/>
-      <c r="P13" s="45" t="inlineStr"/>
-      <c r="Q13" s="47">
+      <c r="M12" s="43" t="inlineStr"/>
+      <c r="N12" s="43" t="inlineStr"/>
+      <c r="O12" s="45" t="inlineStr"/>
+      <c r="P12" s="45" t="inlineStr"/>
+      <c r="Q12" s="47">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>UI-010</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>BoardTest 0→2</t>
         </is>
       </c>
-      <c r="C14" s="50" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="48" t="inlineStr">
+      <c r="D13" s="48" t="inlineStr">
         <is>
           <t>stable0</t>
         </is>
       </c>
-      <c r="E14" s="48" t="inlineStr">
+      <c r="E13" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از درصد پایدار صفر شروع کن.
 گام ۲: درصد خام را از 0 به 2 ببر (v_bat حدود 21140 میلی‌ولت).
@@ -2295,68 +2229,68 @@
 گام ۴: درصد پایدار باید اول 1 شود، نه مستقیم 2؛ پریدن مستقیم به 2 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F14" s="50" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>raw2</t>
         </is>
       </c>
-      <c r="G14" s="50" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>stable0→1 ابتدا 1 نه 2</t>
-        </is>
-      </c>
-      <c r="I14" s="48" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H13" s="48" t="inlineStr">
+        <is>
+          <t>درصد پایدار اول 1 می‌شود، نه اینکه مستقیم بپرد روی 2</t>
+        </is>
+      </c>
+      <c r="I13" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 1 نه 2. FAIL: مستقیم 2</t>
-        </is>
-      </c>
-      <c r="K14" s="48" t="inlineStr"/>
-      <c r="L14" s="46" t="inlineStr">
+      <c r="J13" s="48" t="inlineStr">
+        <is>
+          <t>اول 1 شود؛ پرش مستقیم به 2 = رد</t>
+        </is>
+      </c>
+      <c r="K13" s="48" t="inlineStr"/>
+      <c r="L13" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="48" t="inlineStr"/>
-      <c r="N14" s="48" t="inlineStr"/>
-      <c r="O14" s="50" t="inlineStr"/>
-      <c r="P14" s="50" t="inlineStr"/>
-      <c r="Q14" s="51">
+      <c r="M13" s="48" t="inlineStr"/>
+      <c r="N13" s="48" t="inlineStr"/>
+      <c r="O13" s="50" t="inlineStr"/>
+      <c r="P13" s="50" t="inlineStr"/>
+      <c r="Q13" s="51">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>UI-011</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>Charging 5% 56/57/58</t>
         </is>
       </c>
-      <c r="C15" s="44" t="inlineStr">
+      <c r="C14" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Charging Input24V Battery25V</t>
         </is>
       </c>
-      <c r="E15" s="43" t="inlineStr">
+      <c r="E14" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 25 ولت وصل باشد تا وضعیت Charging شود و درصد پایدار شارژ روی 57 نشسته باشد.
 گام ۲: اسیلوسکوپ را روی LED زرد بگذار.
@@ -2364,165 +2298,234 @@
 گام ۴: درصد پایدار همان 57 می‌ماند و چشمک زرد ثابت است: روشنی 430 و خاموشی 570 میلی‌ثانیه، بدون ریست شدن فاز.</t>
         </is>
       </c>
-      <c r="F15" s="45" t="inlineStr">
+      <c r="F14" s="45" t="inlineStr">
         <is>
           <t>v_in24000 v_bat25000 raw57→56/58</t>
         </is>
       </c>
-      <c r="G15" s="45" t="inlineStr">
+      <c r="G14" s="45" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H15" s="43" t="inlineStr">
-        <is>
-          <t>chargingStable57 حفظ, yellow On430 Off570 ثابت, فاز reset نشود</t>
-        </is>
-      </c>
-      <c r="I15" s="43" t="inlineStr">
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>درصد پایدار شارژ همان 57 می‌ماند و زرد منظم چشمک می‌زند؛ ریتم ثابت و بدون پرش</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="inlineStr">
         <is>
           <t>زرد فاز حفظ</t>
         </is>
       </c>
-      <c r="J15" s="43" t="inlineStr">
-        <is>
-          <t>PASS: stable57 فاز حفظ. FAIL: 56/58 یا reset</t>
-        </is>
-      </c>
-      <c r="K15" s="43" t="inlineStr"/>
-      <c r="L15" s="46" t="inlineStr">
+      <c r="J14" s="43" t="inlineStr">
+        <is>
+          <t>پایدار و ریتم ثابت؛ عوض شدن با نویز یا پرش ریتم = رد</t>
+        </is>
+      </c>
+      <c r="K14" s="43" t="inlineStr"/>
+      <c r="L14" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="43" t="inlineStr"/>
-      <c r="N15" s="43" t="inlineStr"/>
-      <c r="O15" s="45" t="inlineStr"/>
-      <c r="P15" s="45" t="inlineStr"/>
-      <c r="Q15" s="47">
+      <c r="M14" s="43" t="inlineStr"/>
+      <c r="N14" s="43" t="inlineStr"/>
+      <c r="O14" s="45" t="inlineStr"/>
+      <c r="P14" s="45" t="inlineStr"/>
+      <c r="Q14" s="47">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>UI-012</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>Charging 5% 53..61</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E16" s="48" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 در Charging شروع کن.
 گام ۲: درصد خام را اول به 53 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار؛ بعد به 61 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار.
 گام ۳: چون اختلاف کمتر از 5 است، درصد پایدار باید همان 57 بماند و چشمک زرد هیچ تغییری نکند؛ هر تغییری یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>raw53 raw61</t>
         </is>
       </c>
-      <c r="G16" s="50" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>1s each</t>
         </is>
       </c>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>57 حفظ، زرد ثابت</t>
-        </is>
-      </c>
-      <c r="I16" s="48" t="inlineStr">
+      <c r="H15" s="48" t="inlineStr">
+        <is>
+          <t>درصد پایدار همان 57 می‌ماند و چشمک زرد هیچ تغییری نمی‌کند</t>
+        </is>
+      </c>
+      <c r="I15" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J16" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 57 حفظ. FAIL: تغییر</t>
-        </is>
-      </c>
-      <c r="K16" s="48" t="inlineStr"/>
-      <c r="L16" s="46" t="inlineStr">
+      <c r="J15" s="48" t="inlineStr">
+        <is>
+          <t>57 بماند؛ هر تغییری = رد</t>
+        </is>
+      </c>
+      <c r="K15" s="48" t="inlineStr"/>
+      <c r="L15" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="48" t="inlineStr"/>
-      <c r="N16" s="48" t="inlineStr"/>
-      <c r="O16" s="50" t="inlineStr"/>
-      <c r="P16" s="50" t="inlineStr"/>
-      <c r="Q16" s="51">
+      <c r="M15" s="48" t="inlineStr"/>
+      <c r="N15" s="48" t="inlineStr"/>
+      <c r="O15" s="50" t="inlineStr"/>
+      <c r="P15" s="50" t="inlineStr"/>
+      <c r="Q15" s="51">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="40.5" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>UI-013</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Charging 5% خروج</t>
         </is>
       </c>
-      <c r="C17" s="44" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>stable57</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E16" s="43" t="inlineStr">
         <is>
           <t>گام ۱: از stable=57 در Charging شروع کن.
 گام ۲: درصد خام را به 52 ببر (اختلاف 5) و بعد به 62 ببر (اختلاف 5)؛ هر کدام را ببین.
 گام ۳: این بار درصد پایدار باید اول 52 و بعد 62 شود، و زمان‌های چشمک زرد از مرز بعدی اعمال شوند، بدون اینکه فاز ریست شود؛ ماندن روی 57 یعنی رد تست.</t>
         </is>
       </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>raw52→62</t>
+        </is>
+      </c>
+      <c r="G16" s="45" t="inlineStr">
+        <is>
+          <t>کمتر از یک ثانیه</t>
+        </is>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>درصد پایدار اول 52 و بعد 62 می‌شود؛ ریتم زرد با درصد عوض می‌شود ولی چشمک از نو شروع نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="inlineStr">
+        <is>
+          <t>از مرز بعدی</t>
+        </is>
+      </c>
+      <c r="J16" s="43" t="inlineStr">
+        <is>
+          <t>پایدار 52 بعد 62 شود؛ ماندن روی 57 = رد</t>
+        </is>
+      </c>
+      <c r="K16" s="43" t="inlineStr"/>
+      <c r="L16" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M16" s="43" t="inlineStr"/>
+      <c r="N16" s="43" t="inlineStr"/>
+      <c r="O16" s="45" t="inlineStr"/>
+      <c r="P16" s="45" t="inlineStr"/>
+      <c r="Q16" s="47">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>UI-015</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Full 100/95 enter</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Charging valid</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: وضعیت Charging با snapshot معتبر باشد.
+گام ۲: درصد خام باتری را روی 99 بگذار و 500 میلی‌ثانیه نگه دار؛ بعد روی 100 بگذار و 500 میلی‌ثانیه نگه دار.
+گام ۳: روی 99 باید Charging باشد؛ روی 100 باید InputOk شود: سبز ثابت و زرد خاموش.
+گام ۴: اگر روی 99 هم InputOk شد، تست رد است.</t>
+        </is>
+      </c>
       <c r="F17" s="45" t="inlineStr">
         <is>
-          <t>raw52→62</t>
+          <t>raw99→100</t>
         </is>
       </c>
       <c r="G17" s="45" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>500ms each</t>
         </is>
       </c>
       <c r="H17" s="43" t="inlineStr">
         <is>
-          <t>stable→52 سپس 62, yellow زمان جدید از مرز بعدی فاز حفظ</t>
+          <t>روی 99 وضعیت شارژ است (زرد چشمک‌زن) و روی 100 می‌شود ورودی خوب (سبز ثابت و زرد خاموش)</t>
         </is>
       </c>
       <c r="I17" s="43" t="inlineStr">
         <is>
-          <t>از مرز بعدی</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="43" t="inlineStr">
         <is>
-          <t>PASS: stable52/62. FAIL: 57 حفظ</t>
+          <t>ورود روی 100 باشد؛ ورودی خوب شدن روی 99 = رد</t>
         </is>
       </c>
       <c r="K17" s="43" t="inlineStr"/>
@@ -2536,19 +2539,19 @@
       <c r="O17" s="45" t="inlineStr"/>
       <c r="P17" s="45" t="inlineStr"/>
       <c r="Q17" s="47">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="42" t="inlineStr">
         <is>
-          <t>UI-014</t>
+          <t>UI-016</t>
         </is>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Charging yellow phase</t>
+          <t>Full 100/95 stay</t>
         </is>
       </c>
       <c r="C18" s="49" t="inlineStr">
@@ -2558,40 +2561,40 @@
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Charging 25V On430</t>
+          <t>InputOk active</t>
         </is>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
-گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
-گام ۳: تا 600 میلی‌ثانیه نگاه کن: روشنی باید تا 430 کامل ادامه پیدا کند و بعد خاموش شود.
-گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
+          <t>گام ۱: وضعیت InputOk فعال باشد (درصد 100).
+گام ۲: درصد خام را این‌طوری نگه دار: 99، بعد 96، بعد 95؛ هر کدام 500 میلی‌ثانیه.
+گام ۳: در هر سه حالت باید همان InputOk بماند و سبز ثابت باشد.
+گام ۴: افتادن به Charging در این بازه یعنی رد تست (خروج فقط زیر 95 است).</t>
         </is>
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>On430 jitter56</t>
+          <t>raw99 96 95</t>
         </is>
       </c>
       <c r="G18" s="50" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>500ms each</t>
         </is>
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
-          <t>ON تا 430 حفظ سپس OFF</t>
+          <t>تا وقتی درصد بالای 95 است همان ورودی خوب می‌ماند و سبز ثابت است</t>
         </is>
       </c>
       <c r="I18" s="48" t="inlineStr">
         <is>
-          <t>ON حفظ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="48" t="inlineStr">
         <is>
-          <t>PASS: restart نشد. FAIL: restart</t>
+          <t>در هر سه مقدار بماند؛ افتادن به شارژ = رد</t>
         </is>
       </c>
       <c r="K18" s="48" t="inlineStr"/>
@@ -2605,19 +2608,19 @@
       <c r="O18" s="50" t="inlineStr"/>
       <c r="P18" s="50" t="inlineStr"/>
       <c r="Q18" s="51">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>UI-015</t>
+          <t>UI-017</t>
         </is>
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>Full 100/95 enter</t>
+          <t>Full 95 exit</t>
         </is>
       </c>
       <c r="C19" s="44" t="inlineStr">
@@ -2627,30 +2630,30 @@
       </c>
       <c r="D19" s="43" t="inlineStr">
         <is>
-          <t>Charging valid</t>
+          <t>InputOk active</t>
         </is>
       </c>
       <c r="E19" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: وضعیت Charging با snapshot معتبر باشد.
-گام ۲: درصد خام باتری را روی 99 بگذار و 500 میلی‌ثانیه نگه دار؛ بعد روی 100 بگذار و 500 میلی‌ثانیه نگه دار.
-گام ۳: روی 99 باید Charging باشد؛ روی 100 باید InputOk شود: سبز ثابت و زرد خاموش.
-گام ۴: اگر روی 99 هم InputOk شد، تست رد است.</t>
+          <t>گام ۱: وضعیت InputOk فعال باشد.
+گام ۲: درصد خام را روی 94 بگذار (زیر 95).
+گام ۳: 100 میلی‌ثانیه صبر کن.
+گام ۴: باید برگردد به Charging: سبز ثابت و زرد با هیسترزیس 5 درصدی چشمک بزند؛ ماندن در InputOk یعنی رد تست.</t>
         </is>
       </c>
       <c r="F19" s="45" t="inlineStr">
         <is>
-          <t>raw99→100</t>
+          <t>raw94</t>
         </is>
       </c>
       <c r="G19" s="45" t="inlineStr">
         <is>
-          <t>500ms each</t>
+          <t>کمتر از یک ثانیه</t>
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr">
         <is>
-          <t>99→Charging، 100→InputOk سبز ثابت زرد خاموش</t>
+          <t>برمی‌گردد به شارژ: سبز ثابت و زرد دوباره چشمک‌زن</t>
         </is>
       </c>
       <c r="I19" s="43" t="inlineStr">
@@ -2660,7 +2663,7 @@
       </c>
       <c r="J19" s="43" t="inlineStr">
         <is>
-          <t>PASS: ورود 100. FAIL: 99 InputOk</t>
+          <t>زیر 95 به شارژ برگردد؛ ماندن در ورودی خوب = رد</t>
         </is>
       </c>
       <c r="K19" s="43" t="inlineStr"/>
@@ -2674,239 +2677,32 @@
       <c r="O19" s="45" t="inlineStr"/>
       <c r="P19" s="45" t="inlineStr"/>
       <c r="Q19" s="47">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="42" t="inlineStr">
         <is>
-          <t>UI-016</t>
-        </is>
-      </c>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>Full 100/95 stay</t>
-        </is>
-      </c>
-      <c r="C20" s="49" t="inlineStr">
+          <t>UI-019</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>InputOk non-blocking</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="48" t="inlineStr">
-        <is>
-          <t>InputOk active</t>
-        </is>
-      </c>
-      <c r="E20" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: وضعیت InputOk فعال باشد (درصد 100).
-گام ۲: درصد خام را این‌طوری نگه دار: 99، بعد 96، بعد 95؛ هر کدام 500 میلی‌ثانیه.
-گام ۳: در هر سه حالت باید همان InputOk بماند و سبز ثابت باشد.
-گام ۴: افتادن به Charging در این بازه یعنی رد تست (خروج فقط زیر 95 است).</t>
-        </is>
-      </c>
-      <c r="F20" s="50" t="inlineStr">
-        <is>
-          <t>raw99 96 95</t>
-        </is>
-      </c>
-      <c r="G20" s="50" t="inlineStr">
-        <is>
-          <t>500ms each</t>
-        </is>
-      </c>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>همچنان InputOk سبز ثابت</t>
-        </is>
-      </c>
-      <c r="I20" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="48" t="inlineStr">
-        <is>
-          <t>PASS: ماندن. FAIL: Charging</t>
-        </is>
-      </c>
-      <c r="K20" s="48" t="inlineStr"/>
-      <c r="L20" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M20" s="48" t="inlineStr"/>
-      <c r="N20" s="48" t="inlineStr"/>
-      <c r="O20" s="50" t="inlineStr"/>
-      <c r="P20" s="50" t="inlineStr"/>
-      <c r="Q20" s="51">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>UI-017</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>Full 95 exit</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>InputOk active</t>
-        </is>
-      </c>
-      <c r="E21" s="43" t="inlineStr">
-        <is>
-          <t>گام ۱: وضعیت InputOk فعال باشد.
-گام ۲: درصد خام را روی 94 بگذار (زیر 95).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: باید برگردد به Charging: سبز ثابت و زرد با هیسترزیس 5 درصدی چشمک بزند؛ ماندن در InputOk یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F21" s="45" t="inlineStr">
-        <is>
-          <t>raw94</t>
-        </is>
-      </c>
-      <c r="G21" s="45" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H21" s="43" t="inlineStr">
-        <is>
-          <t>Charging دوباره: سبز ثابت زرد چشمک 5%</t>
-        </is>
-      </c>
-      <c r="I21" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="43" t="inlineStr">
-        <is>
-          <t>PASS: 94→Charging. FAIL: InputOk ماند</t>
-        </is>
-      </c>
-      <c r="K21" s="43" t="inlineStr"/>
-      <c r="L21" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M21" s="43" t="inlineStr"/>
-      <c r="N21" s="43" t="inlineStr"/>
-      <c r="O21" s="45" t="inlineStr"/>
-      <c r="P21" s="45" t="inlineStr"/>
-      <c r="Q21" s="47">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>UI-018</t>
-        </is>
-      </c>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>BatteryRun phase preserve</t>
-        </is>
-      </c>
-      <c r="C22" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D22" s="48" t="inlineStr">
-        <is>
-          <t>BatteryRun 25V stable57 ON570</t>
-        </is>
-      </c>
-      <c r="E22" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: BatteryRun با باتری 25 ولت و درصد پایدار 57 باشد تا سبز در فاز روشنی 570 میلی‌ثانیه‌ای باشد.
-گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (پایدار همان 57 می‌ماند).
-گام ۳: تا 700 میلی‌ثانیه نگاه کن: روشنی باید تا 570 کامل ادامه پیدا کند و بعد 430 خاموشی بیاید.
-گام ۴: اگر روشنی وسطش از نو شروع شد، تست رد است.</t>
-        </is>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>On570 jitter56</t>
-        </is>
-      </c>
-      <c r="G22" s="50" t="inlineStr">
-        <is>
-          <t>700ms</t>
-        </is>
-      </c>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>ON تا 570 حفظ سپس OFF430</t>
-        </is>
-      </c>
-      <c r="I22" s="48" t="inlineStr">
-        <is>
-          <t>ON حفظ570</t>
-        </is>
-      </c>
-      <c r="J22" s="48" t="inlineStr">
-        <is>
-          <t>PASS: restart نشد. FAIL: restart</t>
-        </is>
-      </c>
-      <c r="K22" s="48" t="inlineStr"/>
-      <c r="L22" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M22" s="48" t="inlineStr"/>
-      <c r="N22" s="48" t="inlineStr"/>
-      <c r="O22" s="50" t="inlineStr"/>
-      <c r="P22" s="50" t="inlineStr"/>
-      <c r="Q22" s="51">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>UI-019</t>
-        </is>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
-        <is>
-          <t>InputOk non-blocking</t>
-        </is>
-      </c>
-      <c r="C23" s="44" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Input 24V Battery28V</t>
         </is>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E20" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 28 ولت بده تا وضعیت InputOk شود.
 گام ۲: هر 10 میلی‌ثانیه Ui_Tick را صدا بزن و زمان برگشتنش را اندازه بگیر.
@@ -2914,68 +2710,68 @@
 گام ۴: معیار: هیچ تأخیر (delay) بلندی مثل 500 میلی‌ثانیه نباید باشد؛ بودن delay یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F23" s="45" t="inlineStr">
+      <c r="F20" s="45" t="inlineStr">
         <is>
           <t>v_in24000 v_bat28000</t>
         </is>
       </c>
-      <c r="G23" s="45" t="inlineStr">
+      <c r="G20" s="45" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H23" s="43" t="inlineStr">
-        <is>
-          <t>سبز ثابت بوق خاموش Ui_Tick سریع</t>
-        </is>
-      </c>
-      <c r="I23" s="43" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
+        <is>
+          <t>سبز ثابت، بوق خاموش و دستگاه بدون هیچ مکث و هنگی کار می‌کند</t>
+        </is>
+      </c>
+      <c r="I20" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="43" t="inlineStr">
-        <is>
-          <t>PASS: بدون 500ms. FAIL: delay</t>
-        </is>
-      </c>
-      <c r="K23" s="43" t="inlineStr"/>
-      <c r="L23" s="46" t="inlineStr">
+      <c r="J20" s="43" t="inlineStr">
+        <is>
+          <t>هیچ مکث و هنگی نباشد = قبول</t>
+        </is>
+      </c>
+      <c r="K20" s="43" t="inlineStr"/>
+      <c r="L20" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="43" t="inlineStr"/>
-      <c r="N23" s="43" t="inlineStr"/>
-      <c r="O23" s="45" t="inlineStr"/>
-      <c r="P23" s="45" t="inlineStr"/>
-      <c r="Q23" s="47">
+      <c r="M20" s="43" t="inlineStr"/>
+      <c r="N20" s="43" t="inlineStr"/>
+      <c r="O20" s="45" t="inlineStr"/>
+      <c r="P20" s="45" t="inlineStr"/>
+      <c r="Q20" s="47">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>UI-020</t>
         </is>
       </c>
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B21" s="48" t="inlineStr">
         <is>
           <t>Charging non-blocking</t>
         </is>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="48" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Input24V Battery25V</t>
         </is>
       </c>
-      <c r="E24" s="48" t="inlineStr">
+      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>گام ۱: ورودی 24 ولت و باتری 25 ولت بده تا وضعیت Charging شود (درصد خام 57).
 گام ۲: اسیلوسکوپ را روی LED زرد بگذار و هر 10 میلی‌ثانیه Ui_Tick را صدا بزن.
@@ -2983,68 +2779,68 @@
 گام ۴: تیک باید سریع برگردد؛ هیچ blocking یا delay یک‌ثانیه‌ای نباید باشد.</t>
         </is>
       </c>
-      <c r="F24" s="50" t="inlineStr">
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>v_in24000 v_bat25000 raw57</t>
         </is>
       </c>
-      <c r="G24" s="50" t="inlineStr">
+      <c r="G21" s="50" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H24" s="48" t="inlineStr">
-        <is>
-          <t>سبز ثابت زرد فاز-محور بدون delay1s</t>
-        </is>
-      </c>
-      <c r="I24" s="48" t="inlineStr">
+      <c r="H21" s="48" t="inlineStr">
+        <is>
+          <t>سبز ثابت و زرد منظم چشمک می‌زند و دستگاه هنگ نمی‌کند</t>
+        </is>
+      </c>
+      <c r="I21" s="48" t="inlineStr">
         <is>
           <t>زرد فاز حفظ</t>
         </is>
       </c>
-      <c r="J24" s="48" t="inlineStr">
-        <is>
-          <t>PASS: non-blocking. FAIL: blocking</t>
-        </is>
-      </c>
-      <c r="K24" s="48" t="inlineStr"/>
-      <c r="L24" s="46" t="inlineStr">
+      <c r="J21" s="48" t="inlineStr">
+        <is>
+          <t>بدون هنگ و مکث = قبول</t>
+        </is>
+      </c>
+      <c r="K21" s="48" t="inlineStr"/>
+      <c r="L21" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M24" s="48" t="inlineStr"/>
-      <c r="N24" s="48" t="inlineStr"/>
-      <c r="O24" s="50" t="inlineStr"/>
-      <c r="P24" s="50" t="inlineStr"/>
-      <c r="Q24" s="51">
+      <c r="M21" s="48" t="inlineStr"/>
+      <c r="N21" s="48" t="inlineStr"/>
+      <c r="O21" s="50" t="inlineStr"/>
+      <c r="P21" s="50" t="inlineStr"/>
+      <c r="Q21" s="51">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
       </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>v_in28.5V</t>
         </is>
       </c>
-      <c r="E25" s="43" t="inlineStr">
+      <c r="E22" s="43" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را روی 28.5 ولت (28500 میلی‌ولت) بگذار.
 گام ۲: باید چهرهٔ اضافه‌ولتاژ بیاید: سبز ثابت، زرد خاموش، قرمز با دورهٔ 1 ثانیه و 50 درصد روشنی، و بوق 1 ثانیه‌ای هر 10 ثانیه.
@@ -3052,68 +2848,68 @@
 گام ۴: ولتاژ را به 26000 بیاور: حالا باید چهره پاک شود. کل تست 12 ثانیه؛ پاک شدن زودتر از 27000 یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F25" s="45" t="inlineStr">
+      <c r="F22" s="45" t="inlineStr">
         <is>
           <t>28500→27500→26000</t>
         </is>
       </c>
-      <c r="G25" s="45" t="inlineStr">
+      <c r="G22" s="45" t="inlineStr">
         <is>
           <t>12s</t>
         </is>
       </c>
-      <c r="H25" s="43" t="inlineStr">
-        <is>
-          <t>سبز ثابت زرد خاموش قرمز50%1s بوق1s/10s؛ 27500 حفظ 27000 پاک</t>
-        </is>
-      </c>
-      <c r="I25" s="43" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
+        <is>
+          <t>روی 28.5 ولت: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی 27.5 همان چهره می‌ماند؛ روی 26 چهره پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I22" s="43" t="inlineStr">
         <is>
           <t>قرمز50%</t>
         </is>
       </c>
-      <c r="J25" s="43" t="inlineStr">
-        <is>
-          <t>PASS: 27/28 hysteresis. FAIL: زود پاک</t>
-        </is>
-      </c>
-      <c r="K25" s="43" t="inlineStr"/>
-      <c r="L25" s="46" t="inlineStr">
+      <c r="J22" s="43" t="inlineStr">
+        <is>
+          <t>حفظ روی 27.5 و پاک شدن روی 26؛ پاک شدن زودتر = رد</t>
+        </is>
+      </c>
+      <c r="K22" s="43" t="inlineStr"/>
+      <c r="L22" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M25" s="43" t="inlineStr"/>
-      <c r="N25" s="43" t="inlineStr"/>
-      <c r="O25" s="45" t="inlineStr"/>
-      <c r="P25" s="45" t="inlineStr"/>
-      <c r="Q25" s="47">
+      <c r="M22" s="43" t="inlineStr"/>
+      <c r="N22" s="43" t="inlineStr"/>
+      <c r="O22" s="45" t="inlineStr"/>
+      <c r="P22" s="45" t="inlineStr"/>
+      <c r="Q22" s="47">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>UI-022</t>
         </is>
       </c>
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B23" s="48" t="inlineStr">
         <is>
           <t>Snapshot invalid</t>
         </is>
       </c>
-      <c r="C26" s="49" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>هر سناریو</t>
         </is>
       </c>
-      <c r="E26" s="48" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr">
         <is>
           <t>گام ۱: در هر سناریویی که هستی (فرقی نمی‌کند) snapshot را نامعتبر کن: valid=false یا اشاره‌گر NULL بده.
 گام ۲: 500 میلی‌ثانیه نگاه کن.
@@ -3121,68 +2917,68 @@
 گام ۴: روشن ماندن هر LED یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F26" s="50" t="inlineStr">
+      <c r="F23" s="50" t="inlineStr">
         <is>
           <t>valid false</t>
         </is>
       </c>
-      <c r="G26" s="50" t="inlineStr">
-        <is>
-          <t>500ms</t>
-        </is>
-      </c>
-      <c r="H26" s="48" t="inlineStr">
+      <c r="G23" s="50" t="inlineStr">
+        <is>
+          <t>نیم ثانیه</t>
+        </is>
+      </c>
+      <c r="H23" s="48" t="inlineStr">
         <is>
           <t>safe-off همه خاموش flag false فاز reset stable حفظ</t>
         </is>
       </c>
-      <c r="I26" s="48" t="inlineStr">
+      <c r="I23" s="48" t="inlineStr">
         <is>
           <t>reset</t>
         </is>
       </c>
-      <c r="J26" s="48" t="inlineStr">
+      <c r="J23" s="48" t="inlineStr">
         <is>
           <t>PASS: safe-off. FAIL: LED(flag)true</t>
         </is>
       </c>
-      <c r="K26" s="48" t="inlineStr"/>
-      <c r="L26" s="46" t="inlineStr">
+      <c r="K23" s="48" t="inlineStr"/>
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M26" s="48" t="inlineStr"/>
-      <c r="N26" s="48" t="inlineStr"/>
-      <c r="O26" s="50" t="inlineStr"/>
-      <c r="P26" s="50" t="inlineStr"/>
-      <c r="Q26" s="51">
+      <c r="M23" s="48" t="inlineStr"/>
+      <c r="N23" s="48" t="inlineStr"/>
+      <c r="O23" s="50" t="inlineStr"/>
+      <c r="P23" s="50" t="inlineStr"/>
+      <c r="Q23" s="51">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="42" t="inlineStr">
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>UI-023</t>
         </is>
       </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>Low Alarm 21/21.2</t>
         </is>
       </c>
-      <c r="C27" s="44" t="inlineStr">
+      <c r="C24" s="44" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E24" s="43" t="inlineStr">
         <is>
           <t>گام ۱: snapshot معتبر باشد و ولتاژ باتری را این‌طوری حرکت بده: اول 20900، بعد 21100، بعد 21200 میلی‌ولت؛ هر کدام 1 ثانیه.
 گام ۲: پرچم «باتری کم» را نگاه کن.
@@ -3190,68 +2986,68 @@
 گام ۴: معیار قبولی هیسترزیس 21 و 21.2 ولت است؛ تغییر فوری بدون هیسترزیس یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F27" s="45" t="inlineStr">
+      <c r="F24" s="45" t="inlineStr">
         <is>
           <t>20900/21100/21200</t>
         </is>
       </c>
-      <c r="G27" s="45" t="inlineStr">
+      <c r="G24" s="45" t="inlineStr">
         <is>
           <t>1s each</t>
         </is>
       </c>
-      <c r="H27" s="43" t="inlineStr">
-        <is>
-          <t>flag true حفظ false</t>
-        </is>
-      </c>
-      <c r="I27" s="43" t="inlineStr">
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>پرچم باتری کم با کمی تأخیر می‌آید و بالا و پایین نمی‌پرد (هیسترزیس دارد)</t>
+        </is>
+      </c>
+      <c r="I24" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J27" s="43" t="inlineStr">
-        <is>
-          <t>PASS: 21/21.2 hysteresis. FAIL: فوری</t>
-        </is>
-      </c>
-      <c r="K27" s="43" t="inlineStr"/>
-      <c r="L27" s="46" t="inlineStr">
+      <c r="J24" s="43" t="inlineStr">
+        <is>
+          <t>آمدن با هیسترزیس؛ تغییر فوری و پرپر زدن = رد</t>
+        </is>
+      </c>
+      <c r="K24" s="43" t="inlineStr"/>
+      <c r="L24" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M27" s="43" t="inlineStr"/>
-      <c r="N27" s="43" t="inlineStr"/>
-      <c r="O27" s="45" t="inlineStr"/>
-      <c r="P27" s="45" t="inlineStr"/>
-      <c r="Q27" s="47">
+      <c r="M24" s="43" t="inlineStr"/>
+      <c r="N24" s="43" t="inlineStr"/>
+      <c r="O24" s="45" t="inlineStr"/>
+      <c r="P24" s="45" t="inlineStr"/>
+      <c r="Q24" s="47">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="42" t="inlineStr">
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B25" s="48" t="inlineStr">
         <is>
           <t>Input switch 20/21</t>
         </is>
       </c>
-      <c r="C28" s="49" t="inlineStr">
+      <c r="C25" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D28" s="48" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>BatteryRun↔Charging</t>
         </is>
       </c>
-      <c r="E28" s="48" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را روی 19 ولت بگذار تا وضعیت BatteryRun باشد.
 گام ۲: ورودی را به 22 ولت بالا ببر: باید Charging یا InputOk شود.
@@ -3259,514 +3055,448 @@
 گام ۴: کل رفت‌وبرگشت 2 ثانیه؛ اطراف 20.5 ولت هیچ فلیکری نباید دیده شود (هیسترزیس 20 و 21 ولت).</t>
         </is>
       </c>
-      <c r="F28" s="50" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>19V/22V</t>
         </is>
       </c>
-      <c r="G28" s="50" t="inlineStr">
+      <c r="G25" s="50" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H28" s="48" t="inlineStr">
-        <is>
-          <t>19V BatteryRun 22V Charging/InputOk بدون فلیکر20.5V</t>
-        </is>
-      </c>
-      <c r="I28" s="48" t="inlineStr">
+      <c r="H25" s="48" t="inlineStr">
+        <is>
+          <t>روی 19 ولت وضعیت روی باتری است و روی 22 ولت شارژ یا ورودی خوب؛ وسط راه هیچ چشمک و رفت‌وبرگشت بی‌دلیلی نیست</t>
+        </is>
+      </c>
+      <c r="I25" s="48" t="inlineStr">
         <is>
           <t>حفظ</t>
         </is>
       </c>
-      <c r="J28" s="48" t="inlineStr">
-        <is>
-          <t>PASS: 20/21. FAIL: فلیکر</t>
-        </is>
-      </c>
-      <c r="K28" s="48" t="inlineStr"/>
-      <c r="L28" s="46" t="inlineStr">
+      <c r="J25" s="48" t="inlineStr">
+        <is>
+          <t>بدون رفت‌وبرگشت بی‌دلیل؛ فلیکر وسط راه = رد</t>
+        </is>
+      </c>
+      <c r="K25" s="48" t="inlineStr"/>
+      <c r="L25" s="46" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M28" s="48" t="inlineStr"/>
-      <c r="N28" s="48" t="inlineStr"/>
-      <c r="O28" s="50" t="inlineStr"/>
-      <c r="P28" s="50" t="inlineStr"/>
-      <c r="Q28" s="51">
+      <c r="M25" s="48" t="inlineStr"/>
+      <c r="N25" s="48" t="inlineStr"/>
+      <c r="O25" s="50" t="inlineStr"/>
+      <c r="P25" s="50" t="inlineStr"/>
+      <c r="Q25" s="51">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="42" t="inlineStr">
-        <is>
-          <t>UI-025</t>
-        </is>
-      </c>
-      <c r="B29" s="43" t="inlineStr">
-        <is>
-          <t>Mapping PA3/PA2</t>
-        </is>
-      </c>
-      <c r="C29" s="44" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Measurement</t>
-        </is>
-      </c>
-      <c r="E29" s="43" t="inlineStr">
-        <is>
-          <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
-گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
-گام ۳: چک کن v_bat از PA3 و raw2 می‌آید و v_in از PA2 و raw1.
-گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F29" s="45" t="inlineStr">
-        <is>
-          <t>PA2/PA3 1V</t>
-        </is>
-      </c>
-      <c r="G29" s="45" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="H29" s="43" t="inlineStr">
-        <is>
-          <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
-        </is>
-      </c>
-      <c r="I29" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="43" t="inlineStr">
-        <is>
-          <t>PASS: mapping. FAIL: جابجایی</t>
-        </is>
-      </c>
-      <c r="K29" s="43" t="inlineStr"/>
-      <c r="L29" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M29" s="43" t="inlineStr"/>
-      <c r="N29" s="43" t="inlineStr"/>
-      <c r="O29" s="45" t="inlineStr"/>
-      <c r="P29" s="45" t="inlineStr"/>
-      <c r="Q29" s="47">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="42" t="inlineStr">
-        <is>
-          <t>UI-028</t>
-        </is>
-      </c>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>Task starvation</t>
-        </is>
-      </c>
-      <c r="C30" s="49" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>همه سناریوها</t>
-        </is>
-      </c>
-      <c r="E30" s="48" t="inlineStr">
-        <is>
-          <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
-گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
-گام ۳: task_ui، تسک اندازه‌گیری و تسک کنترل هر سه باید هر 10 میلی‌ثانیه اجرا شوند.
-گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
-        </is>
-      </c>
-      <c r="F30" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="50" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H30" s="48" t="inlineStr">
-        <is>
-          <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
-        </is>
-      </c>
-      <c r="I30" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="48" t="inlineStr">
-        <is>
-          <t>PASS: بدون starvation. FAIL: delay500/1000</t>
-        </is>
-      </c>
-      <c r="K30" s="48" t="inlineStr"/>
-      <c r="L30" s="46" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M30" s="48" t="inlineStr"/>
-      <c r="N30" s="48" t="inlineStr"/>
-      <c r="O30" s="50" t="inlineStr"/>
-      <c r="P30" s="50" t="inlineStr"/>
-      <c r="Q30" s="51">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="40.5" customHeight="1">
-      <c r="A31" s="42" t="inlineStr">
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>UI-030</t>
         </is>
       </c>
-      <c r="B31" s="48" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C31" s="50" t="inlineStr">
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D31" s="48" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E31" s="48" t="inlineStr">
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن و چند دیالوگ پنل (تأیید و خطا) پشت سر هم بساز.
 گام ۲: هم‌زمان چراغ‌های روی برد را 3 ثانیه نگاه کن.
 گام ۳: UI برد باید کاملاً مستقل از پنل کار خودش را بکند؛ دیالوگ‌ها فقط داخل مرورگر هستند و نباید هیچ اثری روی LED یا بوق برد بگذارند.</t>
         </is>
       </c>
-      <c r="F31" s="50" t="inlineStr">
+      <c r="F26" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="50" t="inlineStr">
+      <c r="G26" s="50" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H31" s="48" t="inlineStr">
+      <c r="H26" s="48" t="inlineStr">
         <is>
           <t>UI مستقل از پنل؛ دیالوگ‌ها فقط در مرورگر</t>
         </is>
       </c>
-      <c r="I31" s="48" t="inlineStr">
+      <c r="I26" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="48" t="inlineStr">
+      <c r="J26" s="48" t="inlineStr">
         <is>
           <t>بدون تداخل</t>
         </is>
       </c>
-      <c r="K31" s="48" t="n"/>
-      <c r="L31" s="55" t="inlineStr">
+      <c r="K26" s="48" t="n"/>
+      <c r="L26" s="55" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M31" s="48" t="n"/>
-      <c r="N31" s="48" t="n"/>
-      <c r="O31" s="50" t="inlineStr">
+      <c r="M26" s="48" t="n"/>
+      <c r="N26" s="48" t="n"/>
+      <c r="O26" s="50" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P31" s="50" t="n"/>
-      <c r="Q31" s="51" t="inlineStr">
+      <c r="P26" s="50" t="n"/>
+      <c r="Q26" s="51" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="Q27" s="56">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="Q28" s="56">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="Q29" s="56">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="Q30" s="56">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="40.5" customHeight="1">
+      <c r="Q31" s="56">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="54" customHeight="1">
       <c r="Q32" s="56">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="40.5" customHeight="1">
       <c r="Q33" s="56">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="40.5" customHeight="1">
       <c r="Q34" s="56">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="56">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="56">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="56">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="56">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="56">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="56">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="56">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="56">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="56">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="56">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="56">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="56">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="56">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="56">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="56">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="56">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="56">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="56">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="56">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
+        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="56">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
+        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="Q55" s="56">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
+        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="Q56" s="56">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
+        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="Q57" s="56">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
+        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="Q58" s="56">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
+        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="Q59" s="56">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="Q60" s="56">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="Q61" s="56">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
+        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="Q62" s="56">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
+        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="Q63" s="56">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
+        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="Q64" s="56">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="Q65" s="56">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="Q66" s="56">
-        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="Q67" s="56">
-        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="Q68" s="56">
-        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="Q69" s="56">
-        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="Q70" s="56">
-        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="Q71" s="56">
         <f>IF(OR(L74="",L74="در انتظار"),"",IF(Q74="",TODAY(),Q74))</f>
         <v/>
       </c>
     </row>
+    <row r="67" ht="54" customHeight="1">
+      <c r="A67" s="42" t="inlineStr">
+        <is>
+          <t>UI-031</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی درصد</t>
+        </is>
+      </c>
+      <c r="C67" s="45" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>دستگاه روی باتری در حال کار، درصد شارژ معلوم</t>
+        </is>
+      </c>
+      <c r="E67" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را روی باتری روشن کن تا درصد شارژ و چشمک سبز معلوم باشد.
+گام ۲: فقط ولتاژ ورودی را بالا و پایین کن (به باتری دست نزن).
+گام ۳: درصد و چشمک سبز نباید هیچ تغییری کند.
+گام ۴: حالا فقط ولتاژ باتری را عوض کن؛ درصد باید عوض شود.</t>
+        </is>
+      </c>
+      <c r="F67" s="43" t="inlineStr">
+        <is>
+          <t>تغییر جدا جدا ورودی و باتری</t>
+        </is>
+      </c>
+      <c r="G67" s="45" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H67" s="43" t="inlineStr">
+        <is>
+          <t>درصد فقط از باتری می‌آید، نه از ورودی</t>
+        </is>
+      </c>
+      <c r="I67" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="43" t="inlineStr">
+        <is>
+          <t>با ورودی ثابت بماند و با باتری عوض شود</t>
+        </is>
+      </c>
+      <c r="K67" s="43" t="inlineStr"/>
+      <c r="L67" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M67" s="43" t="n"/>
+      <c r="N67" s="43" t="n"/>
+      <c r="O67" s="45" t="n"/>
+      <c r="P67" s="45" t="n"/>
+      <c r="Q67" s="47">
+        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q71"/>
+  <autoFilter ref="A4:Q67"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="L5:L114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" location="'برنامه تست'!A6"/>
-    <hyperlink ref="E10" location="'برنامه تست'!A9"/>
-    <hyperlink ref="E11" location="'برنامه تست'!A9"/>
-    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
+    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="E9" location="'برنامه تست'!A8"/>
+    <hyperlink ref="E10" location="'برنامه تست'!A8"/>
+    <hyperlink ref="E11" location="'برنامه تست'!A10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3774,6 +3504,614 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="75" t="inlineStr">
+        <is>
+          <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="76" t="inlineStr">
+        <is>
+          <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>ورودی‌ها (v_bat/v_in/raw)</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="36" t="inlineStr">
+        <is>
+          <t>LED/بوق — انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>فاز چشمک — انتظار</t>
+        </is>
+      </c>
+      <c r="J4" s="36" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="L4" s="36" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="36" t="inlineStr">
+        <is>
+          <t>شرح ایراد</t>
+        </is>
+      </c>
+      <c r="N4" s="36" t="inlineStr">
+        <is>
+          <t>مدرک تست</t>
+        </is>
+      </c>
+      <c r="O4" s="36" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="36" t="inlineStr">
+        <is>
+          <t>تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="36" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>UI-001</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Mapping PA3→v_bat</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>برد روشن, valid</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
+گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
+گام ۳: 100 میلی‌ثانیه صبر کن و raw2 و v_bat24_mv را بخوان.
+گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
+        </is>
+      </c>
+      <c r="F5" s="45" t="inlineStr">
+        <is>
+          <t>PA3 2.0V pin → v_bat≈22352mV, v_in 24V</t>
+        </is>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="43" t="inlineStr">
+        <is>
+          <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
+        </is>
+      </c>
+      <c r="K5" s="43" t="n"/>
+      <c r="L5" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="43" t="n"/>
+      <c r="N5" s="43" t="n"/>
+      <c r="O5" s="45" t="n"/>
+      <c r="P5" s="45" t="n"/>
+      <c r="Q5" s="47">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>UI-014</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>Charging yellow phase</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>Charging 25V On430</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
+گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
+گام ۳: تا 600 میلی‌ثانیه نگاه کن: روشنی باید تا 430 کامل ادامه پیدا کند و بعد خاموش شود.
+گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
+        <is>
+          <t>On430 jitter56</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="inlineStr">
+        <is>
+          <t>600ms</t>
+        </is>
+      </c>
+      <c r="H6" s="48" t="inlineStr">
+        <is>
+          <t>ON تا 430 حفظ سپس OFF</t>
+        </is>
+      </c>
+      <c r="I6" s="48" t="inlineStr">
+        <is>
+          <t>ON حفظ</t>
+        </is>
+      </c>
+      <c r="J6" s="48" t="inlineStr">
+        <is>
+          <t>PASS: restart نشد. FAIL: restart</t>
+        </is>
+      </c>
+      <c r="K6" s="48" t="n"/>
+      <c r="L6" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="48" t="n"/>
+      <c r="N6" s="48" t="n"/>
+      <c r="O6" s="50" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="51">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>UI-018</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>BatteryRun phase preserve</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>BatteryRun 25V stable57 ON570</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: BatteryRun با باتری 25 ولت و درصد پایدار 57 باشد تا سبز در فاز روشنی 570 میلی‌ثانیه‌ای باشد.
+گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (پایدار همان 57 می‌ماند).
+گام ۳: تا 700 میلی‌ثانیه نگاه کن: روشنی باید تا 570 کامل ادامه پیدا کند و بعد 430 خاموشی بیاید.
+گام ۴: اگر روشنی وسطش از نو شروع شد، تست رد است.</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>On570 jitter56</t>
+        </is>
+      </c>
+      <c r="G7" s="50" t="inlineStr">
+        <is>
+          <t>700ms</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="inlineStr">
+        <is>
+          <t>ON تا 570 حفظ سپس OFF430</t>
+        </is>
+      </c>
+      <c r="I7" s="48" t="inlineStr">
+        <is>
+          <t>ON حفظ570</t>
+        </is>
+      </c>
+      <c r="J7" s="48" t="inlineStr">
+        <is>
+          <t>PASS: restart نشد. FAIL: restart</t>
+        </is>
+      </c>
+      <c r="K7" s="48" t="n"/>
+      <c r="L7" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M7" s="48" t="n"/>
+      <c r="N7" s="48" t="n"/>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="51">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>UI-025</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Mapping PA3/PA2</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
+گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
+گام ۳: چک کن v_bat از PA3 و raw2 می‌آید و v_in از PA2 و raw1.
+گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F8" s="45" t="inlineStr">
+        <is>
+          <t>PA2/PA3 1V</t>
+        </is>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>PASS: mapping. FAIL: جابجایی</t>
+        </is>
+      </c>
+      <c r="K8" s="43" t="n"/>
+      <c r="L8" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="43" t="n"/>
+      <c r="N8" s="43" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="45" t="n"/>
+      <c r="Q8" s="47">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>UI-028</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Task starvation</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>همه سناریوها</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
+گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
+گام ۳: task_ui، تسک اندازه‌گیری و تسک کنترل هر سه باید هر 10 میلی‌ثانیه اجرا شوند.
+گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="50" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H9" s="48" t="inlineStr">
+        <is>
+          <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
+        </is>
+      </c>
+      <c r="I9" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="48" t="inlineStr">
+        <is>
+          <t>PASS: بدون starvation. FAIL: delay500/1000</t>
+        </is>
+      </c>
+      <c r="K9" s="48" t="n"/>
+      <c r="L9" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="48" t="n"/>
+      <c r="N9" s="48" t="n"/>
+      <c r="O9" s="50" t="n"/>
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="51">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="56">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="56">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="56">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="56">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="56">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="56">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="56">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="56">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="56">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="56">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="56">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="56">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="56">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="56">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="56">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="56">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="56">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="56">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="56">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="56">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q9"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -4246,7 +4584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -4893,24 +5231,24 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
-    <hyperlink ref="F4" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F5" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F4" location="'تست‌های آزمایشگاهی'!A5"/>
+    <hyperlink ref="F5" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
-    <hyperlink ref="F6" location="'برنامه تست'!A28"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
     <hyperlink ref="F7" location="'تست‌های برنامه‌نویسی'!A5"/>
-    <hyperlink ref="F8" location="'برنامه تست'!A6"/>
-    <hyperlink ref="F9" location="'برنامه تست'!A6"/>
-    <hyperlink ref="F10" location="'برنامه تست'!A15"/>
-    <hyperlink ref="F11" location="'برنامه تست'!A15"/>
-    <hyperlink ref="F12" location="'برنامه تست'!A19"/>
-    <hyperlink ref="F13" location="'برنامه تست'!A6"/>
-    <hyperlink ref="F14" location="'برنامه تست'!A15"/>
-    <hyperlink ref="F15" location="'برنامه تست'!A28"/>
-    <hyperlink ref="F16" location="'برنامه تست'!A25"/>
-    <hyperlink ref="F17" location="'برنامه تست'!A27"/>
-    <hyperlink ref="F18" location="'برنامه تست'!A9"/>
-    <hyperlink ref="F19" location="'برنامه تست'!A26"/>
+    <hyperlink ref="F8" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F9" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F10" location="'برنامه تست'!A14"/>
+    <hyperlink ref="F11" location="'برنامه تست'!A14"/>
+    <hyperlink ref="F12" location="'برنامه تست'!A17"/>
+    <hyperlink ref="F13" location="'برنامه تست'!A5"/>
+    <hyperlink ref="F14" location="'برنامه تست'!A14"/>
+    <hyperlink ref="F15" location="'برنامه تست'!A25"/>
+    <hyperlink ref="F16" location="'برنامه تست'!A22"/>
+    <hyperlink ref="F17" location="'برنامه تست'!A24"/>
+    <hyperlink ref="F18" location="'برنامه تست'!A8"/>
+    <hyperlink ref="F19" location="'برنامه تست'!A23"/>
     <hyperlink ref="F20" location="'تست‌های برنامه‌نویسی'!A5"/>
     <hyperlink ref="F21" location="'تست‌های برنامه‌نویسی'!A5"/>
   </hyperlinks>
@@ -4918,7 +5256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -5183,7 +5521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -5496,14 +5834,14 @@
     <mergeCell ref="A20:F20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D14" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D14" location="'تست‌های آزمایشگاهی'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -5634,7 +5972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1519,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="F4" s="36" t="inlineStr">
         <is>
-          <t>ورودی‌ها (v_bat/v_in/raw)</t>
+          <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
       <c r="G4" s="36" t="inlineStr">
@@ -1667,40 +1667,39 @@
       </c>
       <c r="D5" s="48" t="inlineStr">
         <is>
-          <t>BatteryRun, valid, InputDisconnected</t>
+          <t>دستگاه فقط روی باتری کار می‌کند (برق شهر قطع)؛ به‌جای باتری یک منبع آزمایشگاهی ۲۴ ولت گذاشته‌ای و درصد حدود نصف است</t>
         </is>
       </c>
       <c r="E5" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: برد در BatteryRun با snapshot معتبر و ورودی قطع باشد و درصد پایدار (stable) روی 57 نشسته باشد (باتری 25 ولت، raw=57).
-گام ۲: اسیلوسکوپ را روی LED سبز بگذار.
-گام ۳: درصدی را که می‌آید بین 56 و 58 نویز بده (هر 100 میلی‌ثانیه یکی) و 5 ثانیه نگاه کن.
-گام ۴: درصد پایدار باید همان 57 بماند و چشمک سبز ثابت باشد: خاموشی 430 و روشنی 570 میلی‌ثانیه، بدون اینکه فاز از نو شروع شود.</t>
+          <t>گام ۱: منبع را آن‌قدر تنظیم کن که درصد باتری حدود ۵۷ شود و چشمک سبز جا بیفتد.
+گام ۲: ولتاژ منبع را خیلی کم بالا و پایین کن، در حدی که درصد بین ۵۶ و ۵۸ بازی کند.
+گام ۳: یک دقیقه فقط به چراغ سبز نگاه کن.</t>
         </is>
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>v_bat25000 raw57 →56/58 jitter</t>
+          <t>لرزش کوچک ولتاژ باتری دور درصد ۵۷</t>
         </is>
       </c>
       <c r="G5" s="50" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H5" s="48" t="inlineStr">
         <is>
-          <t>درصد پایدار همان 57 می‌ماند و چشمک سبز منظم است؛ ریتم چشمک نه تکان می‌خورد نه از نو شروع می‌شود</t>
+          <t>چشمک سبز با همان ریتم قبلی ادامه می‌دهد؛ نه تند و کند می‌شود نه از اول شروع می‌شود</t>
         </is>
       </c>
       <c r="I5" s="48" t="inlineStr">
         <is>
-          <t>فاز حفظ On/Off ثابت</t>
+          <t>ریتم ثابت و بی‌پرش</t>
         </is>
       </c>
       <c r="J5" s="48" t="inlineStr">
         <is>
-          <t>درصد و ریتم ثابت بمانند؛ عوض شدن درصد با نویز یا پریدن ریتم = رد</t>
+          <t>ریتم ثابت بماند = قبول؛ پریدن یا عوض‌شدن ریتم با هر تغییر کوچک = رد</t>
         </is>
       </c>
       <c r="K5" s="48" t="inlineStr"/>
@@ -1734,42 +1733,41 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>stable57</t>
-        </is>
-      </c>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>گام ۱: از stable=57 شروع کن (پایان UI-002).
-گام ۲: درصد خام را به 55 پایین بیاور (v_bat حدود 24850 میلی‌ولت).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: درصد پایدار باید 55 شده باشد و چشمک سبز از مرز بعدی با خاموشی 450 و روشنی 550 ادامه پیدا کند، بدون ریست شدن فاز؛ ماندن روی 57 یعنی رد تست.</t>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا درصد به حدود ۵۵ برسد.
+گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
+گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
         </is>
       </c>
       <c r="F6" s="45" t="inlineStr">
         <is>
-          <t>raw55</t>
+          <t>کم‌کردن آرام ولتاژ باتری تا درصد ۵۵</t>
         </is>
       </c>
       <c r="G6" s="45" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>نیم دقیقه</t>
         </is>
       </c>
       <c r="H6" s="43" t="inlineStr">
         <is>
-          <t>درصد پایدار به 55 می‌رسد و چشمک سبز کمی تندتر می‌شود (خاموشی بیشتر از قبل)، بدون پرش ناگهانی</t>
-        </is>
-      </c>
-      <c r="I6" s="43" t="inlineStr">
-        <is>
-          <t>تغییر از مرز بعدی</t>
+          <t>درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر می‌شود (خاموشی‌اش بیشتر از قبل)</t>
+        </is>
+      </c>
+      <c r="I6" s="52" t="inlineStr">
+        <is>
+          <t>تندتر از UI-002، بدون پرش ناگهانی</t>
         </is>
       </c>
       <c r="J6" s="43" t="inlineStr">
         <is>
-          <t>پایدار 55 شود؛ ماندن روی 57 = رد</t>
+          <t>پایدار روی ۵۵ با ریتم تندتر = قبول؛ ماندن روی ۵۷ = رد</t>
         </is>
       </c>
       <c r="K6" s="43" t="inlineStr"/>
@@ -1803,42 +1801,41 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t>stable57</t>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
         </is>
       </c>
       <c r="E7" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: از stable=57 شروع کن.
-گام ۲: درصد خام را به 59 بالا ببر (v_bat حدود 25130 میلی‌ولت).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: درصد پایدار باید 59 شده باشد و چشمک سبز از مرز بعدی با خاموشی 410 و روشنی 590 ادامه پیدا کند، بدون ریست شدن فاز.</t>
+          <t>گام ۱: ولتاژ منبع را آرام بالا ببر تا درصد به حدود ۵۹ برسد.
+گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
+گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
         </is>
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>raw59</t>
+          <t>بالابردن آرام ولتاژ باتری تا درصد ۵۹</t>
         </is>
       </c>
       <c r="G7" s="50" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>نیم دقیقه</t>
         </is>
       </c>
       <c r="H7" s="48" t="inlineStr">
         <is>
-          <t>درصد پایدار به 59 می‌رسد و چشمک سبز کمی کندتر می‌شود (روشنی بیشتر از قبل)، بدون پرش ناگهانی</t>
-        </is>
-      </c>
-      <c r="I7" s="48" t="inlineStr">
-        <is>
-          <t>حفظ</t>
+          <t>درصد روی ۵۹ می‌ایستد و چشمک سبز کمی کندتر می‌شود (روشن بودنش بیشتر از قبل)</t>
+        </is>
+      </c>
+      <c r="I7" s="53" t="inlineStr">
+        <is>
+          <t>کندتر از UI-002، بدون پرش ناگهانی</t>
         </is>
       </c>
       <c r="J7" s="48" t="inlineStr">
         <is>
-          <t>پایدار 59 شود؛ ماندن روی 57 = رد</t>
+          <t>پایدار روی ۵۹ با ریتم کندتر = قبول؛ ماندن روی ۵۷ = رد</t>
         </is>
       </c>
       <c r="K7" s="48" t="inlineStr"/>
@@ -1864,7 +1861,7 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t>0% critical raw0</t>
+          <t>باتری خالیِ کامل (درصد صفر)</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
@@ -1874,40 +1871,39 @@
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>BatteryRun 21V یا کمتر</t>
+          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: برد در BatteryRun باشد و ولتاژ باتری را دقیقاً روی 21 ولت (21000 میلی‌ولت) بگذار تا درصد خام و پایدار هر دو صفر شوند.
-گام ۲: هر سه LED و بوق را 12 ثانیه زیر نظر بگیر.
-گام ۳: همهٔ LEDها باید خاموش بمانند.
-گام ۴: بوق باید فقط یک بار و 10 ثانیه باشد و بعد تا وقتی درصد از صفر بیرون نیامده ساکت بماند؛ بوق تکراری یا LED روشن یعنی رد تست.</t>
+          <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا باتری تقریباً خالی شود و درصد به صفر برسد.
+گام ۲: از لحظهٔ صفر شدن، به بوق و چراغ‌ها دقت کن.
+گام ۳: همان ولتاژ را نگه دار و یک دقیقه صبر کن.</t>
         </is>
       </c>
       <c r="F8" s="45" t="inlineStr">
         <is>
-          <t>v_bat21000 raw0 stable0</t>
+          <t>باتری نزدیک خالی کامل (درصد صفر)</t>
         </is>
       </c>
       <c r="G8" s="45" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H8" s="43" t="inlineStr">
         <is>
-          <t>همه LED خاموش، یک بوق 10s سپس خاموش تا خروج از 0%</t>
+          <t>یک بوق بلند حدود ده ثانیه می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود تا وقتی باتری از خالیِ کامل بیرون بیاید</t>
         </is>
       </c>
       <c r="I8" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بعد از بوق: همه خاموش</t>
         </is>
       </c>
       <c r="J8" s="43" t="inlineStr">
         <is>
-          <t>PASS: یک 10s سپس خاموش. FAIL: مکرر/LED روشن</t>
+          <t>فقط یک بوق بلند و بعد خاموشی = قبول؛ بوق تکراری یا چراغ روشنِ مانده = رد</t>
         </is>
       </c>
       <c r="K8" s="43" t="inlineStr"/>
@@ -1941,42 +1937,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>stable0 Critical 10s</t>
-        </is>
-      </c>
-      <c r="E9" s="53" t="inlineStr">
-        <is>
-          <t>گام ۱: از وضعیت بحرانی صفر درصد شروع کن و بگذار بوق یک‌بارهٔ 10 ثانیه‌ای شروع شود (پایان UI-005).
-گام ۲: درصد خام را بین 0 و 1 نویز بده: 0، بعد 1، بعد 0، بعد 1، هر کدام 200 میلی‌ثانیه.
-گام ۳: 12 ثانیه نگاه کن.
-گام ۴: درصد پایدار باید صفر بماند (تغییر کمتر از 2 شمرده نمی‌شود)، بوق نباید از نو شروع شود و LEDها خاموش می‌مانند.</t>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-005؛ درصد روی صفر و بوق بحرانی تمام شده</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را خیلی کم بالا و پایین کن، دور مرز صفر و یک درصد.
+گام ۲: دو دقیقه به چراغ‌ها و بوق گوش بده.</t>
         </is>
       </c>
       <c r="F9" s="50" t="inlineStr">
         <is>
-          <t>raw0/1 jitter</t>
+          <t>بازی ولتاژ دور مرز ۰ و ۱ درصد</t>
         </is>
       </c>
       <c r="G9" s="50" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H9" s="48" t="inlineStr">
         <is>
-          <t>stable0 حفظ (&lt;2) بوق restart نشود LED خاموش</t>
+          <t>بوق بحرانی دوباره شروع نمی‌شود و چراغ‌ها بی‌دلیل روشن و خاموش نمی‌شوند</t>
         </is>
       </c>
       <c r="I9" s="48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>خاموش و آرام</t>
         </is>
       </c>
       <c r="J9" s="48" t="inlineStr">
         <is>
-          <t>PASS: یک بار. FAIL: restart</t>
+          <t>آرام ماندن = قبول؛ شروع دوبارهٔ بوق با هر نوسان کوچک = رد</t>
         </is>
       </c>
       <c r="K9" s="48" t="inlineStr"/>
@@ -2002,7 +1996,7 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>1% مستقل raw1</t>
+          <t>درصد ۱ (نزدیک خالی)</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
@@ -2012,40 +2006,38 @@
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>Stable0 خروج به1</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="inlineStr">
-        <is>
-          <t>گام ۱: از درصد پایدار صفر شروع کن.
-گام ۲: درصد خام را از 0 به 1 ببر (v_bat حدود 21070 میلی‌ولت) و همان‌جا نگه دار.
-گام ۳: 3 ثانیه نگاه کن.
-گام ۴: درصد پایدار باید 1 شود؛ علامتش سه‌بوق هر 20 ثانیه و چشمک سبز با خاموشی 990 و روشنی فقط 10 میلی‌ثانیه است؛ رفتار بحرانی (UI-005) یعنی رد تست.</t>
+          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را طوری تنظیم کن که درصد روی ۱ بایستد (باتری تقریباً خالی ولی نه صفر).
+گام ۲: دو دقیقه چراغ سبز و بوق را زیر نظر بگیر.</t>
         </is>
       </c>
       <c r="F10" s="45" t="inlineStr">
         <is>
-          <t>raw1 stable1</t>
+          <t>درصد پایدار ۱</t>
         </is>
       </c>
       <c r="G10" s="45" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H10" s="43" t="inlineStr">
         <is>
-          <t>درصد پایدار 1 می‌شود؛ سه‌بوق هر از چندی و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
+          <t>هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
         </is>
       </c>
       <c r="I10" s="43" t="inlineStr">
         <is>
-          <t>سه‌بوق</t>
+          <t>برق‌های کوتاه و کم</t>
         </is>
       </c>
       <c r="J10" s="43" t="inlineStr">
         <is>
-          <t>پایدار 1 با همان رفتار؛ رفتار بحرانی درصد صفر = رد</t>
+          <t>همین رفتار = قبول؛ رفتارِ درصد صفر (بوق بلند و خاموشی کامل) = رد</t>
         </is>
       </c>
       <c r="K10" s="43" t="inlineStr"/>
@@ -2079,41 +2071,40 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>stable1</t>
-        </is>
-      </c>
-      <c r="E11" s="53" t="inlineStr">
-        <is>
-          <t>گام ۱: از درصد پایدار 1 شروع کن (پایان UI-007).
-گام ۲: درصد خام را به 2 ببر (v_bat حدود 21140 میلی‌ولت) و 1 ثانیه نگه دار.
-گام ۳: درصد پایدار باید همان 1 بماند (چون رسیدن به 3 لازم است تا از 1 بیرون بیاید) و همان سه‌بوق ادامه داشته باشد؛ رفتن به 2 یعنی رد تست.</t>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را خیلی کم بالا ببر، آن‌قدر که درصد هنوز ۲ نشده باشد.
+گام ۲: یک دقیقه رفتار را نگاه کن.</t>
         </is>
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>raw2</t>
+          <t>بالا بردن جزئی از درصد ۱</t>
         </is>
       </c>
       <c r="G11" s="50" t="inlineStr">
         <is>
-          <t>1s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H11" s="48" t="inlineStr">
         <is>
-          <t>درصد پایدار همان 1 می‌ماند و همان سه‌بوق ادامه دارد</t>
+          <t>همان رفتار درصد ۱ می‌ماند: سه بوق هر از چندی و برق کوتاه سبز</t>
         </is>
       </c>
       <c r="I11" s="48" t="inlineStr">
         <is>
-          <t>حفظ</t>
+          <t>بدون تغییر</t>
         </is>
       </c>
       <c r="J11" s="48" t="inlineStr">
         <is>
-          <t>پایدار 1 بماند؛ رفتن به 2 = رد</t>
+          <t>ماندن روی رفتار ۱ = قبول؛ پریدن به الگوی درصد ۲ = رد</t>
         </is>
       </c>
       <c r="K11" s="48" t="inlineStr"/>
@@ -2147,42 +2138,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>stable1</t>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
         </is>
       </c>
       <c r="E12" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: از درصد پایدار 1 شروع کن.
-گام ۲: درصد خام را مستقیم روی 3 بگذار (v_bat حدود 21210 میلی‌ولت).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: درصد پایدار باید 2 شده باشد و الگوی بوق به الگوی درصد 2 عوض شود؛ ماندن روی 1 یعنی رد تست.</t>
+          <t>گام ۱: ولتاژ را آرام بالا ببر تا درصد به ۲ برسد و ثابت شود.
+گام ۲: یک دقیقه به الگوی بوق گوش بده و با درصد ۱ مقایسه کن.</t>
         </is>
       </c>
       <c r="F12" s="45" t="inlineStr">
         <is>
-          <t>raw3</t>
+          <t>بالا بردن ولتاژ تا درصد ۲</t>
         </is>
       </c>
       <c r="G12" s="45" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H12" s="43" t="inlineStr">
         <is>
-          <t>درصد پایدار 2 می‌شود و الگوی بوق به الگوی باند ۲ عوض می‌شود</t>
+          <t>الگوی بوق به الگوی ملایم‌ترِ درصد ۲ عوض می‌شود و سبز بیشتر از قبل روشن می‌ماند</t>
         </is>
       </c>
       <c r="I12" s="43" t="inlineStr">
         <is>
-          <t>حفظ</t>
+          <t>روشن‌تر از درصد ۱</t>
         </is>
       </c>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>پایدار 2 شود؛ ماندن روی 1 = رد</t>
+          <t>عوض‌شدن الگو روی ۲ = قبول؛ ماندن روی الگوی ۱ = رد</t>
         </is>
       </c>
       <c r="K12" s="43" t="inlineStr"/>
@@ -2218,40 +2207,38 @@
       </c>
       <c r="D13" s="48" t="inlineStr">
         <is>
-          <t>stable0</t>
+          <t>دستگاه فقط روی باتری؛ منبع از درصد صفر شروع می‌کند</t>
         </is>
       </c>
       <c r="E13" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: از درصد پایدار صفر شروع کن.
-گام ۲: درصد خام را از 0 به 2 ببر (v_bat حدود 21140 میلی‌ولت).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: درصد پایدار باید اول 1 شود، نه مستقیم 2؛ پریدن مستقیم به 2 یعنی رد تست.</t>
+          <t>گام ۱: ولتاژ را از صفر خیلی آرام بالا بیاور.
+گام ۲: به ترتیبِ الگوها دقت کن: اول باید رفتار درصد ۱ دیده شود و بعد درصد ۲.</t>
         </is>
       </c>
       <c r="F13" s="50" t="inlineStr">
         <is>
-          <t>raw2</t>
+          <t>بالا آمدن آرام از ۰ به ۲ درصد</t>
         </is>
       </c>
       <c r="G13" s="50" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H13" s="48" t="inlineStr">
         <is>
-          <t>درصد پایدار اول 1 می‌شود، نه اینکه مستقیم بپرد روی 2</t>
+          <t>اول الگوی درصد ۱ (سه بوق و برق کوتاه) و بعد الگوی درصد ۲ می‌آید</t>
         </is>
       </c>
       <c r="I13" s="48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>گذار پله‌ای ۱ بعد ۲</t>
         </is>
       </c>
       <c r="J13" s="48" t="inlineStr">
         <is>
-          <t>اول 1 شود؛ پرش مستقیم به 2 = رد</t>
+          <t>دیدن هر دو پله به ترتیب = قبول؛ پرش مستقیم به الگوی ۲ = رد</t>
         </is>
       </c>
       <c r="K13" s="48" t="inlineStr"/>
@@ -2287,40 +2274,38 @@
       </c>
       <c r="D14" s="43" t="inlineStr">
         <is>
-          <t>Charging Input24V Battery25V</t>
+          <t>برق شهر وصل و باتری واقعی در حال شارژ است؛ درصد حدود نصف</t>
         </is>
       </c>
       <c r="E14" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: ورودی 24 ولت و باتری 25 ولت وصل باشد تا وضعیت Charging شود و درصد پایدار شارژ روی 57 نشسته باشد.
-گام ۲: اسیلوسکوپ را روی LED زرد بگذار.
-گام ۳: درصد خام را بین 56 و 58 نویز بده (هر 100 میلی‌ثانیه) و 5 ثانیه نگاه کن.
-گام ۴: درصد پایدار همان 57 می‌ماند و چشمک زرد ثابت است: روشنی 430 و خاموشی 570 میلی‌ثانیه، بدون ریست شدن فاز.</t>
+          <t>گام ۱: دستگاه را به شارژ بزن و صبر کن درصد دور ۵۷ ثابت شود.
+گام ۲: یک دقیقه فقط چراغ زرد را نگاه کن.</t>
         </is>
       </c>
       <c r="F14" s="45" t="inlineStr">
         <is>
-          <t>v_in24000 v_bat25000 raw57→56/58</t>
+          <t>شارژ عادی با درصد میانی</t>
         </is>
       </c>
       <c r="G14" s="45" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H14" s="43" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ همان 57 می‌ماند و زرد منظم چشمک می‌زند؛ ریتم ثابت و بدون پرش</t>
+          <t>زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند</t>
         </is>
       </c>
       <c r="I14" s="43" t="inlineStr">
         <is>
-          <t>زرد فاز حفظ</t>
+          <t>ریتم ثابت</t>
         </is>
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>پایدار و ریتم ثابت؛ عوض شدن با نویز یا پرش ریتم = رد</t>
+          <t>ریتم ثابت = قبول؛ پرش یا توقف چشمک = رد</t>
         </is>
       </c>
       <c r="K14" s="43" t="inlineStr"/>
@@ -2354,41 +2339,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>stable57</t>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-011؛ در حال شارژ با درصد حدود ۵۷</t>
         </is>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: از stable=57 در Charging شروع کن.
-گام ۲: درصد خام را اول به 53 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار؛ بعد به 61 ببر (اختلاف 4) و 500 میلی‌ثانیه نگه دار.
-گام ۳: چون اختلاف کمتر از 5 است، درصد پایدار باید همان 57 بماند و چشمک زرد هیچ تغییری نکند؛ هر تغییری یعنی رد تست.</t>
+          <t>گام ۱: حین شارژ، ولتاژ باتری را با یک مصرف کوچک یا منبع کمی بالا و پایین کن (درصد دور ۵۷ بازی کند).
+گام ۲: یک دقیقه چراغ زرد را نگاه کن.</t>
         </is>
       </c>
       <c r="F15" s="50" t="inlineStr">
         <is>
-          <t>raw53 raw61</t>
+          <t>بازی کوچک درصد حین شارژ</t>
         </is>
       </c>
       <c r="G15" s="50" t="inlineStr">
         <is>
-          <t>1s each</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H15" s="48" t="inlineStr">
         <is>
-          <t>درصد پایدار همان 57 می‌ماند و چشمک زرد هیچ تغییری نمی‌کند</t>
+          <t>چشمک زرد هیچ تغییری نمی‌کند و با همان ریتم ادامه می‌دهد</t>
         </is>
       </c>
       <c r="I15" s="48" t="inlineStr">
         <is>
-          <t>حفظ</t>
+          <t>بدون تغییر</t>
         </is>
       </c>
       <c r="J15" s="48" t="inlineStr">
         <is>
-          <t>57 بماند؛ هر تغییری = رد</t>
+          <t>ثابت ماندن = قبول؛ عوض‌شدن ریتم با نوسان کوچک = رد</t>
         </is>
       </c>
       <c r="K15" s="48" t="inlineStr"/>
@@ -2424,39 +2408,39 @@
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>stable57</t>
+          <t>برق شهر وصل و دستگاه در حال شارژ؛ درصد حدود ۵۷</t>
         </is>
       </c>
       <c r="E16" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: از stable=57 در Charging شروع کن.
-گام ۲: درصد خام را به 52 ببر (اختلاف 5) و بعد به 62 ببر (اختلاف 5)؛ هر کدام را ببین.
-گام ۳: این بار درصد پایدار باید اول 52 و بعد 62 شود، و زمان‌های چشمک زرد از مرز بعدی اعمال شوند، بدون اینکه فاز ریست شود؛ ماندن روی 57 یعنی رد تست.</t>
+          <t>گام ۱: درصد شارژ را با منبع یا مصرف واقعی اول به حدود ۵۲ ببر و ثابت کن.
+گام ۲: بعد به حدود ۶۲ ببر و ثابت کن.
+گام ۳: موقع جابه‌جایی‌ها به زرد نگاه کن که قطع و وصل ناگهانی نکند.</t>
         </is>
       </c>
       <c r="F16" s="45" t="inlineStr">
         <is>
-          <t>raw52→62</t>
+          <t>درصد شارژ ۵۷ بعد ۵۲ بعد ۶۲</t>
         </is>
       </c>
       <c r="G16" s="45" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H16" s="43" t="inlineStr">
         <is>
-          <t>درصد پایدار اول 52 و بعد 62 می‌شود؛ ریتم زرد با درصد عوض می‌شود ولی چشمک از نو شروع نمی‌شود</t>
+          <t>ریتم زرد با درصد عوض می‌شود ولی چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد</t>
         </is>
       </c>
       <c r="I16" s="43" t="inlineStr">
         <is>
-          <t>از مرز بعدی</t>
+          <t>ریتم تازه، بدون راه‌اندازی از صفر</t>
         </is>
       </c>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>پایدار 52 بعد 62 شود؛ ماندن روی 57 = رد</t>
+          <t>تغییر نرم ریتم = قبول؛ ماندن روی ریتم ۵۷ یا پرش ناگهانی = رد</t>
         </is>
       </c>
       <c r="K16" s="43" t="inlineStr"/>
@@ -2492,40 +2476,39 @@
       </c>
       <c r="D17" s="43" t="inlineStr">
         <is>
-          <t>Charging valid</t>
+          <t>باتری در حال شارژ و نزدیک پر شدن است</t>
         </is>
       </c>
       <c r="E17" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: وضعیت Charging با snapshot معتبر باشد.
-گام ۲: درصد خام باتری را روی 99 بگذار و 500 میلی‌ثانیه نگه دار؛ بعد روی 100 بگذار و 500 میلی‌ثانیه نگه دار.
-گام ۳: روی 99 باید Charging باشد؛ روی 100 باید InputOk شود: سبز ثابت و زرد خاموش.
-گام ۴: اگر روی 99 هم InputOk شد، تست رد است.</t>
+          <t>گام ۱: شارژ را ادامه بده و درصد را زیر نظر بگیر.
+گام ۲: روی ۹۹ درصد چراغ‌ها را چک کن: هنوز باید شارژ باشد (زرد چشمک‌زن).
+گام ۳: بگذار به ۱۰۰ برسد و دوباره نگاه کن.</t>
         </is>
       </c>
       <c r="F17" s="45" t="inlineStr">
         <is>
-          <t>raw99→100</t>
+          <t>رسیدن درصد شارژ از ۹۹ به ۱۰۰</t>
         </is>
       </c>
       <c r="G17" s="45" t="inlineStr">
         <is>
-          <t>500ms each</t>
+          <t>تا پر شدن باتری</t>
         </is>
       </c>
       <c r="H17" s="43" t="inlineStr">
         <is>
-          <t>روی 99 وضعیت شارژ است (زرد چشمک‌زن) و روی 100 می‌شود ورودی خوب (سبز ثابت و زرد خاموش)</t>
+          <t>فقط روی ۱۰۰ ورودی خوب می‌شود: سبز ثابت و زرد خاموش؛ روی ۹۹ هنوز زرد چشمک می‌زند</t>
         </is>
       </c>
       <c r="I17" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>۱۰۰: سبز ثابت</t>
         </is>
       </c>
       <c r="J17" s="43" t="inlineStr">
         <is>
-          <t>ورود روی 100 باشد؛ ورودی خوب شدن روی 99 = رد</t>
+          <t>ورودی خوب دقیقاً روی ۱۰۰ = قبول؛ سبز ثابت روی ۹۹ = رد</t>
         </is>
       </c>
       <c r="K17" s="43" t="inlineStr"/>
@@ -2559,42 +2542,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="48" t="inlineStr">
-        <is>
-          <t>InputOk active</t>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-015؛ درصد روی ۱۰۰ و سبز ثابت است</t>
         </is>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: وضعیت InputOk فعال باشد (درصد 100).
-گام ۲: درصد خام را این‌طوری نگه دار: 99، بعد 96، بعد 95؛ هر کدام 500 میلی‌ثانیه.
-گام ۳: در هر سه حالت باید همان InputOk بماند و سبز ثابت باشد.
-گام ۴: افتادن به Charging در این بازه یعنی رد تست (خروج فقط زیر 95 است).</t>
+          <t>گام ۱: با یک مصرف کوچک درصد را بین ۹۵ و ۱۰۰ نگه دار و چند بار بالا پایینش کن.
+گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>raw99 96 95</t>
+          <t>درصد بین ۹۵ تا ۱۰۰</t>
         </is>
       </c>
       <c r="G18" s="50" t="inlineStr">
         <is>
-          <t>500ms each</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
-          <t>تا وقتی درصد بالای 95 است همان ورودی خوب می‌ماند و سبز ثابت است</t>
+          <t>تا وقتی درصد بالای ۹۵ است همان ورودی خوب می‌ماند: سبز ثابت و زرد خاموش</t>
         </is>
       </c>
       <c r="I18" s="48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>سبز ثابت</t>
         </is>
       </c>
       <c r="J18" s="48" t="inlineStr">
         <is>
-          <t>در هر سه مقدار بماند؛ افتادن به شارژ = رد</t>
+          <t>ماندن در هر سه وضعیت = قبول؛ افتادن به چشمک زرد شارژ = رد</t>
         </is>
       </c>
       <c r="K18" s="48" t="inlineStr"/>
@@ -2628,42 +2609,40 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>InputOk active</t>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-016؛ درصد بالای ۹۵ و سبز ثابت است</t>
         </is>
       </c>
       <c r="E19" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: وضعیت InputOk فعال باشد.
-گام ۲: درصد خام را روی 94 بگذار (زیر 95).
-گام ۳: 100 میلی‌ثانیه صبر کن.
-گام ۴: باید برگردد به Charging: سبز ثابت و زرد با هیسترزیس 5 درصدی چشمک بزند؛ ماندن در InputOk یعنی رد تست.</t>
+          <t>گام ۱: یک بار واقعی روی باتری بکش تا درصد زیر ۹۵ بیاید.
+گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
       <c r="F19" s="45" t="inlineStr">
         <is>
-          <t>raw94</t>
+          <t>افت درصد شارژ به زیر ۹۵</t>
         </is>
       </c>
       <c r="G19" s="45" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr">
         <is>
-          <t>برمی‌گردد به شارژ: سبز ثابت و زرد دوباره چشمک‌زن</t>
+          <t>برمی‌گردد به وضعیت شارژ: سبز از ثابت درمی‌آید و زرد دوباره چشمک می‌زند</t>
         </is>
       </c>
       <c r="I19" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>برگشت به چشمک زرد</t>
         </is>
       </c>
       <c r="J19" s="43" t="inlineStr">
         <is>
-          <t>زیر 95 به شارژ برگردد؛ ماندن در ورودی خوب = رد</t>
+          <t>برگشت زیر ۹۵ = قبول؛ ماندن روی سبز ثابت = رد</t>
         </is>
       </c>
       <c r="K19" s="43" t="inlineStr"/>
@@ -2699,40 +2678,38 @@
       </c>
       <c r="D20" s="43" t="inlineStr">
         <is>
-          <t>Input 24V Battery28V</t>
+          <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
         </is>
       </c>
       <c r="E20" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: ورودی 24 ولت و باتری 28 ولت بده تا وضعیت InputOk شود.
-گام ۲: هر 10 میلی‌ثانیه Ui_Tick را صدا بزن و زمان برگشتنش را اندازه بگیر.
-گام ۳: یک ثانیه ادامه بده: سبز باید ثابت، بوق خاموش و هر تیک در کمتر از 1 میلی‌ثانیه برگردد.
-گام ۴: معیار: هیچ تأخیر (delay) بلندی مثل 500 میلی‌ثانیه نباید باشد؛ بودن delay یعنی رد تست.</t>
+          <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
+گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
         </is>
       </c>
       <c r="F20" s="45" t="inlineStr">
         <is>
-          <t>v_in24000 v_bat28000</t>
+          <t>کار هم‌زمان با پنل روی ورودی خوب</t>
         </is>
       </c>
       <c r="G20" s="45" t="inlineStr">
         <is>
-          <t>1s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H20" s="43" t="inlineStr">
         <is>
-          <t>سبز ثابت، بوق خاموش و دستگاه بدون هیچ مکث و هنگی کار می‌کند</t>
+          <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
         </is>
       </c>
       <c r="I20" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>سبز ثابت</t>
         </is>
       </c>
       <c r="J20" s="43" t="inlineStr">
         <is>
-          <t>هیچ مکث و هنگی نباشد = قبول</t>
+          <t>بدون هنگ و مکث = قبول؛ هر مکث یا ریست = رد</t>
         </is>
       </c>
       <c r="K20" s="43" t="inlineStr"/>
@@ -2768,40 +2745,38 @@
       </c>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>Input24V Battery25V</t>
+          <t>برق شهر وصل و باتری در حال شارژ است (زرد چشمک‌زن)</t>
         </is>
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: ورودی 24 ولت و باتری 25 ولت بده تا وضعیت Charging شود (درصد خام 57).
-گام ۲: اسیلوسکوپ را روی LED زرد بگذار و هر 10 میلی‌ثانیه Ui_Tick را صدا بزن.
-گام ۳: 3 ثانیه نگاه کن: سبز ثابت و زرد فاز‌محور با روشنی 430 و خاموشی 570 چشمک بزند.
-گام ۴: تیک باید سریع برگردد؛ هیچ blocking یا delay یک‌ثانیه‌ای نباید باشد.</t>
+          <t>گام ۱: حین شارژ با پنل کار کن و چند پارامتر بخوان.
+گام ۲: دو دقیقه دستگاه را زیر نظر بگیر.</t>
         </is>
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>v_in24000 v_bat25000 raw57</t>
+          <t>کار با پنل حین شارژ</t>
         </is>
       </c>
       <c r="G21" s="50" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H21" s="48" t="inlineStr">
         <is>
-          <t>سبز ثابت و زرد منظم چشمک می‌زند و دستگاه هنگ نمی‌کند</t>
+          <t>زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست</t>
         </is>
       </c>
       <c r="I21" s="48" t="inlineStr">
         <is>
-          <t>زرد فاز حفظ</t>
+          <t>چشمک منظم زرد</t>
         </is>
       </c>
       <c r="J21" s="48" t="inlineStr">
         <is>
-          <t>بدون هنگ و مکث = قبول</t>
+          <t>بدون هنگ = قبول؛ هنگ یا قطع ارتباط = رد</t>
         </is>
       </c>
       <c r="K21" s="48" t="inlineStr"/>
@@ -2837,40 +2812,40 @@
       </c>
       <c r="D22" s="43" t="inlineStr">
         <is>
-          <t>v_in28.5V</t>
+          <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
         </is>
       </c>
       <c r="E22" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: ولتاژ ورودی را روی 28.5 ولت (28500 میلی‌ولت) بگذار.
-گام ۲: باید چهرهٔ اضافه‌ولتاژ بیاید: سبز ثابت، زرد خاموش، قرمز با دورهٔ 1 ثانیه و 50 درصد روشنی، و بوق 1 ثانیه‌ای هر 10 ثانیه.
-گام ۳: ولتاژ را به 27500 پایین بیاور و نگه دار: چهره باید حفظ شود (هنوز زیر 27 پاک نمی‌شود).
-گام ۴: ولتاژ را به 26000 بیاور: حالا باید چهره پاک شود. کل تست 12 ثانیه؛ پاک شدن زودتر از 27000 یعنی رد تست.</t>
+          <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
+گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
+گام ۳: ولتاژ را تا حدود ۲۷٫۵ پایین بیاور و نگه دار؛ چهره باید بماند.
+گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
         </is>
       </c>
       <c r="F22" s="45" t="inlineStr">
         <is>
-          <t>28500→27500→26000</t>
+          <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
         </is>
       </c>
       <c r="G22" s="45" t="inlineStr">
         <is>
-          <t>12s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H22" s="43" t="inlineStr">
         <is>
-          <t>روی 28.5 ولت: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی 27.5 همان چهره می‌ماند؛ روی 26 چهره پاک می‌شود</t>
+          <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
         </is>
       </c>
       <c r="I22" s="43" t="inlineStr">
         <is>
-          <t>قرمز50%</t>
+          <t>قرمز چشمک‌زن با سبز ثابت</t>
         </is>
       </c>
       <c r="J22" s="43" t="inlineStr">
         <is>
-          <t>حفظ روی 27.5 و پاک شدن روی 26؛ پاک شدن زودتر = رد</t>
+          <t>آمدن، ماندن و پاک‌شدن در همان حدود = قبول؛ پاک‌شدن زودتر یا نیامدن = رد</t>
         </is>
       </c>
       <c r="K22" s="43" t="inlineStr"/>
@@ -2906,40 +2881,39 @@
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>هر سناریو</t>
+          <t>دستگاه روشن و در حال کار عادی است</t>
         </is>
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: در هر سناریویی که هستی (فرقی نمی‌کند) snapshot را نامعتبر کن: valid=false یا اشاره‌گر NULL بده.
-گام ۲: 500 میلی‌ثانیه نگاه کن.
-گام ۳: همهٔ LEDها و بوق باید خاموش شوند (safe-off)، همهٔ پرچم‌ها false و فاز از نو شروع شود، ولی درصد پایدار حفظ شود.
-گام ۴: روشن ماندن هر LED یعنی رد تست.</t>
+          <t>گام ۱: سیم حس‌کردن ولتاژ باتری را لحظه‌ای جدا کن (دستگاه اندازهٔ تازه ندارد).
+گام ۲: به چراغ‌ها و بوق نگاه کن؛ نباید الگوی دیوانه‌وار یا بوق بی‌دلیل بیاید.
+گام ۳: سیم را وصل کن؛ رفتار عادی باید برگردد.</t>
         </is>
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>valid false</t>
+          <t>قطع و وصل کوتاه سیم حس باتری</t>
         </is>
       </c>
       <c r="G23" s="50" t="inlineStr">
         <is>
-          <t>نیم ثانیه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H23" s="48" t="inlineStr">
         <is>
-          <t>safe-off همه خاموش flag false فاز reset stable حفظ</t>
+          <t>حین قطع، چهرهٔ سالم قبلی آرام می‌ماند و دستگاه هنگ نمی‌کند؛ با وصل مجدد همه‌چیز عادی می‌شود</t>
         </is>
       </c>
       <c r="I23" s="48" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>بدون الگوی تازهٔ خطادار</t>
         </is>
       </c>
       <c r="J23" s="48" t="inlineStr">
         <is>
-          <t>PASS: safe-off. FAIL: LED(flag)true</t>
+          <t>آرام ماندن و برگشت عادی = قبول؛ هنگ، بوق بی‌دلیل یا چراغ قاطی = رد</t>
         </is>
       </c>
       <c r="K23" s="48" t="inlineStr"/>
@@ -2975,40 +2949,38 @@
       </c>
       <c r="D24" s="43" t="inlineStr">
         <is>
-          <t>valid</t>
+          <t>دستگاه روی باتری کار می‌کند؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
       <c r="E24" s="43" t="inlineStr">
         <is>
-          <t>گام ۱: snapshot معتبر باشد و ولتاژ باتری را این‌طوری حرکت بده: اول 20900، بعد 21100، بعد 21200 میلی‌ولت؛ هر کدام 1 ثانیه.
-گام ۲: پرچم «باتری کم» را نگاه کن.
-گام ۳: پرچم باید روی گذر از 21000 ست شود و تا وقتی زیر 21200 هستیم با همان منطق هیسترزیس حفظ شود و فوری بالا و پایین نپرد.
-گام ۴: معیار قبولی هیسترزیس 21 و 21.2 ولت است؛ تغییر فوری بدون هیسترزیس یعنی رد تست.</t>
+          <t>گام ۱: ولتاژ باتری را آرام تا نزدیک مرز باتری کم (حدود ۲۱ ولت) پایین بیاور.
+گام ۲: کمی دور همان مرز بالا و پایینش کن و چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
       <c r="F24" s="45" t="inlineStr">
         <is>
-          <t>20900/21100/21200</t>
+          <t>باتری دور مرز ۲۱ ولت</t>
         </is>
       </c>
       <c r="G24" s="45" t="inlineStr">
         <is>
-          <t>1s each</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H24" s="43" t="inlineStr">
         <is>
-          <t>پرچم باتری کم با کمی تأخیر می‌آید و بالا و پایین نمی‌پرد (هیسترزیس دارد)</t>
+          <t>چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود</t>
         </is>
       </c>
       <c r="I24" s="43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایدار، بدون فلیکر</t>
         </is>
       </c>
       <c r="J24" s="43" t="inlineStr">
         <is>
-          <t>آمدن با هیسترزیس؛ تغییر فوری و پرپر زدن = رد</t>
+          <t>بدون پرپر = قبول؛ رفت‌وبرگشت تند چراغ‌ها = رد</t>
         </is>
       </c>
       <c r="K24" s="43" t="inlineStr"/>
@@ -3044,40 +3016,38 @@
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>BatteryRun↔Charging</t>
+          <t>ورودی از منبع آزمایشگاهی می‌آید؛ باتری وصل است</t>
         </is>
       </c>
       <c r="E25" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: ورودی را روی 19 ولت بگذار تا وضعیت BatteryRun باشد.
-گام ۲: ورودی را به 22 ولت بالا ببر: باید Charging یا InputOk شود.
-گام ۳: دوباره به 19 ولت برگردان: باید BatteryRun شود.
-گام ۴: کل رفت‌وبرگشت 2 ثانیه؛ اطراف 20.5 ولت هیچ فلیکری نباید دیده شود (هیسترزیس 20 و 21 ولت).</t>
+          <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
+گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
         </is>
       </c>
       <c r="F25" s="50" t="inlineStr">
         <is>
-          <t>19V/22V</t>
+          <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
         </is>
       </c>
       <c r="G25" s="50" t="inlineStr">
         <is>
-          <t>2s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H25" s="48" t="inlineStr">
         <is>
-          <t>روی 19 ولت وضعیت روی باتری است و روی 22 ولت شارژ یا ورودی خوب؛ وسط راه هیچ چشمک و رفت‌وبرگشت بی‌دلیلی نیست</t>
+          <t>وضعیت ورودی فقط وقتی واقعاً از مرز رد می‌شوی عوض می‌شود؛ وسط راه هیچ رفت‌وبرگشت بی‌دلیلی نیست</t>
         </is>
       </c>
       <c r="I25" s="48" t="inlineStr">
         <is>
-          <t>حفظ</t>
+          <t>گذار تکی و تمیز</t>
         </is>
       </c>
       <c r="J25" s="48" t="inlineStr">
         <is>
-          <t>بدون رفت‌وبرگشت بی‌دلیل؛ فلیکر وسط راه = رد</t>
+          <t>بدون رفت‌وبرگشت بی‌دلیل = قبول؛ فلیکر وسط راه = رد</t>
         </is>
       </c>
       <c r="K25" s="48" t="inlineStr"/>
@@ -3113,39 +3083,39 @@
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل به دستگاه وصل و دستگاه در حال کار عادی است</t>
         </is>
       </c>
       <c r="E26" s="48" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن و چند دیالوگ پنل (تأیید و خطا) پشت سر هم بساز.
-گام ۲: هم‌زمان چراغ‌های روی برد را 3 ثانیه نگاه کن.
-گام ۳: UI برد باید کاملاً مستقل از پنل کار خودش را بکند؛ دیالوگ‌ها فقط داخل مرورگر هستند و نباید هیچ اثری روی LED یا بوق برد بگذارند.</t>
+          <t>گام ۱: در پنل یک پیام یا دیالوگ باز کن.
+گام ۲: هم‌زمان چراغ‌های دستگاه را نگاه کن.
+گام ۳: دیالوگ را ببند.</t>
         </is>
       </c>
       <c r="F26" s="50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>باز و بسته‌کردن دیالوگ پنل</t>
         </is>
       </c>
       <c r="G26" s="50" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H26" s="48" t="inlineStr">
         <is>
-          <t>UI مستقل از پنل؛ دیالوگ‌ها فقط در مرورگر</t>
+          <t>دیالوگ پنل چراغ‌ها و بوق دستگاه را به هم نمی‌ریزد؛ رفتار عادی ادامه دارد</t>
         </is>
       </c>
       <c r="I26" s="48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بدون تغییر</t>
         </is>
       </c>
       <c r="J26" s="48" t="inlineStr">
         <is>
-          <t>بدون تداخل</t>
+          <t>استقلال کامل دیالوگ و چراغ‌ها = قبول؛ هر اثر متقابل = رد</t>
         </is>
       </c>
       <c r="K26" s="48" t="n"/>
@@ -3474,6 +3444,283 @@
       <c r="P67" s="45" t="n"/>
       <c r="Q67" s="47">
         <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>UI-032</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="inlineStr">
+        <is>
+          <t>خطای ۶: قطع باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
+        </is>
+      </c>
+      <c r="E68" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
+گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
+گام ۳: در پنل ببین جریان شارژ صفر شده.
+گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="F68" s="43" t="inlineStr">
+        <is>
+          <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="G68" s="45" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H68" s="43" t="inlineStr">
+        <is>
+          <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
+        </is>
+      </c>
+      <c r="I68" s="43" t="inlineStr">
+        <is>
+          <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
+        </is>
+      </c>
+      <c r="J68" s="43" t="inlineStr">
+        <is>
+          <t>دقیقاً همین چهره و برگشت تمیز = قبول؛ هر چراغ اشتباه یا پاک‌نشدن = رد</t>
+        </is>
+      </c>
+      <c r="K68" s="43" t="n"/>
+      <c r="L68" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M68" s="43" t="n"/>
+      <c r="N68" s="43" t="n"/>
+      <c r="O68" s="45" t="n"/>
+      <c r="P68" s="45" t="n"/>
+      <c r="Q68" s="47">
+        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>UI-033</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="inlineStr">
+        <is>
+          <t>خطای ۷: خرابی یک کانال شارژ</t>
+        </is>
+      </c>
+      <c r="C69" s="45" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
+گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
+گام ۳: فیوز را سر جایش بگذار؛ خطا نباید پاک شود.
+گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="inlineStr">
+        <is>
+          <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
+        </is>
+      </c>
+      <c r="G69" s="45" t="inlineStr">
+        <is>
+          <t>پنج دقیقه</t>
+        </is>
+      </c>
+      <c r="H69" s="43" t="inlineStr">
+        <is>
+          <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I69" s="43" t="inlineStr">
+        <is>
+          <t>هر سه چراغ با یک ریتم مشترک</t>
+        </is>
+      </c>
+      <c r="J69" s="43" t="inlineStr">
+        <is>
+          <t>قفل و پاک‌شدن فقط با ریست = قبول؛ پاک‌شدن با جا زدن فیوز = رد</t>
+        </is>
+      </c>
+      <c r="K69" s="43" t="n"/>
+      <c r="L69" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M69" s="43" t="n"/>
+      <c r="N69" s="43" t="n"/>
+      <c r="O69" s="45" t="n"/>
+      <c r="P69" s="45" t="n"/>
+      <c r="Q69" s="47">
+        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
+          <t>UI-034</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>باتری خراب (سناریوی ۶): قرمز ثابت</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>از پنل، زمان سناریوی باتری خراب را موقتاً روی چند دقیقه بگذار (مقدار واقعی یک شبانه‌روز است)؛ یک باتری خالی داری</t>
+        </is>
+      </c>
+      <c r="E70" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت پر و شناور شود.
+گام ۲: بعد از گذشت زمان تنظیم‌شده چراغ‌ها را ببین: قرمز باید ثابت روشن باشد، نه چشمک‌زن.
+گام ۳: ببین شارژ همان باتری متوقف شده و دیگر شروع نمی‌شود.
+گام ۴: باتری را با یک باتری سالم عوض کن: قفل پاک و شارژ عادی شروع می‌شود.
+گام ۵: زمان سناریو را از پنل به مقدار واقعی برگردان.</t>
+        </is>
+      </c>
+      <c r="F70" s="43" t="inlineStr">
+        <is>
+          <t>شارژ باتری خالی با زمان کوتاه‌شده از پنل</t>
+        </is>
+      </c>
+      <c r="G70" s="45" t="inlineStr">
+        <is>
+          <t>چند دقیقه + زمان تنظیم‌شده</t>
+        </is>
+      </c>
+      <c r="H70" s="43" t="inlineStr">
+        <is>
+          <t>قرمز ثابت می‌ماند، شارژ آن باتری برای همیشه می‌ایستد و فقط با تعویض باتری پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I70" s="43" t="inlineStr">
+        <is>
+          <t>قرمز ثابت، بدون چشمک</t>
+        </is>
+      </c>
+      <c r="J70" s="43" t="inlineStr">
+        <is>
+          <t>قرمز ثابت و توقف تا تعویض = قبول؛ چشمک‌زدن قرمز یا شارژ دوبارهٔ همان باتری = رد</t>
+        </is>
+      </c>
+      <c r="K70" s="43" t="n"/>
+      <c r="L70" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M70" s="43" t="n"/>
+      <c r="N70" s="43" t="n"/>
+      <c r="O70" s="45" t="n"/>
+      <c r="P70" s="45" t="n"/>
+      <c r="Q70" s="47">
+        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="42" t="inlineStr">
+        <is>
+          <t>UI-035</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t>عدم‌توازن باتری: قرمز چشمک‌زن تنها</t>
+        </is>
+      </c>
+      <c r="C71" s="45" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>دو باتری ۱۲ ولت داری که یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای؛ برای زود دیدن، از پنل حدّ رویداد مجاز را موقتاً کم کن</t>
+        </is>
+      </c>
+      <c r="E71" s="43" t="inlineStr">
+        <is>
+          <t>گام ۱: باتری‌های نابرابر را وصل و دستگاه را مدتی به کار بگذار تا حکم عدم‌توازن قفل شود.
+گام ۲: چراغ‌ها را ببین: فقط قرمز چشمک می‌زند؛ سبز و زرد خاموش‌اند و هر از چندی یک بوق کوتاه می‌آید.
+گام ۳: هر دو باتری را با باتری‌های سالم و هم‌شارژ عوض کن.
+گام ۴: چند دقیقه صبر کن تا قفل خودش پاک شود.</t>
+        </is>
+      </c>
+      <c r="F71" s="43" t="inlineStr">
+        <is>
+          <t>باتری‌های نابرابر و بعد تعویض با سالم</t>
+        </is>
+      </c>
+      <c r="G71" s="45" t="inlineStr">
+        <is>
+          <t>نیم ساعت</t>
+        </is>
+      </c>
+      <c r="H71" s="43" t="inlineStr">
+        <is>
+          <t>در قفل: قرمز چشمک‌زنِ تنها بدون سبز و زرد؛ با تعویض باتری قفل خودکار پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I71" s="43" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن، بقیه خاموش</t>
+        </is>
+      </c>
+      <c r="J71" s="43" t="inlineStr">
+        <is>
+          <t>همین چهره و پاک‌شدن با تعویض = قبول؛ روشن‌ماندن سبز/زرد یا پاک‌نشدن = رد</t>
+        </is>
+      </c>
+      <c r="K71" s="43" t="n"/>
+      <c r="L71" s="46" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M71" s="43" t="n"/>
+      <c r="N71" s="43" t="n"/>
+      <c r="O71" s="45" t="n"/>
+      <c r="P71" s="45" t="n"/>
+      <c r="Q71" s="47">
+        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
         <v/>
       </c>
     </row>
@@ -3493,10 +3740,16 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="E9" location="'برنامه تست'!A8"/>
-    <hyperlink ref="E10" location="'برنامه تست'!A8"/>
-    <hyperlink ref="E11" location="'برنامه تست'!A10"/>
+    <hyperlink ref="D6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="I6" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D7" location="'برنامه تست'!A5"/>
+    <hyperlink ref="I7" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D9" location="'برنامه تست'!A8"/>
+    <hyperlink ref="D11" location="'برنامه تست'!A10"/>
+    <hyperlink ref="D12" location="'برنامه تست'!A10"/>
+    <hyperlink ref="D15" location="'برنامه تست'!A14"/>
+    <hyperlink ref="D18" location="'برنامه تست'!A17"/>
+    <hyperlink ref="D19" location="'برنامه تست'!A18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="64">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -277,6 +277,107 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00262626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00404040"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -513,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -732,6 +833,127 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1121,370 +1343,400 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول UI — BatteryRun 2%+0/1, Charging 5%, InputOk 100/95</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="80" t="n"/>
+      <c r="H1" s="80" t="n"/>
+      <c r="I1" s="80" t="n"/>
+      <c r="J1" s="80" t="n"/>
+      <c r="K1" s="80" t="n"/>
+      <c r="L1" s="80" t="n"/>
+      <c r="M1" s="80" t="n"/>
+      <c r="N1" s="80" t="n"/>
+      <c r="O1" s="80" t="n"/>
+      <c r="P1" s="80" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>PA3/ADC1_IN3/raw2/v_bat24 → BatteryRun/Charging | PA2/ADC1_IN2/raw1/v_in → ورودی | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
         </is>
       </c>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
+      <c r="N2" s="80" t="n"/>
+      <c r="O2" s="80" t="n"/>
+      <c r="P2" s="80" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="82" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="73" t="n"/>
-      <c r="J3" s="73" t="n"/>
-      <c r="K3" s="73" t="n"/>
-      <c r="L3" s="73" t="n"/>
-      <c r="M3" s="73" t="n"/>
-      <c r="N3" s="73" t="n"/>
-      <c r="O3" s="73" t="n"/>
-      <c r="P3" s="74" t="n"/>
+      <c r="B3" s="83" t="n"/>
+      <c r="C3" s="83" t="n"/>
+      <c r="D3" s="83" t="n"/>
+      <c r="E3" s="83" t="n"/>
+      <c r="F3" s="83" t="n"/>
+      <c r="G3" s="83" t="n"/>
+      <c r="H3" s="83" t="n"/>
+      <c r="I3" s="83" t="n"/>
+      <c r="J3" s="83" t="n"/>
+      <c r="K3" s="83" t="n"/>
+      <c r="L3" s="83" t="n"/>
+      <c r="M3" s="83" t="n"/>
+      <c r="N3" s="83" t="n"/>
+      <c r="O3" s="83" t="n"/>
+      <c r="P3" s="84" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n"/>
-      <c r="C4" s="28" t="n"/>
-      <c r="D4" s="28" t="n"/>
-      <c r="E4" s="28" t="n"/>
-      <c r="F4" s="28" t="n"/>
-      <c r="G4" s="28" t="n"/>
-      <c r="H4" s="28" t="n"/>
-      <c r="I4" s="28" t="n"/>
-      <c r="J4" s="28" t="n"/>
-      <c r="K4" s="28" t="n"/>
-      <c r="L4" s="28" t="n"/>
-      <c r="M4" s="28" t="n"/>
-      <c r="N4" s="28" t="n"/>
-      <c r="O4" s="28" t="n"/>
-      <c r="P4" s="29" t="n"/>
+      <c r="B4" s="86" t="n"/>
+      <c r="C4" s="86" t="n"/>
+      <c r="D4" s="86" t="n"/>
+      <c r="E4" s="86" t="n"/>
+      <c r="F4" s="86" t="n"/>
+      <c r="G4" s="86" t="n"/>
+      <c r="H4" s="86" t="n"/>
+      <c r="I4" s="86" t="n"/>
+      <c r="J4" s="86" t="n"/>
+      <c r="K4" s="86" t="n"/>
+      <c r="L4" s="86" t="n"/>
+      <c r="M4" s="86" t="n"/>
+      <c r="N4" s="86" t="n"/>
+      <c r="O4" s="86" t="n"/>
+      <c r="P4" s="87" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>منبع و mapping</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
-      <c r="K5" s="28" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" s="28" t="n"/>
-      <c r="O5" s="28" t="n"/>
-      <c r="P5" s="29" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="n"/>
+      <c r="F5" s="86" t="n"/>
+      <c r="G5" s="86" t="n"/>
+      <c r="H5" s="86" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="86" t="n"/>
+      <c r="L5" s="86" t="n"/>
+      <c r="M5" s="86" t="n"/>
+      <c r="N5" s="86" t="n"/>
+      <c r="O5" s="86" t="n"/>
+      <c r="P5" s="87" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="85" t="inlineStr">
         <is>
           <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n"/>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="28" t="n"/>
-      <c r="K6" s="28" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="28" t="n"/>
-      <c r="N6" s="28" t="n"/>
-      <c r="O6" s="28" t="n"/>
-      <c r="P6" s="29" t="n"/>
+      <c r="B6" s="86" t="n"/>
+      <c r="C6" s="86" t="n"/>
+      <c r="D6" s="86" t="n"/>
+      <c r="E6" s="86" t="n"/>
+      <c r="F6" s="86" t="n"/>
+      <c r="G6" s="86" t="n"/>
+      <c r="H6" s="86" t="n"/>
+      <c r="I6" s="86" t="n"/>
+      <c r="J6" s="86" t="n"/>
+      <c r="K6" s="86" t="n"/>
+      <c r="L6" s="86" t="n"/>
+      <c r="M6" s="86" t="n"/>
+      <c r="N6" s="86" t="n"/>
+      <c r="O6" s="86" t="n"/>
+      <c r="P6" s="87" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>BatteryRun 2%+0/1</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="28" t="n"/>
-      <c r="H7" s="28" t="n"/>
-      <c r="I7" s="28" t="n"/>
-      <c r="J7" s="28" t="n"/>
-      <c r="K7" s="28" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="28" t="n"/>
-      <c r="N7" s="28" t="n"/>
-      <c r="O7" s="28" t="n"/>
-      <c r="P7" s="29" t="n"/>
+      <c r="B7" s="86" t="n"/>
+      <c r="C7" s="86" t="n"/>
+      <c r="D7" s="86" t="n"/>
+      <c r="E7" s="86" t="n"/>
+      <c r="F7" s="86" t="n"/>
+      <c r="G7" s="86" t="n"/>
+      <c r="H7" s="86" t="n"/>
+      <c r="I7" s="86" t="n"/>
+      <c r="J7" s="86" t="n"/>
+      <c r="K7" s="86" t="n"/>
+      <c r="L7" s="86" t="n"/>
+      <c r="M7" s="86" t="n"/>
+      <c r="N7" s="86" t="n"/>
+      <c r="O7" s="86" t="n"/>
+      <c r="P7" s="87" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n"/>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="28" t="n"/>
-      <c r="I8" s="28" t="n"/>
-      <c r="J8" s="28" t="n"/>
-      <c r="K8" s="28" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="28" t="n"/>
-      <c r="N8" s="28" t="n"/>
-      <c r="O8" s="28" t="n"/>
-      <c r="P8" s="29" t="n"/>
+      <c r="B8" s="86" t="n"/>
+      <c r="C8" s="86" t="n"/>
+      <c r="D8" s="86" t="n"/>
+      <c r="E8" s="86" t="n"/>
+      <c r="F8" s="86" t="n"/>
+      <c r="G8" s="86" t="n"/>
+      <c r="H8" s="86" t="n"/>
+      <c r="I8" s="86" t="n"/>
+      <c r="J8" s="86" t="n"/>
+      <c r="K8" s="86" t="n"/>
+      <c r="L8" s="86" t="n"/>
+      <c r="M8" s="86" t="n"/>
+      <c r="N8" s="86" t="n"/>
+      <c r="O8" s="86" t="n"/>
+      <c r="P8" s="87" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="28" t="n"/>
-      <c r="K9" s="28" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="28" t="n"/>
-      <c r="N9" s="28" t="n"/>
-      <c r="O9" s="28" t="n"/>
-      <c r="P9" s="29" t="n"/>
+      <c r="B9" s="86" t="n"/>
+      <c r="C9" s="86" t="n"/>
+      <c r="D9" s="86" t="n"/>
+      <c r="E9" s="86" t="n"/>
+      <c r="F9" s="86" t="n"/>
+      <c r="G9" s="86" t="n"/>
+      <c r="H9" s="86" t="n"/>
+      <c r="I9" s="86" t="n"/>
+      <c r="J9" s="86" t="n"/>
+      <c r="K9" s="86" t="n"/>
+      <c r="L9" s="86" t="n"/>
+      <c r="M9" s="86" t="n"/>
+      <c r="N9" s="86" t="n"/>
+      <c r="O9" s="86" t="n"/>
+      <c r="P9" s="87" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="85" t="inlineStr">
         <is>
           <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="28" t="n"/>
-      <c r="K10" s="28" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="28" t="n"/>
-      <c r="N10" s="28" t="n"/>
-      <c r="O10" s="28" t="n"/>
-      <c r="P10" s="29" t="n"/>
+      <c r="B10" s="86" t="n"/>
+      <c r="C10" s="86" t="n"/>
+      <c r="D10" s="86" t="n"/>
+      <c r="E10" s="86" t="n"/>
+      <c r="F10" s="86" t="n"/>
+      <c r="G10" s="86" t="n"/>
+      <c r="H10" s="86" t="n"/>
+      <c r="I10" s="86" t="n"/>
+      <c r="J10" s="86" t="n"/>
+      <c r="K10" s="86" t="n"/>
+      <c r="L10" s="86" t="n"/>
+      <c r="M10" s="86" t="n"/>
+      <c r="N10" s="86" t="n"/>
+      <c r="O10" s="86" t="n"/>
+      <c r="P10" s="87" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>فول InputOk/Charging 100/95</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="28" t="n"/>
-      <c r="K11" s="28" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="28" t="n"/>
-      <c r="N11" s="28" t="n"/>
-      <c r="O11" s="28" t="n"/>
-      <c r="P11" s="29" t="n"/>
+      <c r="B11" s="86" t="n"/>
+      <c r="C11" s="86" t="n"/>
+      <c r="D11" s="86" t="n"/>
+      <c r="E11" s="86" t="n"/>
+      <c r="F11" s="86" t="n"/>
+      <c r="G11" s="86" t="n"/>
+      <c r="H11" s="86" t="n"/>
+      <c r="I11" s="86" t="n"/>
+      <c r="J11" s="86" t="n"/>
+      <c r="K11" s="86" t="n"/>
+      <c r="L11" s="86" t="n"/>
+      <c r="M11" s="86" t="n"/>
+      <c r="N11" s="86" t="n"/>
+      <c r="O11" s="86" t="n"/>
+      <c r="P11" s="87" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="28" t="n"/>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="28" t="n"/>
-      <c r="P12" s="29" t="n"/>
+      <c r="B12" s="86" t="n"/>
+      <c r="C12" s="86" t="n"/>
+      <c r="D12" s="86" t="n"/>
+      <c r="E12" s="86" t="n"/>
+      <c r="F12" s="86" t="n"/>
+      <c r="G12" s="86" t="n"/>
+      <c r="H12" s="86" t="n"/>
+      <c r="I12" s="86" t="n"/>
+      <c r="J12" s="86" t="n"/>
+      <c r="K12" s="86" t="n"/>
+      <c r="L12" s="86" t="n"/>
+      <c r="M12" s="86" t="n"/>
+      <c r="N12" s="86" t="n"/>
+      <c r="O12" s="86" t="n"/>
+      <c r="P12" s="87" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>حفظ فاز</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="28" t="n"/>
-      <c r="K13" s="28" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="28" t="n"/>
-      <c r="N13" s="28" t="n"/>
-      <c r="O13" s="28" t="n"/>
-      <c r="P13" s="29" t="n"/>
+      <c r="B13" s="86" t="n"/>
+      <c r="C13" s="86" t="n"/>
+      <c r="D13" s="86" t="n"/>
+      <c r="E13" s="86" t="n"/>
+      <c r="F13" s="86" t="n"/>
+      <c r="G13" s="86" t="n"/>
+      <c r="H13" s="86" t="n"/>
+      <c r="I13" s="86" t="n"/>
+      <c r="J13" s="86" t="n"/>
+      <c r="K13" s="86" t="n"/>
+      <c r="L13" s="86" t="n"/>
+      <c r="M13" s="86" t="n"/>
+      <c r="N13" s="86" t="n"/>
+      <c r="O13" s="86" t="n"/>
+      <c r="P13" s="87" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="85" t="inlineStr">
         <is>
           <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="28" t="n"/>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="28" t="n"/>
-      <c r="N14" s="28" t="n"/>
-      <c r="O14" s="28" t="n"/>
-      <c r="P14" s="29" t="n"/>
+      <c r="B14" s="86" t="n"/>
+      <c r="C14" s="86" t="n"/>
+      <c r="D14" s="86" t="n"/>
+      <c r="E14" s="86" t="n"/>
+      <c r="F14" s="86" t="n"/>
+      <c r="G14" s="86" t="n"/>
+      <c r="H14" s="86" t="n"/>
+      <c r="I14" s="86" t="n"/>
+      <c r="J14" s="86" t="n"/>
+      <c r="K14" s="86" t="n"/>
+      <c r="L14" s="86" t="n"/>
+      <c r="M14" s="86" t="n"/>
+      <c r="N14" s="86" t="n"/>
+      <c r="O14" s="86" t="n"/>
+      <c r="P14" s="87" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>غیرمسدودکننده</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="28" t="n"/>
-      <c r="K15" s="28" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="28" t="n"/>
-      <c r="N15" s="28" t="n"/>
-      <c r="O15" s="28" t="n"/>
-      <c r="P15" s="29" t="n"/>
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="86" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="86" t="n"/>
+      <c r="F15" s="86" t="n"/>
+      <c r="G15" s="86" t="n"/>
+      <c r="H15" s="86" t="n"/>
+      <c r="I15" s="86" t="n"/>
+      <c r="J15" s="86" t="n"/>
+      <c r="K15" s="86" t="n"/>
+      <c r="L15" s="86" t="n"/>
+      <c r="M15" s="86" t="n"/>
+      <c r="N15" s="86" t="n"/>
+      <c r="O15" s="86" t="n"/>
+      <c r="P15" s="87" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="85" t="inlineStr">
         <is>
           <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="28" t="n"/>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="28" t="n"/>
-      <c r="N16" s="28" t="n"/>
-      <c r="O16" s="28" t="n"/>
-      <c r="P16" s="29" t="n"/>
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="86" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="86" t="n"/>
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="86" t="n"/>
+      <c r="H16" s="86" t="n"/>
+      <c r="I16" s="86" t="n"/>
+      <c r="J16" s="86" t="n"/>
+      <c r="K16" s="86" t="n"/>
+      <c r="L16" s="86" t="n"/>
+      <c r="M16" s="86" t="n"/>
+      <c r="N16" s="86" t="n"/>
+      <c r="O16" s="86" t="n"/>
+      <c r="P16" s="87" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>RTOS و حافظه</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="28" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="28" t="n"/>
-      <c r="N17" s="28" t="n"/>
-      <c r="O17" s="28" t="n"/>
-      <c r="P17" s="29" t="n"/>
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="86" t="n"/>
+      <c r="H17" s="86" t="n"/>
+      <c r="I17" s="86" t="n"/>
+      <c r="J17" s="86" t="n"/>
+      <c r="K17" s="86" t="n"/>
+      <c r="L17" s="86" t="n"/>
+      <c r="M17" s="86" t="n"/>
+      <c r="N17" s="86" t="n"/>
+      <c r="O17" s="86" t="n"/>
+      <c r="P17" s="87" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="85" t="inlineStr">
         <is>
           <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n"/>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="28" t="n"/>
-      <c r="G18" s="28" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="28" t="n"/>
-      <c r="K18" s="28" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="28" t="n"/>
-      <c r="O18" s="28" t="n"/>
-      <c r="P18" s="29" t="n"/>
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="86" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="86" t="n"/>
+      <c r="F18" s="86" t="n"/>
+      <c r="G18" s="86" t="n"/>
+      <c r="H18" s="86" t="n"/>
+      <c r="I18" s="86" t="n"/>
+      <c r="J18" s="86" t="n"/>
+      <c r="K18" s="86" t="n"/>
+      <c r="L18" s="86" t="n"/>
+      <c r="M18" s="86" t="n"/>
+      <c r="N18" s="86" t="n"/>
+      <c r="O18" s="86" t="n"/>
+      <c r="P18" s="87" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1542,1280 +1794,1328 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="80" t="n"/>
+      <c r="H1" s="80" t="n"/>
+      <c r="I1" s="80" t="n"/>
+      <c r="J1" s="80" t="n"/>
+      <c r="K1" s="80" t="n"/>
+      <c r="L1" s="80" t="n"/>
+      <c r="M1" s="80" t="n"/>
+      <c r="N1" s="80" t="n"/>
+      <c r="O1" s="80" t="n"/>
+      <c r="P1" s="80" t="n"/>
+      <c r="Q1" s="80" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>ورودی mV، درصد 0-100، زمان ms. BatteryRun PA3 stable2%، Charging PA3 stable5% و زرد، Full 100/95 با raw.</t>
         </is>
       </c>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
+      <c r="N2" s="80" t="n"/>
+      <c r="O2" s="80" t="n"/>
+      <c r="P2" s="80" t="n"/>
+      <c r="Q2" s="80" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable, ورودی present/overvoltage, فاز LED/بوق با اسکوپ 10ms. InputOk/Charging سریع برگردد.</t>
         </is>
       </c>
+      <c r="B3" s="80" t="n"/>
+      <c r="C3" s="80" t="n"/>
+      <c r="D3" s="80" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
+      <c r="G3" s="80" t="n"/>
+      <c r="H3" s="80" t="n"/>
+      <c r="I3" s="80" t="n"/>
+      <c r="J3" s="80" t="n"/>
+      <c r="K3" s="80" t="n"/>
+      <c r="L3" s="80" t="n"/>
+      <c r="M3" s="80" t="n"/>
+      <c r="N3" s="80" t="n"/>
+      <c r="O3" s="80" t="n"/>
+      <c r="P3" s="80" t="n"/>
+      <c r="Q3" s="80" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="36" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="36" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="36" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="36" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="36" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="92" t="inlineStr">
         <is>
           <t>UI-002</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>BatteryRun 2% 56/57/58</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری کار می‌کند (برق شهر قطع)؛ به‌جای باتری یک منبع آزمایشگاهی ۲۴ ولت گذاشته‌ای و درصد حدود نصف است</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>گام ۱: منبع را آن‌قدر تنظیم کن که درصد باتری حدود ۵۷ شود و چشمک سبز جا بیفتد.
 گام ۲: ولتاژ منبع را خیلی کم بالا و پایین کن، در حدی که درصد بین ۵۶ و ۵۸ بازی کند.
 گام ۳: یک دقیقه فقط به چراغ سبز نگاه کن.</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>لرزش کوچک ولتاژ باتری دور درصد ۵۷</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="93" t="inlineStr">
         <is>
           <t>چشمک سبز با همان ریتم قبلی ادامه می‌دهد؛ نه تند و کند می‌شود نه از اول شروع می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="93" t="inlineStr">
         <is>
           <t>ریتم ثابت و بی‌پرش</t>
         </is>
       </c>
-      <c r="J5" s="48" t="inlineStr">
+      <c r="J5" s="93" t="inlineStr">
         <is>
           <t>ریتم ثابت بماند = قبول؛ پریدن یا عوض‌شدن ریتم با هر تغییر کوچک = رد</t>
         </is>
       </c>
-      <c r="K5" s="48" t="inlineStr"/>
-      <c r="L5" s="46" t="inlineStr">
+      <c r="K5" s="93" t="inlineStr"/>
+      <c r="L5" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="48" t="inlineStr"/>
-      <c r="N5" s="48" t="inlineStr"/>
-      <c r="O5" s="50" t="inlineStr"/>
-      <c r="P5" s="50" t="inlineStr"/>
-      <c r="Q5" s="51">
+      <c r="M5" s="93" t="inlineStr"/>
+      <c r="N5" s="93" t="inlineStr"/>
+      <c r="O5" s="95" t="inlineStr"/>
+      <c r="P5" s="95" t="inlineStr"/>
+      <c r="Q5" s="97">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>UI-003</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>BatteryRun 57→55</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="100" t="inlineStr">
         <is>
           <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا درصد به حدود ۵۵ برسد.
 گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
 گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F6" s="45" t="inlineStr">
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>کم‌کردن آرام ولتاژ باتری تا درصد ۵۵</t>
         </is>
       </c>
-      <c r="G6" s="45" t="inlineStr">
+      <c r="G6" s="101" t="inlineStr">
         <is>
           <t>نیم دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر می‌شود (خاموشی‌اش بیشتر از قبل)</t>
         </is>
       </c>
-      <c r="I6" s="52" t="inlineStr">
+      <c r="I6" s="100" t="inlineStr">
         <is>
           <t>تندتر از UI-002، بدون پرش ناگهانی</t>
         </is>
       </c>
-      <c r="J6" s="43" t="inlineStr">
+      <c r="J6" s="98" t="inlineStr">
         <is>
           <t>پایدار روی ۵۵ با ریتم تندتر = قبول؛ ماندن روی ۵۷ = رد</t>
         </is>
       </c>
-      <c r="K6" s="43" t="inlineStr"/>
-      <c r="L6" s="46" t="inlineStr">
+      <c r="K6" s="98" t="inlineStr"/>
+      <c r="L6" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="43" t="inlineStr"/>
-      <c r="N6" s="43" t="inlineStr"/>
-      <c r="O6" s="45" t="inlineStr"/>
-      <c r="P6" s="45" t="inlineStr"/>
-      <c r="Q6" s="47">
+      <c r="M6" s="98" t="inlineStr"/>
+      <c r="N6" s="98" t="inlineStr"/>
+      <c r="O6" s="101" t="inlineStr"/>
+      <c r="P6" s="101" t="inlineStr"/>
+      <c r="Q6" s="102">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>UI-004</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>BatteryRun 57→59</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
         </is>
       </c>
-      <c r="E7" s="48" t="inlineStr">
+      <c r="E7" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام بالا ببر تا درصد به حدود ۵۹ برسد.
 گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
 گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F7" s="50" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>بالابردن آرام ولتاژ باتری تا درصد ۵۹</t>
         </is>
       </c>
-      <c r="G7" s="50" t="inlineStr">
+      <c r="G7" s="95" t="inlineStr">
         <is>
           <t>نیم دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="48" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>درصد روی ۵۹ می‌ایستد و چشمک سبز کمی کندتر می‌شود (روشن بودنش بیشتر از قبل)</t>
         </is>
       </c>
-      <c r="I7" s="53" t="inlineStr">
+      <c r="I7" s="103" t="inlineStr">
         <is>
           <t>کندتر از UI-002، بدون پرش ناگهانی</t>
         </is>
       </c>
-      <c r="J7" s="48" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>پایدار روی ۵۹ با ریتم کندتر = قبول؛ ماندن روی ۵۷ = رد</t>
         </is>
       </c>
-      <c r="K7" s="48" t="inlineStr"/>
-      <c r="L7" s="46" t="inlineStr">
+      <c r="K7" s="93" t="inlineStr"/>
+      <c r="L7" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="48" t="inlineStr"/>
-      <c r="N7" s="48" t="inlineStr"/>
-      <c r="O7" s="50" t="inlineStr"/>
-      <c r="P7" s="50" t="inlineStr"/>
-      <c r="Q7" s="51">
+      <c r="M7" s="93" t="inlineStr"/>
+      <c r="N7" s="93" t="inlineStr"/>
+      <c r="O7" s="95" t="inlineStr"/>
+      <c r="P7" s="95" t="inlineStr"/>
+      <c r="Q7" s="97">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="92" t="inlineStr">
         <is>
           <t>UI-005</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>باتری خالیِ کامل (درصد صفر)</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="98" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا باتری تقریباً خالی شود و درصد به صفر برسد.
 گام ۲: از لحظهٔ صفر شدن، به بوق و چراغ‌ها دقت کن.
 گام ۳: همان ولتاژ را نگه دار و یک دقیقه صبر کن.</t>
         </is>
       </c>
-      <c r="F8" s="45" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>باتری نزدیک خالی کامل (درصد صفر)</t>
         </is>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G8" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="98" t="inlineStr">
         <is>
           <t>یک بوق بلند حدود ده ثانیه می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود تا وقتی باتری از خالیِ کامل بیرون بیاید</t>
         </is>
       </c>
-      <c r="I8" s="43" t="inlineStr">
+      <c r="I8" s="98" t="inlineStr">
         <is>
           <t>بعد از بوق: همه خاموش</t>
         </is>
       </c>
-      <c r="J8" s="43" t="inlineStr">
+      <c r="J8" s="98" t="inlineStr">
         <is>
           <t>فقط یک بوق بلند و بعد خاموشی = قبول؛ بوق تکراری یا چراغ روشنِ مانده = رد</t>
         </is>
       </c>
-      <c r="K8" s="43" t="inlineStr"/>
-      <c r="L8" s="46" t="inlineStr">
+      <c r="K8" s="98" t="inlineStr"/>
+      <c r="L8" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="43" t="inlineStr"/>
-      <c r="N8" s="43" t="inlineStr"/>
-      <c r="O8" s="45" t="inlineStr"/>
-      <c r="P8" s="45" t="inlineStr"/>
-      <c r="Q8" s="47">
+      <c r="M8" s="98" t="inlineStr"/>
+      <c r="N8" s="98" t="inlineStr"/>
+      <c r="O8" s="101" t="inlineStr"/>
+      <c r="P8" s="101" t="inlineStr"/>
+      <c r="Q8" s="102">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="92" t="inlineStr">
         <is>
           <t>UI-006</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>0↔1 نویز</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-005؛ درصد روی صفر و بوق بحرانی تمام شده</t>
         </is>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را خیلی کم بالا و پایین کن، دور مرز صفر و یک درصد.
 گام ۲: دو دقیقه به چراغ‌ها و بوق گوش بده.</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
+      <c r="F9" s="95" t="inlineStr">
         <is>
           <t>بازی ولتاژ دور مرز ۰ و ۱ درصد</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G9" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H9" s="93" t="inlineStr">
         <is>
           <t>بوق بحرانی دوباره شروع نمی‌شود و چراغ‌ها بی‌دلیل روشن و خاموش نمی‌شوند</t>
         </is>
       </c>
-      <c r="I9" s="48" t="inlineStr">
+      <c r="I9" s="93" t="inlineStr">
         <is>
           <t>خاموش و آرام</t>
         </is>
       </c>
-      <c r="J9" s="48" t="inlineStr">
+      <c r="J9" s="93" t="inlineStr">
         <is>
           <t>آرام ماندن = قبول؛ شروع دوبارهٔ بوق با هر نوسان کوچک = رد</t>
         </is>
       </c>
-      <c r="K9" s="48" t="inlineStr"/>
-      <c r="L9" s="46" t="inlineStr">
+      <c r="K9" s="93" t="inlineStr"/>
+      <c r="L9" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="48" t="inlineStr"/>
-      <c r="N9" s="48" t="inlineStr"/>
-      <c r="O9" s="50" t="inlineStr"/>
-      <c r="P9" s="50" t="inlineStr"/>
-      <c r="Q9" s="51">
+      <c r="M9" s="93" t="inlineStr"/>
+      <c r="N9" s="93" t="inlineStr"/>
+      <c r="O9" s="95" t="inlineStr"/>
+      <c r="P9" s="95" t="inlineStr"/>
+      <c r="Q9" s="97">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="92" t="inlineStr">
         <is>
           <t>UI-007</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="98" t="inlineStr">
         <is>
           <t>درصد ۱ (نزدیک خالی)</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="98" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E10" s="43" t="inlineStr">
+      <c r="E10" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را طوری تنظیم کن که درصد روی ۱ بایستد (باتری تقریباً خالی ولی نه صفر).
 گام ۲: دو دقیقه چراغ سبز و بوق را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F10" s="45" t="inlineStr">
+      <c r="F10" s="101" t="inlineStr">
         <is>
           <t>درصد پایدار ۱</t>
         </is>
       </c>
-      <c r="G10" s="45" t="inlineStr">
+      <c r="G10" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H10" s="98" t="inlineStr">
         <is>
           <t>هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
         </is>
       </c>
-      <c r="I10" s="43" t="inlineStr">
+      <c r="I10" s="98" t="inlineStr">
         <is>
           <t>برق‌های کوتاه و کم</t>
         </is>
       </c>
-      <c r="J10" s="43" t="inlineStr">
+      <c r="J10" s="98" t="inlineStr">
         <is>
           <t>همین رفتار = قبول؛ رفتارِ درصد صفر (بوق بلند و خاموشی کامل) = رد</t>
         </is>
       </c>
-      <c r="K10" s="43" t="inlineStr"/>
-      <c r="L10" s="46" t="inlineStr">
+      <c r="K10" s="98" t="inlineStr"/>
+      <c r="L10" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="43" t="inlineStr"/>
-      <c r="N10" s="43" t="inlineStr"/>
-      <c r="O10" s="45" t="inlineStr"/>
-      <c r="P10" s="45" t="inlineStr"/>
-      <c r="Q10" s="47">
+      <c r="M10" s="98" t="inlineStr"/>
+      <c r="N10" s="98" t="inlineStr"/>
+      <c r="O10" s="101" t="inlineStr"/>
+      <c r="P10" s="101" t="inlineStr"/>
+      <c r="Q10" s="102">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+      <c r="A11" s="92" t="inlineStr">
         <is>
           <t>UI-008</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>1% →2 حفظ/خروج</t>
         </is>
       </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="95" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-007؛ درصد روی ۱</t>
         </is>
       </c>
-      <c r="E11" s="48" t="inlineStr">
+      <c r="E11" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را خیلی کم بالا ببر، آن‌قدر که درصد هنوز ۲ نشده باشد.
 گام ۲: یک دقیقه رفتار را نگاه کن.</t>
         </is>
       </c>
-      <c r="F11" s="50" t="inlineStr">
+      <c r="F11" s="95" t="inlineStr">
         <is>
           <t>بالا بردن جزئی از درصد ۱</t>
         </is>
       </c>
-      <c r="G11" s="50" t="inlineStr">
+      <c r="G11" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="48" t="inlineStr">
+      <c r="H11" s="93" t="inlineStr">
         <is>
           <t>همان رفتار درصد ۱ می‌ماند: سه بوق هر از چندی و برق کوتاه سبز</t>
         </is>
       </c>
-      <c r="I11" s="48" t="inlineStr">
+      <c r="I11" s="93" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="J11" s="48" t="inlineStr">
+      <c r="J11" s="93" t="inlineStr">
         <is>
           <t>ماندن روی رفتار ۱ = قبول؛ پریدن به الگوی درصد ۲ = رد</t>
         </is>
       </c>
-      <c r="K11" s="48" t="inlineStr"/>
-      <c r="L11" s="46" t="inlineStr">
+      <c r="K11" s="93" t="inlineStr"/>
+      <c r="L11" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="48" t="inlineStr"/>
-      <c r="N11" s="48" t="inlineStr"/>
-      <c r="O11" s="50" t="inlineStr"/>
-      <c r="P11" s="50" t="inlineStr"/>
-      <c r="Q11" s="51">
+      <c r="M11" s="93" t="inlineStr"/>
+      <c r="N11" s="93" t="inlineStr"/>
+      <c r="O11" s="95" t="inlineStr"/>
+      <c r="P11" s="95" t="inlineStr"/>
+      <c r="Q11" s="97">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>UI-009</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>1% →2 خروج با3</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="100" t="inlineStr">
         <is>
           <t>ادامهٔ UI-007؛ درصد روی ۱</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E12" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را آرام بالا ببر تا درصد به ۲ برسد و ثابت شود.
 گام ۲: یک دقیقه به الگوی بوق گوش بده و با درصد ۱ مقایسه کن.</t>
         </is>
       </c>
-      <c r="F12" s="45" t="inlineStr">
+      <c r="F12" s="101" t="inlineStr">
         <is>
           <t>بالا بردن ولتاژ تا درصد ۲</t>
         </is>
       </c>
-      <c r="G12" s="45" t="inlineStr">
+      <c r="G12" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H12" s="98" t="inlineStr">
         <is>
           <t>الگوی بوق به الگوی ملایم‌ترِ درصد ۲ عوض می‌شود و سبز بیشتر از قبل روشن می‌ماند</t>
         </is>
       </c>
-      <c r="I12" s="43" t="inlineStr">
+      <c r="I12" s="98" t="inlineStr">
         <is>
           <t>روشن‌تر از درصد ۱</t>
         </is>
       </c>
-      <c r="J12" s="43" t="inlineStr">
+      <c r="J12" s="98" t="inlineStr">
         <is>
           <t>عوض‌شدن الگو روی ۲ = قبول؛ ماندن روی الگوی ۱ = رد</t>
         </is>
       </c>
-      <c r="K12" s="43" t="inlineStr"/>
-      <c r="L12" s="46" t="inlineStr">
+      <c r="K12" s="98" t="inlineStr"/>
+      <c r="L12" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="43" t="inlineStr"/>
-      <c r="N12" s="43" t="inlineStr"/>
-      <c r="O12" s="45" t="inlineStr"/>
-      <c r="P12" s="45" t="inlineStr"/>
-      <c r="Q12" s="47">
+      <c r="M12" s="98" t="inlineStr"/>
+      <c r="N12" s="98" t="inlineStr"/>
+      <c r="O12" s="101" t="inlineStr"/>
+      <c r="P12" s="101" t="inlineStr"/>
+      <c r="Q12" s="102">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="92" t="inlineStr">
         <is>
           <t>UI-010</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="93" t="inlineStr">
         <is>
           <t>BoardTest 0→2</t>
         </is>
       </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="C13" s="95" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="48" t="inlineStr">
+      <c r="D13" s="93" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری؛ منبع از درصد صفر شروع می‌کند</t>
         </is>
       </c>
-      <c r="E13" s="48" t="inlineStr">
+      <c r="E13" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را از صفر خیلی آرام بالا بیاور.
 گام ۲: به ترتیبِ الگوها دقت کن: اول باید رفتار درصد ۱ دیده شود و بعد درصد ۲.</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="F13" s="95" t="inlineStr">
         <is>
           <t>بالا آمدن آرام از ۰ به ۲ درصد</t>
         </is>
       </c>
-      <c r="G13" s="50" t="inlineStr">
+      <c r="G13" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="48" t="inlineStr">
+      <c r="H13" s="93" t="inlineStr">
         <is>
           <t>اول الگوی درصد ۱ (سه بوق و برق کوتاه) و بعد الگوی درصد ۲ می‌آید</t>
         </is>
       </c>
-      <c r="I13" s="48" t="inlineStr">
+      <c r="I13" s="93" t="inlineStr">
         <is>
           <t>گذار پله‌ای ۱ بعد ۲</t>
         </is>
       </c>
-      <c r="J13" s="48" t="inlineStr">
+      <c r="J13" s="93" t="inlineStr">
         <is>
           <t>دیدن هر دو پله به ترتیب = قبول؛ پرش مستقیم به الگوی ۲ = رد</t>
         </is>
       </c>
-      <c r="K13" s="48" t="inlineStr"/>
-      <c r="L13" s="46" t="inlineStr">
+      <c r="K13" s="93" t="inlineStr"/>
+      <c r="L13" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="48" t="inlineStr"/>
-      <c r="N13" s="48" t="inlineStr"/>
-      <c r="O13" s="50" t="inlineStr"/>
-      <c r="P13" s="50" t="inlineStr"/>
-      <c r="Q13" s="51">
+      <c r="M13" s="93" t="inlineStr"/>
+      <c r="N13" s="93" t="inlineStr"/>
+      <c r="O13" s="95" t="inlineStr"/>
+      <c r="P13" s="95" t="inlineStr"/>
+      <c r="Q13" s="97">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="92" t="inlineStr">
         <is>
           <t>UI-011</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>Charging 5% 56/57/58</t>
         </is>
       </c>
-      <c r="C14" s="44" t="inlineStr">
+      <c r="C14" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="98" t="inlineStr">
         <is>
           <t>برق شهر وصل و باتری واقعی در حال شارژ است؛ درصد حدود نصف</t>
         </is>
       </c>
-      <c r="E14" s="43" t="inlineStr">
+      <c r="E14" s="98" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را به شارژ بزن و صبر کن درصد دور ۵۷ ثابت شود.
 گام ۲: یک دقیقه فقط چراغ زرد را نگاه کن.</t>
         </is>
       </c>
-      <c r="F14" s="45" t="inlineStr">
+      <c r="F14" s="101" t="inlineStr">
         <is>
           <t>شارژ عادی با درصد میانی</t>
         </is>
       </c>
-      <c r="G14" s="45" t="inlineStr">
+      <c r="G14" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="43" t="inlineStr">
+      <c r="H14" s="98" t="inlineStr">
         <is>
           <t>زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند</t>
         </is>
       </c>
-      <c r="I14" s="43" t="inlineStr">
+      <c r="I14" s="98" t="inlineStr">
         <is>
           <t>ریتم ثابت</t>
         </is>
       </c>
-      <c r="J14" s="43" t="inlineStr">
+      <c r="J14" s="98" t="inlineStr">
         <is>
           <t>ریتم ثابت = قبول؛ پرش یا توقف چشمک = رد</t>
         </is>
       </c>
-      <c r="K14" s="43" t="inlineStr"/>
-      <c r="L14" s="46" t="inlineStr">
+      <c r="K14" s="98" t="inlineStr"/>
+      <c r="L14" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="43" t="inlineStr"/>
-      <c r="N14" s="43" t="inlineStr"/>
-      <c r="O14" s="45" t="inlineStr"/>
-      <c r="P14" s="45" t="inlineStr"/>
-      <c r="Q14" s="47">
+      <c r="M14" s="98" t="inlineStr"/>
+      <c r="N14" s="98" t="inlineStr"/>
+      <c r="O14" s="101" t="inlineStr"/>
+      <c r="P14" s="101" t="inlineStr"/>
+      <c r="Q14" s="102">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="92" t="inlineStr">
         <is>
           <t>UI-012</t>
         </is>
       </c>
-      <c r="B15" s="48" t="inlineStr">
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>Charging 5% 53..61</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-011؛ در حال شارژ با درصد حدود ۵۷</t>
         </is>
       </c>
-      <c r="E15" s="48" t="inlineStr">
+      <c r="E15" s="93" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ، ولتاژ باتری را با یک مصرف کوچک یا منبع کمی بالا و پایین کن (درصد دور ۵۷ بازی کند).
 گام ۲: یک دقیقه چراغ زرد را نگاه کن.</t>
         </is>
       </c>
-      <c r="F15" s="50" t="inlineStr">
+      <c r="F15" s="95" t="inlineStr">
         <is>
           <t>بازی کوچک درصد حین شارژ</t>
         </is>
       </c>
-      <c r="G15" s="50" t="inlineStr">
+      <c r="G15" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="48" t="inlineStr">
+      <c r="H15" s="93" t="inlineStr">
         <is>
           <t>چشمک زرد هیچ تغییری نمی‌کند و با همان ریتم ادامه می‌دهد</t>
         </is>
       </c>
-      <c r="I15" s="48" t="inlineStr">
+      <c r="I15" s="93" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="J15" s="48" t="inlineStr">
+      <c r="J15" s="93" t="inlineStr">
         <is>
           <t>ثابت ماندن = قبول؛ عوض‌شدن ریتم با نوسان کوچک = رد</t>
         </is>
       </c>
-      <c r="K15" s="48" t="inlineStr"/>
-      <c r="L15" s="46" t="inlineStr">
+      <c r="K15" s="93" t="inlineStr"/>
+      <c r="L15" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M15" s="48" t="inlineStr"/>
-      <c r="N15" s="48" t="inlineStr"/>
-      <c r="O15" s="50" t="inlineStr"/>
-      <c r="P15" s="50" t="inlineStr"/>
-      <c r="Q15" s="51">
+      <c r="M15" s="93" t="inlineStr"/>
+      <c r="N15" s="93" t="inlineStr"/>
+      <c r="O15" s="95" t="inlineStr"/>
+      <c r="P15" s="95" t="inlineStr"/>
+      <c r="Q15" s="97">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="92" t="inlineStr">
         <is>
           <t>UI-013</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="98" t="inlineStr">
         <is>
           <t>Charging 5% خروج</t>
         </is>
       </c>
-      <c r="C16" s="44" t="inlineStr">
+      <c r="C16" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="98" t="inlineStr">
         <is>
           <t>برق شهر وصل و دستگاه در حال شارژ؛ درصد حدود ۵۷</t>
         </is>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E16" s="98" t="inlineStr">
         <is>
           <t>گام ۱: درصد شارژ را با منبع یا مصرف واقعی اول به حدود ۵۲ ببر و ثابت کن.
 گام ۲: بعد به حدود ۶۲ ببر و ثابت کن.
 گام ۳: موقع جابه‌جایی‌ها به زرد نگاه کن که قطع و وصل ناگهانی نکند.</t>
         </is>
       </c>
-      <c r="F16" s="45" t="inlineStr">
+      <c r="F16" s="101" t="inlineStr">
         <is>
           <t>درصد شارژ ۵۷ بعد ۵۲ بعد ۶۲</t>
         </is>
       </c>
-      <c r="G16" s="45" t="inlineStr">
+      <c r="G16" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="H16" s="98" t="inlineStr">
         <is>
           <t>ریتم زرد با درصد عوض می‌شود ولی چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد</t>
         </is>
       </c>
-      <c r="I16" s="43" t="inlineStr">
+      <c r="I16" s="98" t="inlineStr">
         <is>
           <t>ریتم تازه، بدون راه‌اندازی از صفر</t>
         </is>
       </c>
-      <c r="J16" s="43" t="inlineStr">
+      <c r="J16" s="98" t="inlineStr">
         <is>
           <t>تغییر نرم ریتم = قبول؛ ماندن روی ریتم ۵۷ یا پرش ناگهانی = رد</t>
         </is>
       </c>
-      <c r="K16" s="43" t="inlineStr"/>
-      <c r="L16" s="46" t="inlineStr">
+      <c r="K16" s="98" t="inlineStr"/>
+      <c r="L16" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M16" s="43" t="inlineStr"/>
-      <c r="N16" s="43" t="inlineStr"/>
-      <c r="O16" s="45" t="inlineStr"/>
-      <c r="P16" s="45" t="inlineStr"/>
-      <c r="Q16" s="47">
+      <c r="M16" s="98" t="inlineStr"/>
+      <c r="N16" s="98" t="inlineStr"/>
+      <c r="O16" s="101" t="inlineStr"/>
+      <c r="P16" s="101" t="inlineStr"/>
+      <c r="Q16" s="102">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="40.5" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="92" t="inlineStr">
         <is>
           <t>UI-015</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>Full 100/95 enter</t>
         </is>
       </c>
-      <c r="C17" s="44" t="inlineStr">
+      <c r="C17" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="98" t="inlineStr">
         <is>
           <t>باتری در حال شارژ و نزدیک پر شدن است</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="98" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده و درصد را زیر نظر بگیر.
 گام ۲: روی ۹۹ درصد چراغ‌ها را چک کن: هنوز باید شارژ باشد (زرد چشمک‌زن).
 گام ۳: بگذار به ۱۰۰ برسد و دوباره نگاه کن.</t>
         </is>
       </c>
-      <c r="F17" s="45" t="inlineStr">
+      <c r="F17" s="101" t="inlineStr">
         <is>
           <t>رسیدن درصد شارژ از ۹۹ به ۱۰۰</t>
         </is>
       </c>
-      <c r="G17" s="45" t="inlineStr">
+      <c r="G17" s="101" t="inlineStr">
         <is>
           <t>تا پر شدن باتری</t>
         </is>
       </c>
-      <c r="H17" s="43" t="inlineStr">
+      <c r="H17" s="98" t="inlineStr">
         <is>
           <t>فقط روی ۱۰۰ ورودی خوب می‌شود: سبز ثابت و زرد خاموش؛ روی ۹۹ هنوز زرد چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I17" s="43" t="inlineStr">
+      <c r="I17" s="98" t="inlineStr">
         <is>
           <t>۱۰۰: سبز ثابت</t>
         </is>
       </c>
-      <c r="J17" s="43" t="inlineStr">
+      <c r="J17" s="98" t="inlineStr">
         <is>
           <t>ورودی خوب دقیقاً روی ۱۰۰ = قبول؛ سبز ثابت روی ۹۹ = رد</t>
         </is>
       </c>
-      <c r="K17" s="43" t="inlineStr"/>
-      <c r="L17" s="46" t="inlineStr">
+      <c r="K17" s="98" t="inlineStr"/>
+      <c r="L17" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="43" t="inlineStr"/>
-      <c r="N17" s="43" t="inlineStr"/>
-      <c r="O17" s="45" t="inlineStr"/>
-      <c r="P17" s="45" t="inlineStr"/>
-      <c r="Q17" s="47">
+      <c r="M17" s="98" t="inlineStr"/>
+      <c r="N17" s="98" t="inlineStr"/>
+      <c r="O17" s="101" t="inlineStr"/>
+      <c r="P17" s="101" t="inlineStr"/>
+      <c r="Q17" s="102">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="92" t="inlineStr">
         <is>
           <t>UI-016</t>
         </is>
       </c>
-      <c r="B18" s="48" t="inlineStr">
+      <c r="B18" s="93" t="inlineStr">
         <is>
           <t>Full 100/95 stay</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="53" t="inlineStr">
+      <c r="D18" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-015؛ درصد روی ۱۰۰ و سبز ثابت است</t>
         </is>
       </c>
-      <c r="E18" s="48" t="inlineStr">
+      <c r="E18" s="93" t="inlineStr">
         <is>
           <t>گام ۱: با یک مصرف کوچک درصد را بین ۹۵ و ۱۰۰ نگه دار و چند بار بالا پایینش کن.
 گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F18" s="50" t="inlineStr">
+      <c r="F18" s="95" t="inlineStr">
         <is>
           <t>درصد بین ۹۵ تا ۱۰۰</t>
         </is>
       </c>
-      <c r="G18" s="50" t="inlineStr">
+      <c r="G18" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="48" t="inlineStr">
+      <c r="H18" s="93" t="inlineStr">
         <is>
           <t>تا وقتی درصد بالای ۹۵ است همان ورودی خوب می‌ماند: سبز ثابت و زرد خاموش</t>
         </is>
       </c>
-      <c r="I18" s="48" t="inlineStr">
+      <c r="I18" s="93" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="J18" s="48" t="inlineStr">
+      <c r="J18" s="93" t="inlineStr">
         <is>
           <t>ماندن در هر سه وضعیت = قبول؛ افتادن به چشمک زرد شارژ = رد</t>
         </is>
       </c>
-      <c r="K18" s="48" t="inlineStr"/>
-      <c r="L18" s="46" t="inlineStr">
+      <c r="K18" s="93" t="inlineStr"/>
+      <c r="L18" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M18" s="48" t="inlineStr"/>
-      <c r="N18" s="48" t="inlineStr"/>
-      <c r="O18" s="50" t="inlineStr"/>
-      <c r="P18" s="50" t="inlineStr"/>
-      <c r="Q18" s="51">
+      <c r="M18" s="93" t="inlineStr"/>
+      <c r="N18" s="93" t="inlineStr"/>
+      <c r="O18" s="95" t="inlineStr"/>
+      <c r="P18" s="95" t="inlineStr"/>
+      <c r="Q18" s="97">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="92" t="inlineStr">
         <is>
           <t>UI-017</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="98" t="inlineStr">
         <is>
           <t>Full 95 exit</t>
         </is>
       </c>
-      <c r="C19" s="44" t="inlineStr">
+      <c r="C19" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D19" s="52" t="inlineStr">
+      <c r="D19" s="100" t="inlineStr">
         <is>
           <t>ادامهٔ UI-016؛ درصد بالای ۹۵ و سبز ثابت است</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="98" t="inlineStr">
         <is>
           <t>گام ۱: یک بار واقعی روی باتری بکش تا درصد زیر ۹۵ بیاید.
 گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="101" t="inlineStr">
         <is>
           <t>افت درصد شارژ به زیر ۹۵</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="43" t="inlineStr">
+      <c r="H19" s="98" t="inlineStr">
         <is>
           <t>برمی‌گردد به وضعیت شارژ: سبز از ثابت درمی‌آید و زرد دوباره چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I19" s="43" t="inlineStr">
+      <c r="I19" s="98" t="inlineStr">
         <is>
           <t>برگشت به چشمک زرد</t>
         </is>
       </c>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="J19" s="98" t="inlineStr">
         <is>
           <t>برگشت زیر ۹۵ = قبول؛ ماندن روی سبز ثابت = رد</t>
         </is>
       </c>
-      <c r="K19" s="43" t="inlineStr"/>
-      <c r="L19" s="46" t="inlineStr">
+      <c r="K19" s="98" t="inlineStr"/>
+      <c r="L19" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M19" s="43" t="inlineStr"/>
-      <c r="N19" s="43" t="inlineStr"/>
-      <c r="O19" s="45" t="inlineStr"/>
-      <c r="P19" s="45" t="inlineStr"/>
-      <c r="Q19" s="47">
+      <c r="M19" s="98" t="inlineStr"/>
+      <c r="N19" s="98" t="inlineStr"/>
+      <c r="O19" s="101" t="inlineStr"/>
+      <c r="P19" s="101" t="inlineStr"/>
+      <c r="Q19" s="102">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="92" t="inlineStr">
         <is>
           <t>UI-019</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>InputOk non-blocking</t>
         </is>
       </c>
-      <c r="C20" s="44" t="inlineStr">
+      <c r="C20" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="98" t="inlineStr">
         <is>
           <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="98" t="inlineStr">
         <is>
           <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
 گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
         </is>
       </c>
-      <c r="F20" s="45" t="inlineStr">
+      <c r="F20" s="101" t="inlineStr">
         <is>
           <t>کار هم‌زمان با پنل روی ورودی خوب</t>
         </is>
       </c>
-      <c r="G20" s="45" t="inlineStr">
+      <c r="G20" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="43" t="inlineStr">
+      <c r="H20" s="98" t="inlineStr">
         <is>
           <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
         </is>
       </c>
-      <c r="I20" s="43" t="inlineStr">
+      <c r="I20" s="98" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="J20" s="43" t="inlineStr">
+      <c r="J20" s="98" t="inlineStr">
         <is>
           <t>بدون هنگ و مکث = قبول؛ هر مکث یا ریست = رد</t>
         </is>
       </c>
-      <c r="K20" s="43" t="inlineStr"/>
-      <c r="L20" s="46" t="inlineStr">
+      <c r="K20" s="98" t="inlineStr"/>
+      <c r="L20" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="43" t="inlineStr"/>
-      <c r="N20" s="43" t="inlineStr"/>
-      <c r="O20" s="45" t="inlineStr"/>
-      <c r="P20" s="45" t="inlineStr"/>
-      <c r="Q20" s="47">
+      <c r="M20" s="98" t="inlineStr"/>
+      <c r="N20" s="98" t="inlineStr"/>
+      <c r="O20" s="101" t="inlineStr"/>
+      <c r="P20" s="101" t="inlineStr"/>
+      <c r="Q20" s="102">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="92" t="inlineStr">
         <is>
           <t>UI-020</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="93" t="inlineStr">
         <is>
           <t>Charging non-blocking</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D21" s="93" t="inlineStr">
         <is>
           <t>برق شهر وصل و باتری در حال شارژ است (زرد چشمک‌زن)</t>
         </is>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="93" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ با پنل کار کن و چند پارامتر بخوان.
 گام ۲: دو دقیقه دستگاه را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F21" s="50" t="inlineStr">
+      <c r="F21" s="95" t="inlineStr">
         <is>
           <t>کار با پنل حین شارژ</t>
         </is>
       </c>
-      <c r="G21" s="50" t="inlineStr">
+      <c r="G21" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="H21" s="93" t="inlineStr">
         <is>
           <t>زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست</t>
         </is>
       </c>
-      <c r="I21" s="48" t="inlineStr">
+      <c r="I21" s="93" t="inlineStr">
         <is>
           <t>چشمک منظم زرد</t>
         </is>
       </c>
-      <c r="J21" s="48" t="inlineStr">
+      <c r="J21" s="93" t="inlineStr">
         <is>
           <t>بدون هنگ = قبول؛ هنگ یا قطع ارتباط = رد</t>
         </is>
       </c>
-      <c r="K21" s="48" t="inlineStr"/>
-      <c r="L21" s="46" t="inlineStr">
+      <c r="K21" s="93" t="inlineStr"/>
+      <c r="L21" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M21" s="48" t="inlineStr"/>
-      <c r="N21" s="48" t="inlineStr"/>
-      <c r="O21" s="50" t="inlineStr"/>
-      <c r="P21" s="50" t="inlineStr"/>
-      <c r="Q21" s="51">
+      <c r="M21" s="93" t="inlineStr"/>
+      <c r="N21" s="93" t="inlineStr"/>
+      <c r="O21" s="95" t="inlineStr"/>
+      <c r="P21" s="95" t="inlineStr"/>
+      <c r="Q21" s="97">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="92" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
       </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="98" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
       </c>
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="98" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E22" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
 گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
@@ -2823,583 +3123,1223 @@
 گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
         </is>
       </c>
-      <c r="F22" s="45" t="inlineStr">
+      <c r="F22" s="101" t="inlineStr">
         <is>
           <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
         </is>
       </c>
-      <c r="G22" s="45" t="inlineStr">
+      <c r="G22" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H22" s="43" t="inlineStr">
+      <c r="H22" s="98" t="inlineStr">
         <is>
           <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
         </is>
       </c>
-      <c r="I22" s="43" t="inlineStr">
+      <c r="I22" s="98" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن با سبز ثابت</t>
         </is>
       </c>
-      <c r="J22" s="43" t="inlineStr">
+      <c r="J22" s="98" t="inlineStr">
         <is>
           <t>آمدن، ماندن و پاک‌شدن در همان حدود = قبول؛ پاک‌شدن زودتر یا نیامدن = رد</t>
         </is>
       </c>
-      <c r="K22" s="43" t="inlineStr"/>
-      <c r="L22" s="46" t="inlineStr">
+      <c r="K22" s="98" t="inlineStr"/>
+      <c r="L22" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="43" t="inlineStr"/>
-      <c r="N22" s="43" t="inlineStr"/>
-      <c r="O22" s="45" t="inlineStr"/>
-      <c r="P22" s="45" t="inlineStr"/>
-      <c r="Q22" s="47">
+      <c r="M22" s="98" t="inlineStr"/>
+      <c r="N22" s="98" t="inlineStr"/>
+      <c r="O22" s="101" t="inlineStr"/>
+      <c r="P22" s="101" t="inlineStr"/>
+      <c r="Q22" s="102">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="92" t="inlineStr">
         <is>
           <t>UI-022</t>
         </is>
       </c>
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="93" t="inlineStr">
         <is>
           <t>Snapshot invalid</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="48" t="inlineStr">
+      <c r="D23" s="93" t="inlineStr">
         <is>
           <t>دستگاه روشن و در حال کار عادی است</t>
         </is>
       </c>
-      <c r="E23" s="48" t="inlineStr">
+      <c r="E23" s="93" t="inlineStr">
         <is>
           <t>گام ۱: سیم حس‌کردن ولتاژ باتری را لحظه‌ای جدا کن (دستگاه اندازهٔ تازه ندارد).
 گام ۲: به چراغ‌ها و بوق نگاه کن؛ نباید الگوی دیوانه‌وار یا بوق بی‌دلیل بیاید.
 گام ۳: سیم را وصل کن؛ رفتار عادی باید برگردد.</t>
         </is>
       </c>
-      <c r="F23" s="50" t="inlineStr">
+      <c r="F23" s="95" t="inlineStr">
         <is>
           <t>قطع و وصل کوتاه سیم حس باتری</t>
         </is>
       </c>
-      <c r="G23" s="50" t="inlineStr">
+      <c r="G23" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H23" s="48" t="inlineStr">
+      <c r="H23" s="93" t="inlineStr">
         <is>
           <t>حین قطع، چهرهٔ سالم قبلی آرام می‌ماند و دستگاه هنگ نمی‌کند؛ با وصل مجدد همه‌چیز عادی می‌شود</t>
         </is>
       </c>
-      <c r="I23" s="48" t="inlineStr">
+      <c r="I23" s="93" t="inlineStr">
         <is>
           <t>بدون الگوی تازهٔ خطادار</t>
         </is>
       </c>
-      <c r="J23" s="48" t="inlineStr">
+      <c r="J23" s="93" t="inlineStr">
         <is>
           <t>آرام ماندن و برگشت عادی = قبول؛ هنگ، بوق بی‌دلیل یا چراغ قاطی = رد</t>
         </is>
       </c>
-      <c r="K23" s="48" t="inlineStr"/>
-      <c r="L23" s="46" t="inlineStr">
+      <c r="K23" s="93" t="inlineStr"/>
+      <c r="L23" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M23" s="48" t="inlineStr"/>
-      <c r="N23" s="48" t="inlineStr"/>
-      <c r="O23" s="50" t="inlineStr"/>
-      <c r="P23" s="50" t="inlineStr"/>
-      <c r="Q23" s="51">
+      <c r="M23" s="93" t="inlineStr"/>
+      <c r="N23" s="93" t="inlineStr"/>
+      <c r="O23" s="95" t="inlineStr"/>
+      <c r="P23" s="95" t="inlineStr"/>
+      <c r="Q23" s="97">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="92" t="inlineStr">
         <is>
           <t>UI-023</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="98" t="inlineStr">
         <is>
           <t>Low Alarm 21/21.2</t>
         </is>
       </c>
-      <c r="C24" s="44" t="inlineStr">
+      <c r="C24" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="98" t="inlineStr">
         <is>
           <t>دستگاه روی باتری کار می‌کند؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E24" s="43" t="inlineStr">
+      <c r="E24" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ باتری را آرام تا نزدیک مرز باتری کم (حدود ۲۱ ولت) پایین بیاور.
 گام ۲: کمی دور همان مرز بالا و پایینش کن و چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F24" s="45" t="inlineStr">
+      <c r="F24" s="101" t="inlineStr">
         <is>
           <t>باتری دور مرز ۲۱ ولت</t>
         </is>
       </c>
-      <c r="G24" s="45" t="inlineStr">
+      <c r="G24" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H24" s="43" t="inlineStr">
+      <c r="H24" s="98" t="inlineStr">
         <is>
           <t>چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود</t>
         </is>
       </c>
-      <c r="I24" s="43" t="inlineStr">
+      <c r="I24" s="98" t="inlineStr">
         <is>
           <t>پایدار، بدون فلیکر</t>
         </is>
       </c>
-      <c r="J24" s="43" t="inlineStr">
+      <c r="J24" s="98" t="inlineStr">
         <is>
           <t>بدون پرپر = قبول؛ رفت‌وبرگشت تند چراغ‌ها = رد</t>
         </is>
       </c>
-      <c r="K24" s="43" t="inlineStr"/>
-      <c r="L24" s="46" t="inlineStr">
+      <c r="K24" s="98" t="inlineStr"/>
+      <c r="L24" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M24" s="43" t="inlineStr"/>
-      <c r="N24" s="43" t="inlineStr"/>
-      <c r="O24" s="45" t="inlineStr"/>
-      <c r="P24" s="45" t="inlineStr"/>
-      <c r="Q24" s="47">
+      <c r="M24" s="98" t="inlineStr"/>
+      <c r="N24" s="98" t="inlineStr"/>
+      <c r="O24" s="101" t="inlineStr"/>
+      <c r="P24" s="101" t="inlineStr"/>
+      <c r="Q24" s="102">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="92" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="93" t="inlineStr">
         <is>
           <t>Input switch 20/21</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D25" s="48" t="inlineStr">
+      <c r="D25" s="93" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E25" s="48" t="inlineStr">
+      <c r="E25" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
 گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
         </is>
       </c>
-      <c r="F25" s="50" t="inlineStr">
+      <c r="F25" s="95" t="inlineStr">
         <is>
           <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
         </is>
       </c>
-      <c r="G25" s="50" t="inlineStr">
+      <c r="G25" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H25" s="48" t="inlineStr">
+      <c r="H25" s="93" t="inlineStr">
         <is>
           <t>وضعیت ورودی فقط وقتی واقعاً از مرز رد می‌شوی عوض می‌شود؛ وسط راه هیچ رفت‌وبرگشت بی‌دلیلی نیست</t>
         </is>
       </c>
-      <c r="I25" s="48" t="inlineStr">
+      <c r="I25" s="93" t="inlineStr">
         <is>
           <t>گذار تکی و تمیز</t>
         </is>
       </c>
-      <c r="J25" s="48" t="inlineStr">
+      <c r="J25" s="93" t="inlineStr">
         <is>
           <t>بدون رفت‌وبرگشت بی‌دلیل = قبول؛ فلیکر وسط راه = رد</t>
         </is>
       </c>
-      <c r="K25" s="48" t="inlineStr"/>
-      <c r="L25" s="46" t="inlineStr">
+      <c r="K25" s="93" t="inlineStr"/>
+      <c r="L25" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M25" s="48" t="inlineStr"/>
-      <c r="N25" s="48" t="inlineStr"/>
-      <c r="O25" s="50" t="inlineStr"/>
-      <c r="P25" s="50" t="inlineStr"/>
-      <c r="Q25" s="51">
+      <c r="M25" s="93" t="inlineStr"/>
+      <c r="N25" s="93" t="inlineStr"/>
+      <c r="O25" s="95" t="inlineStr"/>
+      <c r="P25" s="95" t="inlineStr"/>
+      <c r="Q25" s="97">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="92" t="inlineStr">
         <is>
           <t>UI-030</t>
         </is>
       </c>
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C26" s="50" t="inlineStr">
+      <c r="C26" s="95" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D26" s="93" t="inlineStr">
         <is>
           <t>پنل به دستگاه وصل و دستگاه در حال کار عادی است</t>
         </is>
       </c>
-      <c r="E26" s="48" t="inlineStr">
+      <c r="E26" s="93" t="inlineStr">
         <is>
           <t>گام ۱: در پنل یک پیام یا دیالوگ باز کن.
 گام ۲: هم‌زمان چراغ‌های دستگاه را نگاه کن.
 گام ۳: دیالوگ را ببند.</t>
         </is>
       </c>
-      <c r="F26" s="50" t="inlineStr">
+      <c r="F26" s="95" t="inlineStr">
         <is>
           <t>باز و بسته‌کردن دیالوگ پنل</t>
         </is>
       </c>
-      <c r="G26" s="50" t="inlineStr">
+      <c r="G26" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H26" s="48" t="inlineStr">
+      <c r="H26" s="93" t="inlineStr">
         <is>
           <t>دیالوگ پنل چراغ‌ها و بوق دستگاه را به هم نمی‌ریزد؛ رفتار عادی ادامه دارد</t>
         </is>
       </c>
-      <c r="I26" s="48" t="inlineStr">
+      <c r="I26" s="93" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="J26" s="48" t="inlineStr">
+      <c r="J26" s="93" t="inlineStr">
         <is>
           <t>استقلال کامل دیالوگ و چراغ‌ها = قبول؛ هر اثر متقابل = رد</t>
         </is>
       </c>
-      <c r="K26" s="48" t="n"/>
-      <c r="L26" s="55" t="inlineStr">
+      <c r="K26" s="93" t="n"/>
+      <c r="L26" s="104" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M26" s="48" t="n"/>
-      <c r="N26" s="48" t="n"/>
-      <c r="O26" s="50" t="inlineStr">
+      <c r="M26" s="93" t="n"/>
+      <c r="N26" s="93" t="n"/>
+      <c r="O26" s="95" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P26" s="50" t="n"/>
-      <c r="Q26" s="51" t="inlineStr">
+      <c r="P26" s="95" t="n"/>
+      <c r="Q26" s="97" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="Q27" s="56">
+      <c r="A27" s="80" t="n"/>
+      <c r="B27" s="80" t="n"/>
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="80" t="n"/>
+      <c r="E27" s="80" t="n"/>
+      <c r="F27" s="80" t="n"/>
+      <c r="G27" s="80" t="n"/>
+      <c r="H27" s="80" t="n"/>
+      <c r="I27" s="80" t="n"/>
+      <c r="J27" s="80" t="n"/>
+      <c r="K27" s="80" t="n"/>
+      <c r="L27" s="80" t="n"/>
+      <c r="M27" s="80" t="n"/>
+      <c r="N27" s="80" t="n"/>
+      <c r="O27" s="80" t="n"/>
+      <c r="P27" s="80" t="n"/>
+      <c r="Q27" s="105">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="54" customHeight="1">
-      <c r="Q28" s="56">
+      <c r="A28" s="80" t="n"/>
+      <c r="B28" s="80" t="n"/>
+      <c r="C28" s="80" t="n"/>
+      <c r="D28" s="80" t="n"/>
+      <c r="E28" s="80" t="n"/>
+      <c r="F28" s="80" t="n"/>
+      <c r="G28" s="80" t="n"/>
+      <c r="H28" s="80" t="n"/>
+      <c r="I28" s="80" t="n"/>
+      <c r="J28" s="80" t="n"/>
+      <c r="K28" s="80" t="n"/>
+      <c r="L28" s="80" t="n"/>
+      <c r="M28" s="80" t="n"/>
+      <c r="N28" s="80" t="n"/>
+      <c r="O28" s="80" t="n"/>
+      <c r="P28" s="80" t="n"/>
+      <c r="Q28" s="105">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="54" customHeight="1">
-      <c r="Q29" s="56">
+      <c r="A29" s="80" t="n"/>
+      <c r="B29" s="80" t="n"/>
+      <c r="C29" s="80" t="n"/>
+      <c r="D29" s="80" t="n"/>
+      <c r="E29" s="80" t="n"/>
+      <c r="F29" s="80" t="n"/>
+      <c r="G29" s="80" t="n"/>
+      <c r="H29" s="80" t="n"/>
+      <c r="I29" s="80" t="n"/>
+      <c r="J29" s="80" t="n"/>
+      <c r="K29" s="80" t="n"/>
+      <c r="L29" s="80" t="n"/>
+      <c r="M29" s="80" t="n"/>
+      <c r="N29" s="80" t="n"/>
+      <c r="O29" s="80" t="n"/>
+      <c r="P29" s="80" t="n"/>
+      <c r="Q29" s="105">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="54" customHeight="1">
-      <c r="Q30" s="56">
+      <c r="A30" s="80" t="n"/>
+      <c r="B30" s="80" t="n"/>
+      <c r="C30" s="80" t="n"/>
+      <c r="D30" s="80" t="n"/>
+      <c r="E30" s="80" t="n"/>
+      <c r="F30" s="80" t="n"/>
+      <c r="G30" s="80" t="n"/>
+      <c r="H30" s="80" t="n"/>
+      <c r="I30" s="80" t="n"/>
+      <c r="J30" s="80" t="n"/>
+      <c r="K30" s="80" t="n"/>
+      <c r="L30" s="80" t="n"/>
+      <c r="M30" s="80" t="n"/>
+      <c r="N30" s="80" t="n"/>
+      <c r="O30" s="80" t="n"/>
+      <c r="P30" s="80" t="n"/>
+      <c r="Q30" s="105">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="40.5" customHeight="1">
-      <c r="Q31" s="56">
+      <c r="A31" s="80" t="n"/>
+      <c r="B31" s="80" t="n"/>
+      <c r="C31" s="80" t="n"/>
+      <c r="D31" s="80" t="n"/>
+      <c r="E31" s="80" t="n"/>
+      <c r="F31" s="80" t="n"/>
+      <c r="G31" s="80" t="n"/>
+      <c r="H31" s="80" t="n"/>
+      <c r="I31" s="80" t="n"/>
+      <c r="J31" s="80" t="n"/>
+      <c r="K31" s="80" t="n"/>
+      <c r="L31" s="80" t="n"/>
+      <c r="M31" s="80" t="n"/>
+      <c r="N31" s="80" t="n"/>
+      <c r="O31" s="80" t="n"/>
+      <c r="P31" s="80" t="n"/>
+      <c r="Q31" s="105">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="54" customHeight="1">
-      <c r="Q32" s="56">
+      <c r="A32" s="80" t="n"/>
+      <c r="B32" s="80" t="n"/>
+      <c r="C32" s="80" t="n"/>
+      <c r="D32" s="80" t="n"/>
+      <c r="E32" s="80" t="n"/>
+      <c r="F32" s="80" t="n"/>
+      <c r="G32" s="80" t="n"/>
+      <c r="H32" s="80" t="n"/>
+      <c r="I32" s="80" t="n"/>
+      <c r="J32" s="80" t="n"/>
+      <c r="K32" s="80" t="n"/>
+      <c r="L32" s="80" t="n"/>
+      <c r="M32" s="80" t="n"/>
+      <c r="N32" s="80" t="n"/>
+      <c r="O32" s="80" t="n"/>
+      <c r="P32" s="80" t="n"/>
+      <c r="Q32" s="105">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="40.5" customHeight="1">
-      <c r="Q33" s="56">
+      <c r="A33" s="80" t="n"/>
+      <c r="B33" s="80" t="n"/>
+      <c r="C33" s="80" t="n"/>
+      <c r="D33" s="80" t="n"/>
+      <c r="E33" s="80" t="n"/>
+      <c r="F33" s="80" t="n"/>
+      <c r="G33" s="80" t="n"/>
+      <c r="H33" s="80" t="n"/>
+      <c r="I33" s="80" t="n"/>
+      <c r="J33" s="80" t="n"/>
+      <c r="K33" s="80" t="n"/>
+      <c r="L33" s="80" t="n"/>
+      <c r="M33" s="80" t="n"/>
+      <c r="N33" s="80" t="n"/>
+      <c r="O33" s="80" t="n"/>
+      <c r="P33" s="80" t="n"/>
+      <c r="Q33" s="105">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="40.5" customHeight="1">
-      <c r="Q34" s="56">
+      <c r="A34" s="80" t="n"/>
+      <c r="B34" s="80" t="n"/>
+      <c r="C34" s="80" t="n"/>
+      <c r="D34" s="80" t="n"/>
+      <c r="E34" s="80" t="n"/>
+      <c r="F34" s="80" t="n"/>
+      <c r="G34" s="80" t="n"/>
+      <c r="H34" s="80" t="n"/>
+      <c r="I34" s="80" t="n"/>
+      <c r="J34" s="80" t="n"/>
+      <c r="K34" s="80" t="n"/>
+      <c r="L34" s="80" t="n"/>
+      <c r="M34" s="80" t="n"/>
+      <c r="N34" s="80" t="n"/>
+      <c r="O34" s="80" t="n"/>
+      <c r="P34" s="80" t="n"/>
+      <c r="Q34" s="105">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="56">
+      <c r="A35" s="80" t="n"/>
+      <c r="B35" s="80" t="n"/>
+      <c r="C35" s="80" t="n"/>
+      <c r="D35" s="80" t="n"/>
+      <c r="E35" s="80" t="n"/>
+      <c r="F35" s="80" t="n"/>
+      <c r="G35" s="80" t="n"/>
+      <c r="H35" s="80" t="n"/>
+      <c r="I35" s="80" t="n"/>
+      <c r="J35" s="80" t="n"/>
+      <c r="K35" s="80" t="n"/>
+      <c r="L35" s="80" t="n"/>
+      <c r="M35" s="80" t="n"/>
+      <c r="N35" s="80" t="n"/>
+      <c r="O35" s="80" t="n"/>
+      <c r="P35" s="80" t="n"/>
+      <c r="Q35" s="105">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="56">
+      <c r="A36" s="80" t="n"/>
+      <c r="B36" s="80" t="n"/>
+      <c r="C36" s="80" t="n"/>
+      <c r="D36" s="80" t="n"/>
+      <c r="E36" s="80" t="n"/>
+      <c r="F36" s="80" t="n"/>
+      <c r="G36" s="80" t="n"/>
+      <c r="H36" s="80" t="n"/>
+      <c r="I36" s="80" t="n"/>
+      <c r="J36" s="80" t="n"/>
+      <c r="K36" s="80" t="n"/>
+      <c r="L36" s="80" t="n"/>
+      <c r="M36" s="80" t="n"/>
+      <c r="N36" s="80" t="n"/>
+      <c r="O36" s="80" t="n"/>
+      <c r="P36" s="80" t="n"/>
+      <c r="Q36" s="105">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="56">
+      <c r="A37" s="80" t="n"/>
+      <c r="B37" s="80" t="n"/>
+      <c r="C37" s="80" t="n"/>
+      <c r="D37" s="80" t="n"/>
+      <c r="E37" s="80" t="n"/>
+      <c r="F37" s="80" t="n"/>
+      <c r="G37" s="80" t="n"/>
+      <c r="H37" s="80" t="n"/>
+      <c r="I37" s="80" t="n"/>
+      <c r="J37" s="80" t="n"/>
+      <c r="K37" s="80" t="n"/>
+      <c r="L37" s="80" t="n"/>
+      <c r="M37" s="80" t="n"/>
+      <c r="N37" s="80" t="n"/>
+      <c r="O37" s="80" t="n"/>
+      <c r="P37" s="80" t="n"/>
+      <c r="Q37" s="105">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="56">
+      <c r="A38" s="80" t="n"/>
+      <c r="B38" s="80" t="n"/>
+      <c r="C38" s="80" t="n"/>
+      <c r="D38" s="80" t="n"/>
+      <c r="E38" s="80" t="n"/>
+      <c r="F38" s="80" t="n"/>
+      <c r="G38" s="80" t="n"/>
+      <c r="H38" s="80" t="n"/>
+      <c r="I38" s="80" t="n"/>
+      <c r="J38" s="80" t="n"/>
+      <c r="K38" s="80" t="n"/>
+      <c r="L38" s="80" t="n"/>
+      <c r="M38" s="80" t="n"/>
+      <c r="N38" s="80" t="n"/>
+      <c r="O38" s="80" t="n"/>
+      <c r="P38" s="80" t="n"/>
+      <c r="Q38" s="105">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="56">
+      <c r="A39" s="80" t="n"/>
+      <c r="B39" s="80" t="n"/>
+      <c r="C39" s="80" t="n"/>
+      <c r="D39" s="80" t="n"/>
+      <c r="E39" s="80" t="n"/>
+      <c r="F39" s="80" t="n"/>
+      <c r="G39" s="80" t="n"/>
+      <c r="H39" s="80" t="n"/>
+      <c r="I39" s="80" t="n"/>
+      <c r="J39" s="80" t="n"/>
+      <c r="K39" s="80" t="n"/>
+      <c r="L39" s="80" t="n"/>
+      <c r="M39" s="80" t="n"/>
+      <c r="N39" s="80" t="n"/>
+      <c r="O39" s="80" t="n"/>
+      <c r="P39" s="80" t="n"/>
+      <c r="Q39" s="105">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="56">
+      <c r="A40" s="80" t="n"/>
+      <c r="B40" s="80" t="n"/>
+      <c r="C40" s="80" t="n"/>
+      <c r="D40" s="80" t="n"/>
+      <c r="E40" s="80" t="n"/>
+      <c r="F40" s="80" t="n"/>
+      <c r="G40" s="80" t="n"/>
+      <c r="H40" s="80" t="n"/>
+      <c r="I40" s="80" t="n"/>
+      <c r="J40" s="80" t="n"/>
+      <c r="K40" s="80" t="n"/>
+      <c r="L40" s="80" t="n"/>
+      <c r="M40" s="80" t="n"/>
+      <c r="N40" s="80" t="n"/>
+      <c r="O40" s="80" t="n"/>
+      <c r="P40" s="80" t="n"/>
+      <c r="Q40" s="105">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="56">
+      <c r="A41" s="80" t="n"/>
+      <c r="B41" s="80" t="n"/>
+      <c r="C41" s="80" t="n"/>
+      <c r="D41" s="80" t="n"/>
+      <c r="E41" s="80" t="n"/>
+      <c r="F41" s="80" t="n"/>
+      <c r="G41" s="80" t="n"/>
+      <c r="H41" s="80" t="n"/>
+      <c r="I41" s="80" t="n"/>
+      <c r="J41" s="80" t="n"/>
+      <c r="K41" s="80" t="n"/>
+      <c r="L41" s="80" t="n"/>
+      <c r="M41" s="80" t="n"/>
+      <c r="N41" s="80" t="n"/>
+      <c r="O41" s="80" t="n"/>
+      <c r="P41" s="80" t="n"/>
+      <c r="Q41" s="105">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="56">
+      <c r="A42" s="80" t="n"/>
+      <c r="B42" s="80" t="n"/>
+      <c r="C42" s="80" t="n"/>
+      <c r="D42" s="80" t="n"/>
+      <c r="E42" s="80" t="n"/>
+      <c r="F42" s="80" t="n"/>
+      <c r="G42" s="80" t="n"/>
+      <c r="H42" s="80" t="n"/>
+      <c r="I42" s="80" t="n"/>
+      <c r="J42" s="80" t="n"/>
+      <c r="K42" s="80" t="n"/>
+      <c r="L42" s="80" t="n"/>
+      <c r="M42" s="80" t="n"/>
+      <c r="N42" s="80" t="n"/>
+      <c r="O42" s="80" t="n"/>
+      <c r="P42" s="80" t="n"/>
+      <c r="Q42" s="105">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="56">
+      <c r="A43" s="80" t="n"/>
+      <c r="B43" s="80" t="n"/>
+      <c r="C43" s="80" t="n"/>
+      <c r="D43" s="80" t="n"/>
+      <c r="E43" s="80" t="n"/>
+      <c r="F43" s="80" t="n"/>
+      <c r="G43" s="80" t="n"/>
+      <c r="H43" s="80" t="n"/>
+      <c r="I43" s="80" t="n"/>
+      <c r="J43" s="80" t="n"/>
+      <c r="K43" s="80" t="n"/>
+      <c r="L43" s="80" t="n"/>
+      <c r="M43" s="80" t="n"/>
+      <c r="N43" s="80" t="n"/>
+      <c r="O43" s="80" t="n"/>
+      <c r="P43" s="80" t="n"/>
+      <c r="Q43" s="105">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="56">
+      <c r="A44" s="80" t="n"/>
+      <c r="B44" s="80" t="n"/>
+      <c r="C44" s="80" t="n"/>
+      <c r="D44" s="80" t="n"/>
+      <c r="E44" s="80" t="n"/>
+      <c r="F44" s="80" t="n"/>
+      <c r="G44" s="80" t="n"/>
+      <c r="H44" s="80" t="n"/>
+      <c r="I44" s="80" t="n"/>
+      <c r="J44" s="80" t="n"/>
+      <c r="K44" s="80" t="n"/>
+      <c r="L44" s="80" t="n"/>
+      <c r="M44" s="80" t="n"/>
+      <c r="N44" s="80" t="n"/>
+      <c r="O44" s="80" t="n"/>
+      <c r="P44" s="80" t="n"/>
+      <c r="Q44" s="105">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="56">
+      <c r="A45" s="80" t="n"/>
+      <c r="B45" s="80" t="n"/>
+      <c r="C45" s="80" t="n"/>
+      <c r="D45" s="80" t="n"/>
+      <c r="E45" s="80" t="n"/>
+      <c r="F45" s="80" t="n"/>
+      <c r="G45" s="80" t="n"/>
+      <c r="H45" s="80" t="n"/>
+      <c r="I45" s="80" t="n"/>
+      <c r="J45" s="80" t="n"/>
+      <c r="K45" s="80" t="n"/>
+      <c r="L45" s="80" t="n"/>
+      <c r="M45" s="80" t="n"/>
+      <c r="N45" s="80" t="n"/>
+      <c r="O45" s="80" t="n"/>
+      <c r="P45" s="80" t="n"/>
+      <c r="Q45" s="105">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="56">
+      <c r="A46" s="80" t="n"/>
+      <c r="B46" s="80" t="n"/>
+      <c r="C46" s="80" t="n"/>
+      <c r="D46" s="80" t="n"/>
+      <c r="E46" s="80" t="n"/>
+      <c r="F46" s="80" t="n"/>
+      <c r="G46" s="80" t="n"/>
+      <c r="H46" s="80" t="n"/>
+      <c r="I46" s="80" t="n"/>
+      <c r="J46" s="80" t="n"/>
+      <c r="K46" s="80" t="n"/>
+      <c r="L46" s="80" t="n"/>
+      <c r="M46" s="80" t="n"/>
+      <c r="N46" s="80" t="n"/>
+      <c r="O46" s="80" t="n"/>
+      <c r="P46" s="80" t="n"/>
+      <c r="Q46" s="105">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="56">
+      <c r="A47" s="80" t="n"/>
+      <c r="B47" s="80" t="n"/>
+      <c r="C47" s="80" t="n"/>
+      <c r="D47" s="80" t="n"/>
+      <c r="E47" s="80" t="n"/>
+      <c r="F47" s="80" t="n"/>
+      <c r="G47" s="80" t="n"/>
+      <c r="H47" s="80" t="n"/>
+      <c r="I47" s="80" t="n"/>
+      <c r="J47" s="80" t="n"/>
+      <c r="K47" s="80" t="n"/>
+      <c r="L47" s="80" t="n"/>
+      <c r="M47" s="80" t="n"/>
+      <c r="N47" s="80" t="n"/>
+      <c r="O47" s="80" t="n"/>
+      <c r="P47" s="80" t="n"/>
+      <c r="Q47" s="105">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="56">
+      <c r="A48" s="80" t="n"/>
+      <c r="B48" s="80" t="n"/>
+      <c r="C48" s="80" t="n"/>
+      <c r="D48" s="80" t="n"/>
+      <c r="E48" s="80" t="n"/>
+      <c r="F48" s="80" t="n"/>
+      <c r="G48" s="80" t="n"/>
+      <c r="H48" s="80" t="n"/>
+      <c r="I48" s="80" t="n"/>
+      <c r="J48" s="80" t="n"/>
+      <c r="K48" s="80" t="n"/>
+      <c r="L48" s="80" t="n"/>
+      <c r="M48" s="80" t="n"/>
+      <c r="N48" s="80" t="n"/>
+      <c r="O48" s="80" t="n"/>
+      <c r="P48" s="80" t="n"/>
+      <c r="Q48" s="105">
         <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="56">
+      <c r="A49" s="80" t="n"/>
+      <c r="B49" s="80" t="n"/>
+      <c r="C49" s="80" t="n"/>
+      <c r="D49" s="80" t="n"/>
+      <c r="E49" s="80" t="n"/>
+      <c r="F49" s="80" t="n"/>
+      <c r="G49" s="80" t="n"/>
+      <c r="H49" s="80" t="n"/>
+      <c r="I49" s="80" t="n"/>
+      <c r="J49" s="80" t="n"/>
+      <c r="K49" s="80" t="n"/>
+      <c r="L49" s="80" t="n"/>
+      <c r="M49" s="80" t="n"/>
+      <c r="N49" s="80" t="n"/>
+      <c r="O49" s="80" t="n"/>
+      <c r="P49" s="80" t="n"/>
+      <c r="Q49" s="105">
         <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="56">
+      <c r="A50" s="80" t="n"/>
+      <c r="B50" s="80" t="n"/>
+      <c r="C50" s="80" t="n"/>
+      <c r="D50" s="80" t="n"/>
+      <c r="E50" s="80" t="n"/>
+      <c r="F50" s="80" t="n"/>
+      <c r="G50" s="80" t="n"/>
+      <c r="H50" s="80" t="n"/>
+      <c r="I50" s="80" t="n"/>
+      <c r="J50" s="80" t="n"/>
+      <c r="K50" s="80" t="n"/>
+      <c r="L50" s="80" t="n"/>
+      <c r="M50" s="80" t="n"/>
+      <c r="N50" s="80" t="n"/>
+      <c r="O50" s="80" t="n"/>
+      <c r="P50" s="80" t="n"/>
+      <c r="Q50" s="105">
         <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="56">
+      <c r="A51" s="80" t="n"/>
+      <c r="B51" s="80" t="n"/>
+      <c r="C51" s="80" t="n"/>
+      <c r="D51" s="80" t="n"/>
+      <c r="E51" s="80" t="n"/>
+      <c r="F51" s="80" t="n"/>
+      <c r="G51" s="80" t="n"/>
+      <c r="H51" s="80" t="n"/>
+      <c r="I51" s="80" t="n"/>
+      <c r="J51" s="80" t="n"/>
+      <c r="K51" s="80" t="n"/>
+      <c r="L51" s="80" t="n"/>
+      <c r="M51" s="80" t="n"/>
+      <c r="N51" s="80" t="n"/>
+      <c r="O51" s="80" t="n"/>
+      <c r="P51" s="80" t="n"/>
+      <c r="Q51" s="105">
         <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="56">
+      <c r="A52" s="80" t="n"/>
+      <c r="B52" s="80" t="n"/>
+      <c r="C52" s="80" t="n"/>
+      <c r="D52" s="80" t="n"/>
+      <c r="E52" s="80" t="n"/>
+      <c r="F52" s="80" t="n"/>
+      <c r="G52" s="80" t="n"/>
+      <c r="H52" s="80" t="n"/>
+      <c r="I52" s="80" t="n"/>
+      <c r="J52" s="80" t="n"/>
+      <c r="K52" s="80" t="n"/>
+      <c r="L52" s="80" t="n"/>
+      <c r="M52" s="80" t="n"/>
+      <c r="N52" s="80" t="n"/>
+      <c r="O52" s="80" t="n"/>
+      <c r="P52" s="80" t="n"/>
+      <c r="Q52" s="105">
         <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="Q53" s="56">
+      <c r="A53" s="80" t="n"/>
+      <c r="B53" s="80" t="n"/>
+      <c r="C53" s="80" t="n"/>
+      <c r="D53" s="80" t="n"/>
+      <c r="E53" s="80" t="n"/>
+      <c r="F53" s="80" t="n"/>
+      <c r="G53" s="80" t="n"/>
+      <c r="H53" s="80" t="n"/>
+      <c r="I53" s="80" t="n"/>
+      <c r="J53" s="80" t="n"/>
+      <c r="K53" s="80" t="n"/>
+      <c r="L53" s="80" t="n"/>
+      <c r="M53" s="80" t="n"/>
+      <c r="N53" s="80" t="n"/>
+      <c r="O53" s="80" t="n"/>
+      <c r="P53" s="80" t="n"/>
+      <c r="Q53" s="105">
         <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="Q54" s="56">
+      <c r="A54" s="80" t="n"/>
+      <c r="B54" s="80" t="n"/>
+      <c r="C54" s="80" t="n"/>
+      <c r="D54" s="80" t="n"/>
+      <c r="E54" s="80" t="n"/>
+      <c r="F54" s="80" t="n"/>
+      <c r="G54" s="80" t="n"/>
+      <c r="H54" s="80" t="n"/>
+      <c r="I54" s="80" t="n"/>
+      <c r="J54" s="80" t="n"/>
+      <c r="K54" s="80" t="n"/>
+      <c r="L54" s="80" t="n"/>
+      <c r="M54" s="80" t="n"/>
+      <c r="N54" s="80" t="n"/>
+      <c r="O54" s="80" t="n"/>
+      <c r="P54" s="80" t="n"/>
+      <c r="Q54" s="105">
         <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="Q55" s="56">
+      <c r="A55" s="80" t="n"/>
+      <c r="B55" s="80" t="n"/>
+      <c r="C55" s="80" t="n"/>
+      <c r="D55" s="80" t="n"/>
+      <c r="E55" s="80" t="n"/>
+      <c r="F55" s="80" t="n"/>
+      <c r="G55" s="80" t="n"/>
+      <c r="H55" s="80" t="n"/>
+      <c r="I55" s="80" t="n"/>
+      <c r="J55" s="80" t="n"/>
+      <c r="K55" s="80" t="n"/>
+      <c r="L55" s="80" t="n"/>
+      <c r="M55" s="80" t="n"/>
+      <c r="N55" s="80" t="n"/>
+      <c r="O55" s="80" t="n"/>
+      <c r="P55" s="80" t="n"/>
+      <c r="Q55" s="105">
         <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="Q56" s="56">
+      <c r="A56" s="80" t="n"/>
+      <c r="B56" s="80" t="n"/>
+      <c r="C56" s="80" t="n"/>
+      <c r="D56" s="80" t="n"/>
+      <c r="E56" s="80" t="n"/>
+      <c r="F56" s="80" t="n"/>
+      <c r="G56" s="80" t="n"/>
+      <c r="H56" s="80" t="n"/>
+      <c r="I56" s="80" t="n"/>
+      <c r="J56" s="80" t="n"/>
+      <c r="K56" s="80" t="n"/>
+      <c r="L56" s="80" t="n"/>
+      <c r="M56" s="80" t="n"/>
+      <c r="N56" s="80" t="n"/>
+      <c r="O56" s="80" t="n"/>
+      <c r="P56" s="80" t="n"/>
+      <c r="Q56" s="105">
         <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="Q57" s="56">
+      <c r="A57" s="80" t="n"/>
+      <c r="B57" s="80" t="n"/>
+      <c r="C57" s="80" t="n"/>
+      <c r="D57" s="80" t="n"/>
+      <c r="E57" s="80" t="n"/>
+      <c r="F57" s="80" t="n"/>
+      <c r="G57" s="80" t="n"/>
+      <c r="H57" s="80" t="n"/>
+      <c r="I57" s="80" t="n"/>
+      <c r="J57" s="80" t="n"/>
+      <c r="K57" s="80" t="n"/>
+      <c r="L57" s="80" t="n"/>
+      <c r="M57" s="80" t="n"/>
+      <c r="N57" s="80" t="n"/>
+      <c r="O57" s="80" t="n"/>
+      <c r="P57" s="80" t="n"/>
+      <c r="Q57" s="105">
         <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="Q58" s="56">
+      <c r="A58" s="80" t="n"/>
+      <c r="B58" s="80" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
+      <c r="Q58" s="105">
         <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="Q59" s="56">
+      <c r="A59" s="80" t="n"/>
+      <c r="B59" s="80" t="n"/>
+      <c r="C59" s="80" t="n"/>
+      <c r="D59" s="80" t="n"/>
+      <c r="E59" s="80" t="n"/>
+      <c r="F59" s="80" t="n"/>
+      <c r="G59" s="80" t="n"/>
+      <c r="H59" s="80" t="n"/>
+      <c r="I59" s="80" t="n"/>
+      <c r="J59" s="80" t="n"/>
+      <c r="K59" s="80" t="n"/>
+      <c r="L59" s="80" t="n"/>
+      <c r="M59" s="80" t="n"/>
+      <c r="N59" s="80" t="n"/>
+      <c r="O59" s="80" t="n"/>
+      <c r="P59" s="80" t="n"/>
+      <c r="Q59" s="105">
         <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="Q60" s="56">
+      <c r="A60" s="80" t="n"/>
+      <c r="B60" s="80" t="n"/>
+      <c r="C60" s="80" t="n"/>
+      <c r="D60" s="80" t="n"/>
+      <c r="E60" s="80" t="n"/>
+      <c r="F60" s="80" t="n"/>
+      <c r="G60" s="80" t="n"/>
+      <c r="H60" s="80" t="n"/>
+      <c r="I60" s="80" t="n"/>
+      <c r="J60" s="80" t="n"/>
+      <c r="K60" s="80" t="n"/>
+      <c r="L60" s="80" t="n"/>
+      <c r="M60" s="80" t="n"/>
+      <c r="N60" s="80" t="n"/>
+      <c r="O60" s="80" t="n"/>
+      <c r="P60" s="80" t="n"/>
+      <c r="Q60" s="105">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="Q61" s="56">
+      <c r="A61" s="80" t="n"/>
+      <c r="B61" s="80" t="n"/>
+      <c r="C61" s="80" t="n"/>
+      <c r="D61" s="80" t="n"/>
+      <c r="E61" s="80" t="n"/>
+      <c r="F61" s="80" t="n"/>
+      <c r="G61" s="80" t="n"/>
+      <c r="H61" s="80" t="n"/>
+      <c r="I61" s="80" t="n"/>
+      <c r="J61" s="80" t="n"/>
+      <c r="K61" s="80" t="n"/>
+      <c r="L61" s="80" t="n"/>
+      <c r="M61" s="80" t="n"/>
+      <c r="N61" s="80" t="n"/>
+      <c r="O61" s="80" t="n"/>
+      <c r="P61" s="80" t="n"/>
+      <c r="Q61" s="105">
         <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="Q62" s="56">
+      <c r="A62" s="80" t="n"/>
+      <c r="B62" s="80" t="n"/>
+      <c r="C62" s="80" t="n"/>
+      <c r="D62" s="80" t="n"/>
+      <c r="E62" s="80" t="n"/>
+      <c r="F62" s="80" t="n"/>
+      <c r="G62" s="80" t="n"/>
+      <c r="H62" s="80" t="n"/>
+      <c r="I62" s="80" t="n"/>
+      <c r="J62" s="80" t="n"/>
+      <c r="K62" s="80" t="n"/>
+      <c r="L62" s="80" t="n"/>
+      <c r="M62" s="80" t="n"/>
+      <c r="N62" s="80" t="n"/>
+      <c r="O62" s="80" t="n"/>
+      <c r="P62" s="80" t="n"/>
+      <c r="Q62" s="105">
         <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="Q63" s="56">
+      <c r="A63" s="80" t="n"/>
+      <c r="B63" s="80" t="n"/>
+      <c r="C63" s="80" t="n"/>
+      <c r="D63" s="80" t="n"/>
+      <c r="E63" s="80" t="n"/>
+      <c r="F63" s="80" t="n"/>
+      <c r="G63" s="80" t="n"/>
+      <c r="H63" s="80" t="n"/>
+      <c r="I63" s="80" t="n"/>
+      <c r="J63" s="80" t="n"/>
+      <c r="K63" s="80" t="n"/>
+      <c r="L63" s="80" t="n"/>
+      <c r="M63" s="80" t="n"/>
+      <c r="N63" s="80" t="n"/>
+      <c r="O63" s="80" t="n"/>
+      <c r="P63" s="80" t="n"/>
+      <c r="Q63" s="105">
         <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="Q64" s="56">
+      <c r="A64" s="80" t="n"/>
+      <c r="B64" s="80" t="n"/>
+      <c r="C64" s="80" t="n"/>
+      <c r="D64" s="80" t="n"/>
+      <c r="E64" s="80" t="n"/>
+      <c r="F64" s="80" t="n"/>
+      <c r="G64" s="80" t="n"/>
+      <c r="H64" s="80" t="n"/>
+      <c r="I64" s="80" t="n"/>
+      <c r="J64" s="80" t="n"/>
+      <c r="K64" s="80" t="n"/>
+      <c r="L64" s="80" t="n"/>
+      <c r="M64" s="80" t="n"/>
+      <c r="N64" s="80" t="n"/>
+      <c r="O64" s="80" t="n"/>
+      <c r="P64" s="80" t="n"/>
+      <c r="Q64" s="105">
         <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="Q65" s="56">
+      <c r="A65" s="80" t="n"/>
+      <c r="B65" s="80" t="n"/>
+      <c r="C65" s="80" t="n"/>
+      <c r="D65" s="80" t="n"/>
+      <c r="E65" s="80" t="n"/>
+      <c r="F65" s="80" t="n"/>
+      <c r="G65" s="80" t="n"/>
+      <c r="H65" s="80" t="n"/>
+      <c r="I65" s="80" t="n"/>
+      <c r="J65" s="80" t="n"/>
+      <c r="K65" s="80" t="n"/>
+      <c r="L65" s="80" t="n"/>
+      <c r="M65" s="80" t="n"/>
+      <c r="N65" s="80" t="n"/>
+      <c r="O65" s="80" t="n"/>
+      <c r="P65" s="80" t="n"/>
+      <c r="Q65" s="105">
         <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="Q66" s="56">
+      <c r="A66" s="80" t="n"/>
+      <c r="B66" s="80" t="n"/>
+      <c r="C66" s="80" t="n"/>
+      <c r="D66" s="80" t="n"/>
+      <c r="E66" s="80" t="n"/>
+      <c r="F66" s="80" t="n"/>
+      <c r="G66" s="80" t="n"/>
+      <c r="H66" s="80" t="n"/>
+      <c r="I66" s="80" t="n"/>
+      <c r="J66" s="80" t="n"/>
+      <c r="K66" s="80" t="n"/>
+      <c r="L66" s="80" t="n"/>
+      <c r="M66" s="80" t="n"/>
+      <c r="N66" s="80" t="n"/>
+      <c r="O66" s="80" t="n"/>
+      <c r="P66" s="80" t="n"/>
+      <c r="Q66" s="105">
         <f>IF(OR(L74="",L74="در انتظار"),"",IF(Q74="",TODAY(),Q74))</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="54" customHeight="1">
-      <c r="A67" s="42" t="inlineStr">
+      <c r="A67" s="92" t="inlineStr">
         <is>
           <t>UI-031</t>
         </is>
       </c>
-      <c r="B67" s="43" t="inlineStr">
+      <c r="B67" s="98" t="inlineStr">
         <is>
           <t>عملکرد واقعی درصد</t>
         </is>
       </c>
-      <c r="C67" s="45" t="inlineStr">
+      <c r="C67" s="101" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D67" s="43" t="inlineStr">
+      <c r="D67" s="98" t="inlineStr">
         <is>
           <t>دستگاه روی باتری در حال کار، درصد شارژ معلوم</t>
         </is>
       </c>
-      <c r="E67" s="43" t="inlineStr">
+      <c r="E67" s="98" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روی باتری روشن کن تا درصد شارژ و چشمک سبز معلوم باشد.
 گام ۲: فقط ولتاژ ورودی را بالا و پایین کن (به باتری دست نزن).
@@ -3407,68 +4347,68 @@
 گام ۴: حالا فقط ولتاژ باتری را عوض کن؛ درصد باید عوض شود.</t>
         </is>
       </c>
-      <c r="F67" s="43" t="inlineStr">
+      <c r="F67" s="98" t="inlineStr">
         <is>
           <t>تغییر جدا جدا ورودی و باتری</t>
         </is>
       </c>
-      <c r="G67" s="45" t="inlineStr">
+      <c r="G67" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H67" s="43" t="inlineStr">
+      <c r="H67" s="98" t="inlineStr">
         <is>
           <t>درصد فقط از باتری می‌آید، نه از ورودی</t>
         </is>
       </c>
-      <c r="I67" s="43" t="inlineStr">
+      <c r="I67" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J67" s="43" t="inlineStr">
+      <c r="J67" s="98" t="inlineStr">
         <is>
           <t>با ورودی ثابت بماند و با باتری عوض شود</t>
         </is>
       </c>
-      <c r="K67" s="43" t="inlineStr"/>
-      <c r="L67" s="46" t="inlineStr">
+      <c r="K67" s="98" t="inlineStr"/>
+      <c r="L67" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M67" s="43" t="n"/>
-      <c r="N67" s="43" t="n"/>
-      <c r="O67" s="45" t="n"/>
-      <c r="P67" s="45" t="n"/>
-      <c r="Q67" s="47">
+      <c r="M67" s="98" t="n"/>
+      <c r="N67" s="98" t="n"/>
+      <c r="O67" s="101" t="n"/>
+      <c r="P67" s="101" t="n"/>
+      <c r="Q67" s="102">
         <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="42" t="inlineStr">
+      <c r="A68" s="92" t="inlineStr">
         <is>
           <t>UI-032</t>
         </is>
       </c>
-      <c r="B68" s="43" t="inlineStr">
+      <c r="B68" s="98" t="inlineStr">
         <is>
           <t>خطای ۶: قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="C68" s="45" t="inlineStr">
+      <c r="C68" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D68" s="43" t="inlineStr">
+      <c r="D68" s="98" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
         </is>
       </c>
-      <c r="E68" s="43" t="inlineStr">
+      <c r="E68" s="98" t="inlineStr">
         <is>
           <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
 گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
@@ -3476,68 +4416,68 @@
 گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
         </is>
       </c>
-      <c r="F68" s="43" t="inlineStr">
+      <c r="F68" s="98" t="inlineStr">
         <is>
           <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G68" s="45" t="inlineStr">
+      <c r="G68" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H68" s="43" t="inlineStr">
+      <c r="H68" s="98" t="inlineStr">
         <is>
           <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
         </is>
       </c>
-      <c r="I68" s="43" t="inlineStr">
+      <c r="I68" s="98" t="inlineStr">
         <is>
           <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
         </is>
       </c>
-      <c r="J68" s="43" t="inlineStr">
+      <c r="J68" s="98" t="inlineStr">
         <is>
           <t>دقیقاً همین چهره و برگشت تمیز = قبول؛ هر چراغ اشتباه یا پاک‌نشدن = رد</t>
         </is>
       </c>
-      <c r="K68" s="43" t="n"/>
-      <c r="L68" s="46" t="inlineStr">
+      <c r="K68" s="98" t="n"/>
+      <c r="L68" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M68" s="43" t="n"/>
-      <c r="N68" s="43" t="n"/>
-      <c r="O68" s="45" t="n"/>
-      <c r="P68" s="45" t="n"/>
-      <c r="Q68" s="47">
+      <c r="M68" s="98" t="n"/>
+      <c r="N68" s="98" t="n"/>
+      <c r="O68" s="101" t="n"/>
+      <c r="P68" s="101" t="n"/>
+      <c r="Q68" s="102">
         <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="42" t="inlineStr">
+      <c r="A69" s="92" t="inlineStr">
         <is>
           <t>UI-033</t>
         </is>
       </c>
-      <c r="B69" s="43" t="inlineStr">
+      <c r="B69" s="98" t="inlineStr">
         <is>
           <t>خطای ۷: خرابی یک کانال شارژ</t>
         </is>
       </c>
-      <c r="C69" s="45" t="inlineStr">
+      <c r="C69" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
+      <c r="D69" s="98" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
         </is>
       </c>
-      <c r="E69" s="43" t="inlineStr">
+      <c r="E69" s="98" t="inlineStr">
         <is>
           <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
 گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
@@ -3545,68 +4485,68 @@
 گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
         </is>
       </c>
-      <c r="F69" s="43" t="inlineStr">
+      <c r="F69" s="98" t="inlineStr">
         <is>
           <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
         </is>
       </c>
-      <c r="G69" s="45" t="inlineStr">
+      <c r="G69" s="101" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H69" s="43" t="inlineStr">
+      <c r="H69" s="98" t="inlineStr">
         <is>
           <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
-      <c r="I69" s="43" t="inlineStr">
+      <c r="I69" s="98" t="inlineStr">
         <is>
           <t>هر سه چراغ با یک ریتم مشترک</t>
         </is>
       </c>
-      <c r="J69" s="43" t="inlineStr">
+      <c r="J69" s="98" t="inlineStr">
         <is>
           <t>قفل و پاک‌شدن فقط با ریست = قبول؛ پاک‌شدن با جا زدن فیوز = رد</t>
         </is>
       </c>
-      <c r="K69" s="43" t="n"/>
-      <c r="L69" s="46" t="inlineStr">
+      <c r="K69" s="98" t="n"/>
+      <c r="L69" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M69" s="43" t="n"/>
-      <c r="N69" s="43" t="n"/>
-      <c r="O69" s="45" t="n"/>
-      <c r="P69" s="45" t="n"/>
-      <c r="Q69" s="47">
+      <c r="M69" s="98" t="n"/>
+      <c r="N69" s="98" t="n"/>
+      <c r="O69" s="101" t="n"/>
+      <c r="P69" s="101" t="n"/>
+      <c r="Q69" s="102">
         <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="42" t="inlineStr">
+      <c r="A70" s="92" t="inlineStr">
         <is>
           <t>UI-034</t>
         </is>
       </c>
-      <c r="B70" s="43" t="inlineStr">
+      <c r="B70" s="98" t="inlineStr">
         <is>
           <t>باتری خراب (سناریوی ۶): قرمز ثابت</t>
         </is>
       </c>
-      <c r="C70" s="45" t="inlineStr">
+      <c r="C70" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
+      <c r="D70" s="98" t="inlineStr">
         <is>
           <t>از پنل، زمان سناریوی باتری خراب را موقتاً روی چند دقیقه بگذار (مقدار واقعی یک شبانه‌روز است)؛ یک باتری خالی داری</t>
         </is>
       </c>
-      <c r="E70" s="43" t="inlineStr">
+      <c r="E70" s="98" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت پر و شناور شود.
 گام ۲: بعد از گذشت زمان تنظیم‌شده چراغ‌ها را ببین: قرمز باید ثابت روشن باشد، نه چشمک‌زن.
@@ -3615,68 +4555,68 @@
 گام ۵: زمان سناریو را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F70" s="43" t="inlineStr">
+      <c r="F70" s="98" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده از پنل</t>
         </is>
       </c>
-      <c r="G70" s="45" t="inlineStr">
+      <c r="G70" s="101" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H70" s="43" t="inlineStr">
+      <c r="H70" s="98" t="inlineStr">
         <is>
           <t>قرمز ثابت می‌ماند، شارژ آن باتری برای همیشه می‌ایستد و فقط با تعویض باتری پاک می‌شود</t>
         </is>
       </c>
-      <c r="I70" s="43" t="inlineStr">
+      <c r="I70" s="98" t="inlineStr">
         <is>
           <t>قرمز ثابت، بدون چشمک</t>
         </is>
       </c>
-      <c r="J70" s="43" t="inlineStr">
+      <c r="J70" s="98" t="inlineStr">
         <is>
           <t>قرمز ثابت و توقف تا تعویض = قبول؛ چشمک‌زدن قرمز یا شارژ دوبارهٔ همان باتری = رد</t>
         </is>
       </c>
-      <c r="K70" s="43" t="n"/>
-      <c r="L70" s="46" t="inlineStr">
+      <c r="K70" s="98" t="n"/>
+      <c r="L70" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M70" s="43" t="n"/>
-      <c r="N70" s="43" t="n"/>
-      <c r="O70" s="45" t="n"/>
-      <c r="P70" s="45" t="n"/>
-      <c r="Q70" s="47">
+      <c r="M70" s="98" t="n"/>
+      <c r="N70" s="98" t="n"/>
+      <c r="O70" s="101" t="n"/>
+      <c r="P70" s="101" t="n"/>
+      <c r="Q70" s="102">
         <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="42" t="inlineStr">
+      <c r="A71" s="92" t="inlineStr">
         <is>
           <t>UI-035</t>
         </is>
       </c>
-      <c r="B71" s="43" t="inlineStr">
+      <c r="B71" s="98" t="inlineStr">
         <is>
           <t>عدم‌توازن باتری: قرمز چشمک‌زن تنها</t>
         </is>
       </c>
-      <c r="C71" s="45" t="inlineStr">
+      <c r="C71" s="101" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
+      <c r="D71" s="98" t="inlineStr">
         <is>
           <t>دو باتری ۱۲ ولت داری که یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای؛ برای زود دیدن، از پنل حدّ رویداد مجاز را موقتاً کم کن</t>
         </is>
       </c>
-      <c r="E71" s="43" t="inlineStr">
+      <c r="E71" s="98" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌های نابرابر را وصل و دستگاه را مدتی به کار بگذار تا حکم عدم‌توازن قفل شود.
 گام ۲: چراغ‌ها را ببین: فقط قرمز چشمک می‌زند؛ سبز و زرد خاموش‌اند و هر از چندی یک بوق کوتاه می‌آید.
@@ -3684,42 +4624,42 @@
 گام ۴: چند دقیقه صبر کن تا قفل خودش پاک شود.</t>
         </is>
       </c>
-      <c r="F71" s="43" t="inlineStr">
+      <c r="F71" s="98" t="inlineStr">
         <is>
           <t>باتری‌های نابرابر و بعد تعویض با سالم</t>
         </is>
       </c>
-      <c r="G71" s="45" t="inlineStr">
+      <c r="G71" s="101" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H71" s="43" t="inlineStr">
+      <c r="H71" s="98" t="inlineStr">
         <is>
           <t>در قفل: قرمز چشمک‌زنِ تنها بدون سبز و زرد؛ با تعویض باتری قفل خودکار پاک می‌شود</t>
         </is>
       </c>
-      <c r="I71" s="43" t="inlineStr">
+      <c r="I71" s="98" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن، بقیه خاموش</t>
         </is>
       </c>
-      <c r="J71" s="43" t="inlineStr">
+      <c r="J71" s="98" t="inlineStr">
         <is>
           <t>همین چهره و پاک‌شدن با تعویض = قبول؛ روشن‌ماندن سبز/زرد یا پاک‌نشدن = رد</t>
         </is>
       </c>
-      <c r="K71" s="43" t="n"/>
-      <c r="L71" s="46" t="inlineStr">
+      <c r="K71" s="98" t="n"/>
+      <c r="L71" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M71" s="43" t="n"/>
-      <c r="N71" s="43" t="n"/>
-      <c r="O71" s="45" t="n"/>
-      <c r="P71" s="45" t="n"/>
-      <c r="Q71" s="47">
+      <c r="M71" s="98" t="n"/>
+      <c r="N71" s="98" t="n"/>
+      <c r="O71" s="101" t="n"/>
+      <c r="P71" s="101" t="n"/>
+      <c r="Q71" s="102">
         <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
         <v/>
       </c>
@@ -3786,129 +4726,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="80" t="n"/>
+      <c r="H1" s="80" t="n"/>
+      <c r="I1" s="80" t="n"/>
+      <c r="J1" s="80" t="n"/>
+      <c r="K1" s="80" t="n"/>
+      <c r="L1" s="80" t="n"/>
+      <c r="M1" s="80" t="n"/>
+      <c r="N1" s="80" t="n"/>
+      <c r="O1" s="80" t="n"/>
+      <c r="P1" s="80" t="n"/>
+      <c r="Q1" s="80" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="76" t="inlineStr">
+      <c r="A2" s="107" t="inlineStr">
         <is>
           <t>این شیت جدا از تست عملی است: اندازه‌گیری روی پایه‌ها، اسیلوسکوپ و تلرانس‌های دقیق میلی‌ثانیه/میکروثانیه. برای بررسی عملکرد واقعی دستگاه لازم نیست؛ برای اعتبارسنجی دقیق سخت‌افزار و زمان‌بندی‌هاست.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
+      <c r="N2" s="80" t="n"/>
+      <c r="O2" s="80" t="n"/>
+      <c r="P2" s="80" t="n"/>
+      <c r="Q2" s="80" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="80" t="n"/>
+      <c r="B3" s="80" t="n"/>
+      <c r="C3" s="80" t="n"/>
+      <c r="D3" s="80" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
+      <c r="G3" s="80" t="n"/>
+      <c r="H3" s="80" t="n"/>
+      <c r="I3" s="80" t="n"/>
+      <c r="J3" s="80" t="n"/>
+      <c r="K3" s="80" t="n"/>
+      <c r="L3" s="80" t="n"/>
+      <c r="M3" s="80" t="n"/>
+      <c r="N3" s="80" t="n"/>
+      <c r="O3" s="80" t="n"/>
+      <c r="P3" s="80" t="n"/>
+      <c r="Q3" s="80" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها (v_bat/v_in/raw)</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="36" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="36" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="36" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="36" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="36" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="92" t="inlineStr">
         <is>
           <t>UI-001</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="98" t="inlineStr">
         <is>
           <t>Mapping PA3→v_bat</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="98" t="inlineStr">
         <is>
           <t>برد روشن, valid</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="98" t="inlineStr">
         <is>
           <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
 گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
@@ -3916,68 +4906,68 @@
 گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="101" t="inlineStr">
         <is>
           <t>PA3 2.0V pin → v_bat≈22352mV, v_in 24V</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="101" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="98" t="inlineStr">
         <is>
           <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="98" t="inlineStr">
         <is>
           <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
         </is>
       </c>
-      <c r="K5" s="43" t="n"/>
-      <c r="L5" s="46" t="inlineStr">
+      <c r="K5" s="98" t="n"/>
+      <c r="L5" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="43" t="n"/>
-      <c r="N5" s="43" t="n"/>
-      <c r="O5" s="45" t="n"/>
-      <c r="P5" s="45" t="n"/>
-      <c r="Q5" s="47">
+      <c r="M5" s="98" t="n"/>
+      <c r="N5" s="98" t="n"/>
+      <c r="O5" s="101" t="n"/>
+      <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="102">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>UI-014</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="93" t="inlineStr">
         <is>
           <t>Charging yellow phase</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="93" t="inlineStr">
         <is>
           <t>Charging 25V On430</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="93" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
 گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
@@ -3985,68 +4975,68 @@
 گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>On430 jitter56</t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G6" s="95" t="inlineStr">
         <is>
           <t>600ms</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="93" t="inlineStr">
         <is>
           <t>ON تا 430 حفظ سپس OFF</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="93" t="inlineStr">
         <is>
           <t>ON حفظ</t>
         </is>
       </c>
-      <c r="J6" s="48" t="inlineStr">
+      <c r="J6" s="93" t="inlineStr">
         <is>
           <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
-      <c r="K6" s="48" t="n"/>
-      <c r="L6" s="46" t="inlineStr">
+      <c r="K6" s="93" t="n"/>
+      <c r="L6" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="48" t="n"/>
-      <c r="N6" s="48" t="n"/>
-      <c r="O6" s="50" t="n"/>
-      <c r="P6" s="50" t="n"/>
-      <c r="Q6" s="51">
+      <c r="M6" s="93" t="n"/>
+      <c r="N6" s="93" t="n"/>
+      <c r="O6" s="95" t="n"/>
+      <c r="P6" s="95" t="n"/>
+      <c r="Q6" s="97">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>UI-018</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>BatteryRun phase preserve</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="48" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
         <is>
           <t>BatteryRun 25V stable57 ON570</t>
         </is>
       </c>
-      <c r="E7" s="48" t="inlineStr">
+      <c r="E7" s="93" t="inlineStr">
         <is>
           <t>گام ۱: BatteryRun با باتری 25 ولت و درصد پایدار 57 باشد تا سبز در فاز روشنی 570 میلی‌ثانیه‌ای باشد.
 گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (پایدار همان 57 می‌ماند).
@@ -4054,68 +5044,68 @@
 گام ۴: اگر روشنی وسطش از نو شروع شد، تست رد است.</t>
         </is>
       </c>
-      <c r="F7" s="50" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>On570 jitter56</t>
         </is>
       </c>
-      <c r="G7" s="50" t="inlineStr">
+      <c r="G7" s="95" t="inlineStr">
         <is>
           <t>700ms</t>
         </is>
       </c>
-      <c r="H7" s="48" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>ON تا 570 حفظ سپس OFF430</t>
         </is>
       </c>
-      <c r="I7" s="48" t="inlineStr">
+      <c r="I7" s="93" t="inlineStr">
         <is>
           <t>ON حفظ570</t>
         </is>
       </c>
-      <c r="J7" s="48" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>PASS: restart نشد. FAIL: restart</t>
         </is>
       </c>
-      <c r="K7" s="48" t="n"/>
-      <c r="L7" s="46" t="inlineStr">
+      <c r="K7" s="93" t="n"/>
+      <c r="L7" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="48" t="n"/>
-      <c r="N7" s="48" t="n"/>
-      <c r="O7" s="50" t="n"/>
-      <c r="P7" s="50" t="n"/>
-      <c r="Q7" s="51">
+      <c r="M7" s="93" t="n"/>
+      <c r="N7" s="93" t="n"/>
+      <c r="O7" s="95" t="n"/>
+      <c r="P7" s="95" t="n"/>
+      <c r="Q7" s="97">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="92" t="inlineStr">
         <is>
           <t>UI-025</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>Mapping PA3/PA2</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="98" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
 گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
@@ -4123,68 +5113,68 @@
 گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F8" s="45" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>PA2/PA3 1V</t>
         </is>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G8" s="101" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="98" t="inlineStr">
         <is>
           <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
         </is>
       </c>
-      <c r="I8" s="43" t="inlineStr">
+      <c r="I8" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="43" t="inlineStr">
+      <c r="J8" s="98" t="inlineStr">
         <is>
           <t>PASS: mapping. FAIL: جابجایی</t>
         </is>
       </c>
-      <c r="K8" s="43" t="n"/>
-      <c r="L8" s="46" t="inlineStr">
+      <c r="K8" s="98" t="n"/>
+      <c r="L8" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="43" t="n"/>
-      <c r="N8" s="43" t="n"/>
-      <c r="O8" s="45" t="n"/>
-      <c r="P8" s="45" t="n"/>
-      <c r="Q8" s="47">
+      <c r="M8" s="98" t="n"/>
+      <c r="N8" s="98" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="101" t="n"/>
+      <c r="Q8" s="102">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="92" t="inlineStr">
         <is>
           <t>UI-028</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>Task starvation</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="48" t="inlineStr">
+      <c r="D9" s="93" t="inlineStr">
         <is>
           <t>همه سناریوها</t>
         </is>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="93" t="inlineStr">
         <is>
           <t>گام ۱: هر سه وضعیت InputOk و Charging و BatteryRun را یکی‌یکی بساز.
 گام ۲: در هر وضعیت 5 ثانیه همهٔ تسک‌ها را زیر نظر بگیر.
@@ -4192,162 +5182,482 @@
 گام ۴: هیچ‌کدام نباید گرسنه بماند؛ delayهای طولانی 500 یا 1000 میلی‌ثانیه‌ای یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
+      <c r="F9" s="95" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G9" s="95" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H9" s="93" t="inlineStr">
         <is>
           <t>ui10ms meas10ms ctrl10ms همه اجرا</t>
         </is>
       </c>
-      <c r="I9" s="48" t="inlineStr">
+      <c r="I9" s="93" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="48" t="inlineStr">
+      <c r="J9" s="93" t="inlineStr">
         <is>
           <t>PASS: بدون starvation. FAIL: delay500/1000</t>
         </is>
       </c>
-      <c r="K9" s="48" t="n"/>
-      <c r="L9" s="46" t="inlineStr">
+      <c r="K9" s="93" t="n"/>
+      <c r="L9" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="48" t="n"/>
-      <c r="N9" s="48" t="n"/>
-      <c r="O9" s="50" t="n"/>
-      <c r="P9" s="50" t="n"/>
-      <c r="Q9" s="51">
+      <c r="M9" s="93" t="n"/>
+      <c r="N9" s="93" t="n"/>
+      <c r="O9" s="95" t="n"/>
+      <c r="P9" s="95" t="n"/>
+      <c r="Q9" s="97">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="56">
+      <c r="A10" s="80" t="n"/>
+      <c r="B10" s="80" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
+      <c r="G10" s="80" t="n"/>
+      <c r="H10" s="80" t="n"/>
+      <c r="I10" s="80" t="n"/>
+      <c r="J10" s="80" t="n"/>
+      <c r="K10" s="80" t="n"/>
+      <c r="L10" s="80" t="n"/>
+      <c r="M10" s="80" t="n"/>
+      <c r="N10" s="80" t="n"/>
+      <c r="O10" s="80" t="n"/>
+      <c r="P10" s="80" t="n"/>
+      <c r="Q10" s="105">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="56">
+      <c r="A11" s="80" t="n"/>
+      <c r="B11" s="80" t="n"/>
+      <c r="C11" s="80" t="n"/>
+      <c r="D11" s="80" t="n"/>
+      <c r="E11" s="80" t="n"/>
+      <c r="F11" s="80" t="n"/>
+      <c r="G11" s="80" t="n"/>
+      <c r="H11" s="80" t="n"/>
+      <c r="I11" s="80" t="n"/>
+      <c r="J11" s="80" t="n"/>
+      <c r="K11" s="80" t="n"/>
+      <c r="L11" s="80" t="n"/>
+      <c r="M11" s="80" t="n"/>
+      <c r="N11" s="80" t="n"/>
+      <c r="O11" s="80" t="n"/>
+      <c r="P11" s="80" t="n"/>
+      <c r="Q11" s="105">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="56">
+      <c r="A12" s="80" t="n"/>
+      <c r="B12" s="80" t="n"/>
+      <c r="C12" s="80" t="n"/>
+      <c r="D12" s="80" t="n"/>
+      <c r="E12" s="80" t="n"/>
+      <c r="F12" s="80" t="n"/>
+      <c r="G12" s="80" t="n"/>
+      <c r="H12" s="80" t="n"/>
+      <c r="I12" s="80" t="n"/>
+      <c r="J12" s="80" t="n"/>
+      <c r="K12" s="80" t="n"/>
+      <c r="L12" s="80" t="n"/>
+      <c r="M12" s="80" t="n"/>
+      <c r="N12" s="80" t="n"/>
+      <c r="O12" s="80" t="n"/>
+      <c r="P12" s="80" t="n"/>
+      <c r="Q12" s="105">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="56">
+      <c r="A13" s="80" t="n"/>
+      <c r="B13" s="80" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
+      <c r="G13" s="80" t="n"/>
+      <c r="H13" s="80" t="n"/>
+      <c r="I13" s="80" t="n"/>
+      <c r="J13" s="80" t="n"/>
+      <c r="K13" s="80" t="n"/>
+      <c r="L13" s="80" t="n"/>
+      <c r="M13" s="80" t="n"/>
+      <c r="N13" s="80" t="n"/>
+      <c r="O13" s="80" t="n"/>
+      <c r="P13" s="80" t="n"/>
+      <c r="Q13" s="105">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="56">
+      <c r="A14" s="80" t="n"/>
+      <c r="B14" s="80" t="n"/>
+      <c r="C14" s="80" t="n"/>
+      <c r="D14" s="80" t="n"/>
+      <c r="E14" s="80" t="n"/>
+      <c r="F14" s="80" t="n"/>
+      <c r="G14" s="80" t="n"/>
+      <c r="H14" s="80" t="n"/>
+      <c r="I14" s="80" t="n"/>
+      <c r="J14" s="80" t="n"/>
+      <c r="K14" s="80" t="n"/>
+      <c r="L14" s="80" t="n"/>
+      <c r="M14" s="80" t="n"/>
+      <c r="N14" s="80" t="n"/>
+      <c r="O14" s="80" t="n"/>
+      <c r="P14" s="80" t="n"/>
+      <c r="Q14" s="105">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="56">
+      <c r="A15" s="80" t="n"/>
+      <c r="B15" s="80" t="n"/>
+      <c r="C15" s="80" t="n"/>
+      <c r="D15" s="80" t="n"/>
+      <c r="E15" s="80" t="n"/>
+      <c r="F15" s="80" t="n"/>
+      <c r="G15" s="80" t="n"/>
+      <c r="H15" s="80" t="n"/>
+      <c r="I15" s="80" t="n"/>
+      <c r="J15" s="80" t="n"/>
+      <c r="K15" s="80" t="n"/>
+      <c r="L15" s="80" t="n"/>
+      <c r="M15" s="80" t="n"/>
+      <c r="N15" s="80" t="n"/>
+      <c r="O15" s="80" t="n"/>
+      <c r="P15" s="80" t="n"/>
+      <c r="Q15" s="105">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="56">
+      <c r="A16" s="80" t="n"/>
+      <c r="B16" s="80" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
+      <c r="G16" s="80" t="n"/>
+      <c r="H16" s="80" t="n"/>
+      <c r="I16" s="80" t="n"/>
+      <c r="J16" s="80" t="n"/>
+      <c r="K16" s="80" t="n"/>
+      <c r="L16" s="80" t="n"/>
+      <c r="M16" s="80" t="n"/>
+      <c r="N16" s="80" t="n"/>
+      <c r="O16" s="80" t="n"/>
+      <c r="P16" s="80" t="n"/>
+      <c r="Q16" s="105">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="56">
+      <c r="A17" s="80" t="n"/>
+      <c r="B17" s="80" t="n"/>
+      <c r="C17" s="80" t="n"/>
+      <c r="D17" s="80" t="n"/>
+      <c r="E17" s="80" t="n"/>
+      <c r="F17" s="80" t="n"/>
+      <c r="G17" s="80" t="n"/>
+      <c r="H17" s="80" t="n"/>
+      <c r="I17" s="80" t="n"/>
+      <c r="J17" s="80" t="n"/>
+      <c r="K17" s="80" t="n"/>
+      <c r="L17" s="80" t="n"/>
+      <c r="M17" s="80" t="n"/>
+      <c r="N17" s="80" t="n"/>
+      <c r="O17" s="80" t="n"/>
+      <c r="P17" s="80" t="n"/>
+      <c r="Q17" s="105">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="56">
+      <c r="A18" s="80" t="n"/>
+      <c r="B18" s="80" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
+      <c r="G18" s="80" t="n"/>
+      <c r="H18" s="80" t="n"/>
+      <c r="I18" s="80" t="n"/>
+      <c r="J18" s="80" t="n"/>
+      <c r="K18" s="80" t="n"/>
+      <c r="L18" s="80" t="n"/>
+      <c r="M18" s="80" t="n"/>
+      <c r="N18" s="80" t="n"/>
+      <c r="O18" s="80" t="n"/>
+      <c r="P18" s="80" t="n"/>
+      <c r="Q18" s="105">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="56">
+      <c r="A19" s="80" t="n"/>
+      <c r="B19" s="80" t="n"/>
+      <c r="C19" s="80" t="n"/>
+      <c r="D19" s="80" t="n"/>
+      <c r="E19" s="80" t="n"/>
+      <c r="F19" s="80" t="n"/>
+      <c r="G19" s="80" t="n"/>
+      <c r="H19" s="80" t="n"/>
+      <c r="I19" s="80" t="n"/>
+      <c r="J19" s="80" t="n"/>
+      <c r="K19" s="80" t="n"/>
+      <c r="L19" s="80" t="n"/>
+      <c r="M19" s="80" t="n"/>
+      <c r="N19" s="80" t="n"/>
+      <c r="O19" s="80" t="n"/>
+      <c r="P19" s="80" t="n"/>
+      <c r="Q19" s="105">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="56">
+      <c r="A20" s="80" t="n"/>
+      <c r="B20" s="80" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
+      <c r="G20" s="80" t="n"/>
+      <c r="H20" s="80" t="n"/>
+      <c r="I20" s="80" t="n"/>
+      <c r="J20" s="80" t="n"/>
+      <c r="K20" s="80" t="n"/>
+      <c r="L20" s="80" t="n"/>
+      <c r="M20" s="80" t="n"/>
+      <c r="N20" s="80" t="n"/>
+      <c r="O20" s="80" t="n"/>
+      <c r="P20" s="80" t="n"/>
+      <c r="Q20" s="105">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="56">
+      <c r="A21" s="80" t="n"/>
+      <c r="B21" s="80" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
+      <c r="G21" s="80" t="n"/>
+      <c r="H21" s="80" t="n"/>
+      <c r="I21" s="80" t="n"/>
+      <c r="J21" s="80" t="n"/>
+      <c r="K21" s="80" t="n"/>
+      <c r="L21" s="80" t="n"/>
+      <c r="M21" s="80" t="n"/>
+      <c r="N21" s="80" t="n"/>
+      <c r="O21" s="80" t="n"/>
+      <c r="P21" s="80" t="n"/>
+      <c r="Q21" s="105">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="56">
+      <c r="A22" s="80" t="n"/>
+      <c r="B22" s="80" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
+      <c r="G22" s="80" t="n"/>
+      <c r="H22" s="80" t="n"/>
+      <c r="I22" s="80" t="n"/>
+      <c r="J22" s="80" t="n"/>
+      <c r="K22" s="80" t="n"/>
+      <c r="L22" s="80" t="n"/>
+      <c r="M22" s="80" t="n"/>
+      <c r="N22" s="80" t="n"/>
+      <c r="O22" s="80" t="n"/>
+      <c r="P22" s="80" t="n"/>
+      <c r="Q22" s="105">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="56">
+      <c r="A23" s="80" t="n"/>
+      <c r="B23" s="80" t="n"/>
+      <c r="C23" s="80" t="n"/>
+      <c r="D23" s="80" t="n"/>
+      <c r="E23" s="80" t="n"/>
+      <c r="F23" s="80" t="n"/>
+      <c r="G23" s="80" t="n"/>
+      <c r="H23" s="80" t="n"/>
+      <c r="I23" s="80" t="n"/>
+      <c r="J23" s="80" t="n"/>
+      <c r="K23" s="80" t="n"/>
+      <c r="L23" s="80" t="n"/>
+      <c r="M23" s="80" t="n"/>
+      <c r="N23" s="80" t="n"/>
+      <c r="O23" s="80" t="n"/>
+      <c r="P23" s="80" t="n"/>
+      <c r="Q23" s="105">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="56">
+      <c r="A24" s="80" t="n"/>
+      <c r="B24" s="80" t="n"/>
+      <c r="C24" s="80" t="n"/>
+      <c r="D24" s="80" t="n"/>
+      <c r="E24" s="80" t="n"/>
+      <c r="F24" s="80" t="n"/>
+      <c r="G24" s="80" t="n"/>
+      <c r="H24" s="80" t="n"/>
+      <c r="I24" s="80" t="n"/>
+      <c r="J24" s="80" t="n"/>
+      <c r="K24" s="80" t="n"/>
+      <c r="L24" s="80" t="n"/>
+      <c r="M24" s="80" t="n"/>
+      <c r="N24" s="80" t="n"/>
+      <c r="O24" s="80" t="n"/>
+      <c r="P24" s="80" t="n"/>
+      <c r="Q24" s="105">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="56">
+      <c r="A25" s="80" t="n"/>
+      <c r="B25" s="80" t="n"/>
+      <c r="C25" s="80" t="n"/>
+      <c r="D25" s="80" t="n"/>
+      <c r="E25" s="80" t="n"/>
+      <c r="F25" s="80" t="n"/>
+      <c r="G25" s="80" t="n"/>
+      <c r="H25" s="80" t="n"/>
+      <c r="I25" s="80" t="n"/>
+      <c r="J25" s="80" t="n"/>
+      <c r="K25" s="80" t="n"/>
+      <c r="L25" s="80" t="n"/>
+      <c r="M25" s="80" t="n"/>
+      <c r="N25" s="80" t="n"/>
+      <c r="O25" s="80" t="n"/>
+      <c r="P25" s="80" t="n"/>
+      <c r="Q25" s="105">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="56">
+      <c r="A26" s="80" t="n"/>
+      <c r="B26" s="80" t="n"/>
+      <c r="C26" s="80" t="n"/>
+      <c r="D26" s="80" t="n"/>
+      <c r="E26" s="80" t="n"/>
+      <c r="F26" s="80" t="n"/>
+      <c r="G26" s="80" t="n"/>
+      <c r="H26" s="80" t="n"/>
+      <c r="I26" s="80" t="n"/>
+      <c r="J26" s="80" t="n"/>
+      <c r="K26" s="80" t="n"/>
+      <c r="L26" s="80" t="n"/>
+      <c r="M26" s="80" t="n"/>
+      <c r="N26" s="80" t="n"/>
+      <c r="O26" s="80" t="n"/>
+      <c r="P26" s="80" t="n"/>
+      <c r="Q26" s="105">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="56">
+      <c r="A27" s="80" t="n"/>
+      <c r="B27" s="80" t="n"/>
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="80" t="n"/>
+      <c r="E27" s="80" t="n"/>
+      <c r="F27" s="80" t="n"/>
+      <c r="G27" s="80" t="n"/>
+      <c r="H27" s="80" t="n"/>
+      <c r="I27" s="80" t="n"/>
+      <c r="J27" s="80" t="n"/>
+      <c r="K27" s="80" t="n"/>
+      <c r="L27" s="80" t="n"/>
+      <c r="M27" s="80" t="n"/>
+      <c r="N27" s="80" t="n"/>
+      <c r="O27" s="80" t="n"/>
+      <c r="P27" s="80" t="n"/>
+      <c r="Q27" s="105">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="56">
+      <c r="A28" s="80" t="n"/>
+      <c r="B28" s="80" t="n"/>
+      <c r="C28" s="80" t="n"/>
+      <c r="D28" s="80" t="n"/>
+      <c r="E28" s="80" t="n"/>
+      <c r="F28" s="80" t="n"/>
+      <c r="G28" s="80" t="n"/>
+      <c r="H28" s="80" t="n"/>
+      <c r="I28" s="80" t="n"/>
+      <c r="J28" s="80" t="n"/>
+      <c r="K28" s="80" t="n"/>
+      <c r="L28" s="80" t="n"/>
+      <c r="M28" s="80" t="n"/>
+      <c r="N28" s="80" t="n"/>
+      <c r="O28" s="80" t="n"/>
+      <c r="P28" s="80" t="n"/>
+      <c r="Q28" s="105">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="56">
+      <c r="A29" s="80" t="n"/>
+      <c r="B29" s="80" t="n"/>
+      <c r="C29" s="80" t="n"/>
+      <c r="D29" s="80" t="n"/>
+      <c r="E29" s="80" t="n"/>
+      <c r="F29" s="80" t="n"/>
+      <c r="G29" s="80" t="n"/>
+      <c r="H29" s="80" t="n"/>
+      <c r="I29" s="80" t="n"/>
+      <c r="J29" s="80" t="n"/>
+      <c r="K29" s="80" t="n"/>
+      <c r="L29" s="80" t="n"/>
+      <c r="M29" s="80" t="n"/>
+      <c r="N29" s="80" t="n"/>
+      <c r="O29" s="80" t="n"/>
+      <c r="P29" s="80" t="n"/>
+      <c r="Q29" s="105">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
@@ -4394,129 +5704,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="80" t="n"/>
+      <c r="H1" s="80" t="n"/>
+      <c r="I1" s="80" t="n"/>
+      <c r="J1" s="80" t="n"/>
+      <c r="K1" s="80" t="n"/>
+      <c r="L1" s="80" t="n"/>
+      <c r="M1" s="80" t="n"/>
+      <c r="N1" s="80" t="n"/>
+      <c r="O1" s="80" t="n"/>
+      <c r="P1" s="80" t="n"/>
+      <c r="Q1" s="80" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="76" t="inlineStr">
+      <c r="A2" s="80" t="n"/>
+      <c r="B2" s="107" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
+      <c r="N2" s="80" t="n"/>
+      <c r="O2" s="80" t="n"/>
+      <c r="P2" s="80" t="n"/>
+      <c r="Q2" s="80" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="80" t="n"/>
+      <c r="B3" s="80" t="n"/>
+      <c r="C3" s="80" t="n"/>
+      <c r="D3" s="80" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
+      <c r="G3" s="80" t="n"/>
+      <c r="H3" s="80" t="n"/>
+      <c r="I3" s="80" t="n"/>
+      <c r="J3" s="80" t="n"/>
+      <c r="K3" s="80" t="n"/>
+      <c r="L3" s="80" t="n"/>
+      <c r="M3" s="80" t="n"/>
+      <c r="N3" s="80" t="n"/>
+      <c r="O3" s="80" t="n"/>
+      <c r="P3" s="80" t="n"/>
+      <c r="Q3" s="80" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها (v_bat/v_in/raw)</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="36" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="36" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="36" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="36" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="36" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="92" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>RTOS static + stack</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>همه taskها</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
 گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
@@ -4524,303 +5884,623 @@
 گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="50" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="93" t="inlineStr">
         <is>
           <t>همه static UI512 Meas768 Ctrl1024 high-water&gt;20%</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="93" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="48" t="inlineStr">
+      <c r="J5" s="93" t="inlineStr">
         <is>
           <t>PASS: static no overflow. FAIL: dynamic/overflow</t>
         </is>
       </c>
-      <c r="K5" s="48" t="n"/>
-      <c r="L5" s="46" t="inlineStr">
+      <c r="K5" s="93" t="n"/>
+      <c r="L5" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="48" t="n"/>
-      <c r="N5" s="48" t="n"/>
-      <c r="O5" s="50" t="n"/>
-      <c r="P5" s="50" t="n"/>
-      <c r="Q5" s="51">
+      <c r="M5" s="93" t="n"/>
+      <c r="N5" s="93" t="n"/>
+      <c r="O5" s="95" t="n"/>
+      <c r="P5" s="95" t="n"/>
+      <c r="Q5" s="97">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>UI-027</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>No extra RTOS</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="98" t="inlineStr">
         <is>
           <t>hysteresis UI</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="98" t="inlineStr">
         <is>
           <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
 گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
 گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="45" t="inlineStr">
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="45" t="inlineStr">
+      <c r="G6" s="101" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>هیچ شئ جدید برای hysteresis</t>
         </is>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I6" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="43" t="inlineStr">
+      <c r="J6" s="98" t="inlineStr">
         <is>
           <t>PASS: بدون شئ. FAIL: شئ جدید</t>
         </is>
       </c>
-      <c r="K6" s="43" t="n"/>
-      <c r="L6" s="46" t="inlineStr">
+      <c r="K6" s="98" t="n"/>
+      <c r="L6" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="43" t="n"/>
-      <c r="N6" s="43" t="n"/>
-      <c r="O6" s="45" t="n"/>
-      <c r="P6" s="45" t="n"/>
-      <c r="Q6" s="47">
+      <c r="M6" s="98" t="n"/>
+      <c r="N6" s="98" t="n"/>
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="101" t="n"/>
+      <c r="Q6" s="102">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>UI-029</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="98" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="108" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="98" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E7" s="43" t="inlineStr">
+      <c r="E7" s="98" t="inlineStr">
         <is>
           <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
 گام ۲: 2 ثانیه نگاه کن.
 گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="45" t="inlineStr">
+      <c r="F7" s="101" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" s="45" t="inlineStr">
+      <c r="G7" s="101" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H7" s="43" t="inlineStr">
+      <c r="H7" s="98" t="inlineStr">
         <is>
           <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
         </is>
       </c>
-      <c r="I7" s="43" t="inlineStr">
+      <c r="I7" s="98" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J7" s="43" t="inlineStr">
+      <c r="J7" s="98" t="inlineStr">
         <is>
           <t>LED خاموش بدون درصد کاذب</t>
         </is>
       </c>
-      <c r="K7" s="43" t="n"/>
-      <c r="L7" s="55" t="inlineStr">
+      <c r="K7" s="98" t="n"/>
+      <c r="L7" s="104" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M7" s="43" t="n"/>
-      <c r="N7" s="43" t="n"/>
-      <c r="O7" s="45" t="inlineStr">
+      <c r="M7" s="98" t="n"/>
+      <c r="N7" s="98" t="n"/>
+      <c r="O7" s="101" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" s="45" t="n"/>
-      <c r="Q7" s="47" t="inlineStr">
+      <c r="P7" s="101" t="n"/>
+      <c r="Q7" s="102" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="56">
+      <c r="A8" s="80" t="n"/>
+      <c r="B8" s="80" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="80" t="n"/>
+      <c r="F8" s="80" t="n"/>
+      <c r="G8" s="80" t="n"/>
+      <c r="H8" s="80" t="n"/>
+      <c r="I8" s="80" t="n"/>
+      <c r="J8" s="80" t="n"/>
+      <c r="K8" s="80" t="n"/>
+      <c r="L8" s="80" t="n"/>
+      <c r="M8" s="80" t="n"/>
+      <c r="N8" s="80" t="n"/>
+      <c r="O8" s="80" t="n"/>
+      <c r="P8" s="80" t="n"/>
+      <c r="Q8" s="105">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="56">
+      <c r="A9" s="80" t="n"/>
+      <c r="B9" s="80" t="n"/>
+      <c r="C9" s="80" t="n"/>
+      <c r="D9" s="80" t="n"/>
+      <c r="E9" s="80" t="n"/>
+      <c r="F9" s="80" t="n"/>
+      <c r="G9" s="80" t="n"/>
+      <c r="H9" s="80" t="n"/>
+      <c r="I9" s="80" t="n"/>
+      <c r="J9" s="80" t="n"/>
+      <c r="K9" s="80" t="n"/>
+      <c r="L9" s="80" t="n"/>
+      <c r="M9" s="80" t="n"/>
+      <c r="N9" s="80" t="n"/>
+      <c r="O9" s="80" t="n"/>
+      <c r="P9" s="80" t="n"/>
+      <c r="Q9" s="105">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="56">
+      <c r="A10" s="80" t="n"/>
+      <c r="B10" s="80" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
+      <c r="G10" s="80" t="n"/>
+      <c r="H10" s="80" t="n"/>
+      <c r="I10" s="80" t="n"/>
+      <c r="J10" s="80" t="n"/>
+      <c r="K10" s="80" t="n"/>
+      <c r="L10" s="80" t="n"/>
+      <c r="M10" s="80" t="n"/>
+      <c r="N10" s="80" t="n"/>
+      <c r="O10" s="80" t="n"/>
+      <c r="P10" s="80" t="n"/>
+      <c r="Q10" s="105">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="56">
+      <c r="A11" s="80" t="n"/>
+      <c r="B11" s="80" t="n"/>
+      <c r="C11" s="80" t="n"/>
+      <c r="D11" s="80" t="n"/>
+      <c r="E11" s="80" t="n"/>
+      <c r="F11" s="80" t="n"/>
+      <c r="G11" s="80" t="n"/>
+      <c r="H11" s="80" t="n"/>
+      <c r="I11" s="80" t="n"/>
+      <c r="J11" s="80" t="n"/>
+      <c r="K11" s="80" t="n"/>
+      <c r="L11" s="80" t="n"/>
+      <c r="M11" s="80" t="n"/>
+      <c r="N11" s="80" t="n"/>
+      <c r="O11" s="80" t="n"/>
+      <c r="P11" s="80" t="n"/>
+      <c r="Q11" s="105">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="56">
+      <c r="A12" s="80" t="n"/>
+      <c r="B12" s="80" t="n"/>
+      <c r="C12" s="80" t="n"/>
+      <c r="D12" s="80" t="n"/>
+      <c r="E12" s="80" t="n"/>
+      <c r="F12" s="80" t="n"/>
+      <c r="G12" s="80" t="n"/>
+      <c r="H12" s="80" t="n"/>
+      <c r="I12" s="80" t="n"/>
+      <c r="J12" s="80" t="n"/>
+      <c r="K12" s="80" t="n"/>
+      <c r="L12" s="80" t="n"/>
+      <c r="M12" s="80" t="n"/>
+      <c r="N12" s="80" t="n"/>
+      <c r="O12" s="80" t="n"/>
+      <c r="P12" s="80" t="n"/>
+      <c r="Q12" s="105">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="56">
+      <c r="A13" s="80" t="n"/>
+      <c r="B13" s="80" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
+      <c r="G13" s="80" t="n"/>
+      <c r="H13" s="80" t="n"/>
+      <c r="I13" s="80" t="n"/>
+      <c r="J13" s="80" t="n"/>
+      <c r="K13" s="80" t="n"/>
+      <c r="L13" s="80" t="n"/>
+      <c r="M13" s="80" t="n"/>
+      <c r="N13" s="80" t="n"/>
+      <c r="O13" s="80" t="n"/>
+      <c r="P13" s="80" t="n"/>
+      <c r="Q13" s="105">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="56">
+      <c r="A14" s="80" t="n"/>
+      <c r="B14" s="80" t="n"/>
+      <c r="C14" s="80" t="n"/>
+      <c r="D14" s="80" t="n"/>
+      <c r="E14" s="80" t="n"/>
+      <c r="F14" s="80" t="n"/>
+      <c r="G14" s="80" t="n"/>
+      <c r="H14" s="80" t="n"/>
+      <c r="I14" s="80" t="n"/>
+      <c r="J14" s="80" t="n"/>
+      <c r="K14" s="80" t="n"/>
+      <c r="L14" s="80" t="n"/>
+      <c r="M14" s="80" t="n"/>
+      <c r="N14" s="80" t="n"/>
+      <c r="O14" s="80" t="n"/>
+      <c r="P14" s="80" t="n"/>
+      <c r="Q14" s="105">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="56">
+      <c r="A15" s="80" t="n"/>
+      <c r="B15" s="80" t="n"/>
+      <c r="C15" s="80" t="n"/>
+      <c r="D15" s="80" t="n"/>
+      <c r="E15" s="80" t="n"/>
+      <c r="F15" s="80" t="n"/>
+      <c r="G15" s="80" t="n"/>
+      <c r="H15" s="80" t="n"/>
+      <c r="I15" s="80" t="n"/>
+      <c r="J15" s="80" t="n"/>
+      <c r="K15" s="80" t="n"/>
+      <c r="L15" s="80" t="n"/>
+      <c r="M15" s="80" t="n"/>
+      <c r="N15" s="80" t="n"/>
+      <c r="O15" s="80" t="n"/>
+      <c r="P15" s="80" t="n"/>
+      <c r="Q15" s="105">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="56">
+      <c r="A16" s="80" t="n"/>
+      <c r="B16" s="80" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
+      <c r="G16" s="80" t="n"/>
+      <c r="H16" s="80" t="n"/>
+      <c r="I16" s="80" t="n"/>
+      <c r="J16" s="80" t="n"/>
+      <c r="K16" s="80" t="n"/>
+      <c r="L16" s="80" t="n"/>
+      <c r="M16" s="80" t="n"/>
+      <c r="N16" s="80" t="n"/>
+      <c r="O16" s="80" t="n"/>
+      <c r="P16" s="80" t="n"/>
+      <c r="Q16" s="105">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="56">
+      <c r="A17" s="80" t="n"/>
+      <c r="B17" s="80" t="n"/>
+      <c r="C17" s="80" t="n"/>
+      <c r="D17" s="80" t="n"/>
+      <c r="E17" s="80" t="n"/>
+      <c r="F17" s="80" t="n"/>
+      <c r="G17" s="80" t="n"/>
+      <c r="H17" s="80" t="n"/>
+      <c r="I17" s="80" t="n"/>
+      <c r="J17" s="80" t="n"/>
+      <c r="K17" s="80" t="n"/>
+      <c r="L17" s="80" t="n"/>
+      <c r="M17" s="80" t="n"/>
+      <c r="N17" s="80" t="n"/>
+      <c r="O17" s="80" t="n"/>
+      <c r="P17" s="80" t="n"/>
+      <c r="Q17" s="105">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="56">
+      <c r="A18" s="80" t="n"/>
+      <c r="B18" s="80" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
+      <c r="G18" s="80" t="n"/>
+      <c r="H18" s="80" t="n"/>
+      <c r="I18" s="80" t="n"/>
+      <c r="J18" s="80" t="n"/>
+      <c r="K18" s="80" t="n"/>
+      <c r="L18" s="80" t="n"/>
+      <c r="M18" s="80" t="n"/>
+      <c r="N18" s="80" t="n"/>
+      <c r="O18" s="80" t="n"/>
+      <c r="P18" s="80" t="n"/>
+      <c r="Q18" s="105">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="56">
+      <c r="A19" s="80" t="n"/>
+      <c r="B19" s="80" t="n"/>
+      <c r="C19" s="80" t="n"/>
+      <c r="D19" s="80" t="n"/>
+      <c r="E19" s="80" t="n"/>
+      <c r="F19" s="80" t="n"/>
+      <c r="G19" s="80" t="n"/>
+      <c r="H19" s="80" t="n"/>
+      <c r="I19" s="80" t="n"/>
+      <c r="J19" s="80" t="n"/>
+      <c r="K19" s="80" t="n"/>
+      <c r="L19" s="80" t="n"/>
+      <c r="M19" s="80" t="n"/>
+      <c r="N19" s="80" t="n"/>
+      <c r="O19" s="80" t="n"/>
+      <c r="P19" s="80" t="n"/>
+      <c r="Q19" s="105">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="56">
+      <c r="A20" s="80" t="n"/>
+      <c r="B20" s="80" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
+      <c r="G20" s="80" t="n"/>
+      <c r="H20" s="80" t="n"/>
+      <c r="I20" s="80" t="n"/>
+      <c r="J20" s="80" t="n"/>
+      <c r="K20" s="80" t="n"/>
+      <c r="L20" s="80" t="n"/>
+      <c r="M20" s="80" t="n"/>
+      <c r="N20" s="80" t="n"/>
+      <c r="O20" s="80" t="n"/>
+      <c r="P20" s="80" t="n"/>
+      <c r="Q20" s="105">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="56">
+      <c r="A21" s="80" t="n"/>
+      <c r="B21" s="80" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
+      <c r="G21" s="80" t="n"/>
+      <c r="H21" s="80" t="n"/>
+      <c r="I21" s="80" t="n"/>
+      <c r="J21" s="80" t="n"/>
+      <c r="K21" s="80" t="n"/>
+      <c r="L21" s="80" t="n"/>
+      <c r="M21" s="80" t="n"/>
+      <c r="N21" s="80" t="n"/>
+      <c r="O21" s="80" t="n"/>
+      <c r="P21" s="80" t="n"/>
+      <c r="Q21" s="105">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="56">
+      <c r="A22" s="80" t="n"/>
+      <c r="B22" s="80" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
+      <c r="G22" s="80" t="n"/>
+      <c r="H22" s="80" t="n"/>
+      <c r="I22" s="80" t="n"/>
+      <c r="J22" s="80" t="n"/>
+      <c r="K22" s="80" t="n"/>
+      <c r="L22" s="80" t="n"/>
+      <c r="M22" s="80" t="n"/>
+      <c r="N22" s="80" t="n"/>
+      <c r="O22" s="80" t="n"/>
+      <c r="P22" s="80" t="n"/>
+      <c r="Q22" s="105">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="56">
+      <c r="A23" s="80" t="n"/>
+      <c r="B23" s="80" t="n"/>
+      <c r="C23" s="80" t="n"/>
+      <c r="D23" s="80" t="n"/>
+      <c r="E23" s="80" t="n"/>
+      <c r="F23" s="80" t="n"/>
+      <c r="G23" s="80" t="n"/>
+      <c r="H23" s="80" t="n"/>
+      <c r="I23" s="80" t="n"/>
+      <c r="J23" s="80" t="n"/>
+      <c r="K23" s="80" t="n"/>
+      <c r="L23" s="80" t="n"/>
+      <c r="M23" s="80" t="n"/>
+      <c r="N23" s="80" t="n"/>
+      <c r="O23" s="80" t="n"/>
+      <c r="P23" s="80" t="n"/>
+      <c r="Q23" s="105">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="56">
+      <c r="A24" s="80" t="n"/>
+      <c r="B24" s="80" t="n"/>
+      <c r="C24" s="80" t="n"/>
+      <c r="D24" s="80" t="n"/>
+      <c r="E24" s="80" t="n"/>
+      <c r="F24" s="80" t="n"/>
+      <c r="G24" s="80" t="n"/>
+      <c r="H24" s="80" t="n"/>
+      <c r="I24" s="80" t="n"/>
+      <c r="J24" s="80" t="n"/>
+      <c r="K24" s="80" t="n"/>
+      <c r="L24" s="80" t="n"/>
+      <c r="M24" s="80" t="n"/>
+      <c r="N24" s="80" t="n"/>
+      <c r="O24" s="80" t="n"/>
+      <c r="P24" s="80" t="n"/>
+      <c r="Q24" s="105">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="56">
+      <c r="A25" s="80" t="n"/>
+      <c r="B25" s="80" t="n"/>
+      <c r="C25" s="80" t="n"/>
+      <c r="D25" s="80" t="n"/>
+      <c r="E25" s="80" t="n"/>
+      <c r="F25" s="80" t="n"/>
+      <c r="G25" s="80" t="n"/>
+      <c r="H25" s="80" t="n"/>
+      <c r="I25" s="80" t="n"/>
+      <c r="J25" s="80" t="n"/>
+      <c r="K25" s="80" t="n"/>
+      <c r="L25" s="80" t="n"/>
+      <c r="M25" s="80" t="n"/>
+      <c r="N25" s="80" t="n"/>
+      <c r="O25" s="80" t="n"/>
+      <c r="P25" s="80" t="n"/>
+      <c r="Q25" s="105">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="56">
+      <c r="A26" s="80" t="n"/>
+      <c r="B26" s="80" t="n"/>
+      <c r="C26" s="80" t="n"/>
+      <c r="D26" s="80" t="n"/>
+      <c r="E26" s="80" t="n"/>
+      <c r="F26" s="80" t="n"/>
+      <c r="G26" s="80" t="n"/>
+      <c r="H26" s="80" t="n"/>
+      <c r="I26" s="80" t="n"/>
+      <c r="J26" s="80" t="n"/>
+      <c r="K26" s="80" t="n"/>
+      <c r="L26" s="80" t="n"/>
+      <c r="M26" s="80" t="n"/>
+      <c r="N26" s="80" t="n"/>
+      <c r="O26" s="80" t="n"/>
+      <c r="P26" s="80" t="n"/>
+      <c r="Q26" s="105">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="56">
+      <c r="A27" s="80" t="n"/>
+      <c r="B27" s="80" t="n"/>
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="80" t="n"/>
+      <c r="E27" s="80" t="n"/>
+      <c r="F27" s="80" t="n"/>
+      <c r="G27" s="80" t="n"/>
+      <c r="H27" s="80" t="n"/>
+      <c r="I27" s="80" t="n"/>
+      <c r="J27" s="80" t="n"/>
+      <c r="K27" s="80" t="n"/>
+      <c r="L27" s="80" t="n"/>
+      <c r="M27" s="80" t="n"/>
+      <c r="N27" s="80" t="n"/>
+      <c r="O27" s="80" t="n"/>
+      <c r="P27" s="80" t="n"/>
+      <c r="Q27" s="105">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
@@ -4856,622 +6536,632 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>مرجع سریع UI — هیسترزیس 2%/5%/100.95 و نگاشت</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>هیسترزیس: ورودی 20/21 (1000mV), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
         </is>
       </c>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="57" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="57" t="inlineStr">
+      <c r="B3" s="109" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="57" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>رفتار</t>
         </is>
       </c>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D3" s="109" t="inlineStr">
         <is>
           <t>ثابت / محل</t>
         </is>
       </c>
-      <c r="E3" s="57" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="F3" s="57" t="inlineStr">
+      <c r="F3" s="109" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="110" t="inlineStr">
         <is>
           <t>PA3 mapping</t>
         </is>
       </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="110" t="inlineStr">
         <is>
           <t>PA3 pin13 ADC1_IN3 → raw2 → v_bat24_mv → BatteryRun/Charging</t>
         </is>
       </c>
-      <c r="C4" s="58" t="inlineStr">
+      <c r="C4" s="110" t="inlineStr">
         <is>
           <t>فقط v_bat</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="111" t="inlineStr">
         <is>
           <t>board_pins.h:PIN_ADC_24_BAT</t>
         </is>
       </c>
-      <c r="E4" s="58" t="inlineStr">
+      <c r="E4" s="110" t="inlineStr">
         <is>
           <t>PA3→BatteryRun</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="111" t="inlineStr">
         <is>
           <t>UI-001,025</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>PA2 mapping</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t>PA2 pin12 ADC1_IN2 → raw1 → v_in_mv → ورودی</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>فقط v_in</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="112" t="inlineStr">
         <is>
           <t>PIN_ADC_24_IN</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="112" t="inlineStr">
         <is>
           <t>PA2→Input</t>
         </is>
       </c>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="F5" s="113" t="inlineStr">
         <is>
           <t>UI-001,025</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="110" t="inlineStr">
         <is>
           <t>PB4</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="110" t="inlineStr">
         <is>
           <t>MCU_INT_24_IN EXTI دو لبه</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="110" t="inlineStr">
         <is>
           <t>فقط ورودی</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="111" t="inlineStr">
         <is>
           <t>board_pins.h</t>
         </is>
       </c>
-      <c r="E6" s="58" t="inlineStr">
+      <c r="E6" s="110" t="inlineStr">
         <is>
           <t>PB4→ورودی</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="111" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>PB5/PB11</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="112" t="inlineStr">
         <is>
           <t>PB5 Q1 McuPowerPath, PB11 Q17 Changeover</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>بدون تغییر UI</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="113" t="inlineStr">
         <is>
           <t>board_pins.h</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="112" t="inlineStr">
         <is>
           <t>ممنوع UI</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
+      <c r="F7" s="113" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="110" t="inlineStr">
         <is>
           <t>Battery 2%+0/1</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="110" t="inlineStr">
         <is>
           <t>stable0→raw&gt;=2→1, stable1:0→0 &gt;=3→2 else1</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="110" t="inlineStr">
         <is>
           <t>جلوگیری 0↔1</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="110" t="inlineStr">
         <is>
           <t>RUN_HYSTERESIS 2 ZERO2 ONE3</t>
         </is>
       </c>
-      <c r="E8" s="58" t="inlineStr">
+      <c r="E8" s="110" t="inlineStr">
         <is>
           <t>0/1 جدا</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="111" t="inlineStr">
         <is>
           <t>UI-002-010</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t>Battery diff</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>|raw-stable|&gt;=2 → update else keep</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="112" t="inlineStr">
         <is>
           <t>56↔57 حفظ</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="112" t="inlineStr">
         <is>
           <t>RUN_HYSTERESIS 2</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="112" t="inlineStr">
         <is>
           <t>فقط BatteryRun</t>
         </is>
       </c>
-      <c r="F9" s="61" t="inlineStr">
+      <c r="F9" s="113" t="inlineStr">
         <is>
           <t>UI-002-004</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="110" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="110" t="inlineStr">
         <is>
           <t>|raw-stable|&gt;=5 → update else keep, 53..61 حفظ</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="110" t="inlineStr">
         <is>
           <t>پایدار زرد</t>
         </is>
       </c>
-      <c r="D10" s="58" t="inlineStr">
+      <c r="D10" s="110" t="inlineStr">
         <is>
           <t>CHARGING_HYSTERESIS 5</t>
         </is>
       </c>
-      <c r="E10" s="58" t="inlineStr">
+      <c r="E10" s="110" t="inlineStr">
         <is>
           <t>فقط Charging</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="111" t="inlineStr">
         <is>
           <t>UI-011-013</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t>Charging yellow</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="112" t="inlineStr">
         <is>
           <t>remaining=100-stable5, On=remaining*10(min10)</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="112" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="112" t="inlineStr">
         <is>
           <t>ChargingStable</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="112" t="inlineStr">
         <is>
           <t>Off=1000-On</t>
         </is>
       </c>
-      <c r="F11" s="61" t="inlineStr">
+      <c r="F11" s="113" t="inlineStr">
         <is>
           <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="110" t="inlineStr">
         <is>
           <t>Full 100/95</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="110" t="inlineStr">
         <is>
           <t>&gt;=100 InputOk, &lt;95 Charging, else hold</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C12" s="110" t="inlineStr">
         <is>
           <t>جلوگیری 28V پرش</t>
         </is>
       </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="110" t="inlineStr">
         <is>
           <t>FULL_ENTER 100 FULL_EXIT95</t>
         </is>
       </c>
-      <c r="E12" s="58" t="inlineStr">
+      <c r="E12" s="110" t="inlineStr">
         <is>
           <t>stateful</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr">
+      <c r="F12" s="111" t="inlineStr">
         <is>
           <t>UI-015-017</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t>Green phase</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>stable تغییر فاز reset نه، از مرز بعدی</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="112" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="112" t="inlineStr">
         <is>
           <t>UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="E13" s="112" t="inlineStr">
         <is>
           <t>500m hysteresis</t>
         </is>
       </c>
-      <c r="F13" s="61" t="inlineStr">
+      <c r="F13" s="113" t="inlineStr">
         <is>
           <t>UI-002,018</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="110" t="inlineStr">
         <is>
           <t>Yellow phase</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="110" t="inlineStr">
         <is>
           <t>stable5 تغییر فاز reset نه</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="110" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="110" t="inlineStr">
         <is>
           <t>UpdateChargingYellowBlink</t>
         </is>
       </c>
-      <c r="E14" s="58" t="inlineStr">
+      <c r="E14" s="110" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr">
+      <c r="F14" s="111" t="inlineStr">
         <is>
           <t>UI-011,014</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Input present</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>&gt;=21000 وصل &lt;=20000 قطع</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="112" t="inlineStr">
         <is>
           <t>هیسترزیس20/21</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="112" t="inlineStr">
         <is>
           <t>INPUT_CONNECTED</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="112" t="inlineStr">
         <is>
           <t>1000mV</t>
         </is>
       </c>
-      <c r="F15" s="61" t="inlineStr">
+      <c r="F15" s="113" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="110" t="inlineStr">
         <is>
           <t>Overvoltage</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="110" t="inlineStr">
         <is>
           <t>&gt;28000 خطا &lt;=27000 پاک</t>
         </is>
       </c>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="110" t="inlineStr">
         <is>
           <t>قرمز50%+بوق10s</t>
         </is>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="110" t="inlineStr">
         <is>
           <t>OVERVOLTAGE</t>
         </is>
       </c>
-      <c r="E16" s="58" t="inlineStr">
+      <c r="E16" s="110" t="inlineStr">
         <is>
           <t>27/28</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr">
+      <c r="F16" s="111" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="112" t="inlineStr">
         <is>
           <t>Low Alarm</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t>&lt;21000 set &gt;=21200 clear</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="112" t="inlineStr">
         <is>
           <t>پیوسته flag</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="112" t="inlineStr">
         <is>
           <t>LOW_BATTERY</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="112" t="inlineStr">
         <is>
           <t>21000/21200</t>
         </is>
       </c>
-      <c r="F17" s="61" t="inlineStr">
+      <c r="F17" s="113" t="inlineStr">
         <is>
           <t>UI-023</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="110" t="inlineStr">
         <is>
           <t>0% critical</t>
         </is>
       </c>
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="110" t="inlineStr">
         <is>
           <t>&lt;1% 10s یک بار سپس خاموش</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="110" t="inlineStr">
         <is>
           <t>تا خروج 0 تکرار نه</t>
         </is>
       </c>
-      <c r="D18" s="58" t="inlineStr">
+      <c r="D18" s="110" t="inlineStr">
         <is>
           <t>CRITICAL 1</t>
         </is>
       </c>
-      <c r="E18" s="58" t="inlineStr">
+      <c r="E18" s="110" t="inlineStr">
         <is>
           <t>stable0</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr">
+      <c r="F18" s="111" t="inlineStr">
         <is>
           <t>UI-005,006</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="112" t="inlineStr">
         <is>
           <t>Snapshot invalid</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="112" t="inlineStr">
         <is>
           <t>valid false/NULL→safe-off</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="112" t="inlineStr">
         <is>
           <t>flag false phase reset</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="112" t="inlineStr">
         <is>
           <t>Ui_Tick</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="112" t="inlineStr">
         <is>
           <t>no stale</t>
         </is>
       </c>
-      <c r="F19" s="61" t="inlineStr">
+      <c r="F19" s="113" t="inlineStr">
         <is>
           <t>UI-022</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="110" t="inlineStr">
         <is>
           <t>RTOS static</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="110" t="inlineStr">
         <is>
           <t>DYNAMIC 0 cb/stack</t>
         </is>
       </c>
-      <c r="C20" s="58" t="inlineStr">
+      <c r="C20" s="110" t="inlineStr">
         <is>
           <t>همه static</t>
         </is>
       </c>
-      <c r="D20" s="58" t="inlineStr">
+      <c r="D20" s="110" t="inlineStr">
         <is>
           <t>FreeRTOSConfig</t>
         </is>
       </c>
-      <c r="E20" s="58" t="inlineStr">
+      <c r="E20" s="110" t="inlineStr">
         <is>
           <t>word/byte</t>
         </is>
       </c>
-      <c r="F20" s="59" t="inlineStr">
+      <c r="F20" s="111" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="112" t="inlineStr">
         <is>
           <t>Stack</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="112" t="inlineStr">
         <is>
           <t>UI128 Meas192 Ctrl256</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="112" t="inlineStr">
         <is>
           <t>high-water&gt;20%</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="112" t="inlineStr">
         <is>
           <t>rtos_config</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="E21" s="112" t="inlineStr">
         <is>
           <t>512/768/1024B</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="113" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
@@ -5535,235 +7225,259 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس 2%/5%/100.95 و فاز</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="80" t="n"/>
+      <c r="H1" s="80" t="n"/>
+      <c r="I1" s="80" t="n"/>
+      <c r="J1" s="80" t="n"/>
+      <c r="K1" s="80" t="n"/>
+      <c r="L1" s="80" t="n"/>
+      <c r="M1" s="80" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="114" t="inlineStr">
         <is>
           <t>برای هر «رد» یک ردیف؛ فاز چشمک و هیسترزیس 0/1 را با اسکوپ ثبت.</t>
         </is>
       </c>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
+      <c r="G2" s="80" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="80" t="n"/>
+      <c r="J2" s="80" t="n"/>
+      <c r="K2" s="80" t="n"/>
+      <c r="L2" s="80" t="n"/>
+      <c r="M2" s="80" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="82" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="82" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="82" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="36" t="inlineStr">
+      <c r="D3" s="82" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="E3" s="82" t="inlineStr">
         <is>
           <t>شرح کوتاه</t>
         </is>
       </c>
-      <c r="F3" s="36" t="inlineStr">
+      <c r="F3" s="82" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="36" t="inlineStr">
+      <c r="G3" s="82" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="36" t="inlineStr">
+      <c r="H3" s="82" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="36" t="inlineStr">
+      <c r="I3" s="82" t="inlineStr">
         <is>
           <t>مدرک/عکس</t>
         </is>
       </c>
-      <c r="J3" s="36" t="inlineStr">
+      <c r="J3" s="82" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="K3" s="36" t="inlineStr">
+      <c r="K3" s="82" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="36" t="inlineStr">
+      <c r="L3" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M3" s="36" t="inlineStr">
+      <c r="M3" s="82" t="inlineStr">
         <is>
           <t>تأیید رفع</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="17" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr"/>
-      <c r="C4" s="17" t="inlineStr"/>
-      <c r="D4" s="17" t="inlineStr"/>
-      <c r="E4" s="17" t="inlineStr"/>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="17" t="inlineStr"/>
-      <c r="J4" s="17" t="inlineStr"/>
-      <c r="K4" s="17" t="inlineStr"/>
-      <c r="L4" s="17" t="inlineStr"/>
-      <c r="M4" s="17" t="inlineStr"/>
+      <c r="A4" s="115" t="inlineStr"/>
+      <c r="B4" s="115" t="inlineStr"/>
+      <c r="C4" s="115" t="inlineStr"/>
+      <c r="D4" s="115" t="inlineStr"/>
+      <c r="E4" s="115" t="inlineStr"/>
+      <c r="F4" s="115" t="inlineStr"/>
+      <c r="G4" s="115" t="inlineStr"/>
+      <c r="H4" s="115" t="inlineStr"/>
+      <c r="I4" s="115" t="inlineStr"/>
+      <c r="J4" s="115" t="inlineStr"/>
+      <c r="K4" s="115" t="inlineStr"/>
+      <c r="L4" s="115" t="inlineStr"/>
+      <c r="M4" s="115" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="18" t="inlineStr"/>
-      <c r="B5" s="18" t="inlineStr"/>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="18" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr"/>
-      <c r="F5" s="18" t="inlineStr"/>
-      <c r="G5" s="18" t="inlineStr"/>
-      <c r="H5" s="18" t="inlineStr"/>
-      <c r="I5" s="18" t="inlineStr"/>
-      <c r="J5" s="18" t="inlineStr"/>
-      <c r="K5" s="18" t="inlineStr"/>
-      <c r="L5" s="18" t="inlineStr"/>
-      <c r="M5" s="18" t="inlineStr"/>
+      <c r="A5" s="116" t="inlineStr"/>
+      <c r="B5" s="116" t="inlineStr"/>
+      <c r="C5" s="116" t="inlineStr"/>
+      <c r="D5" s="116" t="inlineStr"/>
+      <c r="E5" s="116" t="inlineStr"/>
+      <c r="F5" s="116" t="inlineStr"/>
+      <c r="G5" s="116" t="inlineStr"/>
+      <c r="H5" s="116" t="inlineStr"/>
+      <c r="I5" s="116" t="inlineStr"/>
+      <c r="J5" s="116" t="inlineStr"/>
+      <c r="K5" s="116" t="inlineStr"/>
+      <c r="L5" s="116" t="inlineStr"/>
+      <c r="M5" s="116" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="17" t="inlineStr"/>
-      <c r="B6" s="17" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
+      <c r="A6" s="115" t="inlineStr"/>
+      <c r="B6" s="115" t="inlineStr"/>
+      <c r="C6" s="115" t="inlineStr"/>
+      <c r="D6" s="115" t="inlineStr"/>
+      <c r="E6" s="115" t="inlineStr"/>
+      <c r="F6" s="115" t="inlineStr"/>
+      <c r="G6" s="115" t="inlineStr"/>
+      <c r="H6" s="115" t="inlineStr"/>
+      <c r="I6" s="115" t="inlineStr"/>
+      <c r="J6" s="115" t="inlineStr"/>
+      <c r="K6" s="115" t="inlineStr"/>
+      <c r="L6" s="115" t="inlineStr"/>
+      <c r="M6" s="115" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr"/>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="18" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
-      <c r="I7" s="18" t="inlineStr"/>
-      <c r="J7" s="18" t="inlineStr"/>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="18" t="inlineStr"/>
-      <c r="M7" s="18" t="inlineStr"/>
+      <c r="A7" s="116" t="inlineStr"/>
+      <c r="B7" s="116" t="inlineStr"/>
+      <c r="C7" s="116" t="inlineStr"/>
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="116" t="inlineStr"/>
+      <c r="F7" s="116" t="inlineStr"/>
+      <c r="G7" s="116" t="inlineStr"/>
+      <c r="H7" s="116" t="inlineStr"/>
+      <c r="I7" s="116" t="inlineStr"/>
+      <c r="J7" s="116" t="inlineStr"/>
+      <c r="K7" s="116" t="inlineStr"/>
+      <c r="L7" s="116" t="inlineStr"/>
+      <c r="M7" s="116" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="17" t="inlineStr"/>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr"/>
-      <c r="L8" s="17" t="inlineStr"/>
-      <c r="M8" s="17" t="inlineStr"/>
+      <c r="A8" s="115" t="inlineStr"/>
+      <c r="B8" s="115" t="inlineStr"/>
+      <c r="C8" s="115" t="inlineStr"/>
+      <c r="D8" s="115" t="inlineStr"/>
+      <c r="E8" s="115" t="inlineStr"/>
+      <c r="F8" s="115" t="inlineStr"/>
+      <c r="G8" s="115" t="inlineStr"/>
+      <c r="H8" s="115" t="inlineStr"/>
+      <c r="I8" s="115" t="inlineStr"/>
+      <c r="J8" s="115" t="inlineStr"/>
+      <c r="K8" s="115" t="inlineStr"/>
+      <c r="L8" s="115" t="inlineStr"/>
+      <c r="M8" s="115" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="18" t="inlineStr"/>
-      <c r="M9" s="18" t="inlineStr"/>
+      <c r="A9" s="116" t="inlineStr"/>
+      <c r="B9" s="116" t="inlineStr"/>
+      <c r="C9" s="116" t="inlineStr"/>
+      <c r="D9" s="116" t="inlineStr"/>
+      <c r="E9" s="116" t="inlineStr"/>
+      <c r="F9" s="116" t="inlineStr"/>
+      <c r="G9" s="116" t="inlineStr"/>
+      <c r="H9" s="116" t="inlineStr"/>
+      <c r="I9" s="116" t="inlineStr"/>
+      <c r="J9" s="116" t="inlineStr"/>
+      <c r="K9" s="116" t="inlineStr"/>
+      <c r="L9" s="116" t="inlineStr"/>
+      <c r="M9" s="116" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="17" t="inlineStr"/>
-      <c r="B10" s="17" t="inlineStr"/>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="17" t="inlineStr"/>
-      <c r="M10" s="17" t="inlineStr"/>
+      <c r="A10" s="115" t="inlineStr"/>
+      <c r="B10" s="115" t="inlineStr"/>
+      <c r="C10" s="115" t="inlineStr"/>
+      <c r="D10" s="115" t="inlineStr"/>
+      <c r="E10" s="115" t="inlineStr"/>
+      <c r="F10" s="115" t="inlineStr"/>
+      <c r="G10" s="115" t="inlineStr"/>
+      <c r="H10" s="115" t="inlineStr"/>
+      <c r="I10" s="115" t="inlineStr"/>
+      <c r="J10" s="115" t="inlineStr"/>
+      <c r="K10" s="115" t="inlineStr"/>
+      <c r="L10" s="115" t="inlineStr"/>
+      <c r="M10" s="115" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="18" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr"/>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="18" t="inlineStr"/>
-      <c r="M11" s="18" t="inlineStr"/>
+      <c r="A11" s="116" t="inlineStr"/>
+      <c r="B11" s="116" t="inlineStr"/>
+      <c r="C11" s="116" t="inlineStr"/>
+      <c r="D11" s="116" t="inlineStr"/>
+      <c r="E11" s="116" t="inlineStr"/>
+      <c r="F11" s="116" t="inlineStr"/>
+      <c r="G11" s="116" t="inlineStr"/>
+      <c r="H11" s="116" t="inlineStr"/>
+      <c r="I11" s="116" t="inlineStr"/>
+      <c r="J11" s="116" t="inlineStr"/>
+      <c r="K11" s="116" t="inlineStr"/>
+      <c r="L11" s="116" t="inlineStr"/>
+      <c r="M11" s="116" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="17" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr"/>
-      <c r="L12" s="17" t="inlineStr"/>
-      <c r="M12" s="17" t="inlineStr"/>
+      <c r="A12" s="115" t="inlineStr"/>
+      <c r="B12" s="115" t="inlineStr"/>
+      <c r="C12" s="115" t="inlineStr"/>
+      <c r="D12" s="115" t="inlineStr"/>
+      <c r="E12" s="115" t="inlineStr"/>
+      <c r="F12" s="115" t="inlineStr"/>
+      <c r="G12" s="115" t="inlineStr"/>
+      <c r="H12" s="115" t="inlineStr"/>
+      <c r="I12" s="115" t="inlineStr"/>
+      <c r="J12" s="115" t="inlineStr"/>
+      <c r="K12" s="115" t="inlineStr"/>
+      <c r="L12" s="115" t="inlineStr"/>
+      <c r="M12" s="115" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="18" t="inlineStr"/>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="18" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr"/>
-      <c r="F13" s="18" t="inlineStr"/>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="18" t="inlineStr"/>
-      <c r="I13" s="18" t="inlineStr"/>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr"/>
-      <c r="L13" s="18" t="inlineStr"/>
-      <c r="M13" s="18" t="inlineStr"/>
+      <c r="A13" s="116" t="inlineStr"/>
+      <c r="B13" s="116" t="inlineStr"/>
+      <c r="C13" s="116" t="inlineStr"/>
+      <c r="D13" s="116" t="inlineStr"/>
+      <c r="E13" s="116" t="inlineStr"/>
+      <c r="F13" s="116" t="inlineStr"/>
+      <c r="G13" s="116" t="inlineStr"/>
+      <c r="H13" s="116" t="inlineStr"/>
+      <c r="I13" s="116" t="inlineStr"/>
+      <c r="J13" s="116" t="inlineStr"/>
+      <c r="K13" s="116" t="inlineStr"/>
+      <c r="L13" s="116" t="inlineStr"/>
+      <c r="M13" s="116" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5793,290 +7507,340 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — UI — 2%/5%/100.95</t>
         </is>
       </c>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+      <c r="D1" s="80" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="114" t="inlineStr">
         <is>
           <t>فقط پس از تکمیل تست‌ها و بستن ایرادهای بحرانی/بالا.</t>
         </is>
       </c>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+      <c r="D2" s="80" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="57" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="28" t="n"/>
-      <c r="C3" s="28" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="29" t="n"/>
+      <c r="B3" s="86" t="n"/>
+      <c r="C3" s="86" t="n"/>
+      <c r="D3" s="86" t="n"/>
+      <c r="E3" s="86" t="n"/>
+      <c r="F3" s="87" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="117" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="C4" s="80" t="n"/>
+      <c r="D4" s="117" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="112" t="inlineStr">
         <is>
           <t>UI — BatteryRun/Charging</t>
         </is>
       </c>
+      <c r="F4" s="80" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="117" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t>2026-09-17 (2.2 — 2%+5%+100/95)</t>
         </is>
       </c>
-      <c r="D5" s="63" t="inlineStr">
+      <c r="C5" s="80" t="n"/>
+      <c r="D5" s="117" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="112" t="inlineStr">
         <is>
           <t>2.2 — 2%+5%+ فول+فاز</t>
         </is>
       </c>
+      <c r="F5" s="80" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="117" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="C6" s="80" t="n"/>
+      <c r="D6" s="117" t="inlineStr">
         <is>
           <t>شناسه برد</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr"/>
+      <c r="E6" s="112" t="inlineStr"/>
+      <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="117" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr"/>
-      <c r="D7" s="63" t="inlineStr">
+      <c r="B7" s="112" t="inlineStr"/>
+      <c r="C7" s="80" t="n"/>
+      <c r="D7" s="117" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr"/>
+      <c r="E7" s="112" t="inlineStr"/>
+      <c r="F7" s="80" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="A8" s="117" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr"/>
-      <c r="D8" s="63" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="117" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسکوپ + تایمر10ms</t>
         </is>
       </c>
+      <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="117" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>1000Hz (osKernelGetTickFreq)</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="C9" s="80" t="n"/>
+      <c r="D9" s="117" t="inlineStr">
         <is>
           <t>دوره UI</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="112" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
+      <c r="F9" s="80" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="63" t="inlineStr">
+      <c r="A10" s="117" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>BatteryRun2%+0/1, Charging5%, Full100/95, Low21/21.2</t>
         </is>
       </c>
-      <c r="D10" s="63" t="inlineStr">
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="117" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="112" t="inlineStr">
         <is>
           <t>سبزOff(100-stable)*10 زردOn(100-stable5)*10</t>
         </is>
       </c>
+      <c r="F10" s="80" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="22" t="inlineStr"/>
-      <c r="B11" s="15" t="inlineStr"/>
-      <c r="D11" s="22" t="inlineStr"/>
-      <c r="E11" s="15" t="inlineStr"/>
+      <c r="A11" s="117" t="inlineStr"/>
+      <c r="B11" s="112" t="inlineStr"/>
+      <c r="C11" s="80" t="n"/>
+      <c r="D11" s="117" t="inlineStr"/>
+      <c r="E11" s="112" t="inlineStr"/>
+      <c r="F11" s="80" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>خلاصه وضعیت تست‌ها</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="29" t="n"/>
+      <c r="B12" s="86" t="n"/>
+      <c r="C12" s="86" t="n"/>
+      <c r="D12" s="86" t="n"/>
+      <c r="E12" s="86" t="n"/>
+      <c r="F12" s="87" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="117" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="D13" s="63" t="inlineStr">
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="117" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr"/>
+      <c r="E13" s="112" t="inlineStr"/>
+      <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="63" t="inlineStr">
+      <c r="A14" s="117" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="78" t="inlineStr">
+      <c r="C14" s="80" t="n"/>
+      <c r="D14" s="118" t="inlineStr">
         <is>
           <t>UI-001 تا UI-028</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
+      <c r="E14" s="112" t="inlineStr"/>
+      <c r="F14" s="80" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="A15" s="117" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" s="63" t="inlineStr">
+      <c r="C15" s="80" t="n"/>
+      <c r="D15" s="117" t="inlineStr">
         <is>
           <t>COUNTIF</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr"/>
+      <c r="E15" s="112" t="inlineStr"/>
+      <c r="F15" s="80" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="117" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr"/>
-      <c r="E16" s="15" t="inlineStr"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="117" t="inlineStr"/>
+      <c r="E16" s="112" t="inlineStr"/>
+      <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="A17" s="117" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr"/>
-      <c r="E17" s="15" t="inlineStr"/>
+      <c r="C17" s="80" t="n"/>
+      <c r="D17" s="117" t="inlineStr"/>
+      <c r="E17" s="112" t="inlineStr"/>
+      <c r="F17" s="80" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="63" t="inlineStr">
+      <c r="A18" s="117" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="112" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr"/>
-      <c r="E18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="117" t="inlineStr"/>
+      <c r="E18" s="112" t="inlineStr"/>
+      <c r="F18" s="80" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="80" t="n"/>
+      <c r="B19" s="80" t="n"/>
+      <c r="C19" s="80" t="n"/>
+      <c r="D19" s="80" t="n"/>
+      <c r="E19" s="80" t="n"/>
+      <c r="F19" s="80" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="114" t="inlineStr">
         <is>
           <t>امضا: تست‌کننده ________________  سرپرست ________________  تاریخ ________________</t>
         </is>
       </c>
+      <c r="B20" s="80" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6108,113 +7872,115 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="119" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="120" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="121" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="122" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="123" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="123" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="119" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="123" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="123" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="80" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="119" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="123" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+      <c r="A16" s="123" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="123" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -6240,60 +8006,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول نمایش و بوق (UI)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="80" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="80" t="n"/>
+      <c r="B2" s="80" t="n"/>
+      <c r="C2" s="80" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Ui_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="80" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="80" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="80" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="80" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -378,6 +378,10 @@
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -472,7 +476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -610,11 +614,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -953,6 +958,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1321,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1348,21 +1368,6 @@
           <t>برگه تست و اعتبارسنجی عملی ماژول UI — BatteryRun 2%+0/1, Charging 5%, InputOk 100/95</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
-      <c r="D1" s="80" t="n"/>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
-      <c r="G1" s="80" t="n"/>
-      <c r="H1" s="80" t="n"/>
-      <c r="I1" s="80" t="n"/>
-      <c r="J1" s="80" t="n"/>
-      <c r="K1" s="80" t="n"/>
-      <c r="L1" s="80" t="n"/>
-      <c r="M1" s="80" t="n"/>
-      <c r="N1" s="80" t="n"/>
-      <c r="O1" s="80" t="n"/>
-      <c r="P1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="81" t="inlineStr">
@@ -1370,21 +1375,6 @@
           <t>PA3/ADC1_IN3/raw2/v_bat24 → BatteryRun/Charging | PA2/ADC1_IN2/raw1/v_in → ورودی | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
         </is>
       </c>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-      <c r="D2" s="80" t="n"/>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
-      <c r="G2" s="80" t="n"/>
-      <c r="H2" s="80" t="n"/>
-      <c r="I2" s="80" t="n"/>
-      <c r="J2" s="80" t="n"/>
-      <c r="K2" s="80" t="n"/>
-      <c r="L2" s="80" t="n"/>
-      <c r="M2" s="80" t="n"/>
-      <c r="N2" s="80" t="n"/>
-      <c r="O2" s="80" t="n"/>
-      <c r="P2" s="80" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="82" t="inlineStr">
@@ -1392,21 +1382,21 @@
           <t>هدف فایل</t>
         </is>
       </c>
-      <c r="B3" s="83" t="n"/>
-      <c r="C3" s="83" t="n"/>
-      <c r="D3" s="83" t="n"/>
-      <c r="E3" s="83" t="n"/>
-      <c r="F3" s="83" t="n"/>
-      <c r="G3" s="83" t="n"/>
-      <c r="H3" s="83" t="n"/>
-      <c r="I3" s="83" t="n"/>
-      <c r="J3" s="83" t="n"/>
-      <c r="K3" s="83" t="n"/>
-      <c r="L3" s="83" t="n"/>
-      <c r="M3" s="83" t="n"/>
-      <c r="N3" s="83" t="n"/>
-      <c r="O3" s="83" t="n"/>
-      <c r="P3" s="84" t="n"/>
+      <c r="B3" s="73" t="n"/>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="73" t="n"/>
+      <c r="E3" s="73" t="n"/>
+      <c r="F3" s="73" t="n"/>
+      <c r="G3" s="73" t="n"/>
+      <c r="H3" s="73" t="n"/>
+      <c r="I3" s="73" t="n"/>
+      <c r="J3" s="73" t="n"/>
+      <c r="K3" s="73" t="n"/>
+      <c r="L3" s="73" t="n"/>
+      <c r="M3" s="73" t="n"/>
+      <c r="N3" s="73" t="n"/>
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="74" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
@@ -1414,21 +1404,21 @@
           <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
         </is>
       </c>
-      <c r="B4" s="86" t="n"/>
-      <c r="C4" s="86" t="n"/>
-      <c r="D4" s="86" t="n"/>
-      <c r="E4" s="86" t="n"/>
-      <c r="F4" s="86" t="n"/>
-      <c r="G4" s="86" t="n"/>
-      <c r="H4" s="86" t="n"/>
-      <c r="I4" s="86" t="n"/>
-      <c r="J4" s="86" t="n"/>
-      <c r="K4" s="86" t="n"/>
-      <c r="L4" s="86" t="n"/>
-      <c r="M4" s="86" t="n"/>
-      <c r="N4" s="86" t="n"/>
-      <c r="O4" s="86" t="n"/>
-      <c r="P4" s="87" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="28" t="n"/>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="28" t="n"/>
+      <c r="N4" s="28" t="n"/>
+      <c r="O4" s="28" t="n"/>
+      <c r="P4" s="29" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="88" t="inlineStr">
@@ -1436,21 +1426,21 @@
           <t>منبع و mapping</t>
         </is>
       </c>
-      <c r="B5" s="86" t="n"/>
-      <c r="C5" s="86" t="n"/>
-      <c r="D5" s="86" t="n"/>
-      <c r="E5" s="86" t="n"/>
-      <c r="F5" s="86" t="n"/>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="86" t="n"/>
-      <c r="I5" s="86" t="n"/>
-      <c r="J5" s="86" t="n"/>
-      <c r="K5" s="86" t="n"/>
-      <c r="L5" s="86" t="n"/>
-      <c r="M5" s="86" t="n"/>
-      <c r="N5" s="86" t="n"/>
-      <c r="O5" s="86" t="n"/>
-      <c r="P5" s="87" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="29" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="85" t="inlineStr">
@@ -1458,21 +1448,21 @@
           <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
         </is>
       </c>
-      <c r="B6" s="86" t="n"/>
-      <c r="C6" s="86" t="n"/>
-      <c r="D6" s="86" t="n"/>
-      <c r="E6" s="86" t="n"/>
-      <c r="F6" s="86" t="n"/>
-      <c r="G6" s="86" t="n"/>
-      <c r="H6" s="86" t="n"/>
-      <c r="I6" s="86" t="n"/>
-      <c r="J6" s="86" t="n"/>
-      <c r="K6" s="86" t="n"/>
-      <c r="L6" s="86" t="n"/>
-      <c r="M6" s="86" t="n"/>
-      <c r="N6" s="86" t="n"/>
-      <c r="O6" s="86" t="n"/>
-      <c r="P6" s="87" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="28" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="28" t="n"/>
+      <c r="O6" s="28" t="n"/>
+      <c r="P6" s="29" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="88" t="inlineStr">
@@ -1480,21 +1470,21 @@
           <t>BatteryRun 2%+0/1</t>
         </is>
       </c>
-      <c r="B7" s="86" t="n"/>
-      <c r="C7" s="86" t="n"/>
-      <c r="D7" s="86" t="n"/>
-      <c r="E7" s="86" t="n"/>
-      <c r="F7" s="86" t="n"/>
-      <c r="G7" s="86" t="n"/>
-      <c r="H7" s="86" t="n"/>
-      <c r="I7" s="86" t="n"/>
-      <c r="J7" s="86" t="n"/>
-      <c r="K7" s="86" t="n"/>
-      <c r="L7" s="86" t="n"/>
-      <c r="M7" s="86" t="n"/>
-      <c r="N7" s="86" t="n"/>
-      <c r="O7" s="86" t="n"/>
-      <c r="P7" s="87" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="28" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="29" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="85" t="inlineStr">
@@ -1502,21 +1492,21 @@
           <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
         </is>
       </c>
-      <c r="B8" s="86" t="n"/>
-      <c r="C8" s="86" t="n"/>
-      <c r="D8" s="86" t="n"/>
-      <c r="E8" s="86" t="n"/>
-      <c r="F8" s="86" t="n"/>
-      <c r="G8" s="86" t="n"/>
-      <c r="H8" s="86" t="n"/>
-      <c r="I8" s="86" t="n"/>
-      <c r="J8" s="86" t="n"/>
-      <c r="K8" s="86" t="n"/>
-      <c r="L8" s="86" t="n"/>
-      <c r="M8" s="86" t="n"/>
-      <c r="N8" s="86" t="n"/>
-      <c r="O8" s="86" t="n"/>
-      <c r="P8" s="87" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="28" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+      <c r="O8" s="28" t="n"/>
+      <c r="P8" s="29" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="88" t="inlineStr">
@@ -1524,21 +1514,21 @@
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B9" s="86" t="n"/>
-      <c r="C9" s="86" t="n"/>
-      <c r="D9" s="86" t="n"/>
-      <c r="E9" s="86" t="n"/>
-      <c r="F9" s="86" t="n"/>
-      <c r="G9" s="86" t="n"/>
-      <c r="H9" s="86" t="n"/>
-      <c r="I9" s="86" t="n"/>
-      <c r="J9" s="86" t="n"/>
-      <c r="K9" s="86" t="n"/>
-      <c r="L9" s="86" t="n"/>
-      <c r="M9" s="86" t="n"/>
-      <c r="N9" s="86" t="n"/>
-      <c r="O9" s="86" t="n"/>
-      <c r="P9" s="87" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
+      <c r="P9" s="29" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="85" t="inlineStr">
@@ -1546,21 +1536,21 @@
           <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
         </is>
       </c>
-      <c r="B10" s="86" t="n"/>
-      <c r="C10" s="86" t="n"/>
-      <c r="D10" s="86" t="n"/>
-      <c r="E10" s="86" t="n"/>
-      <c r="F10" s="86" t="n"/>
-      <c r="G10" s="86" t="n"/>
-      <c r="H10" s="86" t="n"/>
-      <c r="I10" s="86" t="n"/>
-      <c r="J10" s="86" t="n"/>
-      <c r="K10" s="86" t="n"/>
-      <c r="L10" s="86" t="n"/>
-      <c r="M10" s="86" t="n"/>
-      <c r="N10" s="86" t="n"/>
-      <c r="O10" s="86" t="n"/>
-      <c r="P10" s="87" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="29" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="88" t="inlineStr">
@@ -1568,21 +1558,21 @@
           <t>فول InputOk/Charging 100/95</t>
         </is>
       </c>
-      <c r="B11" s="86" t="n"/>
-      <c r="C11" s="86" t="n"/>
-      <c r="D11" s="86" t="n"/>
-      <c r="E11" s="86" t="n"/>
-      <c r="F11" s="86" t="n"/>
-      <c r="G11" s="86" t="n"/>
-      <c r="H11" s="86" t="n"/>
-      <c r="I11" s="86" t="n"/>
-      <c r="J11" s="86" t="n"/>
-      <c r="K11" s="86" t="n"/>
-      <c r="L11" s="86" t="n"/>
-      <c r="M11" s="86" t="n"/>
-      <c r="N11" s="86" t="n"/>
-      <c r="O11" s="86" t="n"/>
-      <c r="P11" s="87" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="29" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="85" t="inlineStr">
@@ -1590,21 +1580,21 @@
           <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
         </is>
       </c>
-      <c r="B12" s="86" t="n"/>
-      <c r="C12" s="86" t="n"/>
-      <c r="D12" s="86" t="n"/>
-      <c r="E12" s="86" t="n"/>
-      <c r="F12" s="86" t="n"/>
-      <c r="G12" s="86" t="n"/>
-      <c r="H12" s="86" t="n"/>
-      <c r="I12" s="86" t="n"/>
-      <c r="J12" s="86" t="n"/>
-      <c r="K12" s="86" t="n"/>
-      <c r="L12" s="86" t="n"/>
-      <c r="M12" s="86" t="n"/>
-      <c r="N12" s="86" t="n"/>
-      <c r="O12" s="86" t="n"/>
-      <c r="P12" s="87" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="29" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="88" t="inlineStr">
@@ -1612,21 +1602,21 @@
           <t>حفظ فاز</t>
         </is>
       </c>
-      <c r="B13" s="86" t="n"/>
-      <c r="C13" s="86" t="n"/>
-      <c r="D13" s="86" t="n"/>
-      <c r="E13" s="86" t="n"/>
-      <c r="F13" s="86" t="n"/>
-      <c r="G13" s="86" t="n"/>
-      <c r="H13" s="86" t="n"/>
-      <c r="I13" s="86" t="n"/>
-      <c r="J13" s="86" t="n"/>
-      <c r="K13" s="86" t="n"/>
-      <c r="L13" s="86" t="n"/>
-      <c r="M13" s="86" t="n"/>
-      <c r="N13" s="86" t="n"/>
-      <c r="O13" s="86" t="n"/>
-      <c r="P13" s="87" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="28" t="n"/>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="28" t="n"/>
+      <c r="P13" s="29" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="85" t="inlineStr">
@@ -1634,21 +1624,21 @@
           <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
         </is>
       </c>
-      <c r="B14" s="86" t="n"/>
-      <c r="C14" s="86" t="n"/>
-      <c r="D14" s="86" t="n"/>
-      <c r="E14" s="86" t="n"/>
-      <c r="F14" s="86" t="n"/>
-      <c r="G14" s="86" t="n"/>
-      <c r="H14" s="86" t="n"/>
-      <c r="I14" s="86" t="n"/>
-      <c r="J14" s="86" t="n"/>
-      <c r="K14" s="86" t="n"/>
-      <c r="L14" s="86" t="n"/>
-      <c r="M14" s="86" t="n"/>
-      <c r="N14" s="86" t="n"/>
-      <c r="O14" s="86" t="n"/>
-      <c r="P14" s="87" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
+      <c r="P14" s="29" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="88" t="inlineStr">
@@ -1656,21 +1646,21 @@
           <t>غیرمسدودکننده</t>
         </is>
       </c>
-      <c r="B15" s="86" t="n"/>
-      <c r="C15" s="86" t="n"/>
-      <c r="D15" s="86" t="n"/>
-      <c r="E15" s="86" t="n"/>
-      <c r="F15" s="86" t="n"/>
-      <c r="G15" s="86" t="n"/>
-      <c r="H15" s="86" t="n"/>
-      <c r="I15" s="86" t="n"/>
-      <c r="J15" s="86" t="n"/>
-      <c r="K15" s="86" t="n"/>
-      <c r="L15" s="86" t="n"/>
-      <c r="M15" s="86" t="n"/>
-      <c r="N15" s="86" t="n"/>
-      <c r="O15" s="86" t="n"/>
-      <c r="P15" s="87" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="29" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="85" t="inlineStr">
@@ -1678,21 +1668,21 @@
           <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
         </is>
       </c>
-      <c r="B16" s="86" t="n"/>
-      <c r="C16" s="86" t="n"/>
-      <c r="D16" s="86" t="n"/>
-      <c r="E16" s="86" t="n"/>
-      <c r="F16" s="86" t="n"/>
-      <c r="G16" s="86" t="n"/>
-      <c r="H16" s="86" t="n"/>
-      <c r="I16" s="86" t="n"/>
-      <c r="J16" s="86" t="n"/>
-      <c r="K16" s="86" t="n"/>
-      <c r="L16" s="86" t="n"/>
-      <c r="M16" s="86" t="n"/>
-      <c r="N16" s="86" t="n"/>
-      <c r="O16" s="86" t="n"/>
-      <c r="P16" s="87" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="28" t="n"/>
+      <c r="P16" s="29" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="88" t="inlineStr">
@@ -1700,21 +1690,21 @@
           <t>RTOS و حافظه</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n"/>
-      <c r="C17" s="86" t="n"/>
-      <c r="D17" s="86" t="n"/>
-      <c r="E17" s="86" t="n"/>
-      <c r="F17" s="86" t="n"/>
-      <c r="G17" s="86" t="n"/>
-      <c r="H17" s="86" t="n"/>
-      <c r="I17" s="86" t="n"/>
-      <c r="J17" s="86" t="n"/>
-      <c r="K17" s="86" t="n"/>
-      <c r="L17" s="86" t="n"/>
-      <c r="M17" s="86" t="n"/>
-      <c r="N17" s="86" t="n"/>
-      <c r="O17" s="86" t="n"/>
-      <c r="P17" s="87" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="29" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
@@ -1722,21 +1712,29 @@
           <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n"/>
-      <c r="C18" s="86" t="n"/>
-      <c r="D18" s="86" t="n"/>
-      <c r="E18" s="86" t="n"/>
-      <c r="F18" s="86" t="n"/>
-      <c r="G18" s="86" t="n"/>
-      <c r="H18" s="86" t="n"/>
-      <c r="I18" s="86" t="n"/>
-      <c r="J18" s="86" t="n"/>
-      <c r="K18" s="86" t="n"/>
-      <c r="L18" s="86" t="n"/>
-      <c r="M18" s="86" t="n"/>
-      <c r="N18" s="86" t="n"/>
-      <c r="O18" s="86" t="n"/>
-      <c r="P18" s="87" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="28" t="n"/>
+      <c r="P18" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="124" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1799,22 +1797,6 @@
           <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
-      <c r="D1" s="80" t="n"/>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
-      <c r="G1" s="80" t="n"/>
-      <c r="H1" s="80" t="n"/>
-      <c r="I1" s="80" t="n"/>
-      <c r="J1" s="80" t="n"/>
-      <c r="K1" s="80" t="n"/>
-      <c r="L1" s="80" t="n"/>
-      <c r="M1" s="80" t="n"/>
-      <c r="N1" s="80" t="n"/>
-      <c r="O1" s="80" t="n"/>
-      <c r="P1" s="80" t="n"/>
-      <c r="Q1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="90" t="inlineStr">
@@ -1822,22 +1804,6 @@
           <t>ورودی mV، درصد 0-100، زمان ms. BatteryRun PA3 stable2%، Charging PA3 stable5% و زرد، Full 100/95 با raw.</t>
         </is>
       </c>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-      <c r="D2" s="80" t="n"/>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
-      <c r="G2" s="80" t="n"/>
-      <c r="H2" s="80" t="n"/>
-      <c r="I2" s="80" t="n"/>
-      <c r="J2" s="80" t="n"/>
-      <c r="K2" s="80" t="n"/>
-      <c r="L2" s="80" t="n"/>
-      <c r="M2" s="80" t="n"/>
-      <c r="N2" s="80" t="n"/>
-      <c r="O2" s="80" t="n"/>
-      <c r="P2" s="80" t="n"/>
-      <c r="Q2" s="80" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="91" t="inlineStr">
@@ -1845,22 +1811,6 @@
           <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable, ورودی present/overvoltage, فاز LED/بوق با اسکوپ 10ms. InputOk/Charging سریع برگردد.</t>
         </is>
       </c>
-      <c r="B3" s="80" t="n"/>
-      <c r="C3" s="80" t="n"/>
-      <c r="D3" s="80" t="n"/>
-      <c r="E3" s="80" t="n"/>
-      <c r="F3" s="80" t="n"/>
-      <c r="G3" s="80" t="n"/>
-      <c r="H3" s="80" t="n"/>
-      <c r="I3" s="80" t="n"/>
-      <c r="J3" s="80" t="n"/>
-      <c r="K3" s="80" t="n"/>
-      <c r="L3" s="80" t="n"/>
-      <c r="M3" s="80" t="n"/>
-      <c r="N3" s="80" t="n"/>
-      <c r="O3" s="80" t="n"/>
-      <c r="P3" s="80" t="n"/>
-      <c r="Q3" s="80" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="82" t="inlineStr">
@@ -1910,7 +1860,7 @@
       </c>
       <c r="J4" s="82" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="82" t="inlineStr">
@@ -1952,80 +1902,82 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="92" t="inlineStr">
         <is>
-          <t>UI-002</t>
-        </is>
-      </c>
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>BatteryRun 2% 56/57/58</t>
-        </is>
-      </c>
-      <c r="C5" s="94" t="inlineStr">
+          <t>UI-036</t>
+        </is>
+      </c>
+      <c r="B5" s="98" t="inlineStr">
+        <is>
+          <t>رفتار کلی چراغ سبز</t>
+        </is>
+      </c>
+      <c r="C5" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="93" t="inlineStr">
-        <is>
-          <t>دستگاه فقط روی باتری کار می‌کند (برق شهر قطع)؛ به‌جای باتری یک منبع آزمایشگاهی ۲۴ ولت گذاشته‌ای و درصد حدود نصف است</t>
-        </is>
-      </c>
-      <c r="E5" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: منبع را آن‌قدر تنظیم کن که درصد باتری حدود ۵۷ شود و چشمک سبز جا بیفتد.
-گام ۲: ولتاژ منبع را خیلی کم بالا و پایین کن، در حدی که درصد بین ۵۶ و ۵۸ بازی کند.
-گام ۳: یک دقیقه فقط به چراغ سبز نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F5" s="95" t="inlineStr">
-        <is>
-          <t>لرزش کوچک ولتاژ باتری دور درصد ۵۷</t>
-        </is>
-      </c>
-      <c r="G5" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H5" s="93" t="inlineStr">
-        <is>
-          <t>چشمک سبز با همان ریتم قبلی ادامه می‌دهد؛ نه تند و کند می‌شود نه از اول شروع می‌شود</t>
-        </is>
-      </c>
-      <c r="I5" s="93" t="inlineStr">
-        <is>
-          <t>ریتم ثابت و بی‌پرش</t>
-        </is>
-      </c>
-      <c r="J5" s="93" t="inlineStr">
-        <is>
-          <t>ریتم ثابت بماند = قبول؛ پریدن یا عوض‌شدن ریتم با هر تغییر کوچک = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="93" t="inlineStr"/>
+      <c r="D5" s="98" t="inlineStr">
+        <is>
+          <t>دستگاه سالم؛ باتری وصل؛ منبع آزمایشگاهی برای ورودی؛ باتری نیمه‌پُر</t>
+        </is>
+      </c>
+      <c r="E5" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: ورودی را قطع کن و فقط با باتری کار کن؛ چراغ سبز را نگاه کن.
+گام ۲: ورودی ۲۴ ولت را وصل کن؛ سبز را نگاه کن.
+گام ۳: صبر کن شارژ کامل شود؛ سبز و زرد را نگاه کن.
+گام ۴: ورودی را قطع کن؛ سبز را دوباره نگاه کن.
+گام ۵: ورودی را وصل کن، حین شارژ سیم باتری را بکش و بعد وصل کن؛ سبز را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F5" s="101" t="inlineStr">
+        <is>
+          <t>ورودی قطع و ۲۴ ولت؛ قطع باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="G5" s="101" t="inlineStr">
+        <is>
+          <t>چند دقیقه</t>
+        </is>
+      </c>
+      <c r="H5" s="98" t="inlineStr">
+        <is>
+          <t>روی باتری: سبز چشمک‌زن؛ با ورودی: سبز ثابت؛ شارژ کامل: سبز ثابت و زرد خاموش؛ قطع ورودی: سبز دوباره چشمک‌زن؛ خطای قطع باتری: سبز ثابت می‌ماند</t>
+        </is>
+      </c>
+      <c r="I5" s="98" t="inlineStr">
+        <is>
+          <t>چشمک روی باتری، ثابت با ورودی</t>
+        </is>
+      </c>
+      <c r="J5" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: روی باتری سبز چشمک می‌زند؛ به‌محض وصل ورودی سبز ثابت می‌شود و تا کامل‌شدن شارژ ثابت می‌ماند؛ با قطع ورودی دوباره چشمک می‌زند. اگر جایی سبز خاموش بود یا برعکس رفتار کرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="98" t="n"/>
       <c r="L5" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="93" t="inlineStr"/>
-      <c r="N5" s="93" t="inlineStr"/>
-      <c r="O5" s="95" t="inlineStr"/>
-      <c r="P5" s="95" t="inlineStr"/>
-      <c r="Q5" s="97">
-        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+      <c r="M5" s="98" t="n"/>
+      <c r="N5" s="98" t="n"/>
+      <c r="O5" s="101" t="n"/>
+      <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="102">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="92" t="inlineStr">
         <is>
-          <t>UI-003</t>
+          <t>UI-005</t>
         </is>
       </c>
       <c r="B6" s="98" t="inlineStr">
         <is>
-          <t>BatteryRun 57→55</t>
+          <t>باتری خالیِ کامل (درصد صفر)</t>
         </is>
       </c>
       <c r="C6" s="99" t="inlineStr">
@@ -2033,1089 +1985,215 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="100" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
       <c r="E6" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا درصد به حدود ۵۵ برسد.
-گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
-گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F6" s="101" t="inlineStr">
-        <is>
-          <t>کم‌کردن آرام ولتاژ باتری تا درصد ۵۵</t>
-        </is>
-      </c>
-      <c r="G6" s="101" t="inlineStr">
-        <is>
-          <t>نیم دقیقه</t>
-        </is>
-      </c>
-      <c r="H6" s="98" t="inlineStr">
-        <is>
-          <t>درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر می‌شود (خاموشی‌اش بیشتر از قبل)</t>
-        </is>
-      </c>
-      <c r="I6" s="100" t="inlineStr">
-        <is>
-          <t>تندتر از UI-002، بدون پرش ناگهانی</t>
-        </is>
-      </c>
-      <c r="J6" s="98" t="inlineStr">
-        <is>
-          <t>پایدار روی ۵۵ با ریتم تندتر = قبول؛ ماندن روی ۵۷ = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="98" t="inlineStr"/>
-      <c r="L6" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M6" s="98" t="inlineStr"/>
-      <c r="N6" s="98" t="inlineStr"/>
-      <c r="O6" s="101" t="inlineStr"/>
-      <c r="P6" s="101" t="inlineStr"/>
-      <c r="Q6" s="102">
-        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="92" t="inlineStr">
-        <is>
-          <t>UI-004</t>
-        </is>
-      </c>
-      <c r="B7" s="93" t="inlineStr">
-        <is>
-          <t>BatteryRun 57→59</t>
-        </is>
-      </c>
-      <c r="C7" s="94" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="103" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
-        </is>
-      </c>
-      <c r="E7" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ منبع را آرام بالا ببر تا درصد به حدود ۵۹ برسد.
-گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
-گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F7" s="95" t="inlineStr">
-        <is>
-          <t>بالابردن آرام ولتاژ باتری تا درصد ۵۹</t>
-        </is>
-      </c>
-      <c r="G7" s="95" t="inlineStr">
-        <is>
-          <t>نیم دقیقه</t>
-        </is>
-      </c>
-      <c r="H7" s="93" t="inlineStr">
-        <is>
-          <t>درصد روی ۵۹ می‌ایستد و چشمک سبز کمی کندتر می‌شود (روشن بودنش بیشتر از قبل)</t>
-        </is>
-      </c>
-      <c r="I7" s="103" t="inlineStr">
-        <is>
-          <t>کندتر از UI-002، بدون پرش ناگهانی</t>
-        </is>
-      </c>
-      <c r="J7" s="93" t="inlineStr">
-        <is>
-          <t>پایدار روی ۵۹ با ریتم کندتر = قبول؛ ماندن روی ۵۷ = رد</t>
-        </is>
-      </c>
-      <c r="K7" s="93" t="inlineStr"/>
-      <c r="L7" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="93" t="inlineStr"/>
-      <c r="N7" s="93" t="inlineStr"/>
-      <c r="O7" s="95" t="inlineStr"/>
-      <c r="P7" s="95" t="inlineStr"/>
-      <c r="Q7" s="97">
-        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="92" t="inlineStr">
-        <is>
-          <t>UI-005</t>
-        </is>
-      </c>
-      <c r="B8" s="98" t="inlineStr">
-        <is>
-          <t>باتری خالیِ کامل (درصد صفر)</t>
-        </is>
-      </c>
-      <c r="C8" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="98" t="inlineStr">
-        <is>
-          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
-        </is>
-      </c>
-      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا باتری تقریباً خالی شود و درصد به صفر برسد.
 گام ۲: از لحظهٔ صفر شدن، به بوق و چراغ‌ها دقت کن.
 گام ۳: همان ولتاژ را نگه دار و یک دقیقه صبر کن.</t>
         </is>
       </c>
-      <c r="F8" s="101" t="inlineStr">
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>باتری نزدیک خالی کامل (درصد صفر)</t>
         </is>
       </c>
-      <c r="G8" s="101" t="inlineStr">
+      <c r="G6" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="98" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>یک بوق بلند حدود ده ثانیه می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود تا وقتی باتری از خالیِ کامل بیرون بیاید</t>
         </is>
       </c>
-      <c r="I8" s="98" t="inlineStr">
+      <c r="I6" s="98" t="inlineStr">
         <is>
           <t>بعد از بوق: همه خاموش</t>
         </is>
       </c>
-      <c r="J8" s="98" t="inlineStr">
-        <is>
-          <t>فقط یک بوق بلند و بعد خاموشی = قبول؛ بوق تکراری یا چراغ روشنِ مانده = رد</t>
-        </is>
-      </c>
-      <c r="K8" s="98" t="inlineStr"/>
-      <c r="L8" s="96" t="inlineStr">
+      <c r="J6" s="98" t="inlineStr">
+        <is>
+          <t>باید بشنوید و ببینید: فقط یک بوق بلند حدود ده‌ثانیه‌ای می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود. اگر بوق تکرار شد یا چراغی روشن ماند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="98" t="n"/>
+      <c r="L6" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="98" t="inlineStr"/>
-      <c r="N8" s="98" t="inlineStr"/>
-      <c r="O8" s="101" t="inlineStr"/>
-      <c r="P8" s="101" t="inlineStr"/>
-      <c r="Q8" s="102">
-        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+      <c r="M6" s="98" t="n"/>
+      <c r="N6" s="98" t="n"/>
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="101" t="n"/>
+      <c r="Q6" s="102">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="92" t="inlineStr">
-        <is>
-          <t>UI-006</t>
-        </is>
-      </c>
-      <c r="B9" s="93" t="inlineStr">
-        <is>
-          <t>0↔1 نویز</t>
-        </is>
-      </c>
-      <c r="C9" s="94" t="inlineStr">
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="92" t="inlineStr">
+        <is>
+          <t>UI-015</t>
+        </is>
+      </c>
+      <c r="B7" s="98" t="inlineStr">
+        <is>
+          <t>Full 100/95 enter</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="103" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-005؛ درصد روی صفر و بوق بحرانی تمام شده</t>
-        </is>
-      </c>
-      <c r="E9" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ منبع را خیلی کم بالا و پایین کن، دور مرز صفر و یک درصد.
-گام ۲: دو دقیقه به چراغ‌ها و بوق گوش بده.</t>
-        </is>
-      </c>
-      <c r="F9" s="95" t="inlineStr">
-        <is>
-          <t>بازی ولتاژ دور مرز ۰ و ۱ درصد</t>
-        </is>
-      </c>
-      <c r="G9" s="95" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H9" s="93" t="inlineStr">
-        <is>
-          <t>بوق بحرانی دوباره شروع نمی‌شود و چراغ‌ها بی‌دلیل روشن و خاموش نمی‌شوند</t>
-        </is>
-      </c>
-      <c r="I9" s="93" t="inlineStr">
-        <is>
-          <t>خاموش و آرام</t>
-        </is>
-      </c>
-      <c r="J9" s="93" t="inlineStr">
-        <is>
-          <t>آرام ماندن = قبول؛ شروع دوبارهٔ بوق با هر نوسان کوچک = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="93" t="inlineStr"/>
-      <c r="L9" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="93" t="inlineStr"/>
-      <c r="N9" s="93" t="inlineStr"/>
-      <c r="O9" s="95" t="inlineStr"/>
-      <c r="P9" s="95" t="inlineStr"/>
-      <c r="Q9" s="97">
-        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="92" t="inlineStr">
-        <is>
-          <t>UI-007</t>
-        </is>
-      </c>
-      <c r="B10" s="98" t="inlineStr">
-        <is>
-          <t>درصد ۱ (نزدیک خالی)</t>
-        </is>
-      </c>
-      <c r="C10" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="98" t="inlineStr">
-        <is>
-          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
-        </is>
-      </c>
-      <c r="E10" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ را طوری تنظیم کن که درصد روی ۱ بایستد (باتری تقریباً خالی ولی نه صفر).
-گام ۲: دو دقیقه چراغ سبز و بوق را زیر نظر بگیر.</t>
-        </is>
-      </c>
-      <c r="F10" s="101" t="inlineStr">
-        <is>
-          <t>درصد پایدار ۱</t>
-        </is>
-      </c>
-      <c r="G10" s="101" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H10" s="98" t="inlineStr">
-        <is>
-          <t>هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
-        </is>
-      </c>
-      <c r="I10" s="98" t="inlineStr">
-        <is>
-          <t>برق‌های کوتاه و کم</t>
-        </is>
-      </c>
-      <c r="J10" s="98" t="inlineStr">
-        <is>
-          <t>همین رفتار = قبول؛ رفتارِ درصد صفر (بوق بلند و خاموشی کامل) = رد</t>
-        </is>
-      </c>
-      <c r="K10" s="98" t="inlineStr"/>
-      <c r="L10" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M10" s="98" t="inlineStr"/>
-      <c r="N10" s="98" t="inlineStr"/>
-      <c r="O10" s="101" t="inlineStr"/>
-      <c r="P10" s="101" t="inlineStr"/>
-      <c r="Q10" s="102">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="92" t="inlineStr">
-        <is>
-          <t>UI-008</t>
-        </is>
-      </c>
-      <c r="B11" s="93" t="inlineStr">
-        <is>
-          <t>1% →2 حفظ/خروج</t>
-        </is>
-      </c>
-      <c r="C11" s="95" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D11" s="103" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
-        </is>
-      </c>
-      <c r="E11" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ را خیلی کم بالا ببر، آن‌قدر که درصد هنوز ۲ نشده باشد.
-گام ۲: یک دقیقه رفتار را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F11" s="95" t="inlineStr">
-        <is>
-          <t>بالا بردن جزئی از درصد ۱</t>
-        </is>
-      </c>
-      <c r="G11" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H11" s="93" t="inlineStr">
-        <is>
-          <t>همان رفتار درصد ۱ می‌ماند: سه بوق هر از چندی و برق کوتاه سبز</t>
-        </is>
-      </c>
-      <c r="I11" s="93" t="inlineStr">
-        <is>
-          <t>بدون تغییر</t>
-        </is>
-      </c>
-      <c r="J11" s="93" t="inlineStr">
-        <is>
-          <t>ماندن روی رفتار ۱ = قبول؛ پریدن به الگوی درصد ۲ = رد</t>
-        </is>
-      </c>
-      <c r="K11" s="93" t="inlineStr"/>
-      <c r="L11" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="93" t="inlineStr"/>
-      <c r="N11" s="93" t="inlineStr"/>
-      <c r="O11" s="95" t="inlineStr"/>
-      <c r="P11" s="95" t="inlineStr"/>
-      <c r="Q11" s="97">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="92" t="inlineStr">
-        <is>
-          <t>UI-009</t>
-        </is>
-      </c>
-      <c r="B12" s="98" t="inlineStr">
-        <is>
-          <t>1% →2 خروج با3</t>
-        </is>
-      </c>
-      <c r="C12" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="100" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
-        </is>
-      </c>
-      <c r="E12" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ را آرام بالا ببر تا درصد به ۲ برسد و ثابت شود.
-گام ۲: یک دقیقه به الگوی بوق گوش بده و با درصد ۱ مقایسه کن.</t>
-        </is>
-      </c>
-      <c r="F12" s="101" t="inlineStr">
-        <is>
-          <t>بالا بردن ولتاژ تا درصد ۲</t>
-        </is>
-      </c>
-      <c r="G12" s="101" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H12" s="98" t="inlineStr">
-        <is>
-          <t>الگوی بوق به الگوی ملایم‌ترِ درصد ۲ عوض می‌شود و سبز بیشتر از قبل روشن می‌ماند</t>
-        </is>
-      </c>
-      <c r="I12" s="98" t="inlineStr">
-        <is>
-          <t>روشن‌تر از درصد ۱</t>
-        </is>
-      </c>
-      <c r="J12" s="98" t="inlineStr">
-        <is>
-          <t>عوض‌شدن الگو روی ۲ = قبول؛ ماندن روی الگوی ۱ = رد</t>
-        </is>
-      </c>
-      <c r="K12" s="98" t="inlineStr"/>
-      <c r="L12" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="98" t="inlineStr"/>
-      <c r="N12" s="98" t="inlineStr"/>
-      <c r="O12" s="101" t="inlineStr"/>
-      <c r="P12" s="101" t="inlineStr"/>
-      <c r="Q12" s="102">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="92" t="inlineStr">
-        <is>
-          <t>UI-010</t>
-        </is>
-      </c>
-      <c r="B13" s="93" t="inlineStr">
-        <is>
-          <t>BoardTest 0→2</t>
-        </is>
-      </c>
-      <c r="C13" s="95" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D13" s="93" t="inlineStr">
-        <is>
-          <t>دستگاه فقط روی باتری؛ منبع از درصد صفر شروع می‌کند</t>
-        </is>
-      </c>
-      <c r="E13" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ را از صفر خیلی آرام بالا بیاور.
-گام ۲: به ترتیبِ الگوها دقت کن: اول باید رفتار درصد ۱ دیده شود و بعد درصد ۲.</t>
-        </is>
-      </c>
-      <c r="F13" s="95" t="inlineStr">
-        <is>
-          <t>بالا آمدن آرام از ۰ به ۲ درصد</t>
-        </is>
-      </c>
-      <c r="G13" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H13" s="93" t="inlineStr">
-        <is>
-          <t>اول الگوی درصد ۱ (سه بوق و برق کوتاه) و بعد الگوی درصد ۲ می‌آید</t>
-        </is>
-      </c>
-      <c r="I13" s="93" t="inlineStr">
-        <is>
-          <t>گذار پله‌ای ۱ بعد ۲</t>
-        </is>
-      </c>
-      <c r="J13" s="93" t="inlineStr">
-        <is>
-          <t>دیدن هر دو پله به ترتیب = قبول؛ پرش مستقیم به الگوی ۲ = رد</t>
-        </is>
-      </c>
-      <c r="K13" s="93" t="inlineStr"/>
-      <c r="L13" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="93" t="inlineStr"/>
-      <c r="N13" s="93" t="inlineStr"/>
-      <c r="O13" s="95" t="inlineStr"/>
-      <c r="P13" s="95" t="inlineStr"/>
-      <c r="Q13" s="97">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="92" t="inlineStr">
-        <is>
-          <t>UI-011</t>
-        </is>
-      </c>
-      <c r="B14" s="98" t="inlineStr">
-        <is>
-          <t>Charging 5% 56/57/58</t>
-        </is>
-      </c>
-      <c r="C14" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="98" t="inlineStr">
-        <is>
-          <t>برق شهر وصل و باتری واقعی در حال شارژ است؛ درصد حدود نصف</t>
-        </is>
-      </c>
-      <c r="E14" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: دستگاه را به شارژ بزن و صبر کن درصد دور ۵۷ ثابت شود.
-گام ۲: یک دقیقه فقط چراغ زرد را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F14" s="101" t="inlineStr">
-        <is>
-          <t>شارژ عادی با درصد میانی</t>
-        </is>
-      </c>
-      <c r="G14" s="101" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H14" s="98" t="inlineStr">
-        <is>
-          <t>زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند</t>
-        </is>
-      </c>
-      <c r="I14" s="98" t="inlineStr">
-        <is>
-          <t>ریتم ثابت</t>
-        </is>
-      </c>
-      <c r="J14" s="98" t="inlineStr">
-        <is>
-          <t>ریتم ثابت = قبول؛ پرش یا توقف چشمک = رد</t>
-        </is>
-      </c>
-      <c r="K14" s="98" t="inlineStr"/>
-      <c r="L14" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M14" s="98" t="inlineStr"/>
-      <c r="N14" s="98" t="inlineStr"/>
-      <c r="O14" s="101" t="inlineStr"/>
-      <c r="P14" s="101" t="inlineStr"/>
-      <c r="Q14" s="102">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="92" t="inlineStr">
-        <is>
-          <t>UI-012</t>
-        </is>
-      </c>
-      <c r="B15" s="93" t="inlineStr">
-        <is>
-          <t>Charging 5% 53..61</t>
-        </is>
-      </c>
-      <c r="C15" s="94" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="103" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-011؛ در حال شارژ با درصد حدود ۵۷</t>
-        </is>
-      </c>
-      <c r="E15" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: حین شارژ، ولتاژ باتری را با یک مصرف کوچک یا منبع کمی بالا و پایین کن (درصد دور ۵۷ بازی کند).
-گام ۲: یک دقیقه چراغ زرد را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F15" s="95" t="inlineStr">
-        <is>
-          <t>بازی کوچک درصد حین شارژ</t>
-        </is>
-      </c>
-      <c r="G15" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H15" s="93" t="inlineStr">
-        <is>
-          <t>چشمک زرد هیچ تغییری نمی‌کند و با همان ریتم ادامه می‌دهد</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="inlineStr">
-        <is>
-          <t>بدون تغییر</t>
-        </is>
-      </c>
-      <c r="J15" s="93" t="inlineStr">
-        <is>
-          <t>ثابت ماندن = قبول؛ عوض‌شدن ریتم با نوسان کوچک = رد</t>
-        </is>
-      </c>
-      <c r="K15" s="93" t="inlineStr"/>
-      <c r="L15" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M15" s="93" t="inlineStr"/>
-      <c r="N15" s="93" t="inlineStr"/>
-      <c r="O15" s="95" t="inlineStr"/>
-      <c r="P15" s="95" t="inlineStr"/>
-      <c r="Q15" s="97">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="40.5" customHeight="1">
-      <c r="A16" s="92" t="inlineStr">
-        <is>
-          <t>UI-013</t>
-        </is>
-      </c>
-      <c r="B16" s="98" t="inlineStr">
-        <is>
-          <t>Charging 5% خروج</t>
-        </is>
-      </c>
-      <c r="C16" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D16" s="98" t="inlineStr">
-        <is>
-          <t>برق شهر وصل و دستگاه در حال شارژ؛ درصد حدود ۵۷</t>
-        </is>
-      </c>
-      <c r="E16" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: درصد شارژ را با منبع یا مصرف واقعی اول به حدود ۵۲ ببر و ثابت کن.
-گام ۲: بعد به حدود ۶۲ ببر و ثابت کن.
-گام ۳: موقع جابه‌جایی‌ها به زرد نگاه کن که قطع و وصل ناگهانی نکند.</t>
-        </is>
-      </c>
-      <c r="F16" s="101" t="inlineStr">
-        <is>
-          <t>درصد شارژ ۵۷ بعد ۵۲ بعد ۶۲</t>
-        </is>
-      </c>
-      <c r="G16" s="101" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H16" s="98" t="inlineStr">
-        <is>
-          <t>ریتم زرد با درصد عوض می‌شود ولی چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد</t>
-        </is>
-      </c>
-      <c r="I16" s="98" t="inlineStr">
-        <is>
-          <t>ریتم تازه، بدون راه‌اندازی از صفر</t>
-        </is>
-      </c>
-      <c r="J16" s="98" t="inlineStr">
-        <is>
-          <t>تغییر نرم ریتم = قبول؛ ماندن روی ریتم ۵۷ یا پرش ناگهانی = رد</t>
-        </is>
-      </c>
-      <c r="K16" s="98" t="inlineStr"/>
-      <c r="L16" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M16" s="98" t="inlineStr"/>
-      <c r="N16" s="98" t="inlineStr"/>
-      <c r="O16" s="101" t="inlineStr"/>
-      <c r="P16" s="101" t="inlineStr"/>
-      <c r="Q16" s="102">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="40.5" customHeight="1">
-      <c r="A17" s="92" t="inlineStr">
-        <is>
-          <t>UI-015</t>
-        </is>
-      </c>
-      <c r="B17" s="98" t="inlineStr">
-        <is>
-          <t>Full 100/95 enter</t>
-        </is>
-      </c>
-      <c r="C17" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D17" s="98" t="inlineStr">
+      <c r="D7" s="98" t="inlineStr">
         <is>
           <t>باتری در حال شارژ و نزدیک پر شدن است</t>
         </is>
       </c>
-      <c r="E17" s="98" t="inlineStr">
+      <c r="E7" s="98" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده و درصد را زیر نظر بگیر.
 گام ۲: روی ۹۹ درصد چراغ‌ها را چک کن: هنوز باید شارژ باشد (زرد چشمک‌زن).
 گام ۳: بگذار به ۱۰۰ برسد و دوباره نگاه کن.</t>
         </is>
       </c>
-      <c r="F17" s="101" t="inlineStr">
+      <c r="F7" s="101" t="inlineStr">
         <is>
           <t>رسیدن درصد شارژ از ۹۹ به ۱۰۰</t>
         </is>
       </c>
-      <c r="G17" s="101" t="inlineStr">
+      <c r="G7" s="101" t="inlineStr">
         <is>
           <t>تا پر شدن باتری</t>
         </is>
       </c>
-      <c r="H17" s="98" t="inlineStr">
+      <c r="H7" s="98" t="inlineStr">
         <is>
           <t>فقط روی ۱۰۰ ورودی خوب می‌شود: سبز ثابت و زرد خاموش؛ روی ۹۹ هنوز زرد چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I17" s="98" t="inlineStr">
+      <c r="I7" s="98" t="inlineStr">
         <is>
           <t>۱۰۰: سبز ثابت</t>
         </is>
       </c>
-      <c r="J17" s="98" t="inlineStr">
-        <is>
-          <t>ورودی خوب دقیقاً روی ۱۰۰ = قبول؛ سبز ثابت روی ۹۹ = رد</t>
-        </is>
-      </c>
-      <c r="K17" s="98" t="inlineStr"/>
-      <c r="L17" s="96" t="inlineStr">
+      <c r="J7" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: دقیقاً وقتی شارژ کامل شد زرد خاموش و سبز ثابت می‌شود؛ کمی قبل از کامل‌شدن هنوز زرد چشمک می‌زند. اگر پیش از کامل‌شدن سبز ثابت شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K7" s="98" t="n"/>
+      <c r="L7" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M17" s="98" t="inlineStr"/>
-      <c r="N17" s="98" t="inlineStr"/>
-      <c r="O17" s="101" t="inlineStr"/>
-      <c r="P17" s="101" t="inlineStr"/>
-      <c r="Q17" s="102">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+      <c r="M7" s="98" t="n"/>
+      <c r="N7" s="98" t="n"/>
+      <c r="O7" s="101" t="n"/>
+      <c r="P7" s="101" t="n"/>
+      <c r="Q7" s="102">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="92" t="inlineStr">
-        <is>
-          <t>UI-016</t>
-        </is>
-      </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>Full 100/95 stay</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="92" t="inlineStr">
+        <is>
+          <t>UI-019</t>
+        </is>
+      </c>
+      <c r="B8" s="98" t="inlineStr">
+        <is>
+          <t>InputOk non-blocking</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D18" s="103" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-015؛ درصد روی ۱۰۰ و سبز ثابت است</t>
-        </is>
-      </c>
-      <c r="E18" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: با یک مصرف کوچک درصد را بین ۹۵ و ۱۰۰ نگه دار و چند بار بالا پایینش کن.
-گام ۲: چراغ‌ها را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F18" s="95" t="inlineStr">
-        <is>
-          <t>درصد بین ۹۵ تا ۱۰۰</t>
-        </is>
-      </c>
-      <c r="G18" s="95" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H18" s="93" t="inlineStr">
-        <is>
-          <t>تا وقتی درصد بالای ۹۵ است همان ورودی خوب می‌ماند: سبز ثابت و زرد خاموش</t>
-        </is>
-      </c>
-      <c r="I18" s="93" t="inlineStr">
-        <is>
-          <t>سبز ثابت</t>
-        </is>
-      </c>
-      <c r="J18" s="93" t="inlineStr">
-        <is>
-          <t>ماندن در هر سه وضعیت = قبول؛ افتادن به چشمک زرد شارژ = رد</t>
-        </is>
-      </c>
-      <c r="K18" s="93" t="inlineStr"/>
-      <c r="L18" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M18" s="93" t="inlineStr"/>
-      <c r="N18" s="93" t="inlineStr"/>
-      <c r="O18" s="95" t="inlineStr"/>
-      <c r="P18" s="95" t="inlineStr"/>
-      <c r="Q18" s="97">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="92" t="inlineStr">
-        <is>
-          <t>UI-017</t>
-        </is>
-      </c>
-      <c r="B19" s="98" t="inlineStr">
-        <is>
-          <t>Full 95 exit</t>
-        </is>
-      </c>
-      <c r="C19" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D19" s="100" t="inlineStr">
-        <is>
-          <t>ادامهٔ UI-016؛ درصد بالای ۹۵ و سبز ثابت است</t>
-        </is>
-      </c>
-      <c r="E19" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: یک بار واقعی روی باتری بکش تا درصد زیر ۹۵ بیاید.
-گام ۲: چراغ‌ها را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F19" s="101" t="inlineStr">
-        <is>
-          <t>افت درصد شارژ به زیر ۹۵</t>
-        </is>
-      </c>
-      <c r="G19" s="101" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H19" s="98" t="inlineStr">
-        <is>
-          <t>برمی‌گردد به وضعیت شارژ: سبز از ثابت درمی‌آید و زرد دوباره چشمک می‌زند</t>
-        </is>
-      </c>
-      <c r="I19" s="98" t="inlineStr">
-        <is>
-          <t>برگشت به چشمک زرد</t>
-        </is>
-      </c>
-      <c r="J19" s="98" t="inlineStr">
-        <is>
-          <t>برگشت زیر ۹۵ = قبول؛ ماندن روی سبز ثابت = رد</t>
-        </is>
-      </c>
-      <c r="K19" s="98" t="inlineStr"/>
-      <c r="L19" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M19" s="98" t="inlineStr"/>
-      <c r="N19" s="98" t="inlineStr"/>
-      <c r="O19" s="101" t="inlineStr"/>
-      <c r="P19" s="101" t="inlineStr"/>
-      <c r="Q19" s="102">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="92" t="inlineStr">
-        <is>
-          <t>UI-019</t>
-        </is>
-      </c>
-      <c r="B20" s="98" t="inlineStr">
-        <is>
-          <t>InputOk non-blocking</t>
-        </is>
-      </c>
-      <c r="C20" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D20" s="98" t="inlineStr">
+      <c r="D8" s="98" t="inlineStr">
         <is>
           <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
         </is>
       </c>
-      <c r="E20" s="98" t="inlineStr">
+      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
 گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
         </is>
       </c>
-      <c r="F20" s="101" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>کار هم‌زمان با پنل روی ورودی خوب</t>
         </is>
       </c>
-      <c r="G20" s="101" t="inlineStr">
+      <c r="G8" s="101" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H20" s="98" t="inlineStr">
+      <c r="H8" s="98" t="inlineStr">
         <is>
           <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
         </is>
       </c>
-      <c r="I20" s="98" t="inlineStr">
+      <c r="I8" s="98" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="J20" s="98" t="inlineStr">
-        <is>
-          <t>بدون هنگ و مکث = قبول؛ هر مکث یا ریست = رد</t>
-        </is>
-      </c>
-      <c r="K20" s="98" t="inlineStr"/>
-      <c r="L20" s="96" t="inlineStr">
+      <c r="J8" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: سبز ثابت است، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند. اگر هنگ، مکث یا ریست دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K8" s="98" t="n"/>
+      <c r="L8" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M20" s="98" t="inlineStr"/>
-      <c r="N20" s="98" t="inlineStr"/>
-      <c r="O20" s="101" t="inlineStr"/>
-      <c r="P20" s="101" t="inlineStr"/>
-      <c r="Q20" s="102">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+      <c r="M8" s="98" t="n"/>
+      <c r="N8" s="98" t="n"/>
+      <c r="O8" s="101" t="n"/>
+      <c r="P8" s="101" t="n"/>
+      <c r="Q8" s="102">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="92" t="inlineStr">
-        <is>
-          <t>UI-020</t>
-        </is>
-      </c>
-      <c r="B21" s="93" t="inlineStr">
-        <is>
-          <t>Charging non-blocking</t>
-        </is>
-      </c>
-      <c r="C21" s="94" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="92" t="inlineStr">
+        <is>
+          <t>UI-021</t>
+        </is>
+      </c>
+      <c r="B9" s="98" t="inlineStr">
+        <is>
+          <t>InputOverVoltage</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D21" s="93" t="inlineStr">
-        <is>
-          <t>برق شهر وصل و باتری در حال شارژ است (زرد چشمک‌زن)</t>
-        </is>
-      </c>
-      <c r="E21" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: حین شارژ با پنل کار کن و چند پارامتر بخوان.
-گام ۲: دو دقیقه دستگاه را زیر نظر بگیر.</t>
-        </is>
-      </c>
-      <c r="F21" s="95" t="inlineStr">
-        <is>
-          <t>کار با پنل حین شارژ</t>
-        </is>
-      </c>
-      <c r="G21" s="95" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H21" s="93" t="inlineStr">
-        <is>
-          <t>زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="inlineStr">
-        <is>
-          <t>چشمک منظم زرد</t>
-        </is>
-      </c>
-      <c r="J21" s="93" t="inlineStr">
-        <is>
-          <t>بدون هنگ = قبول؛ هنگ یا قطع ارتباط = رد</t>
-        </is>
-      </c>
-      <c r="K21" s="93" t="inlineStr"/>
-      <c r="L21" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M21" s="93" t="inlineStr"/>
-      <c r="N21" s="93" t="inlineStr"/>
-      <c r="O21" s="95" t="inlineStr"/>
-      <c r="P21" s="95" t="inlineStr"/>
-      <c r="Q21" s="97">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="92" t="inlineStr">
-        <is>
-          <t>UI-021</t>
-        </is>
-      </c>
-      <c r="B22" s="98" t="inlineStr">
-        <is>
-          <t>InputOverVoltage</t>
-        </is>
-      </c>
-      <c r="C22" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D22" s="98" t="inlineStr">
+      <c r="D9" s="98" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E22" s="98" t="inlineStr">
+      <c r="E9" s="98" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
 گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
@@ -3123,1292 +2201,68 @@
 گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
         </is>
       </c>
-      <c r="F22" s="101" t="inlineStr">
+      <c r="F9" s="101" t="inlineStr">
         <is>
           <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
         </is>
       </c>
-      <c r="G22" s="101" t="inlineStr">
+      <c r="G9" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H22" s="98" t="inlineStr">
+      <c r="H9" s="98" t="inlineStr">
         <is>
           <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
         </is>
       </c>
-      <c r="I22" s="98" t="inlineStr">
+      <c r="I9" s="98" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن با سبز ثابت</t>
         </is>
       </c>
-      <c r="J22" s="98" t="inlineStr">
-        <is>
-          <t>آمدن، ماندن و پاک‌شدن در همان حدود = قبول؛ پاک‌شدن زودتر یا نیامدن = رد</t>
-        </is>
-      </c>
-      <c r="K22" s="98" t="inlineStr"/>
-      <c r="L22" s="96" t="inlineStr">
+      <c r="J9" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: روی ولتاژ بالای ورودی سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید؛ با پایین‌آوردن ولتاژ این چهره پاک می‌شود. اگر نیامد یا زود پاک شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K9" s="98" t="n"/>
+      <c r="L9" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M22" s="98" t="inlineStr"/>
-      <c r="N22" s="98" t="inlineStr"/>
-      <c r="O22" s="101" t="inlineStr"/>
-      <c r="P22" s="101" t="inlineStr"/>
-      <c r="Q22" s="102">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+      <c r="M9" s="98" t="n"/>
+      <c r="N9" s="98" t="n"/>
+      <c r="O9" s="101" t="n"/>
+      <c r="P9" s="101" t="n"/>
+      <c r="Q9" s="102">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="92" t="inlineStr">
-        <is>
-          <t>UI-022</t>
-        </is>
-      </c>
-      <c r="B23" s="93" t="inlineStr">
-        <is>
-          <t>Snapshot invalid</t>
-        </is>
-      </c>
-      <c r="C23" s="94" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="92" t="inlineStr">
+        <is>
+          <t>UI-032</t>
+        </is>
+      </c>
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>خطای ۶: قطع باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="C10" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D23" s="93" t="inlineStr">
-        <is>
-          <t>دستگاه روشن و در حال کار عادی است</t>
-        </is>
-      </c>
-      <c r="E23" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: سیم حس‌کردن ولتاژ باتری را لحظه‌ای جدا کن (دستگاه اندازهٔ تازه ندارد).
-گام ۲: به چراغ‌ها و بوق نگاه کن؛ نباید الگوی دیوانه‌وار یا بوق بی‌دلیل بیاید.
-گام ۳: سیم را وصل کن؛ رفتار عادی باید برگردد.</t>
-        </is>
-      </c>
-      <c r="F23" s="95" t="inlineStr">
-        <is>
-          <t>قطع و وصل کوتاه سیم حس باتری</t>
-        </is>
-      </c>
-      <c r="G23" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H23" s="93" t="inlineStr">
-        <is>
-          <t>حین قطع، چهرهٔ سالم قبلی آرام می‌ماند و دستگاه هنگ نمی‌کند؛ با وصل مجدد همه‌چیز عادی می‌شود</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="inlineStr">
-        <is>
-          <t>بدون الگوی تازهٔ خطادار</t>
-        </is>
-      </c>
-      <c r="J23" s="93" t="inlineStr">
-        <is>
-          <t>آرام ماندن و برگشت عادی = قبول؛ هنگ، بوق بی‌دلیل یا چراغ قاطی = رد</t>
-        </is>
-      </c>
-      <c r="K23" s="93" t="inlineStr"/>
-      <c r="L23" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M23" s="93" t="inlineStr"/>
-      <c r="N23" s="93" t="inlineStr"/>
-      <c r="O23" s="95" t="inlineStr"/>
-      <c r="P23" s="95" t="inlineStr"/>
-      <c r="Q23" s="97">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="92" t="inlineStr">
-        <is>
-          <t>UI-023</t>
-        </is>
-      </c>
-      <c r="B24" s="98" t="inlineStr">
-        <is>
-          <t>Low Alarm 21/21.2</t>
-        </is>
-      </c>
-      <c r="C24" s="99" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D24" s="98" t="inlineStr">
-        <is>
-          <t>دستگاه روی باتری کار می‌کند؛ منبع آزمایشگاهی به‌جای باتری</t>
-        </is>
-      </c>
-      <c r="E24" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ باتری را آرام تا نزدیک مرز باتری کم (حدود ۲۱ ولت) پایین بیاور.
-گام ۲: کمی دور همان مرز بالا و پایینش کن و چراغ‌ها را نگاه کن.</t>
-        </is>
-      </c>
-      <c r="F24" s="101" t="inlineStr">
-        <is>
-          <t>باتری دور مرز ۲۱ ولت</t>
-        </is>
-      </c>
-      <c r="G24" s="101" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H24" s="98" t="inlineStr">
-        <is>
-          <t>چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود</t>
-        </is>
-      </c>
-      <c r="I24" s="98" t="inlineStr">
-        <is>
-          <t>پایدار، بدون فلیکر</t>
-        </is>
-      </c>
-      <c r="J24" s="98" t="inlineStr">
-        <is>
-          <t>بدون پرپر = قبول؛ رفت‌وبرگشت تند چراغ‌ها = رد</t>
-        </is>
-      </c>
-      <c r="K24" s="98" t="inlineStr"/>
-      <c r="L24" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M24" s="98" t="inlineStr"/>
-      <c r="N24" s="98" t="inlineStr"/>
-      <c r="O24" s="101" t="inlineStr"/>
-      <c r="P24" s="101" t="inlineStr"/>
-      <c r="Q24" s="102">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="92" t="inlineStr">
-        <is>
-          <t>UI-024</t>
-        </is>
-      </c>
-      <c r="B25" s="93" t="inlineStr">
-        <is>
-          <t>Input switch 20/21</t>
-        </is>
-      </c>
-      <c r="C25" s="94" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D25" s="93" t="inlineStr">
-        <is>
-          <t>ورودی از منبع آزمایشگاهی می‌آید؛ باتری وصل است</t>
-        </is>
-      </c>
-      <c r="E25" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
-گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
-        </is>
-      </c>
-      <c r="F25" s="95" t="inlineStr">
-        <is>
-          <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
-        </is>
-      </c>
-      <c r="G25" s="95" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H25" s="93" t="inlineStr">
-        <is>
-          <t>وضعیت ورودی فقط وقتی واقعاً از مرز رد می‌شوی عوض می‌شود؛ وسط راه هیچ رفت‌وبرگشت بی‌دلیلی نیست</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="inlineStr">
-        <is>
-          <t>گذار تکی و تمیز</t>
-        </is>
-      </c>
-      <c r="J25" s="93" t="inlineStr">
-        <is>
-          <t>بدون رفت‌وبرگشت بی‌دلیل = قبول؛ فلیکر وسط راه = رد</t>
-        </is>
-      </c>
-      <c r="K25" s="93" t="inlineStr"/>
-      <c r="L25" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M25" s="93" t="inlineStr"/>
-      <c r="N25" s="93" t="inlineStr"/>
-      <c r="O25" s="95" t="inlineStr"/>
-      <c r="P25" s="95" t="inlineStr"/>
-      <c r="Q25" s="97">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="92" t="inlineStr">
-        <is>
-          <t>UI-030</t>
-        </is>
-      </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>پنل دیالوگ مستقل</t>
-        </is>
-      </c>
-      <c r="C26" s="95" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D26" s="93" t="inlineStr">
-        <is>
-          <t>پنل به دستگاه وصل و دستگاه در حال کار عادی است</t>
-        </is>
-      </c>
-      <c r="E26" s="93" t="inlineStr">
-        <is>
-          <t>گام ۱: در پنل یک پیام یا دیالوگ باز کن.
-گام ۲: هم‌زمان چراغ‌های دستگاه را نگاه کن.
-گام ۳: دیالوگ را ببند.</t>
-        </is>
-      </c>
-      <c r="F26" s="95" t="inlineStr">
-        <is>
-          <t>باز و بسته‌کردن دیالوگ پنل</t>
-        </is>
-      </c>
-      <c r="G26" s="95" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H26" s="93" t="inlineStr">
-        <is>
-          <t>دیالوگ پنل چراغ‌ها و بوق دستگاه را به هم نمی‌ریزد؛ رفتار عادی ادامه دارد</t>
-        </is>
-      </c>
-      <c r="I26" s="93" t="inlineStr">
-        <is>
-          <t>بدون تغییر</t>
-        </is>
-      </c>
-      <c r="J26" s="93" t="inlineStr">
-        <is>
-          <t>استقلال کامل دیالوگ و چراغ‌ها = قبول؛ هر اثر متقابل = رد</t>
-        </is>
-      </c>
-      <c r="K26" s="93" t="n"/>
-      <c r="L26" s="104" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M26" s="93" t="n"/>
-      <c r="N26" s="93" t="n"/>
-      <c r="O26" s="95" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P26" s="95" t="n"/>
-      <c r="Q26" s="97" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="80" t="n"/>
-      <c r="B27" s="80" t="n"/>
-      <c r="C27" s="80" t="n"/>
-      <c r="D27" s="80" t="n"/>
-      <c r="E27" s="80" t="n"/>
-      <c r="F27" s="80" t="n"/>
-      <c r="G27" s="80" t="n"/>
-      <c r="H27" s="80" t="n"/>
-      <c r="I27" s="80" t="n"/>
-      <c r="J27" s="80" t="n"/>
-      <c r="K27" s="80" t="n"/>
-      <c r="L27" s="80" t="n"/>
-      <c r="M27" s="80" t="n"/>
-      <c r="N27" s="80" t="n"/>
-      <c r="O27" s="80" t="n"/>
-      <c r="P27" s="80" t="n"/>
-      <c r="Q27" s="105">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="80" t="n"/>
-      <c r="B28" s="80" t="n"/>
-      <c r="C28" s="80" t="n"/>
-      <c r="D28" s="80" t="n"/>
-      <c r="E28" s="80" t="n"/>
-      <c r="F28" s="80" t="n"/>
-      <c r="G28" s="80" t="n"/>
-      <c r="H28" s="80" t="n"/>
-      <c r="I28" s="80" t="n"/>
-      <c r="J28" s="80" t="n"/>
-      <c r="K28" s="80" t="n"/>
-      <c r="L28" s="80" t="n"/>
-      <c r="M28" s="80" t="n"/>
-      <c r="N28" s="80" t="n"/>
-      <c r="O28" s="80" t="n"/>
-      <c r="P28" s="80" t="n"/>
-      <c r="Q28" s="105">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="80" t="n"/>
-      <c r="B29" s="80" t="n"/>
-      <c r="C29" s="80" t="n"/>
-      <c r="D29" s="80" t="n"/>
-      <c r="E29" s="80" t="n"/>
-      <c r="F29" s="80" t="n"/>
-      <c r="G29" s="80" t="n"/>
-      <c r="H29" s="80" t="n"/>
-      <c r="I29" s="80" t="n"/>
-      <c r="J29" s="80" t="n"/>
-      <c r="K29" s="80" t="n"/>
-      <c r="L29" s="80" t="n"/>
-      <c r="M29" s="80" t="n"/>
-      <c r="N29" s="80" t="n"/>
-      <c r="O29" s="80" t="n"/>
-      <c r="P29" s="80" t="n"/>
-      <c r="Q29" s="105">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="80" t="n"/>
-      <c r="B30" s="80" t="n"/>
-      <c r="C30" s="80" t="n"/>
-      <c r="D30" s="80" t="n"/>
-      <c r="E30" s="80" t="n"/>
-      <c r="F30" s="80" t="n"/>
-      <c r="G30" s="80" t="n"/>
-      <c r="H30" s="80" t="n"/>
-      <c r="I30" s="80" t="n"/>
-      <c r="J30" s="80" t="n"/>
-      <c r="K30" s="80" t="n"/>
-      <c r="L30" s="80" t="n"/>
-      <c r="M30" s="80" t="n"/>
-      <c r="N30" s="80" t="n"/>
-      <c r="O30" s="80" t="n"/>
-      <c r="P30" s="80" t="n"/>
-      <c r="Q30" s="105">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="40.5" customHeight="1">
-      <c r="A31" s="80" t="n"/>
-      <c r="B31" s="80" t="n"/>
-      <c r="C31" s="80" t="n"/>
-      <c r="D31" s="80" t="n"/>
-      <c r="E31" s="80" t="n"/>
-      <c r="F31" s="80" t="n"/>
-      <c r="G31" s="80" t="n"/>
-      <c r="H31" s="80" t="n"/>
-      <c r="I31" s="80" t="n"/>
-      <c r="J31" s="80" t="n"/>
-      <c r="K31" s="80" t="n"/>
-      <c r="L31" s="80" t="n"/>
-      <c r="M31" s="80" t="n"/>
-      <c r="N31" s="80" t="n"/>
-      <c r="O31" s="80" t="n"/>
-      <c r="P31" s="80" t="n"/>
-      <c r="Q31" s="105">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="80" t="n"/>
-      <c r="B32" s="80" t="n"/>
-      <c r="C32" s="80" t="n"/>
-      <c r="D32" s="80" t="n"/>
-      <c r="E32" s="80" t="n"/>
-      <c r="F32" s="80" t="n"/>
-      <c r="G32" s="80" t="n"/>
-      <c r="H32" s="80" t="n"/>
-      <c r="I32" s="80" t="n"/>
-      <c r="J32" s="80" t="n"/>
-      <c r="K32" s="80" t="n"/>
-      <c r="L32" s="80" t="n"/>
-      <c r="M32" s="80" t="n"/>
-      <c r="N32" s="80" t="n"/>
-      <c r="O32" s="80" t="n"/>
-      <c r="P32" s="80" t="n"/>
-      <c r="Q32" s="105">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="40.5" customHeight="1">
-      <c r="A33" s="80" t="n"/>
-      <c r="B33" s="80" t="n"/>
-      <c r="C33" s="80" t="n"/>
-      <c r="D33" s="80" t="n"/>
-      <c r="E33" s="80" t="n"/>
-      <c r="F33" s="80" t="n"/>
-      <c r="G33" s="80" t="n"/>
-      <c r="H33" s="80" t="n"/>
-      <c r="I33" s="80" t="n"/>
-      <c r="J33" s="80" t="n"/>
-      <c r="K33" s="80" t="n"/>
-      <c r="L33" s="80" t="n"/>
-      <c r="M33" s="80" t="n"/>
-      <c r="N33" s="80" t="n"/>
-      <c r="O33" s="80" t="n"/>
-      <c r="P33" s="80" t="n"/>
-      <c r="Q33" s="105">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="40.5" customHeight="1">
-      <c r="A34" s="80" t="n"/>
-      <c r="B34" s="80" t="n"/>
-      <c r="C34" s="80" t="n"/>
-      <c r="D34" s="80" t="n"/>
-      <c r="E34" s="80" t="n"/>
-      <c r="F34" s="80" t="n"/>
-      <c r="G34" s="80" t="n"/>
-      <c r="H34" s="80" t="n"/>
-      <c r="I34" s="80" t="n"/>
-      <c r="J34" s="80" t="n"/>
-      <c r="K34" s="80" t="n"/>
-      <c r="L34" s="80" t="n"/>
-      <c r="M34" s="80" t="n"/>
-      <c r="N34" s="80" t="n"/>
-      <c r="O34" s="80" t="n"/>
-      <c r="P34" s="80" t="n"/>
-      <c r="Q34" s="105">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="80" t="n"/>
-      <c r="B35" s="80" t="n"/>
-      <c r="C35" s="80" t="n"/>
-      <c r="D35" s="80" t="n"/>
-      <c r="E35" s="80" t="n"/>
-      <c r="F35" s="80" t="n"/>
-      <c r="G35" s="80" t="n"/>
-      <c r="H35" s="80" t="n"/>
-      <c r="I35" s="80" t="n"/>
-      <c r="J35" s="80" t="n"/>
-      <c r="K35" s="80" t="n"/>
-      <c r="L35" s="80" t="n"/>
-      <c r="M35" s="80" t="n"/>
-      <c r="N35" s="80" t="n"/>
-      <c r="O35" s="80" t="n"/>
-      <c r="P35" s="80" t="n"/>
-      <c r="Q35" s="105">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="80" t="n"/>
-      <c r="B36" s="80" t="n"/>
-      <c r="C36" s="80" t="n"/>
-      <c r="D36" s="80" t="n"/>
-      <c r="E36" s="80" t="n"/>
-      <c r="F36" s="80" t="n"/>
-      <c r="G36" s="80" t="n"/>
-      <c r="H36" s="80" t="n"/>
-      <c r="I36" s="80" t="n"/>
-      <c r="J36" s="80" t="n"/>
-      <c r="K36" s="80" t="n"/>
-      <c r="L36" s="80" t="n"/>
-      <c r="M36" s="80" t="n"/>
-      <c r="N36" s="80" t="n"/>
-      <c r="O36" s="80" t="n"/>
-      <c r="P36" s="80" t="n"/>
-      <c r="Q36" s="105">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="80" t="n"/>
-      <c r="B37" s="80" t="n"/>
-      <c r="C37" s="80" t="n"/>
-      <c r="D37" s="80" t="n"/>
-      <c r="E37" s="80" t="n"/>
-      <c r="F37" s="80" t="n"/>
-      <c r="G37" s="80" t="n"/>
-      <c r="H37" s="80" t="n"/>
-      <c r="I37" s="80" t="n"/>
-      <c r="J37" s="80" t="n"/>
-      <c r="K37" s="80" t="n"/>
-      <c r="L37" s="80" t="n"/>
-      <c r="M37" s="80" t="n"/>
-      <c r="N37" s="80" t="n"/>
-      <c r="O37" s="80" t="n"/>
-      <c r="P37" s="80" t="n"/>
-      <c r="Q37" s="105">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="80" t="n"/>
-      <c r="B38" s="80" t="n"/>
-      <c r="C38" s="80" t="n"/>
-      <c r="D38" s="80" t="n"/>
-      <c r="E38" s="80" t="n"/>
-      <c r="F38" s="80" t="n"/>
-      <c r="G38" s="80" t="n"/>
-      <c r="H38" s="80" t="n"/>
-      <c r="I38" s="80" t="n"/>
-      <c r="J38" s="80" t="n"/>
-      <c r="K38" s="80" t="n"/>
-      <c r="L38" s="80" t="n"/>
-      <c r="M38" s="80" t="n"/>
-      <c r="N38" s="80" t="n"/>
-      <c r="O38" s="80" t="n"/>
-      <c r="P38" s="80" t="n"/>
-      <c r="Q38" s="105">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="80" t="n"/>
-      <c r="B39" s="80" t="n"/>
-      <c r="C39" s="80" t="n"/>
-      <c r="D39" s="80" t="n"/>
-      <c r="E39" s="80" t="n"/>
-      <c r="F39" s="80" t="n"/>
-      <c r="G39" s="80" t="n"/>
-      <c r="H39" s="80" t="n"/>
-      <c r="I39" s="80" t="n"/>
-      <c r="J39" s="80" t="n"/>
-      <c r="K39" s="80" t="n"/>
-      <c r="L39" s="80" t="n"/>
-      <c r="M39" s="80" t="n"/>
-      <c r="N39" s="80" t="n"/>
-      <c r="O39" s="80" t="n"/>
-      <c r="P39" s="80" t="n"/>
-      <c r="Q39" s="105">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="80" t="n"/>
-      <c r="B40" s="80" t="n"/>
-      <c r="C40" s="80" t="n"/>
-      <c r="D40" s="80" t="n"/>
-      <c r="E40" s="80" t="n"/>
-      <c r="F40" s="80" t="n"/>
-      <c r="G40" s="80" t="n"/>
-      <c r="H40" s="80" t="n"/>
-      <c r="I40" s="80" t="n"/>
-      <c r="J40" s="80" t="n"/>
-      <c r="K40" s="80" t="n"/>
-      <c r="L40" s="80" t="n"/>
-      <c r="M40" s="80" t="n"/>
-      <c r="N40" s="80" t="n"/>
-      <c r="O40" s="80" t="n"/>
-      <c r="P40" s="80" t="n"/>
-      <c r="Q40" s="105">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="80" t="n"/>
-      <c r="B41" s="80" t="n"/>
-      <c r="C41" s="80" t="n"/>
-      <c r="D41" s="80" t="n"/>
-      <c r="E41" s="80" t="n"/>
-      <c r="F41" s="80" t="n"/>
-      <c r="G41" s="80" t="n"/>
-      <c r="H41" s="80" t="n"/>
-      <c r="I41" s="80" t="n"/>
-      <c r="J41" s="80" t="n"/>
-      <c r="K41" s="80" t="n"/>
-      <c r="L41" s="80" t="n"/>
-      <c r="M41" s="80" t="n"/>
-      <c r="N41" s="80" t="n"/>
-      <c r="O41" s="80" t="n"/>
-      <c r="P41" s="80" t="n"/>
-      <c r="Q41" s="105">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="80" t="n"/>
-      <c r="B42" s="80" t="n"/>
-      <c r="C42" s="80" t="n"/>
-      <c r="D42" s="80" t="n"/>
-      <c r="E42" s="80" t="n"/>
-      <c r="F42" s="80" t="n"/>
-      <c r="G42" s="80" t="n"/>
-      <c r="H42" s="80" t="n"/>
-      <c r="I42" s="80" t="n"/>
-      <c r="J42" s="80" t="n"/>
-      <c r="K42" s="80" t="n"/>
-      <c r="L42" s="80" t="n"/>
-      <c r="M42" s="80" t="n"/>
-      <c r="N42" s="80" t="n"/>
-      <c r="O42" s="80" t="n"/>
-      <c r="P42" s="80" t="n"/>
-      <c r="Q42" s="105">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="80" t="n"/>
-      <c r="B43" s="80" t="n"/>
-      <c r="C43" s="80" t="n"/>
-      <c r="D43" s="80" t="n"/>
-      <c r="E43" s="80" t="n"/>
-      <c r="F43" s="80" t="n"/>
-      <c r="G43" s="80" t="n"/>
-      <c r="H43" s="80" t="n"/>
-      <c r="I43" s="80" t="n"/>
-      <c r="J43" s="80" t="n"/>
-      <c r="K43" s="80" t="n"/>
-      <c r="L43" s="80" t="n"/>
-      <c r="M43" s="80" t="n"/>
-      <c r="N43" s="80" t="n"/>
-      <c r="O43" s="80" t="n"/>
-      <c r="P43" s="80" t="n"/>
-      <c r="Q43" s="105">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="80" t="n"/>
-      <c r="B44" s="80" t="n"/>
-      <c r="C44" s="80" t="n"/>
-      <c r="D44" s="80" t="n"/>
-      <c r="E44" s="80" t="n"/>
-      <c r="F44" s="80" t="n"/>
-      <c r="G44" s="80" t="n"/>
-      <c r="H44" s="80" t="n"/>
-      <c r="I44" s="80" t="n"/>
-      <c r="J44" s="80" t="n"/>
-      <c r="K44" s="80" t="n"/>
-      <c r="L44" s="80" t="n"/>
-      <c r="M44" s="80" t="n"/>
-      <c r="N44" s="80" t="n"/>
-      <c r="O44" s="80" t="n"/>
-      <c r="P44" s="80" t="n"/>
-      <c r="Q44" s="105">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="80" t="n"/>
-      <c r="B45" s="80" t="n"/>
-      <c r="C45" s="80" t="n"/>
-      <c r="D45" s="80" t="n"/>
-      <c r="E45" s="80" t="n"/>
-      <c r="F45" s="80" t="n"/>
-      <c r="G45" s="80" t="n"/>
-      <c r="H45" s="80" t="n"/>
-      <c r="I45" s="80" t="n"/>
-      <c r="J45" s="80" t="n"/>
-      <c r="K45" s="80" t="n"/>
-      <c r="L45" s="80" t="n"/>
-      <c r="M45" s="80" t="n"/>
-      <c r="N45" s="80" t="n"/>
-      <c r="O45" s="80" t="n"/>
-      <c r="P45" s="80" t="n"/>
-      <c r="Q45" s="105">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="80" t="n"/>
-      <c r="B46" s="80" t="n"/>
-      <c r="C46" s="80" t="n"/>
-      <c r="D46" s="80" t="n"/>
-      <c r="E46" s="80" t="n"/>
-      <c r="F46" s="80" t="n"/>
-      <c r="G46" s="80" t="n"/>
-      <c r="H46" s="80" t="n"/>
-      <c r="I46" s="80" t="n"/>
-      <c r="J46" s="80" t="n"/>
-      <c r="K46" s="80" t="n"/>
-      <c r="L46" s="80" t="n"/>
-      <c r="M46" s="80" t="n"/>
-      <c r="N46" s="80" t="n"/>
-      <c r="O46" s="80" t="n"/>
-      <c r="P46" s="80" t="n"/>
-      <c r="Q46" s="105">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="80" t="n"/>
-      <c r="B47" s="80" t="n"/>
-      <c r="C47" s="80" t="n"/>
-      <c r="D47" s="80" t="n"/>
-      <c r="E47" s="80" t="n"/>
-      <c r="F47" s="80" t="n"/>
-      <c r="G47" s="80" t="n"/>
-      <c r="H47" s="80" t="n"/>
-      <c r="I47" s="80" t="n"/>
-      <c r="J47" s="80" t="n"/>
-      <c r="K47" s="80" t="n"/>
-      <c r="L47" s="80" t="n"/>
-      <c r="M47" s="80" t="n"/>
-      <c r="N47" s="80" t="n"/>
-      <c r="O47" s="80" t="n"/>
-      <c r="P47" s="80" t="n"/>
-      <c r="Q47" s="105">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="80" t="n"/>
-      <c r="B48" s="80" t="n"/>
-      <c r="C48" s="80" t="n"/>
-      <c r="D48" s="80" t="n"/>
-      <c r="E48" s="80" t="n"/>
-      <c r="F48" s="80" t="n"/>
-      <c r="G48" s="80" t="n"/>
-      <c r="H48" s="80" t="n"/>
-      <c r="I48" s="80" t="n"/>
-      <c r="J48" s="80" t="n"/>
-      <c r="K48" s="80" t="n"/>
-      <c r="L48" s="80" t="n"/>
-      <c r="M48" s="80" t="n"/>
-      <c r="N48" s="80" t="n"/>
-      <c r="O48" s="80" t="n"/>
-      <c r="P48" s="80" t="n"/>
-      <c r="Q48" s="105">
-        <f>IF(OR(L56="",L56="در انتظار"),"",IF(Q56="",TODAY(),Q56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="80" t="n"/>
-      <c r="B49" s="80" t="n"/>
-      <c r="C49" s="80" t="n"/>
-      <c r="D49" s="80" t="n"/>
-      <c r="E49" s="80" t="n"/>
-      <c r="F49" s="80" t="n"/>
-      <c r="G49" s="80" t="n"/>
-      <c r="H49" s="80" t="n"/>
-      <c r="I49" s="80" t="n"/>
-      <c r="J49" s="80" t="n"/>
-      <c r="K49" s="80" t="n"/>
-      <c r="L49" s="80" t="n"/>
-      <c r="M49" s="80" t="n"/>
-      <c r="N49" s="80" t="n"/>
-      <c r="O49" s="80" t="n"/>
-      <c r="P49" s="80" t="n"/>
-      <c r="Q49" s="105">
-        <f>IF(OR(L57="",L57="در انتظار"),"",IF(Q57="",TODAY(),Q57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="80" t="n"/>
-      <c r="B50" s="80" t="n"/>
-      <c r="C50" s="80" t="n"/>
-      <c r="D50" s="80" t="n"/>
-      <c r="E50" s="80" t="n"/>
-      <c r="F50" s="80" t="n"/>
-      <c r="G50" s="80" t="n"/>
-      <c r="H50" s="80" t="n"/>
-      <c r="I50" s="80" t="n"/>
-      <c r="J50" s="80" t="n"/>
-      <c r="K50" s="80" t="n"/>
-      <c r="L50" s="80" t="n"/>
-      <c r="M50" s="80" t="n"/>
-      <c r="N50" s="80" t="n"/>
-      <c r="O50" s="80" t="n"/>
-      <c r="P50" s="80" t="n"/>
-      <c r="Q50" s="105">
-        <f>IF(OR(L58="",L58="در انتظار"),"",IF(Q58="",TODAY(),Q58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="80" t="n"/>
-      <c r="B51" s="80" t="n"/>
-      <c r="C51" s="80" t="n"/>
-      <c r="D51" s="80" t="n"/>
-      <c r="E51" s="80" t="n"/>
-      <c r="F51" s="80" t="n"/>
-      <c r="G51" s="80" t="n"/>
-      <c r="H51" s="80" t="n"/>
-      <c r="I51" s="80" t="n"/>
-      <c r="J51" s="80" t="n"/>
-      <c r="K51" s="80" t="n"/>
-      <c r="L51" s="80" t="n"/>
-      <c r="M51" s="80" t="n"/>
-      <c r="N51" s="80" t="n"/>
-      <c r="O51" s="80" t="n"/>
-      <c r="P51" s="80" t="n"/>
-      <c r="Q51" s="105">
-        <f>IF(OR(L59="",L59="در انتظار"),"",IF(Q59="",TODAY(),Q59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="80" t="n"/>
-      <c r="B52" s="80" t="n"/>
-      <c r="C52" s="80" t="n"/>
-      <c r="D52" s="80" t="n"/>
-      <c r="E52" s="80" t="n"/>
-      <c r="F52" s="80" t="n"/>
-      <c r="G52" s="80" t="n"/>
-      <c r="H52" s="80" t="n"/>
-      <c r="I52" s="80" t="n"/>
-      <c r="J52" s="80" t="n"/>
-      <c r="K52" s="80" t="n"/>
-      <c r="L52" s="80" t="n"/>
-      <c r="M52" s="80" t="n"/>
-      <c r="N52" s="80" t="n"/>
-      <c r="O52" s="80" t="n"/>
-      <c r="P52" s="80" t="n"/>
-      <c r="Q52" s="105">
-        <f>IF(OR(L60="",L60="در انتظار"),"",IF(Q60="",TODAY(),Q60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="80" t="n"/>
-      <c r="B53" s="80" t="n"/>
-      <c r="C53" s="80" t="n"/>
-      <c r="D53" s="80" t="n"/>
-      <c r="E53" s="80" t="n"/>
-      <c r="F53" s="80" t="n"/>
-      <c r="G53" s="80" t="n"/>
-      <c r="H53" s="80" t="n"/>
-      <c r="I53" s="80" t="n"/>
-      <c r="J53" s="80" t="n"/>
-      <c r="K53" s="80" t="n"/>
-      <c r="L53" s="80" t="n"/>
-      <c r="M53" s="80" t="n"/>
-      <c r="N53" s="80" t="n"/>
-      <c r="O53" s="80" t="n"/>
-      <c r="P53" s="80" t="n"/>
-      <c r="Q53" s="105">
-        <f>IF(OR(L61="",L61="در انتظار"),"",IF(Q61="",TODAY(),Q61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="80" t="n"/>
-      <c r="B54" s="80" t="n"/>
-      <c r="C54" s="80" t="n"/>
-      <c r="D54" s="80" t="n"/>
-      <c r="E54" s="80" t="n"/>
-      <c r="F54" s="80" t="n"/>
-      <c r="G54" s="80" t="n"/>
-      <c r="H54" s="80" t="n"/>
-      <c r="I54" s="80" t="n"/>
-      <c r="J54" s="80" t="n"/>
-      <c r="K54" s="80" t="n"/>
-      <c r="L54" s="80" t="n"/>
-      <c r="M54" s="80" t="n"/>
-      <c r="N54" s="80" t="n"/>
-      <c r="O54" s="80" t="n"/>
-      <c r="P54" s="80" t="n"/>
-      <c r="Q54" s="105">
-        <f>IF(OR(L62="",L62="در انتظار"),"",IF(Q62="",TODAY(),Q62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="80" t="n"/>
-      <c r="B55" s="80" t="n"/>
-      <c r="C55" s="80" t="n"/>
-      <c r="D55" s="80" t="n"/>
-      <c r="E55" s="80" t="n"/>
-      <c r="F55" s="80" t="n"/>
-      <c r="G55" s="80" t="n"/>
-      <c r="H55" s="80" t="n"/>
-      <c r="I55" s="80" t="n"/>
-      <c r="J55" s="80" t="n"/>
-      <c r="K55" s="80" t="n"/>
-      <c r="L55" s="80" t="n"/>
-      <c r="M55" s="80" t="n"/>
-      <c r="N55" s="80" t="n"/>
-      <c r="O55" s="80" t="n"/>
-      <c r="P55" s="80" t="n"/>
-      <c r="Q55" s="105">
-        <f>IF(OR(L63="",L63="در انتظار"),"",IF(Q63="",TODAY(),Q63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="80" t="n"/>
-      <c r="B56" s="80" t="n"/>
-      <c r="C56" s="80" t="n"/>
-      <c r="D56" s="80" t="n"/>
-      <c r="E56" s="80" t="n"/>
-      <c r="F56" s="80" t="n"/>
-      <c r="G56" s="80" t="n"/>
-      <c r="H56" s="80" t="n"/>
-      <c r="I56" s="80" t="n"/>
-      <c r="J56" s="80" t="n"/>
-      <c r="K56" s="80" t="n"/>
-      <c r="L56" s="80" t="n"/>
-      <c r="M56" s="80" t="n"/>
-      <c r="N56" s="80" t="n"/>
-      <c r="O56" s="80" t="n"/>
-      <c r="P56" s="80" t="n"/>
-      <c r="Q56" s="105">
-        <f>IF(OR(L64="",L64="در انتظار"),"",IF(Q64="",TODAY(),Q64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="80" t="n"/>
-      <c r="B57" s="80" t="n"/>
-      <c r="C57" s="80" t="n"/>
-      <c r="D57" s="80" t="n"/>
-      <c r="E57" s="80" t="n"/>
-      <c r="F57" s="80" t="n"/>
-      <c r="G57" s="80" t="n"/>
-      <c r="H57" s="80" t="n"/>
-      <c r="I57" s="80" t="n"/>
-      <c r="J57" s="80" t="n"/>
-      <c r="K57" s="80" t="n"/>
-      <c r="L57" s="80" t="n"/>
-      <c r="M57" s="80" t="n"/>
-      <c r="N57" s="80" t="n"/>
-      <c r="O57" s="80" t="n"/>
-      <c r="P57" s="80" t="n"/>
-      <c r="Q57" s="105">
-        <f>IF(OR(L65="",L65="در انتظار"),"",IF(Q65="",TODAY(),Q65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="80" t="n"/>
-      <c r="B58" s="80" t="n"/>
-      <c r="C58" s="80" t="n"/>
-      <c r="D58" s="80" t="n"/>
-      <c r="E58" s="80" t="n"/>
-      <c r="F58" s="80" t="n"/>
-      <c r="G58" s="80" t="n"/>
-      <c r="H58" s="80" t="n"/>
-      <c r="I58" s="80" t="n"/>
-      <c r="J58" s="80" t="n"/>
-      <c r="K58" s="80" t="n"/>
-      <c r="L58" s="80" t="n"/>
-      <c r="M58" s="80" t="n"/>
-      <c r="N58" s="80" t="n"/>
-      <c r="O58" s="80" t="n"/>
-      <c r="P58" s="80" t="n"/>
-      <c r="Q58" s="105">
-        <f>IF(OR(L66="",L66="در انتظار"),"",IF(Q66="",TODAY(),Q66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="80" t="n"/>
-      <c r="B59" s="80" t="n"/>
-      <c r="C59" s="80" t="n"/>
-      <c r="D59" s="80" t="n"/>
-      <c r="E59" s="80" t="n"/>
-      <c r="F59" s="80" t="n"/>
-      <c r="G59" s="80" t="n"/>
-      <c r="H59" s="80" t="n"/>
-      <c r="I59" s="80" t="n"/>
-      <c r="J59" s="80" t="n"/>
-      <c r="K59" s="80" t="n"/>
-      <c r="L59" s="80" t="n"/>
-      <c r="M59" s="80" t="n"/>
-      <c r="N59" s="80" t="n"/>
-      <c r="O59" s="80" t="n"/>
-      <c r="P59" s="80" t="n"/>
-      <c r="Q59" s="105">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="80" t="n"/>
-      <c r="B60" s="80" t="n"/>
-      <c r="C60" s="80" t="n"/>
-      <c r="D60" s="80" t="n"/>
-      <c r="E60" s="80" t="n"/>
-      <c r="F60" s="80" t="n"/>
-      <c r="G60" s="80" t="n"/>
-      <c r="H60" s="80" t="n"/>
-      <c r="I60" s="80" t="n"/>
-      <c r="J60" s="80" t="n"/>
-      <c r="K60" s="80" t="n"/>
-      <c r="L60" s="80" t="n"/>
-      <c r="M60" s="80" t="n"/>
-      <c r="N60" s="80" t="n"/>
-      <c r="O60" s="80" t="n"/>
-      <c r="P60" s="80" t="n"/>
-      <c r="Q60" s="105">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="80" t="n"/>
-      <c r="B61" s="80" t="n"/>
-      <c r="C61" s="80" t="n"/>
-      <c r="D61" s="80" t="n"/>
-      <c r="E61" s="80" t="n"/>
-      <c r="F61" s="80" t="n"/>
-      <c r="G61" s="80" t="n"/>
-      <c r="H61" s="80" t="n"/>
-      <c r="I61" s="80" t="n"/>
-      <c r="J61" s="80" t="n"/>
-      <c r="K61" s="80" t="n"/>
-      <c r="L61" s="80" t="n"/>
-      <c r="M61" s="80" t="n"/>
-      <c r="N61" s="80" t="n"/>
-      <c r="O61" s="80" t="n"/>
-      <c r="P61" s="80" t="n"/>
-      <c r="Q61" s="105">
-        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="80" t="n"/>
-      <c r="B62" s="80" t="n"/>
-      <c r="C62" s="80" t="n"/>
-      <c r="D62" s="80" t="n"/>
-      <c r="E62" s="80" t="n"/>
-      <c r="F62" s="80" t="n"/>
-      <c r="G62" s="80" t="n"/>
-      <c r="H62" s="80" t="n"/>
-      <c r="I62" s="80" t="n"/>
-      <c r="J62" s="80" t="n"/>
-      <c r="K62" s="80" t="n"/>
-      <c r="L62" s="80" t="n"/>
-      <c r="M62" s="80" t="n"/>
-      <c r="N62" s="80" t="n"/>
-      <c r="O62" s="80" t="n"/>
-      <c r="P62" s="80" t="n"/>
-      <c r="Q62" s="105">
-        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="80" t="n"/>
-      <c r="B63" s="80" t="n"/>
-      <c r="C63" s="80" t="n"/>
-      <c r="D63" s="80" t="n"/>
-      <c r="E63" s="80" t="n"/>
-      <c r="F63" s="80" t="n"/>
-      <c r="G63" s="80" t="n"/>
-      <c r="H63" s="80" t="n"/>
-      <c r="I63" s="80" t="n"/>
-      <c r="J63" s="80" t="n"/>
-      <c r="K63" s="80" t="n"/>
-      <c r="L63" s="80" t="n"/>
-      <c r="M63" s="80" t="n"/>
-      <c r="N63" s="80" t="n"/>
-      <c r="O63" s="80" t="n"/>
-      <c r="P63" s="80" t="n"/>
-      <c r="Q63" s="105">
-        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="80" t="n"/>
-      <c r="B64" s="80" t="n"/>
-      <c r="C64" s="80" t="n"/>
-      <c r="D64" s="80" t="n"/>
-      <c r="E64" s="80" t="n"/>
-      <c r="F64" s="80" t="n"/>
-      <c r="G64" s="80" t="n"/>
-      <c r="H64" s="80" t="n"/>
-      <c r="I64" s="80" t="n"/>
-      <c r="J64" s="80" t="n"/>
-      <c r="K64" s="80" t="n"/>
-      <c r="L64" s="80" t="n"/>
-      <c r="M64" s="80" t="n"/>
-      <c r="N64" s="80" t="n"/>
-      <c r="O64" s="80" t="n"/>
-      <c r="P64" s="80" t="n"/>
-      <c r="Q64" s="105">
-        <f>IF(OR(L72="",L72="در انتظار"),"",IF(Q72="",TODAY(),Q72))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="80" t="n"/>
-      <c r="B65" s="80" t="n"/>
-      <c r="C65" s="80" t="n"/>
-      <c r="D65" s="80" t="n"/>
-      <c r="E65" s="80" t="n"/>
-      <c r="F65" s="80" t="n"/>
-      <c r="G65" s="80" t="n"/>
-      <c r="H65" s="80" t="n"/>
-      <c r="I65" s="80" t="n"/>
-      <c r="J65" s="80" t="n"/>
-      <c r="K65" s="80" t="n"/>
-      <c r="L65" s="80" t="n"/>
-      <c r="M65" s="80" t="n"/>
-      <c r="N65" s="80" t="n"/>
-      <c r="O65" s="80" t="n"/>
-      <c r="P65" s="80" t="n"/>
-      <c r="Q65" s="105">
-        <f>IF(OR(L73="",L73="در انتظار"),"",IF(Q73="",TODAY(),Q73))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="80" t="n"/>
-      <c r="B66" s="80" t="n"/>
-      <c r="C66" s="80" t="n"/>
-      <c r="D66" s="80" t="n"/>
-      <c r="E66" s="80" t="n"/>
-      <c r="F66" s="80" t="n"/>
-      <c r="G66" s="80" t="n"/>
-      <c r="H66" s="80" t="n"/>
-      <c r="I66" s="80" t="n"/>
-      <c r="J66" s="80" t="n"/>
-      <c r="K66" s="80" t="n"/>
-      <c r="L66" s="80" t="n"/>
-      <c r="M66" s="80" t="n"/>
-      <c r="N66" s="80" t="n"/>
-      <c r="O66" s="80" t="n"/>
-      <c r="P66" s="80" t="n"/>
-      <c r="Q66" s="105">
-        <f>IF(OR(L74="",L74="در انتظار"),"",IF(Q74="",TODAY(),Q74))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="54" customHeight="1">
-      <c r="A67" s="92" t="inlineStr">
-        <is>
-          <t>UI-031</t>
-        </is>
-      </c>
-      <c r="B67" s="98" t="inlineStr">
-        <is>
-          <t>عملکرد واقعی درصد</t>
-        </is>
-      </c>
-      <c r="C67" s="101" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D67" s="98" t="inlineStr">
-        <is>
-          <t>دستگاه روی باتری در حال کار، درصد شارژ معلوم</t>
-        </is>
-      </c>
-      <c r="E67" s="98" t="inlineStr">
-        <is>
-          <t>گام ۱: دستگاه را روی باتری روشن کن تا درصد شارژ و چشمک سبز معلوم باشد.
-گام ۲: فقط ولتاژ ورودی را بالا و پایین کن (به باتری دست نزن).
-گام ۳: درصد و چشمک سبز نباید هیچ تغییری کند.
-گام ۴: حالا فقط ولتاژ باتری را عوض کن؛ درصد باید عوض شود.</t>
-        </is>
-      </c>
-      <c r="F67" s="98" t="inlineStr">
-        <is>
-          <t>تغییر جدا جدا ورودی و باتری</t>
-        </is>
-      </c>
-      <c r="G67" s="101" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H67" s="98" t="inlineStr">
-        <is>
-          <t>درصد فقط از باتری می‌آید، نه از ورودی</t>
-        </is>
-      </c>
-      <c r="I67" s="98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="98" t="inlineStr">
-        <is>
-          <t>با ورودی ثابت بماند و با باتری عوض شود</t>
-        </is>
-      </c>
-      <c r="K67" s="98" t="inlineStr"/>
-      <c r="L67" s="96" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M67" s="98" t="n"/>
-      <c r="N67" s="98" t="n"/>
-      <c r="O67" s="101" t="n"/>
-      <c r="P67" s="101" t="n"/>
-      <c r="Q67" s="102">
-        <f>IF(OR(L67="",L67="در انتظار"),"",IF(Q67="",TODAY(),Q67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="92" t="inlineStr">
-        <is>
-          <t>UI-032</t>
-        </is>
-      </c>
-      <c r="B68" s="98" t="inlineStr">
-        <is>
-          <t>خطای ۶: قطع باتری حین شارژ</t>
-        </is>
-      </c>
-      <c r="C68" s="101" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D68" s="98" t="inlineStr">
+      <c r="D10" s="98" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
         </is>
       </c>
-      <c r="E68" s="98" t="inlineStr">
+      <c r="E10" s="98" t="inlineStr">
         <is>
           <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
 گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
@@ -4416,68 +2270,68 @@
 گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
         </is>
       </c>
-      <c r="F68" s="98" t="inlineStr">
+      <c r="F10" s="98" t="inlineStr">
         <is>
           <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G68" s="101" t="inlineStr">
+      <c r="G10" s="101" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H68" s="98" t="inlineStr">
+      <c r="H10" s="98" t="inlineStr">
         <is>
           <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
         </is>
       </c>
-      <c r="I68" s="98" t="inlineStr">
+      <c r="I10" s="98" t="inlineStr">
         <is>
           <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
         </is>
       </c>
-      <c r="J68" s="98" t="inlineStr">
-        <is>
-          <t>دقیقاً همین چهره و برگشت تمیز = قبول؛ هر چراغ اشتباه یا پاک‌نشدن = رد</t>
-        </is>
-      </c>
-      <c r="K68" s="98" t="n"/>
-      <c r="L68" s="96" t="inlineStr">
+      <c r="J10" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: با کشیدن سیم باتری حین شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش)، سبز ثابت می‌ماند، زرد خاموش است و سه بوق دوره‌ای می‌آید و شارژ صفر می‌شود؛ با وصل دوبارهٔ باتری همه‌چیز پاک می‌شود و شارژ برمی‌گردد. اگر چراغی اشتباه بود یا خطا پاک نشد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M68" s="98" t="n"/>
-      <c r="N68" s="98" t="n"/>
-      <c r="O68" s="101" t="n"/>
-      <c r="P68" s="101" t="n"/>
-      <c r="Q68" s="102">
-        <f>IF(OR(L68="",L68="در انتظار"),"",IF(Q68="",TODAY(),Q68))</f>
+      <c r="M10" s="98" t="n"/>
+      <c r="N10" s="98" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="101" t="n"/>
+      <c r="Q10" s="102">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="92" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="92" t="inlineStr">
         <is>
           <t>UI-033</t>
         </is>
       </c>
-      <c r="B69" s="98" t="inlineStr">
+      <c r="B11" s="98" t="inlineStr">
         <is>
           <t>خطای ۷: خرابی یک کانال شارژ</t>
         </is>
       </c>
-      <c r="C69" s="101" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D69" s="98" t="inlineStr">
+      <c r="D11" s="98" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
         </is>
       </c>
-      <c r="E69" s="98" t="inlineStr">
+      <c r="E11" s="98" t="inlineStr">
         <is>
           <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
 گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
@@ -4485,68 +2339,68 @@
 گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
         </is>
       </c>
-      <c r="F69" s="98" t="inlineStr">
+      <c r="F11" s="98" t="inlineStr">
         <is>
           <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
         </is>
       </c>
-      <c r="G69" s="101" t="inlineStr">
+      <c r="G11" s="101" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H69" s="98" t="inlineStr">
+      <c r="H11" s="98" t="inlineStr">
         <is>
           <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
-      <c r="I69" s="98" t="inlineStr">
+      <c r="I11" s="98" t="inlineStr">
         <is>
           <t>هر سه چراغ با یک ریتم مشترک</t>
         </is>
       </c>
-      <c r="J69" s="98" t="inlineStr">
-        <is>
-          <t>قفل و پاک‌شدن فقط با ریست = قبول؛ پاک‌شدن با جا زدن فیوز = رد</t>
-        </is>
-      </c>
-      <c r="K69" s="98" t="n"/>
-      <c r="L69" s="96" t="inlineStr">
+      <c r="J11" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است؛ خطا فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود. اگر با جا زدن فیوز یا خودش پاک شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M69" s="98" t="n"/>
-      <c r="N69" s="98" t="n"/>
-      <c r="O69" s="101" t="n"/>
-      <c r="P69" s="101" t="n"/>
-      <c r="Q69" s="102">
-        <f>IF(OR(L69="",L69="در انتظار"),"",IF(Q69="",TODAY(),Q69))</f>
+      <c r="M11" s="98" t="n"/>
+      <c r="N11" s="98" t="n"/>
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="101" t="n"/>
+      <c r="Q11" s="102">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="92" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>UI-034</t>
         </is>
       </c>
-      <c r="B70" s="98" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>باتری خراب (سناریوی ۶): قرمز ثابت</t>
         </is>
       </c>
-      <c r="C70" s="101" t="inlineStr">
+      <c r="C12" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D70" s="98" t="inlineStr">
+      <c r="D12" s="98" t="inlineStr">
         <is>
           <t>از پنل، زمان سناریوی باتری خراب را موقتاً روی چند دقیقه بگذار (مقدار واقعی یک شبانه‌روز است)؛ یک باتری خالی داری</t>
         </is>
       </c>
-      <c r="E70" s="98" t="inlineStr">
+      <c r="E12" s="98" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت پر و شناور شود.
 گام ۲: بعد از گذشت زمان تنظیم‌شده چراغ‌ها را ببین: قرمز باید ثابت روشن باشد، نه چشمک‌زن.
@@ -4555,68 +2409,540 @@
 گام ۵: زمان سناریو را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F70" s="98" t="inlineStr">
+      <c r="F12" s="98" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده از پنل</t>
         </is>
       </c>
-      <c r="G70" s="101" t="inlineStr">
+      <c r="G12" s="101" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H70" s="98" t="inlineStr">
+      <c r="H12" s="98" t="inlineStr">
         <is>
           <t>قرمز ثابت می‌ماند، شارژ آن باتری برای همیشه می‌ایستد و فقط با تعویض باتری پاک می‌شود</t>
         </is>
       </c>
-      <c r="I70" s="98" t="inlineStr">
+      <c r="I12" s="98" t="inlineStr">
         <is>
           <t>قرمز ثابت، بدون چشمک</t>
         </is>
       </c>
-      <c r="J70" s="98" t="inlineStr">
-        <is>
-          <t>قرمز ثابت و توقف تا تعویض = قبول؛ چشمک‌زدن قرمز یا شارژ دوبارهٔ همان باتری = رد</t>
-        </is>
-      </c>
-      <c r="K70" s="98" t="n"/>
-      <c r="L70" s="96" t="inlineStr">
+      <c r="J12" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: قرمز ثابت و بدون چشمک می‌ماند و آن باتری دیگر شارژ نمی‌شود؛ فقط با تعویض باتری پاک می‌شود. اگر قرمز چشمک زد یا همان باتری دوباره شارژ شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M70" s="98" t="n"/>
-      <c r="N70" s="98" t="n"/>
-      <c r="O70" s="101" t="n"/>
-      <c r="P70" s="101" t="n"/>
-      <c r="Q70" s="102">
-        <f>IF(OR(L70="",L70="در انتظار"),"",IF(Q70="",TODAY(),Q70))</f>
+      <c r="M12" s="98" t="n"/>
+      <c r="N12" s="98" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="101" t="n"/>
+      <c r="Q12" s="102">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="92" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="92" t="inlineStr">
+        <is>
+          <t>UI-007</t>
+        </is>
+      </c>
+      <c r="B13" s="98" t="inlineStr">
+        <is>
+          <t>درصد ۱ (نزدیک خالی)</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D13" s="98" t="inlineStr">
+        <is>
+          <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
+        </is>
+      </c>
+      <c r="E13" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را طوری تنظیم کن که درصد روی ۱ بایستد (باتری تقریباً خالی ولی نه صفر).
+گام ۲: دو دقیقه چراغ سبز و بوق را زیر نظر بگیر.</t>
+        </is>
+      </c>
+      <c r="F13" s="101" t="inlineStr">
+        <is>
+          <t>درصد پایدار ۱</t>
+        </is>
+      </c>
+      <c r="G13" s="101" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H13" s="98" t="inlineStr">
+        <is>
+          <t>هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
+        </is>
+      </c>
+      <c r="I13" s="98" t="inlineStr">
+        <is>
+          <t>برق‌های کوتاه و کم</t>
+        </is>
+      </c>
+      <c r="J13" s="98" t="inlineStr">
+        <is>
+          <t>باید بشنوید و ببینید: هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند. اگر مثل باتریِ کاملاً خالی رفتار کرد (بوق بلند و خاموشی کامل)، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K13" s="98" t="n"/>
+      <c r="L13" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M13" s="98" t="n"/>
+      <c r="N13" s="98" t="n"/>
+      <c r="O13" s="101" t="n"/>
+      <c r="P13" s="101" t="n"/>
+      <c r="Q13" s="102">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="92" t="inlineStr">
+        <is>
+          <t>UI-016</t>
+        </is>
+      </c>
+      <c r="B14" s="93" t="inlineStr">
+        <is>
+          <t>Full 100/95 stay</t>
+        </is>
+      </c>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D14" s="103" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-015؛ درصد روی ۱۰۰ و سبز ثابت است</t>
+        </is>
+      </c>
+      <c r="E14" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: با یک مصرف کوچک درصد را بین ۹۵ و ۱۰۰ نگه دار و چند بار بالا پایینش کن.
+گام ۲: چراغ‌ها را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F14" s="95" t="inlineStr">
+        <is>
+          <t>درصد بین ۹۵ تا ۱۰۰</t>
+        </is>
+      </c>
+      <c r="G14" s="95" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H14" s="93" t="inlineStr">
+        <is>
+          <t>تا وقتی درصد بالای ۹۵ است همان ورودی خوب می‌ماند: سبز ثابت و زرد خاموش</t>
+        </is>
+      </c>
+      <c r="I14" s="93" t="inlineStr">
+        <is>
+          <t>سبز ثابت</t>
+        </is>
+      </c>
+      <c r="J14" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: تا وقتی باتری پر است سبز ثابت می‌ماند و زرد خاموش است. اگر بی‌دلیل به چشمک زرد شارژ برگشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K14" s="93" t="n"/>
+      <c r="L14" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M14" s="93" t="n"/>
+      <c r="N14" s="93" t="n"/>
+      <c r="O14" s="95" t="n"/>
+      <c r="P14" s="95" t="n"/>
+      <c r="Q14" s="97">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="92" t="inlineStr">
+        <is>
+          <t>UI-017</t>
+        </is>
+      </c>
+      <c r="B15" s="98" t="inlineStr">
+        <is>
+          <t>Full 95 exit</t>
+        </is>
+      </c>
+      <c r="C15" s="99" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D15" s="100" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-016؛ درصد بالای ۹۵ و سبز ثابت است</t>
+        </is>
+      </c>
+      <c r="E15" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: یک بار واقعی روی باتری بکش تا درصد زیر ۹۵ بیاید.
+گام ۲: چراغ‌ها را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F15" s="101" t="inlineStr">
+        <is>
+          <t>افت درصد شارژ به زیر ۹۵</t>
+        </is>
+      </c>
+      <c r="G15" s="101" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H15" s="98" t="inlineStr">
+        <is>
+          <t>برمی‌گردد به وضعیت شارژ: سبز از ثابت درمی‌آید و زرد دوباره چشمک می‌زند</t>
+        </is>
+      </c>
+      <c r="I15" s="98" t="inlineStr">
+        <is>
+          <t>برگشت به چشمک زرد</t>
+        </is>
+      </c>
+      <c r="J15" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: وقتی شارژ باتری پایین آمد، زرد دوباره چشمک می‌زند و سبز از ثابت درمی‌آید. اگر روی سبز ثابت ماند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K15" s="98" t="n"/>
+      <c r="L15" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M15" s="98" t="n"/>
+      <c r="N15" s="98" t="n"/>
+      <c r="O15" s="101" t="n"/>
+      <c r="P15" s="101" t="n"/>
+      <c r="Q15" s="102">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="92" t="inlineStr">
+        <is>
+          <t>UI-020</t>
+        </is>
+      </c>
+      <c r="B16" s="93" t="inlineStr">
+        <is>
+          <t>Charging non-blocking</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D16" s="93" t="inlineStr">
+        <is>
+          <t>برق شهر وصل و باتری در حال شارژ است (زرد چشمک‌زن)</t>
+        </is>
+      </c>
+      <c r="E16" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ با پنل کار کن و چند پارامتر بخوان.
+گام ۲: دو دقیقه دستگاه را زیر نظر بگیر.</t>
+        </is>
+      </c>
+      <c r="F16" s="95" t="inlineStr">
+        <is>
+          <t>کار با پنل حین شارژ</t>
+        </is>
+      </c>
+      <c r="G16" s="95" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H16" s="93" t="inlineStr">
+        <is>
+          <t>زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست</t>
+        </is>
+      </c>
+      <c r="I16" s="93" t="inlineStr">
+        <is>
+          <t>چشمک منظم زرد</t>
+        </is>
+      </c>
+      <c r="J16" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست. اگر هنگ یا قطع ارتباط دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K16" s="93" t="n"/>
+      <c r="L16" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M16" s="93" t="n"/>
+      <c r="N16" s="93" t="n"/>
+      <c r="O16" s="95" t="n"/>
+      <c r="P16" s="95" t="n"/>
+      <c r="Q16" s="97">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="92" t="inlineStr">
+        <is>
+          <t>UI-022</t>
+        </is>
+      </c>
+      <c r="B17" s="93" t="inlineStr">
+        <is>
+          <t>Snapshot invalid</t>
+        </is>
+      </c>
+      <c r="C17" s="94" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D17" s="93" t="inlineStr">
+        <is>
+          <t>دستگاه روشن و در حال کار عادی است</t>
+        </is>
+      </c>
+      <c r="E17" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: سیم حس‌کردن ولتاژ باتری را لحظه‌ای جدا کن (دستگاه اندازهٔ تازه ندارد).
+گام ۲: به چراغ‌ها و بوق نگاه کن؛ نباید الگوی دیوانه‌وار یا بوق بی‌دلیل بیاید.
+گام ۳: سیم را وصل کن؛ رفتار عادی باید برگردد.</t>
+        </is>
+      </c>
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>قطع و وصل کوتاه سیم حس باتری</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H17" s="93" t="inlineStr">
+        <is>
+          <t>حین قطع، چهرهٔ سالم قبلی آرام می‌ماند و دستگاه هنگ نمی‌کند؛ با وصل مجدد همه‌چیز عادی می‌شود</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="inlineStr">
+        <is>
+          <t>بدون الگوی تازهٔ خطادار</t>
+        </is>
+      </c>
+      <c r="J17" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: حین قطع اندازه‌گیری، چهرهٔ سالم قبلی آرام می‌ماند و دستگاه هنگ نمی‌کند؛ با وصل مجدد همه‌چیز عادی می‌شود. اگر بوق بی‌دلیل، چراغ قاطی یا هنگ دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K17" s="93" t="n"/>
+      <c r="L17" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M17" s="93" t="n"/>
+      <c r="N17" s="93" t="n"/>
+      <c r="O17" s="95" t="n"/>
+      <c r="P17" s="95" t="n"/>
+      <c r="Q17" s="97">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="92" t="inlineStr">
+        <is>
+          <t>UI-024</t>
+        </is>
+      </c>
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>Input switch 20/21</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D18" s="93" t="inlineStr">
+        <is>
+          <t>ورودی از منبع آزمایشگاهی می‌آید؛ باتری وصل است</t>
+        </is>
+      </c>
+      <c r="E18" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
+گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
+        </is>
+      </c>
+      <c r="F18" s="95" t="inlineStr">
+        <is>
+          <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
+        </is>
+      </c>
+      <c r="G18" s="95" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H18" s="93" t="inlineStr">
+        <is>
+          <t>وضعیت ورودی فقط وقتی واقعاً از مرز رد می‌شوی عوض می‌شود؛ وسط راه هیچ رفت‌وبرگشت بی‌دلیلی نیست</t>
+        </is>
+      </c>
+      <c r="I18" s="93" t="inlineStr">
+        <is>
+          <t>گذار تکی و تمیز</t>
+        </is>
+      </c>
+      <c r="J18" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: با رد شدن واقعی از مرز ورودی، چهره فقط یک‌بار و تمیز عوض می‌شود؛ وسط راه رفت‌وبرگشت بی‌دلیل نیست. اگر فلیکر دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K18" s="93" t="n"/>
+      <c r="L18" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M18" s="93" t="n"/>
+      <c r="N18" s="93" t="n"/>
+      <c r="O18" s="95" t="n"/>
+      <c r="P18" s="95" t="n"/>
+      <c r="Q18" s="97">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="92" t="inlineStr">
+        <is>
+          <t>UI-031</t>
+        </is>
+      </c>
+      <c r="B19" s="98" t="inlineStr">
+        <is>
+          <t>عملکرد واقعی درصد</t>
+        </is>
+      </c>
+      <c r="C19" s="101" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D19" s="98" t="inlineStr">
+        <is>
+          <t>دستگاه روی باتری در حال کار، درصد شارژ معلوم</t>
+        </is>
+      </c>
+      <c r="E19" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را روی باتری روشن کن تا درصد شارژ و چشمک سبز معلوم باشد.
+گام ۲: فقط ولتاژ ورودی را بالا و پایین کن (به باتری دست نزن).
+گام ۳: درصد و چشمک سبز نباید هیچ تغییری کند.
+گام ۴: حالا فقط ولتاژ باتری را عوض کن؛ درصد باید عوض شود.</t>
+        </is>
+      </c>
+      <c r="F19" s="98" t="inlineStr">
+        <is>
+          <t>تغییر جدا جدا ورودی و باتری</t>
+        </is>
+      </c>
+      <c r="G19" s="101" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H19" s="98" t="inlineStr">
+        <is>
+          <t>درصد فقط از باتری می‌آید، نه از ورودی</t>
+        </is>
+      </c>
+      <c r="I19" s="98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: درصد نمایش با ولتاژ باتری عوض می‌شود و با تغییر ولتاژ ورودی ثابت می‌ماند. اگر درصد از ورودی اثر گرفت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K19" s="98" t="n"/>
+      <c r="L19" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M19" s="98" t="n"/>
+      <c r="N19" s="98" t="n"/>
+      <c r="O19" s="101" t="n"/>
+      <c r="P19" s="101" t="n"/>
+      <c r="Q19" s="102">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="92" t="inlineStr">
         <is>
           <t>UI-035</t>
         </is>
       </c>
-      <c r="B71" s="98" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>عدم‌توازن باتری: قرمز چشمک‌زن تنها</t>
         </is>
       </c>
-      <c r="C71" s="101" t="inlineStr">
+      <c r="C20" s="101" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D71" s="98" t="inlineStr">
+      <c r="D20" s="98" t="inlineStr">
         <is>
           <t>دو باتری ۱۲ ولت داری که یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای؛ برای زود دیدن، از پنل حدّ رویداد مجاز را موقتاً کم کن</t>
         </is>
       </c>
-      <c r="E71" s="98" t="inlineStr">
+      <c r="E20" s="98" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌های نابرابر را وصل و دستگاه را مدتی به کار بگذار تا حکم عدم‌توازن قفل شود.
 گام ۲: چراغ‌ها را ببین: فقط قرمز چشمک می‌زند؛ سبز و زرد خاموش‌اند و هر از چندی یک بوق کوتاه می‌آید.
@@ -4624,45 +2950,1599 @@
 گام ۴: چند دقیقه صبر کن تا قفل خودش پاک شود.</t>
         </is>
       </c>
-      <c r="F71" s="98" t="inlineStr">
+      <c r="F20" s="98" t="inlineStr">
         <is>
           <t>باتری‌های نابرابر و بعد تعویض با سالم</t>
         </is>
       </c>
-      <c r="G71" s="101" t="inlineStr">
+      <c r="G20" s="101" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H71" s="98" t="inlineStr">
+      <c r="H20" s="98" t="inlineStr">
         <is>
           <t>در قفل: قرمز چشمک‌زنِ تنها بدون سبز و زرد؛ با تعویض باتری قفل خودکار پاک می‌شود</t>
         </is>
       </c>
-      <c r="I71" s="98" t="inlineStr">
+      <c r="I20" s="98" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن، بقیه خاموش</t>
         </is>
       </c>
-      <c r="J71" s="98" t="inlineStr">
-        <is>
-          <t>همین چهره و پاک‌شدن با تعویض = قبول؛ روشن‌ماندن سبز/زرد یا پاک‌نشدن = رد</t>
-        </is>
-      </c>
-      <c r="K71" s="98" t="n"/>
-      <c r="L71" s="96" t="inlineStr">
+      <c r="J20" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: فقط قرمز چشمک می‌زند و سبز و زرد خاموش‌اند؛ با تعویض باتری قفل خودش پاک می‌شود. اگر سبز یا زرد روشن بود یا قفل پاک نشد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K20" s="98" t="n"/>
+      <c r="L20" s="96" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M71" s="98" t="n"/>
-      <c r="N71" s="98" t="n"/>
-      <c r="O71" s="101" t="n"/>
-      <c r="P71" s="101" t="n"/>
-      <c r="Q71" s="102">
-        <f>IF(OR(L71="",L71="در انتظار"),"",IF(Q71="",TODAY(),Q71))</f>
+      <c r="M20" s="98" t="n"/>
+      <c r="N20" s="98" t="n"/>
+      <c r="O20" s="101" t="n"/>
+      <c r="P20" s="101" t="n"/>
+      <c r="Q20" s="102">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="92" t="inlineStr">
+        <is>
+          <t>UI-002</t>
+        </is>
+      </c>
+      <c r="B21" s="93" t="inlineStr">
+        <is>
+          <t>BatteryRun 2% 56/57/58</t>
+        </is>
+      </c>
+      <c r="C21" s="94" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D21" s="93" t="inlineStr">
+        <is>
+          <t>دستگاه فقط روی باتری کار می‌کند (برق شهر قطع)؛ به‌جای باتری یک منبع آزمایشگاهی ۲۴ ولت گذاشته‌ای و درصد حدود نصف است</t>
+        </is>
+      </c>
+      <c r="E21" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: منبع را آن‌قدر تنظیم کن که درصد باتری حدود ۵۷ شود و چشمک سبز جا بیفتد.
+گام ۲: ولتاژ منبع را خیلی کم بالا و پایین کن، در حدی که درصد بین ۵۶ و ۵۸ بازی کند.
+گام ۳: یک دقیقه فقط به چراغ سبز نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>لرزش کوچک ولتاژ باتری دور درصد ۵۷</t>
+        </is>
+      </c>
+      <c r="G21" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H21" s="93" t="inlineStr">
+        <is>
+          <t>چشمک سبز با همان ریتم قبلی ادامه می‌دهد؛ نه تند و کند می‌شود نه از اول شروع می‌شود</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="inlineStr">
+        <is>
+          <t>ریتم ثابت و بی‌پرش</t>
+        </is>
+      </c>
+      <c r="J21" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: چشمک سبز دقیقاً با همان ریتم قبلی ادامه دارد؛ نه تند و کند می‌شود نه از اول شروع می‌کند. اگر ریتم پرید یا عوض شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K21" s="93" t="n"/>
+      <c r="L21" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M21" s="93" t="n"/>
+      <c r="N21" s="93" t="n"/>
+      <c r="O21" s="95" t="n"/>
+      <c r="P21" s="95" t="n"/>
+      <c r="Q21" s="97">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="92" t="inlineStr">
+        <is>
+          <t>UI-003</t>
+        </is>
+      </c>
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>BatteryRun 57→55</t>
+        </is>
+      </c>
+      <c r="C22" s="99" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D22" s="100" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
+        </is>
+      </c>
+      <c r="E22" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا درصد به حدود ۵۵ برسد.
+گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
+گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F22" s="101" t="inlineStr">
+        <is>
+          <t>کم‌کردن آرام ولتاژ باتری تا درصد ۵۵</t>
+        </is>
+      </c>
+      <c r="G22" s="101" t="inlineStr">
+        <is>
+          <t>نیم دقیقه</t>
+        </is>
+      </c>
+      <c r="H22" s="98" t="inlineStr">
+        <is>
+          <t>درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر می‌شود (خاموشی‌اش بیشتر از قبل)</t>
+        </is>
+      </c>
+      <c r="I22" s="100" t="inlineStr">
+        <is>
+          <t>تندتر از UI-002، بدون پرش ناگهانی</t>
+        </is>
+      </c>
+      <c r="J22" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر از قبل می‌شود، بدون هیچ پرش ناگهانی. اگر روی ۵۷ ماند یا ریتم پرید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K22" s="98" t="n"/>
+      <c r="L22" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M22" s="98" t="n"/>
+      <c r="N22" s="98" t="n"/>
+      <c r="O22" s="101" t="n"/>
+      <c r="P22" s="101" t="n"/>
+      <c r="Q22" s="102">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="92" t="inlineStr">
+        <is>
+          <t>UI-004</t>
+        </is>
+      </c>
+      <c r="B23" s="93" t="inlineStr">
+        <is>
+          <t>BatteryRun 57→59</t>
+        </is>
+      </c>
+      <c r="C23" s="94" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D23" s="103" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
+        </is>
+      </c>
+      <c r="E23" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را آرام بالا ببر تا درصد به حدود ۵۹ برسد.
+گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
+گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>بالابردن آرام ولتاژ باتری تا درصد ۵۹</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
+        <is>
+          <t>نیم دقیقه</t>
+        </is>
+      </c>
+      <c r="H23" s="93" t="inlineStr">
+        <is>
+          <t>درصد روی ۵۹ می‌ایستد و چشمک سبز کمی کندتر می‌شود (روشن بودنش بیشتر از قبل)</t>
+        </is>
+      </c>
+      <c r="I23" s="103" t="inlineStr">
+        <is>
+          <t>کندتر از UI-002، بدون پرش ناگهانی</t>
+        </is>
+      </c>
+      <c r="J23" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: درصد روی ۵۹ می‌ایستد و چشمک سبز کمی کندتر از قبل می‌شود، بدون پرش ناگهانی. اگر روی ۵۷ ماند یا ریتم پرید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K23" s="93" t="n"/>
+      <c r="L23" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M23" s="93" t="n"/>
+      <c r="N23" s="93" t="n"/>
+      <c r="O23" s="95" t="n"/>
+      <c r="P23" s="95" t="n"/>
+      <c r="Q23" s="97">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="92" t="inlineStr">
+        <is>
+          <t>UI-006</t>
+        </is>
+      </c>
+      <c r="B24" s="93" t="inlineStr">
+        <is>
+          <t>0↔1 نویز</t>
+        </is>
+      </c>
+      <c r="C24" s="94" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D24" s="103" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-005؛ درصد روی صفر و بوق بحرانی تمام شده</t>
+        </is>
+      </c>
+      <c r="E24" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ منبع را خیلی کم بالا و پایین کن، دور مرز صفر و یک درصد.
+گام ۲: دو دقیقه به چراغ‌ها و بوق گوش بده.</t>
+        </is>
+      </c>
+      <c r="F24" s="95" t="inlineStr">
+        <is>
+          <t>بازی ولتاژ دور مرز ۰ و ۱ درصد</t>
+        </is>
+      </c>
+      <c r="G24" s="95" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H24" s="93" t="inlineStr">
+        <is>
+          <t>بوق بحرانی دوباره شروع نمی‌شود و چراغ‌ها بی‌دلیل روشن و خاموش نمی‌شوند</t>
+        </is>
+      </c>
+      <c r="I24" s="93" t="inlineStr">
+        <is>
+          <t>خاموش و آرام</t>
+        </is>
+      </c>
+      <c r="J24" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: چراغ‌ها خاموش و آرام می‌مانند و بوق بحرانی با نوسان کوچک دوباره شروع نمی‌شود. اگر بوق یا چراغی بی‌دلیل آمد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K24" s="93" t="n"/>
+      <c r="L24" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M24" s="93" t="n"/>
+      <c r="N24" s="93" t="n"/>
+      <c r="O24" s="95" t="n"/>
+      <c r="P24" s="95" t="n"/>
+      <c r="Q24" s="97">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
+          <t>UI-008</t>
+        </is>
+      </c>
+      <c r="B25" s="93" t="inlineStr">
+        <is>
+          <t>1% →2 حفظ/خروج</t>
+        </is>
+      </c>
+      <c r="C25" s="95" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D25" s="103" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
+        </is>
+      </c>
+      <c r="E25" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را خیلی کم بالا ببر، آن‌قدر که درصد هنوز ۲ نشده باشد.
+گام ۲: یک دقیقه رفتار را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>بالا بردن جزئی از درصد ۱</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H25" s="93" t="inlineStr">
+        <is>
+          <t>همان رفتار درصد ۱ می‌ماند: سه بوق هر از چندی و برق کوتاه سبز</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="inlineStr">
+        <is>
+          <t>بدون تغییر</t>
+        </is>
+      </c>
+      <c r="J25" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: رفتار درصد ۱ می‌ماند؛ سه بوق هر از چندی و برق کوتاه سبز، بدون پریدن به رفتار درصد بالاتر. اگر الگو عوض شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K25" s="93" t="n"/>
+      <c r="L25" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M25" s="93" t="n"/>
+      <c r="N25" s="93" t="n"/>
+      <c r="O25" s="95" t="n"/>
+      <c r="P25" s="95" t="n"/>
+      <c r="Q25" s="97">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>UI-009</t>
+        </is>
+      </c>
+      <c r="B26" s="98" t="inlineStr">
+        <is>
+          <t>1% →2 خروج با3</t>
+        </is>
+      </c>
+      <c r="C26" s="99" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D26" s="100" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-007؛ درصد روی ۱</t>
+        </is>
+      </c>
+      <c r="E26" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را آرام بالا ببر تا درصد به ۲ برسد و ثابت شود.
+گام ۲: یک دقیقه به الگوی بوق گوش بده و با درصد ۱ مقایسه کن.</t>
+        </is>
+      </c>
+      <c r="F26" s="101" t="inlineStr">
+        <is>
+          <t>بالا بردن ولتاژ تا درصد ۲</t>
+        </is>
+      </c>
+      <c r="G26" s="101" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H26" s="98" t="inlineStr">
+        <is>
+          <t>الگوی بوق به الگوی ملایم‌ترِ درصد ۲ عوض می‌شود و سبز بیشتر از قبل روشن می‌ماند</t>
+        </is>
+      </c>
+      <c r="I26" s="98" t="inlineStr">
+        <is>
+          <t>روشن‌تر از درصد ۱</t>
+        </is>
+      </c>
+      <c r="J26" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: از درصد ۲ به بعد الگوی بوق ملایم‌تر می‌شود و سبز بیشتر از قبل روشن می‌ماند. اگر روی الگوی درصد ۱ ماند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K26" s="98" t="n"/>
+      <c r="L26" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M26" s="98" t="n"/>
+      <c r="N26" s="98" t="n"/>
+      <c r="O26" s="101" t="n"/>
+      <c r="P26" s="101" t="n"/>
+      <c r="Q26" s="102">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="92" t="inlineStr">
+        <is>
+          <t>UI-010</t>
+        </is>
+      </c>
+      <c r="B27" s="93" t="inlineStr">
+        <is>
+          <t>BoardTest 0→2</t>
+        </is>
+      </c>
+      <c r="C27" s="95" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D27" s="93" t="inlineStr">
+        <is>
+          <t>دستگاه فقط روی باتری؛ منبع از درصد صفر شروع می‌کند</t>
+        </is>
+      </c>
+      <c r="E27" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ را از صفر خیلی آرام بالا بیاور.
+گام ۲: به ترتیبِ الگوها دقت کن: اول باید رفتار درصد ۱ دیده شود و بعد درصد ۲.</t>
+        </is>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>بالا آمدن آرام از ۰ به ۲ درصد</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H27" s="93" t="inlineStr">
+        <is>
+          <t>اول الگوی درصد ۱ (سه بوق و برق کوتاه) و بعد الگوی درصد ۲ می‌آید</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="inlineStr">
+        <is>
+          <t>گذار پله‌ای ۱ بعد ۲</t>
+        </is>
+      </c>
+      <c r="J27" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: اول الگوی درصد ۱ می‌آید (سه بوق و برق کوتاه) و بعد الگوی درصد ۲؛ هر دو پله به‌ترتیب دیده می‌شوند. اگر مستقیم به الگوی ۲ پرید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K27" s="93" t="n"/>
+      <c r="L27" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M27" s="93" t="n"/>
+      <c r="N27" s="93" t="n"/>
+      <c r="O27" s="95" t="n"/>
+      <c r="P27" s="95" t="n"/>
+      <c r="Q27" s="97">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="92" t="inlineStr">
+        <is>
+          <t>UI-011</t>
+        </is>
+      </c>
+      <c r="B28" s="98" t="inlineStr">
+        <is>
+          <t>Charging 5% 56/57/58</t>
+        </is>
+      </c>
+      <c r="C28" s="99" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D28" s="98" t="inlineStr">
+        <is>
+          <t>برق شهر وصل و باتری واقعی در حال شارژ است؛ درصد حدود نصف</t>
+        </is>
+      </c>
+      <c r="E28" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را به شارژ بزن و صبر کن درصد دور ۵۷ ثابت شود.
+گام ۲: یک دقیقه فقط چراغ زرد را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F28" s="101" t="inlineStr">
+        <is>
+          <t>شارژ عادی با درصد میانی</t>
+        </is>
+      </c>
+      <c r="G28" s="101" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H28" s="98" t="inlineStr">
+        <is>
+          <t>زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند</t>
+        </is>
+      </c>
+      <c r="I28" s="98" t="inlineStr">
+        <is>
+          <t>ریتم ثابت</t>
+        </is>
+      </c>
+      <c r="J28" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند. اگر ریتم پرید یا زرد ایستاد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K28" s="98" t="n"/>
+      <c r="L28" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M28" s="98" t="n"/>
+      <c r="N28" s="98" t="n"/>
+      <c r="O28" s="101" t="n"/>
+      <c r="P28" s="101" t="n"/>
+      <c r="Q28" s="102">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="92" t="inlineStr">
+        <is>
+          <t>UI-012</t>
+        </is>
+      </c>
+      <c r="B29" s="93" t="inlineStr">
+        <is>
+          <t>Charging 5% 53..61</t>
+        </is>
+      </c>
+      <c r="C29" s="94" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D29" s="103" t="inlineStr">
+        <is>
+          <t>ادامهٔ UI-011؛ در حال شارژ با درصد حدود ۵۷</t>
+        </is>
+      </c>
+      <c r="E29" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ، ولتاژ باتری را با یک مصرف کوچک یا منبع کمی بالا و پایین کن (درصد دور ۵۷ بازی کند).
+گام ۲: یک دقیقه چراغ زرد را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>بازی کوچک درصد حین شارژ</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H29" s="93" t="inlineStr">
+        <is>
+          <t>چشمک زرد هیچ تغییری نمی‌کند و با همان ریتم ادامه می‌دهد</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="inlineStr">
+        <is>
+          <t>بدون تغییر</t>
+        </is>
+      </c>
+      <c r="J29" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: چشمک زرد با نوسان کوچک ولتاژ هیچ تغییری نمی‌کند و با همان ریتم ادامه می‌دهد. اگر ریتم عوض شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K29" s="93" t="n"/>
+      <c r="L29" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M29" s="93" t="n"/>
+      <c r="N29" s="93" t="n"/>
+      <c r="O29" s="95" t="n"/>
+      <c r="P29" s="95" t="n"/>
+      <c r="Q29" s="97">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="40.5" customHeight="1">
+      <c r="A30" s="92" t="inlineStr">
+        <is>
+          <t>UI-013</t>
+        </is>
+      </c>
+      <c r="B30" s="98" t="inlineStr">
+        <is>
+          <t>Charging 5% خروج</t>
+        </is>
+      </c>
+      <c r="C30" s="99" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D30" s="98" t="inlineStr">
+        <is>
+          <t>برق شهر وصل و دستگاه در حال شارژ؛ درصد حدود ۵۷</t>
+        </is>
+      </c>
+      <c r="E30" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: درصد شارژ را با منبع یا مصرف واقعی اول به حدود ۵۲ ببر و ثابت کن.
+گام ۲: بعد به حدود ۶۲ ببر و ثابت کن.
+گام ۳: موقع جابه‌جایی‌ها به زرد نگاه کن که قطع و وصل ناگهانی نکند.</t>
+        </is>
+      </c>
+      <c r="F30" s="101" t="inlineStr">
+        <is>
+          <t>درصد شارژ ۵۷ بعد ۵۲ بعد ۶۲</t>
+        </is>
+      </c>
+      <c r="G30" s="101" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H30" s="98" t="inlineStr">
+        <is>
+          <t>ریتم زرد با درصد عوض می‌شود ولی چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد</t>
+        </is>
+      </c>
+      <c r="I30" s="98" t="inlineStr">
+        <is>
+          <t>ریتم تازه، بدون راه‌اندازی از صفر</t>
+        </is>
+      </c>
+      <c r="J30" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: با بزرگ‌شدن تغییر درصد، ریتم زرد نرم عوض می‌شود؛ چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد. اگر روی ریتم قبلی ماند یا پرید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K30" s="98" t="n"/>
+      <c r="L30" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M30" s="98" t="n"/>
+      <c r="N30" s="98" t="n"/>
+      <c r="O30" s="101" t="n"/>
+      <c r="P30" s="101" t="n"/>
+      <c r="Q30" s="102">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="92" t="inlineStr">
+        <is>
+          <t>UI-023</t>
+        </is>
+      </c>
+      <c r="B31" s="98" t="inlineStr">
+        <is>
+          <t>Low Alarm 21/21.2</t>
+        </is>
+      </c>
+      <c r="C31" s="99" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D31" s="98" t="inlineStr">
+        <is>
+          <t>دستگاه روی باتری کار می‌کند؛ منبع آزمایشگاهی به‌جای باتری</t>
+        </is>
+      </c>
+      <c r="E31" s="98" t="inlineStr">
+        <is>
+          <t>گام ۱: ولتاژ باتری را آرام تا نزدیک مرز باتری کم (حدود ۲۱ ولت) پایین بیاور.
+گام ۲: کمی دور همان مرز بالا و پایینش کن و چراغ‌ها را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F31" s="101" t="inlineStr">
+        <is>
+          <t>باتری دور مرز ۲۱ ولت</t>
+        </is>
+      </c>
+      <c r="G31" s="101" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H31" s="98" t="inlineStr">
+        <is>
+          <t>چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود</t>
+        </is>
+      </c>
+      <c r="I31" s="98" t="inlineStr">
+        <is>
+          <t>پایدار، بدون فلیکر</t>
+        </is>
+      </c>
+      <c r="J31" s="98" t="inlineStr">
+        <is>
+          <t>باید ببینید: دور مرز باتریِ کم، چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود. اگر چراغ‌ها رفت‌وبرگشت تند کردند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K31" s="98" t="n"/>
+      <c r="L31" s="96" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M31" s="98" t="n"/>
+      <c r="N31" s="98" t="n"/>
+      <c r="O31" s="101" t="n"/>
+      <c r="P31" s="101" t="n"/>
+      <c r="Q31" s="102">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="92" t="inlineStr">
+        <is>
+          <t>UI-030</t>
+        </is>
+      </c>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>پنل دیالوگ مستقل</t>
+        </is>
+      </c>
+      <c r="C32" s="95" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D32" s="93" t="inlineStr">
+        <is>
+          <t>پنل به دستگاه وصل و دستگاه در حال کار عادی است</t>
+        </is>
+      </c>
+      <c r="E32" s="93" t="inlineStr">
+        <is>
+          <t>گام ۱: در پنل یک پیام یا دیالوگ باز کن.
+گام ۲: هم‌زمان چراغ‌های دستگاه را نگاه کن.
+گام ۳: دیالوگ را ببند.</t>
+        </is>
+      </c>
+      <c r="F32" s="95" t="inlineStr">
+        <is>
+          <t>باز و بسته‌کردن دیالوگ پنل</t>
+        </is>
+      </c>
+      <c r="G32" s="95" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H32" s="93" t="inlineStr">
+        <is>
+          <t>دیالوگ پنل چراغ‌ها و بوق دستگاه را به هم نمی‌ریزد؛ رفتار عادی ادامه دارد</t>
+        </is>
+      </c>
+      <c r="I32" s="93" t="inlineStr">
+        <is>
+          <t>بدون تغییر</t>
+        </is>
+      </c>
+      <c r="J32" s="93" t="inlineStr">
+        <is>
+          <t>باید ببینید: دیالوگ پنل باز و بسته می‌شود و چراغ‌ها و بوق دستگاه دقیقاً مثل قبل ادامه می‌دهند. اگر رفتار چراغ یا بوق به‌هم ریخت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K32" s="93" t="n"/>
+      <c r="L32" s="104" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M32" s="93" t="n"/>
+      <c r="N32" s="93" t="n"/>
+      <c r="O32" s="95" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P32" s="95" t="n"/>
+      <c r="Q32" s="97">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="125" t="n"/>
+      <c r="B33" s="125" t="n"/>
+      <c r="C33" s="125" t="n"/>
+      <c r="D33" s="125" t="n"/>
+      <c r="E33" s="125" t="n"/>
+      <c r="F33" s="125" t="n"/>
+      <c r="G33" s="125" t="n"/>
+      <c r="H33" s="125" t="n"/>
+      <c r="I33" s="125" t="n"/>
+      <c r="J33" s="125" t="n"/>
+      <c r="K33" s="125" t="n"/>
+      <c r="L33" s="125" t="n"/>
+      <c r="M33" s="125" t="n"/>
+      <c r="N33" s="125" t="n"/>
+      <c r="O33" s="125" t="n"/>
+      <c r="P33" s="125" t="n"/>
+      <c r="Q33" s="126" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="125" t="n"/>
+      <c r="B34" s="125" t="n"/>
+      <c r="C34" s="125" t="n"/>
+      <c r="D34" s="125" t="n"/>
+      <c r="E34" s="125" t="n"/>
+      <c r="F34" s="125" t="n"/>
+      <c r="G34" s="125" t="n"/>
+      <c r="H34" s="125" t="n"/>
+      <c r="I34" s="125" t="n"/>
+      <c r="J34" s="125" t="n"/>
+      <c r="K34" s="125" t="n"/>
+      <c r="L34" s="125" t="n"/>
+      <c r="M34" s="125" t="n"/>
+      <c r="N34" s="125" t="n"/>
+      <c r="O34" s="125" t="n"/>
+      <c r="P34" s="125" t="n"/>
+      <c r="Q34" s="126" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="125" t="n"/>
+      <c r="B35" s="125" t="n"/>
+      <c r="C35" s="125" t="n"/>
+      <c r="D35" s="125" t="n"/>
+      <c r="E35" s="125" t="n"/>
+      <c r="F35" s="125" t="n"/>
+      <c r="G35" s="125" t="n"/>
+      <c r="H35" s="125" t="n"/>
+      <c r="I35" s="125" t="n"/>
+      <c r="J35" s="125" t="n"/>
+      <c r="K35" s="125" t="n"/>
+      <c r="L35" s="125" t="n"/>
+      <c r="M35" s="125" t="n"/>
+      <c r="N35" s="125" t="n"/>
+      <c r="O35" s="125" t="n"/>
+      <c r="P35" s="125" t="n"/>
+      <c r="Q35" s="126" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="125" t="n"/>
+      <c r="B36" s="125" t="n"/>
+      <c r="C36" s="125" t="n"/>
+      <c r="D36" s="125" t="n"/>
+      <c r="E36" s="125" t="n"/>
+      <c r="F36" s="125" t="n"/>
+      <c r="G36" s="125" t="n"/>
+      <c r="H36" s="125" t="n"/>
+      <c r="I36" s="125" t="n"/>
+      <c r="J36" s="125" t="n"/>
+      <c r="K36" s="125" t="n"/>
+      <c r="L36" s="125" t="n"/>
+      <c r="M36" s="125" t="n"/>
+      <c r="N36" s="125" t="n"/>
+      <c r="O36" s="125" t="n"/>
+      <c r="P36" s="125" t="n"/>
+      <c r="Q36" s="126" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="125" t="n"/>
+      <c r="B37" s="125" t="n"/>
+      <c r="C37" s="125" t="n"/>
+      <c r="D37" s="125" t="n"/>
+      <c r="E37" s="125" t="n"/>
+      <c r="F37" s="125" t="n"/>
+      <c r="G37" s="125" t="n"/>
+      <c r="H37" s="125" t="n"/>
+      <c r="I37" s="125" t="n"/>
+      <c r="J37" s="125" t="n"/>
+      <c r="K37" s="125" t="n"/>
+      <c r="L37" s="125" t="n"/>
+      <c r="M37" s="125" t="n"/>
+      <c r="N37" s="125" t="n"/>
+      <c r="O37" s="125" t="n"/>
+      <c r="P37" s="125" t="n"/>
+      <c r="Q37" s="126" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="125" t="n"/>
+      <c r="B38" s="125" t="n"/>
+      <c r="C38" s="125" t="n"/>
+      <c r="D38" s="125" t="n"/>
+      <c r="E38" s="125" t="n"/>
+      <c r="F38" s="125" t="n"/>
+      <c r="G38" s="125" t="n"/>
+      <c r="H38" s="125" t="n"/>
+      <c r="I38" s="125" t="n"/>
+      <c r="J38" s="125" t="n"/>
+      <c r="K38" s="125" t="n"/>
+      <c r="L38" s="125" t="n"/>
+      <c r="M38" s="125" t="n"/>
+      <c r="N38" s="125" t="n"/>
+      <c r="O38" s="125" t="n"/>
+      <c r="P38" s="125" t="n"/>
+      <c r="Q38" s="126" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="125" t="n"/>
+      <c r="B39" s="125" t="n"/>
+      <c r="C39" s="125" t="n"/>
+      <c r="D39" s="125" t="n"/>
+      <c r="E39" s="125" t="n"/>
+      <c r="F39" s="125" t="n"/>
+      <c r="G39" s="125" t="n"/>
+      <c r="H39" s="125" t="n"/>
+      <c r="I39" s="125" t="n"/>
+      <c r="J39" s="125" t="n"/>
+      <c r="K39" s="125" t="n"/>
+      <c r="L39" s="125" t="n"/>
+      <c r="M39" s="125" t="n"/>
+      <c r="N39" s="125" t="n"/>
+      <c r="O39" s="125" t="n"/>
+      <c r="P39" s="125" t="n"/>
+      <c r="Q39" s="126" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="125" t="n"/>
+      <c r="B40" s="125" t="n"/>
+      <c r="C40" s="125" t="n"/>
+      <c r="D40" s="125" t="n"/>
+      <c r="E40" s="125" t="n"/>
+      <c r="F40" s="125" t="n"/>
+      <c r="G40" s="125" t="n"/>
+      <c r="H40" s="125" t="n"/>
+      <c r="I40" s="125" t="n"/>
+      <c r="J40" s="125" t="n"/>
+      <c r="K40" s="125" t="n"/>
+      <c r="L40" s="125" t="n"/>
+      <c r="M40" s="125" t="n"/>
+      <c r="N40" s="125" t="n"/>
+      <c r="O40" s="125" t="n"/>
+      <c r="P40" s="125" t="n"/>
+      <c r="Q40" s="126" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="125" t="n"/>
+      <c r="B41" s="125" t="n"/>
+      <c r="C41" s="125" t="n"/>
+      <c r="D41" s="125" t="n"/>
+      <c r="E41" s="125" t="n"/>
+      <c r="F41" s="125" t="n"/>
+      <c r="G41" s="125" t="n"/>
+      <c r="H41" s="125" t="n"/>
+      <c r="I41" s="125" t="n"/>
+      <c r="J41" s="125" t="n"/>
+      <c r="K41" s="125" t="n"/>
+      <c r="L41" s="125" t="n"/>
+      <c r="M41" s="125" t="n"/>
+      <c r="N41" s="125" t="n"/>
+      <c r="O41" s="125" t="n"/>
+      <c r="P41" s="125" t="n"/>
+      <c r="Q41" s="126" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="125" t="n"/>
+      <c r="B42" s="125" t="n"/>
+      <c r="C42" s="125" t="n"/>
+      <c r="D42" s="125" t="n"/>
+      <c r="E42" s="125" t="n"/>
+      <c r="F42" s="125" t="n"/>
+      <c r="G42" s="125" t="n"/>
+      <c r="H42" s="125" t="n"/>
+      <c r="I42" s="125" t="n"/>
+      <c r="J42" s="125" t="n"/>
+      <c r="K42" s="125" t="n"/>
+      <c r="L42" s="125" t="n"/>
+      <c r="M42" s="125" t="n"/>
+      <c r="N42" s="125" t="n"/>
+      <c r="O42" s="125" t="n"/>
+      <c r="P42" s="125" t="n"/>
+      <c r="Q42" s="126" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="125" t="n"/>
+      <c r="B43" s="125" t="n"/>
+      <c r="C43" s="125" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="125" t="n"/>
+      <c r="F43" s="125" t="n"/>
+      <c r="G43" s="125" t="n"/>
+      <c r="H43" s="125" t="n"/>
+      <c r="I43" s="125" t="n"/>
+      <c r="J43" s="125" t="n"/>
+      <c r="K43" s="125" t="n"/>
+      <c r="L43" s="125" t="n"/>
+      <c r="M43" s="125" t="n"/>
+      <c r="N43" s="125" t="n"/>
+      <c r="O43" s="125" t="n"/>
+      <c r="P43" s="125" t="n"/>
+      <c r="Q43" s="126" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="125" t="n"/>
+      <c r="B44" s="125" t="n"/>
+      <c r="C44" s="125" t="n"/>
+      <c r="D44" s="125" t="n"/>
+      <c r="E44" s="125" t="n"/>
+      <c r="F44" s="125" t="n"/>
+      <c r="G44" s="125" t="n"/>
+      <c r="H44" s="125" t="n"/>
+      <c r="I44" s="125" t="n"/>
+      <c r="J44" s="125" t="n"/>
+      <c r="K44" s="125" t="n"/>
+      <c r="L44" s="125" t="n"/>
+      <c r="M44" s="125" t="n"/>
+      <c r="N44" s="125" t="n"/>
+      <c r="O44" s="125" t="n"/>
+      <c r="P44" s="125" t="n"/>
+      <c r="Q44" s="126" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="125" t="n"/>
+      <c r="B45" s="125" t="n"/>
+      <c r="C45" s="125" t="n"/>
+      <c r="D45" s="125" t="n"/>
+      <c r="E45" s="125" t="n"/>
+      <c r="F45" s="125" t="n"/>
+      <c r="G45" s="125" t="n"/>
+      <c r="H45" s="125" t="n"/>
+      <c r="I45" s="125" t="n"/>
+      <c r="J45" s="125" t="n"/>
+      <c r="K45" s="125" t="n"/>
+      <c r="L45" s="125" t="n"/>
+      <c r="M45" s="125" t="n"/>
+      <c r="N45" s="125" t="n"/>
+      <c r="O45" s="125" t="n"/>
+      <c r="P45" s="125" t="n"/>
+      <c r="Q45" s="126" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="125" t="n"/>
+      <c r="B46" s="125" t="n"/>
+      <c r="C46" s="125" t="n"/>
+      <c r="D46" s="125" t="n"/>
+      <c r="E46" s="125" t="n"/>
+      <c r="F46" s="125" t="n"/>
+      <c r="G46" s="125" t="n"/>
+      <c r="H46" s="125" t="n"/>
+      <c r="I46" s="125" t="n"/>
+      <c r="J46" s="125" t="n"/>
+      <c r="K46" s="125" t="n"/>
+      <c r="L46" s="125" t="n"/>
+      <c r="M46" s="125" t="n"/>
+      <c r="N46" s="125" t="n"/>
+      <c r="O46" s="125" t="n"/>
+      <c r="P46" s="125" t="n"/>
+      <c r="Q46" s="126" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="125" t="n"/>
+      <c r="B47" s="125" t="n"/>
+      <c r="C47" s="125" t="n"/>
+      <c r="D47" s="125" t="n"/>
+      <c r="E47" s="125" t="n"/>
+      <c r="F47" s="125" t="n"/>
+      <c r="G47" s="125" t="n"/>
+      <c r="H47" s="125" t="n"/>
+      <c r="I47" s="125" t="n"/>
+      <c r="J47" s="125" t="n"/>
+      <c r="K47" s="125" t="n"/>
+      <c r="L47" s="125" t="n"/>
+      <c r="M47" s="125" t="n"/>
+      <c r="N47" s="125" t="n"/>
+      <c r="O47" s="125" t="n"/>
+      <c r="P47" s="125" t="n"/>
+      <c r="Q47" s="126" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="125" t="n"/>
+      <c r="B48" s="125" t="n"/>
+      <c r="C48" s="125" t="n"/>
+      <c r="D48" s="125" t="n"/>
+      <c r="E48" s="125" t="n"/>
+      <c r="F48" s="125" t="n"/>
+      <c r="G48" s="125" t="n"/>
+      <c r="H48" s="125" t="n"/>
+      <c r="I48" s="125" t="n"/>
+      <c r="J48" s="125" t="n"/>
+      <c r="K48" s="125" t="n"/>
+      <c r="L48" s="125" t="n"/>
+      <c r="M48" s="125" t="n"/>
+      <c r="N48" s="125" t="n"/>
+      <c r="O48" s="125" t="n"/>
+      <c r="P48" s="125" t="n"/>
+      <c r="Q48" s="126" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="125" t="n"/>
+      <c r="B49" s="125" t="n"/>
+      <c r="C49" s="125" t="n"/>
+      <c r="D49" s="125" t="n"/>
+      <c r="E49" s="125" t="n"/>
+      <c r="F49" s="125" t="n"/>
+      <c r="G49" s="125" t="n"/>
+      <c r="H49" s="125" t="n"/>
+      <c r="I49" s="125" t="n"/>
+      <c r="J49" s="125" t="n"/>
+      <c r="K49" s="125" t="n"/>
+      <c r="L49" s="125" t="n"/>
+      <c r="M49" s="125" t="n"/>
+      <c r="N49" s="125" t="n"/>
+      <c r="O49" s="125" t="n"/>
+      <c r="P49" s="125" t="n"/>
+      <c r="Q49" s="126" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="125" t="n"/>
+      <c r="B50" s="125" t="n"/>
+      <c r="C50" s="125" t="n"/>
+      <c r="D50" s="125" t="n"/>
+      <c r="E50" s="125" t="n"/>
+      <c r="F50" s="125" t="n"/>
+      <c r="G50" s="125" t="n"/>
+      <c r="H50" s="125" t="n"/>
+      <c r="I50" s="125" t="n"/>
+      <c r="J50" s="125" t="n"/>
+      <c r="K50" s="125" t="n"/>
+      <c r="L50" s="125" t="n"/>
+      <c r="M50" s="125" t="n"/>
+      <c r="N50" s="125" t="n"/>
+      <c r="O50" s="125" t="n"/>
+      <c r="P50" s="125" t="n"/>
+      <c r="Q50" s="126" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="125" t="n"/>
+      <c r="B51" s="125" t="n"/>
+      <c r="C51" s="125" t="n"/>
+      <c r="D51" s="125" t="n"/>
+      <c r="E51" s="125" t="n"/>
+      <c r="F51" s="125" t="n"/>
+      <c r="G51" s="125" t="n"/>
+      <c r="H51" s="125" t="n"/>
+      <c r="I51" s="125" t="n"/>
+      <c r="J51" s="125" t="n"/>
+      <c r="K51" s="125" t="n"/>
+      <c r="L51" s="125" t="n"/>
+      <c r="M51" s="125" t="n"/>
+      <c r="N51" s="125" t="n"/>
+      <c r="O51" s="125" t="n"/>
+      <c r="P51" s="125" t="n"/>
+      <c r="Q51" s="126" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="125" t="n"/>
+      <c r="B52" s="125" t="n"/>
+      <c r="C52" s="125" t="n"/>
+      <c r="D52" s="125" t="n"/>
+      <c r="E52" s="125" t="n"/>
+      <c r="F52" s="125" t="n"/>
+      <c r="G52" s="125" t="n"/>
+      <c r="H52" s="125" t="n"/>
+      <c r="I52" s="125" t="n"/>
+      <c r="J52" s="125" t="n"/>
+      <c r="K52" s="125" t="n"/>
+      <c r="L52" s="125" t="n"/>
+      <c r="M52" s="125" t="n"/>
+      <c r="N52" s="125" t="n"/>
+      <c r="O52" s="125" t="n"/>
+      <c r="P52" s="125" t="n"/>
+      <c r="Q52" s="126" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="125" t="n"/>
+      <c r="B53" s="125" t="n"/>
+      <c r="C53" s="125" t="n"/>
+      <c r="D53" s="125" t="n"/>
+      <c r="E53" s="125" t="n"/>
+      <c r="F53" s="125" t="n"/>
+      <c r="G53" s="125" t="n"/>
+      <c r="H53" s="125" t="n"/>
+      <c r="I53" s="125" t="n"/>
+      <c r="J53" s="125" t="n"/>
+      <c r="K53" s="125" t="n"/>
+      <c r="L53" s="125" t="n"/>
+      <c r="M53" s="125" t="n"/>
+      <c r="N53" s="125" t="n"/>
+      <c r="O53" s="125" t="n"/>
+      <c r="P53" s="125" t="n"/>
+      <c r="Q53" s="126" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="125" t="n"/>
+      <c r="B54" s="125" t="n"/>
+      <c r="C54" s="125" t="n"/>
+      <c r="D54" s="125" t="n"/>
+      <c r="E54" s="125" t="n"/>
+      <c r="F54" s="125" t="n"/>
+      <c r="G54" s="125" t="n"/>
+      <c r="H54" s="125" t="n"/>
+      <c r="I54" s="125" t="n"/>
+      <c r="J54" s="125" t="n"/>
+      <c r="K54" s="125" t="n"/>
+      <c r="L54" s="125" t="n"/>
+      <c r="M54" s="125" t="n"/>
+      <c r="N54" s="125" t="n"/>
+      <c r="O54" s="125" t="n"/>
+      <c r="P54" s="125" t="n"/>
+      <c r="Q54" s="126" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="125" t="n"/>
+      <c r="B55" s="125" t="n"/>
+      <c r="C55" s="125" t="n"/>
+      <c r="D55" s="125" t="n"/>
+      <c r="E55" s="125" t="n"/>
+      <c r="F55" s="125" t="n"/>
+      <c r="G55" s="125" t="n"/>
+      <c r="H55" s="125" t="n"/>
+      <c r="I55" s="125" t="n"/>
+      <c r="J55" s="125" t="n"/>
+      <c r="K55" s="125" t="n"/>
+      <c r="L55" s="125" t="n"/>
+      <c r="M55" s="125" t="n"/>
+      <c r="N55" s="125" t="n"/>
+      <c r="O55" s="125" t="n"/>
+      <c r="P55" s="125" t="n"/>
+      <c r="Q55" s="126" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="125" t="n"/>
+      <c r="B56" s="125" t="n"/>
+      <c r="C56" s="125" t="n"/>
+      <c r="D56" s="125" t="n"/>
+      <c r="E56" s="125" t="n"/>
+      <c r="F56" s="125" t="n"/>
+      <c r="G56" s="125" t="n"/>
+      <c r="H56" s="125" t="n"/>
+      <c r="I56" s="125" t="n"/>
+      <c r="J56" s="125" t="n"/>
+      <c r="K56" s="125" t="n"/>
+      <c r="L56" s="125" t="n"/>
+      <c r="M56" s="125" t="n"/>
+      <c r="N56" s="125" t="n"/>
+      <c r="O56" s="125" t="n"/>
+      <c r="P56" s="125" t="n"/>
+      <c r="Q56" s="126" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="125" t="n"/>
+      <c r="B57" s="125" t="n"/>
+      <c r="C57" s="125" t="n"/>
+      <c r="D57" s="125" t="n"/>
+      <c r="E57" s="125" t="n"/>
+      <c r="F57" s="125" t="n"/>
+      <c r="G57" s="125" t="n"/>
+      <c r="H57" s="125" t="n"/>
+      <c r="I57" s="125" t="n"/>
+      <c r="J57" s="125" t="n"/>
+      <c r="K57" s="125" t="n"/>
+      <c r="L57" s="125" t="n"/>
+      <c r="M57" s="125" t="n"/>
+      <c r="N57" s="125" t="n"/>
+      <c r="O57" s="125" t="n"/>
+      <c r="P57" s="125" t="n"/>
+      <c r="Q57" s="126" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="125" t="n"/>
+      <c r="B58" s="125" t="n"/>
+      <c r="C58" s="125" t="n"/>
+      <c r="D58" s="125" t="n"/>
+      <c r="E58" s="125" t="n"/>
+      <c r="F58" s="125" t="n"/>
+      <c r="G58" s="125" t="n"/>
+      <c r="H58" s="125" t="n"/>
+      <c r="I58" s="125" t="n"/>
+      <c r="J58" s="125" t="n"/>
+      <c r="K58" s="125" t="n"/>
+      <c r="L58" s="125" t="n"/>
+      <c r="M58" s="125" t="n"/>
+      <c r="N58" s="125" t="n"/>
+      <c r="O58" s="125" t="n"/>
+      <c r="P58" s="125" t="n"/>
+      <c r="Q58" s="126" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="125" t="n"/>
+      <c r="B59" s="125" t="n"/>
+      <c r="C59" s="125" t="n"/>
+      <c r="D59" s="125" t="n"/>
+      <c r="E59" s="125" t="n"/>
+      <c r="F59" s="125" t="n"/>
+      <c r="G59" s="125" t="n"/>
+      <c r="H59" s="125" t="n"/>
+      <c r="I59" s="125" t="n"/>
+      <c r="J59" s="125" t="n"/>
+      <c r="K59" s="125" t="n"/>
+      <c r="L59" s="125" t="n"/>
+      <c r="M59" s="125" t="n"/>
+      <c r="N59" s="125" t="n"/>
+      <c r="O59" s="125" t="n"/>
+      <c r="P59" s="125" t="n"/>
+      <c r="Q59" s="126" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="125" t="n"/>
+      <c r="B60" s="125" t="n"/>
+      <c r="C60" s="125" t="n"/>
+      <c r="D60" s="125" t="n"/>
+      <c r="E60" s="125" t="n"/>
+      <c r="F60" s="125" t="n"/>
+      <c r="G60" s="125" t="n"/>
+      <c r="H60" s="125" t="n"/>
+      <c r="I60" s="125" t="n"/>
+      <c r="J60" s="125" t="n"/>
+      <c r="K60" s="125" t="n"/>
+      <c r="L60" s="125" t="n"/>
+      <c r="M60" s="125" t="n"/>
+      <c r="N60" s="125" t="n"/>
+      <c r="O60" s="125" t="n"/>
+      <c r="P60" s="125" t="n"/>
+      <c r="Q60" s="126" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="125" t="n"/>
+      <c r="B61" s="125" t="n"/>
+      <c r="C61" s="125" t="n"/>
+      <c r="D61" s="125" t="n"/>
+      <c r="E61" s="125" t="n"/>
+      <c r="F61" s="125" t="n"/>
+      <c r="G61" s="125" t="n"/>
+      <c r="H61" s="125" t="n"/>
+      <c r="I61" s="125" t="n"/>
+      <c r="J61" s="125" t="n"/>
+      <c r="K61" s="125" t="n"/>
+      <c r="L61" s="125" t="n"/>
+      <c r="M61" s="125" t="n"/>
+      <c r="N61" s="125" t="n"/>
+      <c r="O61" s="125" t="n"/>
+      <c r="P61" s="125" t="n"/>
+      <c r="Q61" s="126" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="125" t="n"/>
+      <c r="B62" s="125" t="n"/>
+      <c r="C62" s="125" t="n"/>
+      <c r="D62" s="125" t="n"/>
+      <c r="E62" s="125" t="n"/>
+      <c r="F62" s="125" t="n"/>
+      <c r="G62" s="125" t="n"/>
+      <c r="H62" s="125" t="n"/>
+      <c r="I62" s="125" t="n"/>
+      <c r="J62" s="125" t="n"/>
+      <c r="K62" s="125" t="n"/>
+      <c r="L62" s="125" t="n"/>
+      <c r="M62" s="125" t="n"/>
+      <c r="N62" s="125" t="n"/>
+      <c r="O62" s="125" t="n"/>
+      <c r="P62" s="125" t="n"/>
+      <c r="Q62" s="126" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="125" t="n"/>
+      <c r="B63" s="125" t="n"/>
+      <c r="C63" s="125" t="n"/>
+      <c r="D63" s="125" t="n"/>
+      <c r="E63" s="125" t="n"/>
+      <c r="F63" s="125" t="n"/>
+      <c r="G63" s="125" t="n"/>
+      <c r="H63" s="125" t="n"/>
+      <c r="I63" s="125" t="n"/>
+      <c r="J63" s="125" t="n"/>
+      <c r="K63" s="125" t="n"/>
+      <c r="L63" s="125" t="n"/>
+      <c r="M63" s="125" t="n"/>
+      <c r="N63" s="125" t="n"/>
+      <c r="O63" s="125" t="n"/>
+      <c r="P63" s="125" t="n"/>
+      <c r="Q63" s="126" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="125" t="n"/>
+      <c r="B64" s="125" t="n"/>
+      <c r="C64" s="125" t="n"/>
+      <c r="D64" s="125" t="n"/>
+      <c r="E64" s="125" t="n"/>
+      <c r="F64" s="125" t="n"/>
+      <c r="G64" s="125" t="n"/>
+      <c r="H64" s="125" t="n"/>
+      <c r="I64" s="125" t="n"/>
+      <c r="J64" s="125" t="n"/>
+      <c r="K64" s="125" t="n"/>
+      <c r="L64" s="125" t="n"/>
+      <c r="M64" s="125" t="n"/>
+      <c r="N64" s="125" t="n"/>
+      <c r="O64" s="125" t="n"/>
+      <c r="P64" s="125" t="n"/>
+      <c r="Q64" s="126" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="125" t="n"/>
+      <c r="B65" s="125" t="n"/>
+      <c r="C65" s="125" t="n"/>
+      <c r="D65" s="125" t="n"/>
+      <c r="E65" s="125" t="n"/>
+      <c r="F65" s="125" t="n"/>
+      <c r="G65" s="125" t="n"/>
+      <c r="H65" s="125" t="n"/>
+      <c r="I65" s="125" t="n"/>
+      <c r="J65" s="125" t="n"/>
+      <c r="K65" s="125" t="n"/>
+      <c r="L65" s="125" t="n"/>
+      <c r="M65" s="125" t="n"/>
+      <c r="N65" s="125" t="n"/>
+      <c r="O65" s="125" t="n"/>
+      <c r="P65" s="125" t="n"/>
+      <c r="Q65" s="126" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="125" t="n"/>
+      <c r="B66" s="125" t="n"/>
+      <c r="C66" s="125" t="n"/>
+      <c r="D66" s="125" t="n"/>
+      <c r="E66" s="125" t="n"/>
+      <c r="F66" s="125" t="n"/>
+      <c r="G66" s="125" t="n"/>
+      <c r="H66" s="125" t="n"/>
+      <c r="I66" s="125" t="n"/>
+      <c r="J66" s="125" t="n"/>
+      <c r="K66" s="125" t="n"/>
+      <c r="L66" s="125" t="n"/>
+      <c r="M66" s="125" t="n"/>
+      <c r="N66" s="125" t="n"/>
+      <c r="O66" s="125" t="n"/>
+      <c r="P66" s="125" t="n"/>
+      <c r="Q66" s="126" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="127" t="n"/>
+      <c r="B67" s="128" t="n"/>
+      <c r="C67" s="129" t="n"/>
+      <c r="D67" s="128" t="n"/>
+      <c r="E67" s="128" t="n"/>
+      <c r="F67" s="128" t="n"/>
+      <c r="G67" s="129" t="n"/>
+      <c r="H67" s="128" t="n"/>
+      <c r="I67" s="128" t="n"/>
+      <c r="J67" s="128" t="n"/>
+      <c r="K67" s="128" t="n"/>
+      <c r="L67" s="129" t="n"/>
+      <c r="M67" s="128" t="n"/>
+      <c r="N67" s="128" t="n"/>
+      <c r="O67" s="129" t="n"/>
+      <c r="P67" s="129" t="n"/>
+      <c r="Q67" s="130" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="127" t="n"/>
+      <c r="B68" s="128" t="n"/>
+      <c r="C68" s="129" t="n"/>
+      <c r="D68" s="128" t="n"/>
+      <c r="E68" s="128" t="n"/>
+      <c r="F68" s="128" t="n"/>
+      <c r="G68" s="129" t="n"/>
+      <c r="H68" s="128" t="n"/>
+      <c r="I68" s="128" t="n"/>
+      <c r="J68" s="128" t="n"/>
+      <c r="K68" s="128" t="n"/>
+      <c r="L68" s="129" t="n"/>
+      <c r="M68" s="128" t="n"/>
+      <c r="N68" s="128" t="n"/>
+      <c r="O68" s="129" t="n"/>
+      <c r="P68" s="129" t="n"/>
+      <c r="Q68" s="130" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="127" t="n"/>
+      <c r="B69" s="128" t="n"/>
+      <c r="C69" s="129" t="n"/>
+      <c r="D69" s="128" t="n"/>
+      <c r="E69" s="128" t="n"/>
+      <c r="F69" s="128" t="n"/>
+      <c r="G69" s="129" t="n"/>
+      <c r="H69" s="128" t="n"/>
+      <c r="I69" s="128" t="n"/>
+      <c r="J69" s="128" t="n"/>
+      <c r="K69" s="128" t="n"/>
+      <c r="L69" s="129" t="n"/>
+      <c r="M69" s="128" t="n"/>
+      <c r="N69" s="128" t="n"/>
+      <c r="O69" s="129" t="n"/>
+      <c r="P69" s="129" t="n"/>
+      <c r="Q69" s="130" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="127" t="n"/>
+      <c r="B70" s="128" t="n"/>
+      <c r="C70" s="129" t="n"/>
+      <c r="D70" s="128" t="n"/>
+      <c r="E70" s="128" t="n"/>
+      <c r="F70" s="128" t="n"/>
+      <c r="G70" s="129" t="n"/>
+      <c r="H70" s="128" t="n"/>
+      <c r="I70" s="128" t="n"/>
+      <c r="J70" s="128" t="n"/>
+      <c r="K70" s="128" t="n"/>
+      <c r="L70" s="129" t="n"/>
+      <c r="M70" s="128" t="n"/>
+      <c r="N70" s="128" t="n"/>
+      <c r="O70" s="129" t="n"/>
+      <c r="P70" s="129" t="n"/>
+      <c r="Q70" s="130" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="127" t="n"/>
+      <c r="B71" s="128" t="n"/>
+      <c r="C71" s="129" t="n"/>
+      <c r="D71" s="128" t="n"/>
+      <c r="E71" s="128" t="n"/>
+      <c r="F71" s="128" t="n"/>
+      <c r="G71" s="129" t="n"/>
+      <c r="H71" s="128" t="n"/>
+      <c r="I71" s="128" t="n"/>
+      <c r="J71" s="128" t="n"/>
+      <c r="K71" s="128" t="n"/>
+      <c r="L71" s="129" t="n"/>
+      <c r="M71" s="128" t="n"/>
+      <c r="N71" s="128" t="n"/>
+      <c r="O71" s="129" t="n"/>
+      <c r="P71" s="129" t="n"/>
+      <c r="Q71" s="130" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q67"/>
@@ -4671,25 +4551,22 @@
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L5:L114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="L5:L32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="I6" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D7" location="'برنامه تست'!A5"/>
-    <hyperlink ref="I7" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D9" location="'برنامه تست'!A8"/>
-    <hyperlink ref="D11" location="'برنامه تست'!A10"/>
-    <hyperlink ref="D12" location="'برنامه تست'!A10"/>
+    <hyperlink ref="D14" location="'برنامه تست'!A7"/>
     <hyperlink ref="D15" location="'برنامه تست'!A14"/>
-    <hyperlink ref="D18" location="'برنامه تست'!A17"/>
-    <hyperlink ref="D19" location="'برنامه تست'!A18"/>
+    <hyperlink ref="D22" location="'برنامه تست'!A21"/>
+    <hyperlink ref="I22" location="'برنامه تست'!A21"/>
+    <hyperlink ref="D23" location="'برنامه تست'!A21"/>
+    <hyperlink ref="I23" location="'برنامه تست'!A21"/>
+    <hyperlink ref="D24" location="'برنامه تست'!A6"/>
+    <hyperlink ref="D25" location="'برنامه تست'!A13"/>
+    <hyperlink ref="D26" location="'برنامه تست'!A13"/>
+    <hyperlink ref="D29" location="'برنامه تست'!A28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6541,11 +6418,6 @@
           <t>مرجع سریع UI — هیسترزیس 2%/5%/100.95 و نگاشت</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
-      <c r="D1" s="80" t="n"/>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="90" t="inlineStr">
@@ -6553,11 +6425,6 @@
           <t>هیسترزیس: ورودی 20/21 (1000mV), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
         </is>
       </c>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-      <c r="D2" s="80" t="n"/>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="109" t="inlineStr">
@@ -7177,21 +7044,21 @@
     <hyperlink ref="F4" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink ref="F5" location="'تست‌های آزمایشگاهی'!A5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
-    <hyperlink ref="F6" location="'برنامه تست'!A25"/>
+    <hyperlink ref="F6" location="'برنامه تست'!A18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
     <hyperlink ref="F7" location="'تست‌های برنامه‌نویسی'!A5"/>
-    <hyperlink ref="F8" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F9" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F10" location="'برنامه تست'!A14"/>
-    <hyperlink ref="F11" location="'برنامه تست'!A14"/>
-    <hyperlink ref="F12" location="'برنامه تست'!A17"/>
-    <hyperlink ref="F13" location="'برنامه تست'!A5"/>
-    <hyperlink ref="F14" location="'برنامه تست'!A14"/>
-    <hyperlink ref="F15" location="'برنامه تست'!A25"/>
-    <hyperlink ref="F16" location="'برنامه تست'!A22"/>
-    <hyperlink ref="F17" location="'برنامه تست'!A24"/>
-    <hyperlink ref="F18" location="'برنامه تست'!A8"/>
-    <hyperlink ref="F19" location="'برنامه تست'!A23"/>
+    <hyperlink ref="F8" location="'برنامه تست'!A21"/>
+    <hyperlink ref="F9" location="'برنامه تست'!A21"/>
+    <hyperlink ref="F10" location="'برنامه تست'!A28"/>
+    <hyperlink ref="F11" location="'برنامه تست'!A28"/>
+    <hyperlink ref="F12" location="'برنامه تست'!A7"/>
+    <hyperlink ref="F13" location="'برنامه تست'!A21"/>
+    <hyperlink ref="F14" location="'برنامه تست'!A28"/>
+    <hyperlink ref="F15" location="'برنامه تست'!A18"/>
+    <hyperlink ref="F16" location="'برنامه تست'!A9"/>
+    <hyperlink ref="F17" location="'برنامه تست'!A31"/>
+    <hyperlink ref="F18" location="'برنامه تست'!A6"/>
+    <hyperlink ref="F19" location="'برنامه تست'!A17"/>
     <hyperlink ref="F20" location="'تست‌های برنامه‌نویسی'!A5"/>
     <hyperlink ref="F21" location="'تست‌های برنامه‌نویسی'!A5"/>
   </hyperlinks>
@@ -7230,18 +7097,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس 2%/5%/100.95 و فاز</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
-      <c r="D1" s="80" t="n"/>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
-      <c r="G1" s="80" t="n"/>
-      <c r="H1" s="80" t="n"/>
-      <c r="I1" s="80" t="n"/>
-      <c r="J1" s="80" t="n"/>
-      <c r="K1" s="80" t="n"/>
-      <c r="L1" s="80" t="n"/>
-      <c r="M1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="114" t="inlineStr">
@@ -7249,18 +7104,6 @@
           <t>برای هر «رد» یک ردیف؛ فاز چشمک و هیسترزیس 0/1 را با اسکوپ ثبت.</t>
         </is>
       </c>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-      <c r="D2" s="80" t="n"/>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
-      <c r="G2" s="80" t="n"/>
-      <c r="H2" s="80" t="n"/>
-      <c r="I2" s="80" t="n"/>
-      <c r="J2" s="80" t="n"/>
-      <c r="K2" s="80" t="n"/>
-      <c r="L2" s="80" t="n"/>
-      <c r="M2" s="80" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="82" t="inlineStr">
@@ -7512,11 +7355,6 @@
           <t>تأیید نهایی اعتبارسنجی روی برد — UI — 2%/5%/100.95</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
-      <c r="D1" s="80" t="n"/>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="114" t="inlineStr">
@@ -7524,11 +7362,6 @@
           <t>فقط پس از تکمیل تست‌ها و بستن ایرادهای بحرانی/بالا.</t>
         </is>
       </c>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-      <c r="D2" s="80" t="n"/>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="109" t="inlineStr">
@@ -7536,11 +7369,11 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="86" t="n"/>
-      <c r="C3" s="86" t="n"/>
-      <c r="D3" s="86" t="n"/>
-      <c r="E3" s="86" t="n"/>
-      <c r="F3" s="87" t="n"/>
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="29" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="117" t="inlineStr">
@@ -7708,11 +7541,11 @@
           <t>خلاصه وضعیت تست‌ها</t>
         </is>
       </c>
-      <c r="B12" s="86" t="n"/>
-      <c r="C12" s="86" t="n"/>
-      <c r="D12" s="86" t="n"/>
-      <c r="E12" s="86" t="n"/>
-      <c r="F12" s="87" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="29" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="117" t="inlineStr">
@@ -7836,11 +7669,6 @@
           <t>امضا: تست‌کننده ________________  سرپرست ________________  تاریخ ________________</t>
         </is>
       </c>
-      <c r="B20" s="80" t="n"/>
-      <c r="C20" s="80" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8011,8 +7839,6 @@
           <t>ماشین حالت ماژول نمایش و بوق (UI)</t>
         </is>
       </c>
-      <c r="B1" s="80" t="n"/>
-      <c r="C1" s="80" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="80" t="n"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1728,6 +1728,7 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
@@ -2105,56 +2106,58 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8">
       <c r="A8" s="92" t="inlineStr">
         <is>
-          <t>UI-019</t>
+          <t>UI-032</t>
         </is>
       </c>
       <c r="B8" s="98" t="inlineStr">
         <is>
-          <t>InputOk non-blocking</t>
-        </is>
-      </c>
-      <c r="C8" s="99" t="inlineStr">
+          <t>خطای ۶: قطع باتری حین شارژ</t>
+        </is>
+      </c>
+      <c r="C8" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
       <c r="D8" s="98" t="inlineStr">
         <is>
-          <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
+          <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
         </is>
       </c>
       <c r="E8" s="98" t="inlineStr">
         <is>
-          <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
-گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
-        </is>
-      </c>
-      <c r="F8" s="101" t="inlineStr">
-        <is>
-          <t>کار هم‌زمان با پنل روی ورودی خوب</t>
+          <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
+گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
+گام ۳: در پنل ببین جریان شارژ صفر شده.
+گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
+        </is>
+      </c>
+      <c r="F8" s="98" t="inlineStr">
+        <is>
+          <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
         </is>
       </c>
       <c r="G8" s="101" t="inlineStr">
         <is>
-          <t>یک دقیقه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H8" s="98" t="inlineStr">
         <is>
-          <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
+          <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
         </is>
       </c>
       <c r="I8" s="98" t="inlineStr">
         <is>
-          <t>سبز ثابت</t>
+          <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
         </is>
       </c>
       <c r="J8" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: سبز ثابت است، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند. اگر هنگ، مکث یا ریست دیدید، قبول نیست.</t>
+          <t>باید ببینید: با کشیدن سیم باتری حین شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش)، سبز ثابت می‌ماند، زرد خاموش است و سه بوق دوره‌ای می‌آید و شارژ صفر می‌شود؛ با وصل دوبارهٔ باتری همه‌چیز پاک می‌شود و شارژ برمی‌گردد. اگر چراغی اشتباه بود یا خطا پاک نشد، قبول نیست.</t>
         </is>
       </c>
       <c r="K8" s="98" t="n"/>
@@ -2172,58 +2175,58 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9">
       <c r="A9" s="92" t="inlineStr">
         <is>
-          <t>UI-021</t>
+          <t>UI-033</t>
         </is>
       </c>
       <c r="B9" s="98" t="inlineStr">
         <is>
-          <t>InputOverVoltage</t>
-        </is>
-      </c>
-      <c r="C9" s="99" t="inlineStr">
+          <t>خطای ۷: خرابی یک کانال شارژ</t>
+        </is>
+      </c>
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
       <c r="D9" s="98" t="inlineStr">
         <is>
-          <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
+          <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
         </is>
       </c>
       <c r="E9" s="98" t="inlineStr">
         <is>
-          <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
-گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
-گام ۳: ولتاژ را تا حدود ۲۷٫۵ پایین بیاور و نگه دار؛ چهره باید بماند.
-گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
-        </is>
-      </c>
-      <c r="F9" s="101" t="inlineStr">
-        <is>
-          <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
+          <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
+گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
+گام ۳: فیوز را سر جایش بگذار؛ خطا نباید پاک شود.
+گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
+        </is>
+      </c>
+      <c r="F9" s="98" t="inlineStr">
+        <is>
+          <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
         </is>
       </c>
       <c r="G9" s="101" t="inlineStr">
         <is>
-          <t>دو دقیقه</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H9" s="98" t="inlineStr">
         <is>
-          <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
+          <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
       <c r="I9" s="98" t="inlineStr">
         <is>
-          <t>قرمز چشمک‌زن با سبز ثابت</t>
+          <t>هر سه چراغ با یک ریتم مشترک</t>
         </is>
       </c>
       <c r="J9" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: روی ولتاژ بالای ورودی سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید؛ با پایین‌آوردن ولتاژ این چهره پاک می‌شود. اگر نیامد یا زود پاک شد، قبول نیست.</t>
+          <t>باید ببینید: هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است؛ خطا فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود. اگر با جا زدن فیوز یا خودش پاک شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K9" s="98" t="n"/>
@@ -2241,58 +2244,56 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="92" t="inlineStr">
         <is>
-          <t>UI-032</t>
+          <t>UI-019</t>
         </is>
       </c>
       <c r="B10" s="98" t="inlineStr">
         <is>
-          <t>خطای ۶: قطع باتری حین شارژ</t>
-        </is>
-      </c>
-      <c r="C10" s="101" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>InputOk non-blocking</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D10" s="98" t="inlineStr">
         <is>
-          <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
+          <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
         </is>
       </c>
       <c r="E10" s="98" t="inlineStr">
         <is>
-          <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
-گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
-گام ۳: در پنل ببین جریان شارژ صفر شده.
-گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
-        </is>
-      </c>
-      <c r="F10" s="98" t="inlineStr">
-        <is>
-          <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
+          <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
+گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
+        </is>
+      </c>
+      <c r="F10" s="101" t="inlineStr">
+        <is>
+          <t>کار هم‌زمان با پنل روی ورودی خوب</t>
         </is>
       </c>
       <c r="G10" s="101" t="inlineStr">
         <is>
-          <t>دو دقیقه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H10" s="98" t="inlineStr">
         <is>
-          <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
+          <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
         </is>
       </c>
       <c r="I10" s="98" t="inlineStr">
         <is>
-          <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
+          <t>سبز ثابت</t>
         </is>
       </c>
       <c r="J10" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: با کشیدن سیم باتری حین شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش)، سبز ثابت می‌ماند، زرد خاموش است و سه بوق دوره‌ای می‌آید و شارژ صفر می‌شود؛ با وصل دوبارهٔ باتری همه‌چیز پاک می‌شود و شارژ برمی‌گردد. اگر چراغی اشتباه بود یا خطا پاک نشد، قبول نیست.</t>
+          <t>باید ببینید: سبز ثابت است، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند. اگر هنگ، مکث یا ریست دیدید، قبول نیست.</t>
         </is>
       </c>
       <c r="K10" s="98" t="n"/>
@@ -2310,58 +2311,58 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="92" t="inlineStr">
         <is>
-          <t>UI-033</t>
+          <t>UI-021</t>
         </is>
       </c>
       <c r="B11" s="98" t="inlineStr">
         <is>
-          <t>خطای ۷: خرابی یک کانال شارژ</t>
-        </is>
-      </c>
-      <c r="C11" s="101" t="inlineStr">
-        <is>
-          <t>بالا</t>
+          <t>InputOverVoltage</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D11" s="98" t="inlineStr">
         <is>
-          <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
+          <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
         </is>
       </c>
       <c r="E11" s="98" t="inlineStr">
         <is>
-          <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
-گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
-گام ۳: فیوز را سر جایش بگذار؛ خطا نباید پاک شود.
-گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
-        </is>
-      </c>
-      <c r="F11" s="98" t="inlineStr">
-        <is>
-          <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
+          <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
+گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
+گام ۳: ولتاژ را تا حدود ۲۷٫۵ پایین بیاور و نگه دار؛ چهره باید بماند.
+گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
+        </is>
+      </c>
+      <c r="F11" s="101" t="inlineStr">
+        <is>
+          <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
         </is>
       </c>
       <c r="G11" s="101" t="inlineStr">
         <is>
-          <t>پنج دقیقه</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H11" s="98" t="inlineStr">
         <is>
-          <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
+          <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
         </is>
       </c>
       <c r="I11" s="98" t="inlineStr">
         <is>
-          <t>هر سه چراغ با یک ریتم مشترک</t>
+          <t>قرمز چشمک‌زن با سبز ثابت</t>
         </is>
       </c>
       <c r="J11" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است؛ خطا فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود. اگر با جا زدن فیوز یا خودش پاک شد، قبول نیست.</t>
+          <t>باید ببینید: روی ولتاژ بالای ورودی سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید؛ با پایین‌آوردن ولتاژ این چهره پاک می‌شود. اگر نیامد یا زود پاک شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K11" s="98" t="n"/>
@@ -2392,7 +2393,7 @@
       </c>
       <c r="C12" s="101" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D12" s="98" t="inlineStr">
@@ -7055,7 +7056,7 @@
     <hyperlink ref="F13" location="'برنامه تست'!A21"/>
     <hyperlink ref="F14" location="'برنامه تست'!A28"/>
     <hyperlink ref="F15" location="'برنامه تست'!A18"/>
-    <hyperlink ref="F16" location="'برنامه تست'!A9"/>
+    <hyperlink ref="F16" location="'برنامه تست'!A11"/>
     <hyperlink ref="F17" location="'برنامه تست'!A31"/>
     <hyperlink ref="F18" location="'برنامه تست'!A6"/>
     <hyperlink ref="F19" location="'برنامه تست'!A17"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1372,7 +1372,10 @@
     <row r="2">
       <c r="A2" s="81" t="inlineStr">
         <is>
-          <t>PA3/ADC1_IN3/raw2/v_bat24 → BatteryRun/Charging | PA2/ADC1_IN2/raw1/v_in → ورودی | PB4 EXTI | PB5 Q1 | PB11 Q17</t>
+          <t>پایهٔ PA3 (ADC1_IN3) عدد خام دوم (raw2) را می‌دهد و از آن ولتاژ باتری (v_bat24_mv) حساب می‌شود.
+پایهٔ PA2 (ADC1_IN2) عدد خام اول (raw1) را می‌دهد و از آن ولتاژ ورودی حساب می‌شود.
+از باتری، درصد کار روی باتری (BatteryRun) و درصد شارژ (Charging) حساب می‌شود.
+پایهٔ PB4 وقفهٔ ورودی است. PB5 کلید Q1 است. PB11 کلید Q17 است.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1404,11 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>ولیدیشن UI با snapshot واقعی: BatteryRun هیسترزیس 2%+0/1، Charging هیسترزیس 5%، فول InputOk 100/95، حفظ فاز سبز/زرد، non-blocking.</t>
+          <t>این فایل UI را با دادهٔ واقعی چک می‌کند:
+برای درصد روی باتری، هیسترزیس ۲ درصد داریم و برای درصد 0 و 1 قانون جدا داریم.
+برای درصد شارژ، هیسترزیس ۵ درصد داریم.
+شارژ کامل (InputOk) وقتی است که درصد به 100 برسد و تا زیر 95 نیاید، همان می‌ماند.
+فاز چشمک سبز و زرد حفظ می‌شود. هیچ کاری برنامه را متوقف نمی‌کند (non-blocking).</t>
         </is>
       </c>
       <c r="B4" s="28" t="n"/>
@@ -1445,7 +1452,10 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="85" t="inlineStr">
         <is>
-          <t>PA3 پایه13 ADC1_IN3 → BSP_ADC_CHANNEL_24V_BAT 2 → raw2 → v_bat24_mv → UI (PA3 فقط v_bat). PA2 پایه12 ADC1_IN2 → 1 → raw1 → v_in_mv → ورودی. PB4 EXTI، PB5 Q1 McuPowerPath، PB11 Q17 Changeover بدون تغییر.</t>
+          <t>مسیر داده این است:
+پایهٔ PA3 (پایهٔ 13) از کانال ADC1_IN3 خوانده می‌شود (شاخص 2، BSP_ADC_CHANNEL_24V_BAT) و می‌شود عدد خام دوم (raw2) و بعد ولتاژ باتری (v_bat24_mv). UI فقط از همین پایه (PA3) استفاده می‌کند.
+پایهٔ PA2 (پایهٔ 12) از کانال ADC1_IN2 خوانده می‌شود (شاخص 1) و می‌شود عدد خام اول (raw1) و بعد ولتاژ ورودی (v_in_mv).
+پایهٔ PB4 وقفهٔ ورودی است. PB5 کلید Q1 مال McuPowerPath است. PB11 کلید Q17 مال Changeover است و اینجا دست نمی‌خورد.</t>
         </is>
       </c>
       <c r="B6" s="28" t="n"/>
@@ -1489,7 +1499,12 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="85" t="inlineStr">
         <is>
-          <t>stable57 raw56→57 حفظ، 58→57 حفظ، 55→55 تغییر، 59→59 تغییر. stable0 تا raw&gt;=2 روی 0 سپس →1، stable1: raw0→0 &gt;=3→2 else 1. ثابت‌ها: RUN_HYSTERESIS 2, ZERO_EXIT 2, ONE_EXIT 3.</t>
+          <t>درصد پایدار روی باتری این‌طور می‌ماند:
+اگر درصد پایدار 57 باشد و عدد خام 56 یا 58 بیاید، همان 57 می‌ماند. یعنی 57 تکان نمی‌خورد.
+عدد 55 بیاید، درصد می‌شود 55. عدد 59 بیاید، می‌شود 59.
+اگر درصد پایدار 0 باشد: تا وقتی عدد خام زیر 2 است، همان 0 می‌ماند. به 2 که رسید، می‌شود 1.
+اگر درصد پایدار 1 باشد: عدد خام 0 بیاید، می‌شود 0. عدد 3 یا بیشتر بیاید، می‌شود 2. وگرنه همان 1 می‌ماند.
+ثابت‌ها: هیسترزیس کار (RUN_HYSTERESIS) برابر 2، خروج از صفر (ZERO_EXIT) برابر 2 و خروج از یک (ONE_EXIT) برابر 3 است.</t>
         </is>
       </c>
       <c r="B8" s="28" t="n"/>
@@ -1533,7 +1548,12 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="85" t="inlineStr">
         <is>
-          <t>chargingStable57 raw53..61 حفظ (diff&lt;5)، خارج 52/62→change. زمان زرد remaining=100-stable5% . مثال 25V jitter بی‌اثر. ثابت: CHARGING_HYSTERESIS 5.</t>
+          <t>درصد پایدار شارژ این‌طور می‌ماند:
+اگر درصد پایدار 57 باشد و عدد خام بین 53 تا 61 بیاید، همان 57 می‌ماند (اختلاف کمتر از ۵ است).
+اگر عدد خام 52 یا 62 بیاید، درصد عوض می‌شود.
+زمان روشن‌ماندن زرد از درصد باقی‌مانده حساب می‌شود: 100 منهای درصد پایدار، با پله‌های ۵ درصدی.
+لرزش کوچک ولتاژ (مثل 25 ولت) درصد را تکان نمی‌دهد.
+ثابت: هیسترزیس شارژ (CHARGING_HYSTERESIS) برابر 5 است.</t>
         </is>
       </c>
       <c r="B10" s="28" t="n"/>
@@ -1577,7 +1597,10 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="85" t="inlineStr">
         <is>
-          <t>ورود InputOk فقط وقتی خام به 100 برسد؛ ماندن تا خام&lt;95 سپس Charging. جلوگیری پرش 28V. ثابت‌ها: FULL_ENTER 100, FULL_EXIT 95.</t>
+          <t>شارژ کامل (InputOk) فقط وقتی شروع می‌شود که درصد خام به 100 برسد.
+بعد تا وقتی درصد خام زیر 95 نیامده، همان می‌ماند. زیر 95 که آمد، برمی‌گردد به حالت شارژ (Charging).
+این کار جلوی پرش درصد در ولتاژ 28 ولت را می‌گیرد.
+ثابت‌ها: ورود به کامل (FULL_ENTER) برابر 100 و خروج (FULL_EXIT) برابر 95 است.</t>
         </is>
       </c>
       <c r="B12" s="28" t="n"/>
@@ -1621,7 +1644,9 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="85" t="inlineStr">
         <is>
-          <t>تغییر stable فاز reset نکند؛ زمان جدید از مرز بعدی. فقط ورود/خروج سناریو یا invalid/NULL ریست کامل. سبز BatteryRun و زرد Charging هرکدام phase/OnMs/OffMs/startTick مستقل.</t>
+          <t>وقتی درصد پایدار عوض می‌شود، فاز چشمک از اول شروع نمی‌شود. زمان تازه از مرز بعدی حساب می‌شود.
+فقط وقتی سناریو عوض می‌شود یا داده نامعتبر می‌شود، فاز کامل از نو شروع می‌شود.
+سبزِ روی باتری و زردِ شارژ، هر کدام زمان روشن و خاموش و شروع خودشان را دارند.</t>
         </is>
       </c>
       <c r="B14" s="28" t="n"/>
@@ -1665,7 +1690,10 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="85" t="inlineStr">
         <is>
-          <t>InputOk و Charging قبلاً delay 500ms/1s داشتند → اکنون فاز-محور بدون delay داخل سناریو؛ Ui_Tick &lt;1ms، 10ms loop، starvation ندارد. BoardTest یک‌بار init.</t>
+          <t>قبلاً سناریوهای شارژ کامل و شارژ، تأخیر ثابت 500 میلی‌ثانیه و 1 ثانیه داشتند.
+حالا فاز-محورند و داخل سناریو هیچ تأخیری نیست.
+هر اجرای Ui_Tick کمتر از 1 میلی‌ثانیه طول می‌کشد، حلقه هر 10 میلی‌ثانیه است و هیچ تسکی گرسنه نمی‌ماند.
+تست برد یک بار مقداردهی می‌شود.</t>
         </is>
       </c>
       <c r="B16" s="28" t="n"/>
@@ -1709,7 +1737,11 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
         <is>
-          <t>static cb/stack، DYNAMIC 0، word/byte (128/192/256 →512/768/1024B)، high-water، بدون queue/timer/mutex جدید برای hysteresis، Measurement_GetSnapshot کپی ایمن.</t>
+          <t>حافظه فقط استاتیک است (DYNAMIC=0).
+استک تسک‌ها: 128 و 192 و 256 کلمه؛ یعنی 512 و 768 و 1024 بایت.
+پرترین جای استک (high-water) خوانده می‌شود.
+برای هیسترزیس هیچ صف، تایمر یا موتکس تازه‌ای ساخته نشده است.
+خواندن عکس لحظه‌ای از Measurement کپی امن است.</t>
         </is>
       </c>
       <c r="B18" s="28" t="n"/>
@@ -1728,12 +1760,15 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1921,7 @@
       </c>
       <c r="O4" s="82" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="82" t="inlineStr">
@@ -1942,7 +1977,11 @@
       </c>
       <c r="H5" s="98" t="inlineStr">
         <is>
-          <t>روی باتری: سبز چشمک‌زن؛ با ورودی: سبز ثابت؛ شارژ کامل: سبز ثابت و زرد خاموش؛ قطع ورودی: سبز دوباره چشمک‌زن؛ خطای قطع باتری: سبز ثابت می‌ماند</t>
+          <t>روی باتری: سبز چشمک‌زن.
+با ورودی: سبز ثابت.
+شارژ کامل: سبز ثابت و زرد خاموش.
+قطع ورودی: سبز دوباره چشمک‌زن.
+خطای قطع باتری: سبز ثابت می‌ماند.</t>
         </is>
       </c>
       <c r="I5" s="98" t="inlineStr">
@@ -1952,7 +1991,11 @@
       </c>
       <c r="J5" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: روی باتری سبز چشمک می‌زند؛ به‌محض وصل ورودی سبز ثابت می‌شود و تا کامل‌شدن شارژ ثابت می‌ماند؛ با قطع ورودی دوباره چشمک می‌زند. اگر جایی سبز خاموش بود یا برعکس رفتار کرد، قبول نیست.</t>
+          <t>باید ببینید:
+روی باتری، سبز چشمک می‌زند.
+به‌محض وصل ورودی، سبز ثابت می‌شود و تا کامل‌شدن شارژ ثابت می‌ماند.
+با قطع ورودی، سبز دوباره چشمک می‌زند.
+اگر جایی سبز خاموش بود یا برعکس رفتار کرد، قبول نیست.</t>
         </is>
       </c>
       <c r="K5" s="98" t="n"/>
@@ -2130,7 +2173,9 @@
       <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
-گام ۲: چند ثانیه به چراغ‌ها نگاه کن: قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش)، سبز ثابت روشن بماند، زرد خاموش شود و هر چند ثانیه سه بوق کوتاه بیاید.
+گام ۲: چند ثانیه به چراغ‌ها نگاه کن.
+قرمز باید تندتند چشمک بزند (تقریباً نیم ثانیه روشن، نیم ثانیه خاموش).
+سبز ثابت روشن بماند. زرد خاموش شود. هر چند ثانیه سه بوق کوتاه بیاید.
 گام ۳: در پنل ببین جریان شارژ صفر شده.
 گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
         </is>
@@ -2147,7 +2192,8 @@
       </c>
       <c r="H8" s="98" t="inlineStr">
         <is>
-          <t>حین خطا: قرمز چشمک‌تند + سبز ثابت + زرد خاموش + سه بوق دوره‌ای و شارژ متوقف؛ با وصل باتری همه‌چیز پاک و شارژ برمی‌گردد</t>
+          <t>هنگام خطا: قرمز چشمک‌تند، سبز ثابت، زرد خاموش، سه بوق دوره‌ای و شارژ متوقف است.
+با وصل‌کردن باتری، همه‌چیز پاک می‌شود و شارژ برمی‌گردد.</t>
         </is>
       </c>
       <c r="I8" s="98" t="inlineStr">
@@ -2157,7 +2203,12 @@
       </c>
       <c r="J8" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: با کشیدن سیم باتری حین شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش)، سبز ثابت می‌ماند، زرد خاموش است و سه بوق دوره‌ای می‌آید و شارژ صفر می‌شود؛ با وصل دوبارهٔ باتری همه‌چیز پاک می‌شود و شارژ برمی‌گردد. اگر چراغی اشتباه بود یا خطا پاک نشد، قبول نیست.</t>
+          <t>باید ببینید:
+با کشیدن سیم باتری هنگام شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش).
+سبز ثابت می‌ماند و زرد خاموش است.
+سه بوق دوره‌ای می‌آید و شارژ صفر می‌شود.
+با وصل دوبارهٔ باتری، همه‌چیز پاک می‌شود و شارژ برمی‌گردد.
+اگر چراغی اشتباه بود یا خطا پاک نشد، قبول نیست.</t>
         </is>
       </c>
       <c r="K8" s="98" t="n"/>
@@ -2226,7 +2277,10 @@
       </c>
       <c r="J9" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است؛ خطا فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود. اگر با جا زدن فیوز یا خودش پاک شد، قبول نیست.</t>
+          <t>باید ببینید:
+هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است.
+خطا فقط با خاموش و روشن‌کردن دستگاه پاک می‌شود.
+اگر با جا زدن فیوز یا خودش پاک شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K9" s="98" t="n"/>
@@ -2362,7 +2416,10 @@
       </c>
       <c r="J11" s="98" t="inlineStr">
         <is>
-          <t>باید ببینید: روی ولتاژ بالای ورودی سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید؛ با پایین‌آوردن ولتاژ این چهره پاک می‌شود. اگر نیامد یا زود پاک شد، قبول نیست.</t>
+          <t>باید ببینید:
+روی ولتاژ بالای ورودی، سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید.
+با پایین‌آوردن ولتاژ، این چهره پاک می‌شود.
+اگر نیامد یا زود پاک شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K11" s="98" t="n"/>
@@ -2940,7 +2997,8 @@
       </c>
       <c r="D20" s="98" t="inlineStr">
         <is>
-          <t>دو باتری ۱۲ ولت داری که یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای؛ برای زود دیدن، از پنل حدّ رویداد مجاز را موقتاً کم کن</t>
+          <t>دو باتری ۱۲ ولت داری. یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای.
+برای زودتر دیدن نتیجه، از پنل حد رویداد مجاز را موقتاً کم کن.</t>
         </is>
       </c>
       <c r="E20" s="98" t="inlineStr">
@@ -4741,7 +4799,7 @@
       </c>
       <c r="O4" s="82" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="82" t="inlineStr">
@@ -4986,9 +5044,9 @@
       <c r="E8" s="98" t="inlineStr">
         <is>
           <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
-گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی و raw2 باید ولتاژ باتری باشد و هر دو حدود 11176 میلی‌ولت خوانده شوند.
+گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی باشد و raw2 باید ولتاژ باتری. هر دو باید حدود 11176 میلی‌ولت خوانده شوند.
 گام ۳: چک کن v_bat از PA3 و raw2 می‌آید و v_in از PA2 و raw1.
-گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند؛ جابه‌جا بودن این دو یعنی رد تست.</t>
+گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند. جابه‌جا بودن این دو یعنی رد تست.</t>
         </is>
       </c>
       <c r="F8" s="101" t="inlineStr">
@@ -5719,7 +5777,7 @@
       </c>
       <c r="O4" s="82" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="82" t="inlineStr">
@@ -5757,8 +5815,8 @@
       <c r="E5" s="93" t="inlineStr">
         <is>
           <t>گام ۱: در کل Firmware چک کن تخصیص حافظه فقط استاتیک باشد (SUPPORT_DYNAMIC=0).
-گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین و اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (128 و 192 و 256 کلمه).
-گام ۳: مقدار high-water هر استک را بخوان: باید بیشتر از 20 درصد از استک آزاد مانده باشد.
+گام ۲: برای هر تسک، کنترل‌بلوک و استک ثابت را ببین. اندازهٔ استک‌ها را چک کن: UI برابر 512 بایت، Measurement برابر 768 بایت و Control برابر 1024 بایت (همان 128 و 192 و 256 کلمه).
+گام ۳: مقدار high-water هر استک را بخوان. باید بیشتر از 20 درصد از استک آزاد مانده باشد.
 گام ۴: هر تخصیص پویا یا سرریز استک یعنی رد تست.</t>
         </is>
       </c>
@@ -5893,9 +5951,10 @@
       </c>
       <c r="E7" s="98" t="inlineStr">
         <is>
-          <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن (valid=false و هر 9 فیلد صفر).
+          <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن: valid=false و هر 9 فیلد صفر.
 گام ۲: 2 ثانیه نگاه کن.
-گام ۳: UI باید safe-off بماند: همهٔ چراغ‌ها خاموش و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود؛ روشن شدن LED یعنی رد تست.</t>
+گام ۳: UI باید خاموش و امن (safe-off) بماند: همهٔ چراغ‌ها خاموش باشند و هیچ درصد کاذبی از روی v_bat24 زباله حساب نشود.
+گام ۴: روشن‌شدن LED یعنی رد تست.</t>
         </is>
       </c>
       <c r="F7" s="101" t="inlineStr">
@@ -7154,7 +7213,7 @@
       </c>
       <c r="J3" s="82" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="82" t="inlineStr">
@@ -7427,12 +7486,12 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="117" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B6" s="112" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C6" s="80" t="n"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -383,7 +383,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -473,6 +473,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -619,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -973,6 +983,67 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="64" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1363,7 +1434,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="131" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول UI — BatteryRun 2%+0/1, Charging 5%, InputOk 100/95</t>
         </is>
@@ -1380,7 +1451,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="82" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -1428,7 +1499,7 @@
       <c r="P4" s="29" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>منبع و mapping</t>
         </is>
@@ -1475,7 +1546,7 @@
       <c r="P6" s="29" t="n"/>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>BatteryRun 2%+0/1</t>
         </is>
@@ -1524,7 +1595,7 @@
       <c r="P8" s="29" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
@@ -1573,7 +1644,7 @@
       <c r="P10" s="29" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="88" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>فول InputOk/Charging 100/95</t>
         </is>
@@ -1620,7 +1691,7 @@
       <c r="P12" s="29" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>حفظ فاز</t>
         </is>
@@ -1666,7 +1737,7 @@
       <c r="P14" s="29" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>غیرمسدودکننده</t>
         </is>
@@ -1713,7 +1784,7 @@
       <c r="P16" s="29" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>RTOS و حافظه</t>
         </is>
@@ -1760,6 +1831,7 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
@@ -1828,7 +1900,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="89" t="inlineStr">
+      <c r="A1" s="131" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
         </is>
@@ -1849,87 +1921,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="132" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="82" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr">
+      <c r="D4" s="132" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="82" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="82" t="inlineStr">
+      <c r="F4" s="132" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="82" t="inlineStr">
+      <c r="G4" s="132" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="82" t="inlineStr">
+      <c r="H4" s="132" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="82" t="inlineStr">
+      <c r="I4" s="132" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="82" t="inlineStr">
+      <c r="J4" s="132" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="82" t="inlineStr">
+      <c r="K4" s="132" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="82" t="inlineStr">
+      <c r="L4" s="132" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="82" t="inlineStr">
+      <c r="M4" s="132" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="82" t="inlineStr">
+      <c r="N4" s="132" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="82" t="inlineStr">
+      <c r="O4" s="132" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="82" t="inlineStr">
+      <c r="P4" s="132" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="82" t="inlineStr">
+      <c r="Q4" s="132" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1941,7 +2013,7 @@
           <t>UI-036</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>رفتار کلی چراغ سبز</t>
         </is>
@@ -1951,12 +2023,12 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="98" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>دستگاه سالم؛ باتری وصل؛ منبع آزمایشگاهی برای ورودی؛ باتری نیمه‌پُر</t>
         </is>
       </c>
-      <c r="E5" s="98" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را قطع کن و فقط با باتری کار کن؛ چراغ سبز را نگاه کن.
 گام ۲: ورودی ۲۴ ولت را وصل کن؛ سبز را نگاه کن.
@@ -1965,17 +2037,17 @@
 گام ۵: ورودی را وصل کن، حین شارژ سیم باتری را بکش و بعد وصل کن؛ سبز را نگاه کن.</t>
         </is>
       </c>
-      <c r="F5" s="101" t="inlineStr">
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>ورودی قطع و ۲۴ ولت؛ قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>چند دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="98" t="inlineStr">
+      <c r="H5" s="93" t="inlineStr">
         <is>
           <t>روی باتری: سبز چشمک‌زن.
 با ورودی: سبز ثابت.
@@ -1984,12 +2056,12 @@
 خطای قطع باتری: سبز ثابت می‌ماند.</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="93" t="inlineStr">
         <is>
           <t>چشمک روی باتری، ثابت با ورودی</t>
         </is>
       </c>
-      <c r="J5" s="98" t="inlineStr">
+      <c r="J5" s="93" t="inlineStr">
         <is>
           <t>باید ببینید:
 روی باتری، سبز چشمک می‌زند.
@@ -2008,7 +2080,7 @@
       <c r="N5" s="98" t="n"/>
       <c r="O5" s="101" t="n"/>
       <c r="P5" s="101" t="n"/>
-      <c r="Q5" s="102">
+      <c r="Q5" s="97">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -2019,7 +2091,7 @@
           <t>UI-005</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="134" t="inlineStr">
         <is>
           <t>باتری خالیِ کامل (درصد صفر)</t>
         </is>
@@ -2029,39 +2101,39 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="D6" s="134" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E6" s="98" t="inlineStr">
+      <c r="E6" s="134" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا باتری تقریباً خالی شود و درصد به صفر برسد.
 گام ۲: از لحظهٔ صفر شدن، به بوق و چراغ‌ها دقت کن.
 گام ۳: همان ولتاژ را نگه دار و یک دقیقه صبر کن.</t>
         </is>
       </c>
-      <c r="F6" s="101" t="inlineStr">
+      <c r="F6" s="135" t="inlineStr">
         <is>
           <t>باتری نزدیک خالی کامل (درصد صفر)</t>
         </is>
       </c>
-      <c r="G6" s="101" t="inlineStr">
+      <c r="G6" s="135" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="134" t="inlineStr">
         <is>
           <t>یک بوق بلند حدود ده ثانیه می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود تا وقتی باتری از خالیِ کامل بیرون بیاید</t>
         </is>
       </c>
-      <c r="I6" s="98" t="inlineStr">
+      <c r="I6" s="134" t="inlineStr">
         <is>
           <t>بعد از بوق: همه خاموش</t>
         </is>
       </c>
-      <c r="J6" s="98" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>باید بشنوید و ببینید: فقط یک بوق بلند حدود ده‌ثانیه‌ای می‌آید و بعد همهٔ چراغ‌ها خاموش و سکوت می‌شود. اگر بوق تکرار شد یا چراغی روشن ماند، قبول نیست.</t>
         </is>
@@ -2076,7 +2148,7 @@
       <c r="N6" s="98" t="n"/>
       <c r="O6" s="101" t="n"/>
       <c r="P6" s="101" t="n"/>
-      <c r="Q6" s="102">
+      <c r="Q6" s="136">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -2087,7 +2159,7 @@
           <t>UI-015</t>
         </is>
       </c>
-      <c r="B7" s="98" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>Full 100/95 enter</t>
         </is>
@@ -2097,39 +2169,39 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="98" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
         <is>
           <t>باتری در حال شارژ و نزدیک پر شدن است</t>
         </is>
       </c>
-      <c r="E7" s="98" t="inlineStr">
+      <c r="E7" s="93" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را ادامه بده و درصد را زیر نظر بگیر.
 گام ۲: روی ۹۹ درصد چراغ‌ها را چک کن: هنوز باید شارژ باشد (زرد چشمک‌زن).
 گام ۳: بگذار به ۱۰۰ برسد و دوباره نگاه کن.</t>
         </is>
       </c>
-      <c r="F7" s="101" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>رسیدن درصد شارژ از ۹۹ به ۱۰۰</t>
         </is>
       </c>
-      <c r="G7" s="101" t="inlineStr">
+      <c r="G7" s="95" t="inlineStr">
         <is>
           <t>تا پر شدن باتری</t>
         </is>
       </c>
-      <c r="H7" s="98" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>فقط روی ۱۰۰ ورودی خوب می‌شود: سبز ثابت و زرد خاموش؛ روی ۹۹ هنوز زرد چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I7" s="98" t="inlineStr">
+      <c r="I7" s="93" t="inlineStr">
         <is>
           <t>۱۰۰: سبز ثابت</t>
         </is>
       </c>
-      <c r="J7" s="98" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>باید ببینید: دقیقاً وقتی شارژ کامل شد زرد خاموش و سبز ثابت می‌شود؛ کمی قبل از کامل‌شدن هنوز زرد چشمک می‌زند. اگر پیش از کامل‌شدن سبز ثابت شد، قبول نیست.</t>
         </is>
@@ -2144,7 +2216,7 @@
       <c r="N7" s="98" t="n"/>
       <c r="O7" s="101" t="n"/>
       <c r="P7" s="101" t="n"/>
-      <c r="Q7" s="102">
+      <c r="Q7" s="97">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -2155,22 +2227,22 @@
           <t>UI-032</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="134" t="inlineStr">
         <is>
           <t>خطای ۶: قطع باتری حین شارژ</t>
         </is>
       </c>
-      <c r="C8" s="101" t="inlineStr">
+      <c r="C8" s="135" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="98" t="inlineStr">
+      <c r="D8" s="134" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن و باتری واقعی در حال شارژ است (زرد چشمک می‌زند)</t>
         </is>
       </c>
-      <c r="E8" s="98" t="inlineStr">
+      <c r="E8" s="134" t="inlineStr">
         <is>
           <t>گام ۱: وقتی شارژ در جریان است، سیم باتری را از ترمینال جدا کن.
 گام ۲: چند ثانیه به چراغ‌ها نگاه کن.
@@ -2180,28 +2252,28 @@
 گام ۴: سیم باتری را دوباره وصل کن: بعد از چند ثانیه چشمک و بوق قطع و شارژ دوباره شروع می‌شود.</t>
         </is>
       </c>
-      <c r="F8" s="98" t="inlineStr">
+      <c r="F8" s="134" t="inlineStr">
         <is>
           <t>کشیدن و وصل‌کردن سیم باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G8" s="101" t="inlineStr">
+      <c r="G8" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="98" t="inlineStr">
+      <c r="H8" s="134" t="inlineStr">
         <is>
           <t>هنگام خطا: قرمز چشمک‌تند، سبز ثابت، زرد خاموش، سه بوق دوره‌ای و شارژ متوقف است.
 با وصل‌کردن باتری، همه‌چیز پاک می‌شود و شارژ برمی‌گردد.</t>
         </is>
       </c>
-      <c r="I8" s="98" t="inlineStr">
+      <c r="I8" s="134" t="inlineStr">
         <is>
           <t>قرمز حدود نیم‌ثانیه‌ای روشن/خاموش</t>
         </is>
       </c>
-      <c r="J8" s="98" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>باید ببینید:
 با کشیدن سیم باتری هنگام شارژ، قرمز تند چشمک می‌زند (حدود نیم‌ثانیه روشن، نیم‌ثانیه خاموش).
@@ -2221,7 +2293,7 @@
       <c r="N8" s="98" t="n"/>
       <c r="O8" s="101" t="n"/>
       <c r="P8" s="101" t="n"/>
-      <c r="Q8" s="102">
+      <c r="Q8" s="136">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -2232,22 +2304,22 @@
           <t>UI-033</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>خطای ۷: خرابی یک کانال شارژ</t>
         </is>
       </c>
-      <c r="C9" s="101" t="inlineStr">
+      <c r="C9" s="95" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="98" t="inlineStr">
+      <c r="D9" s="93" t="inlineStr">
         <is>
           <t>دستگاه در حال شارژ باتری است؛ فیوز یا سیم خروجی یک کانال شارژ را می‌شناسی</t>
         </is>
       </c>
-      <c r="E9" s="98" t="inlineStr">
+      <c r="E9" s="93" t="inlineStr">
         <is>
           <t>گام ۱: فیوز خروجی یک کانال شارژ را دربیاور تا آن کانال فرمان بگیرد ولی جریان نکشد.
 گام ۲: چند ثانیه صبر کن: هر سه چراغ باید با هم و هم‌زمان چشمک بزنند و شارژ کلاً متوقف شود.
@@ -2255,27 +2327,27 @@
 گام ۴: دستگاه را خاموش و روشن کن؛ فقط آن‌وقت خطا پاک و شارژ عادی می‌شود.</t>
         </is>
       </c>
-      <c r="F9" s="98" t="inlineStr">
+      <c r="F9" s="93" t="inlineStr">
         <is>
           <t>دربیاوردن فیوز یک کانال و خاموش/روشن</t>
         </is>
       </c>
-      <c r="G9" s="101" t="inlineStr">
+      <c r="G9" s="95" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="98" t="inlineStr">
+      <c r="H9" s="93" t="inlineStr">
         <is>
           <t>خطای ۷ قفل می‌شود: هر سه چراغ هم‌زمان چشمک‌زن و شارژ متوقف؛ فقط با خاموش/روشن پاک می‌شود</t>
         </is>
       </c>
-      <c r="I9" s="98" t="inlineStr">
+      <c r="I9" s="93" t="inlineStr">
         <is>
           <t>هر سه چراغ با یک ریتم مشترک</t>
         </is>
       </c>
-      <c r="J9" s="98" t="inlineStr">
+      <c r="J9" s="93" t="inlineStr">
         <is>
           <t>باید ببینید:
 هر سه چراغ با هم و با یک ریتم چشمک می‌زنند و شارژ متوقف است.
@@ -2293,7 +2365,7 @@
       <c r="N9" s="98" t="n"/>
       <c r="O9" s="101" t="n"/>
       <c r="P9" s="101" t="n"/>
-      <c r="Q9" s="102">
+      <c r="Q9" s="97">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -2304,7 +2376,7 @@
           <t>UI-019</t>
         </is>
       </c>
-      <c r="B10" s="98" t="inlineStr">
+      <c r="B10" s="134" t="inlineStr">
         <is>
           <t>InputOk non-blocking</t>
         </is>
@@ -2314,38 +2386,38 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="98" t="inlineStr">
+      <c r="D10" s="134" t="inlineStr">
         <is>
           <t>برق شهر وصل و دستگاه در وضعیت ورودی خوب است (سبز ثابت)</t>
         </is>
       </c>
-      <c r="E10" s="98" t="inlineStr">
+      <c r="E10" s="134" t="inlineStr">
         <is>
           <t>گام ۱: هم‌زمان که سبز ثابت است، با پنل کار کن و چند پارامتر را بخوان و عوض کن.
 گام ۲: به چراغ‌ها و واکنش پنل دقت کن؛ هیچ مکث و هنگی نباید باشد.</t>
         </is>
       </c>
-      <c r="F10" s="101" t="inlineStr">
+      <c r="F10" s="135" t="inlineStr">
         <is>
           <t>کار هم‌زمان با پنل روی ورودی خوب</t>
         </is>
       </c>
-      <c r="G10" s="101" t="inlineStr">
+      <c r="G10" s="135" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="98" t="inlineStr">
+      <c r="H10" s="134" t="inlineStr">
         <is>
           <t>سبز ثابت می‌ماند، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند</t>
         </is>
       </c>
-      <c r="I10" s="98" t="inlineStr">
+      <c r="I10" s="134" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="J10" s="98" t="inlineStr">
+      <c r="J10" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: سبز ثابت است، بوقی نیست و دستگاه و پنل روان و بدون مکث کار می‌کنند. اگر هنگ، مکث یا ریست دیدید، قبول نیست.</t>
         </is>
@@ -2360,7 +2432,7 @@
       <c r="N10" s="98" t="n"/>
       <c r="O10" s="101" t="n"/>
       <c r="P10" s="101" t="n"/>
-      <c r="Q10" s="102">
+      <c r="Q10" s="136">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -2371,7 +2443,7 @@
           <t>UI-021</t>
         </is>
       </c>
-      <c r="B11" s="98" t="inlineStr">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>InputOverVoltage</t>
         </is>
@@ -2381,12 +2453,12 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="98" t="inlineStr">
+      <c r="D11" s="93" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید تا بتوانی ولتاژش را بالا ببری؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E11" s="98" t="inlineStr">
+      <c r="E11" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را آرام بالا ببر تا از حدود ۲۸ ولت رد شود.
 گام ۲: چراغ‌ها را ببین: باید سبز ثابت بماند، قرمز چشمک بزند و هر چند ثانیه چند بوق بیاید.
@@ -2394,27 +2466,27 @@
 گام ۴: تا حدود ۲۶ پایین بیاور؛ چهره باید پاک و رفتار عادی برگردد.</t>
         </is>
       </c>
-      <c r="F11" s="101" t="inlineStr">
+      <c r="F11" s="95" t="inlineStr">
         <is>
           <t>ورودی حدود ۲۸٫۵ بعد ۲۷٫۵ بعد ۲۶ ولت</t>
         </is>
       </c>
-      <c r="G11" s="101" t="inlineStr">
+      <c r="G11" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="98" t="inlineStr">
+      <c r="H11" s="93" t="inlineStr">
         <is>
           <t>روی ولتاژ بالا: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و بوق گهگاه؛ روی ۲۷٫۵ می‌ماند و روی ۲۶ پاک می‌شود</t>
         </is>
       </c>
-      <c r="I11" s="98" t="inlineStr">
+      <c r="I11" s="93" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن با سبز ثابت</t>
         </is>
       </c>
-      <c r="J11" s="98" t="inlineStr">
+      <c r="J11" s="93" t="inlineStr">
         <is>
           <t>باید ببینید:
 روی ولتاژ بالای ورودی، سبز ثابت، زرد خاموش و قرمز چشمک‌زن است و گهگاه بوق می‌آید.
@@ -2432,7 +2504,7 @@
       <c r="N11" s="98" t="n"/>
       <c r="O11" s="101" t="n"/>
       <c r="P11" s="101" t="n"/>
-      <c r="Q11" s="102">
+      <c r="Q11" s="97">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
@@ -2443,22 +2515,22 @@
           <t>UI-034</t>
         </is>
       </c>
-      <c r="B12" s="98" t="inlineStr">
+      <c r="B12" s="134" t="inlineStr">
         <is>
           <t>باتری خراب (سناریوی ۶): قرمز ثابت</t>
         </is>
       </c>
-      <c r="C12" s="101" t="inlineStr">
+      <c r="C12" s="135" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="98" t="inlineStr">
+      <c r="D12" s="134" t="inlineStr">
         <is>
           <t>از پنل، زمان سناریوی باتری خراب را موقتاً روی چند دقیقه بگذار (مقدار واقعی یک شبانه‌روز است)؛ یک باتری خالی داری</t>
         </is>
       </c>
-      <c r="E12" s="98" t="inlineStr">
+      <c r="E12" s="134" t="inlineStr">
         <is>
           <t>گام ۱: باتری خالی را به شارژ بزن و نگذار در این مدت پر و شناور شود.
 گام ۲: بعد از گذشت زمان تنظیم‌شده چراغ‌ها را ببین: قرمز باید ثابت روشن باشد، نه چشمک‌زن.
@@ -2467,27 +2539,27 @@
 گام ۵: زمان سناریو را از پنل به مقدار واقعی برگردان.</t>
         </is>
       </c>
-      <c r="F12" s="98" t="inlineStr">
+      <c r="F12" s="134" t="inlineStr">
         <is>
           <t>شارژ باتری خالی با زمان کوتاه‌شده از پنل</t>
         </is>
       </c>
-      <c r="G12" s="101" t="inlineStr">
+      <c r="G12" s="135" t="inlineStr">
         <is>
           <t>چند دقیقه + زمان تنظیم‌شده</t>
         </is>
       </c>
-      <c r="H12" s="98" t="inlineStr">
+      <c r="H12" s="134" t="inlineStr">
         <is>
           <t>قرمز ثابت می‌ماند، شارژ آن باتری برای همیشه می‌ایستد و فقط با تعویض باتری پاک می‌شود</t>
         </is>
       </c>
-      <c r="I12" s="98" t="inlineStr">
+      <c r="I12" s="134" t="inlineStr">
         <is>
           <t>قرمز ثابت، بدون چشمک</t>
         </is>
       </c>
-      <c r="J12" s="98" t="inlineStr">
+      <c r="J12" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: قرمز ثابت و بدون چشمک می‌ماند و آن باتری دیگر شارژ نمی‌شود؛ فقط با تعویض باتری پاک می‌شود. اگر قرمز چشمک زد یا همان باتری دوباره شارژ شد، قبول نیست.</t>
         </is>
@@ -2502,7 +2574,7 @@
       <c r="N12" s="98" t="n"/>
       <c r="O12" s="101" t="n"/>
       <c r="P12" s="101" t="n"/>
-      <c r="Q12" s="102">
+      <c r="Q12" s="136">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -2513,7 +2585,7 @@
           <t>UI-007</t>
         </is>
       </c>
-      <c r="B13" s="98" t="inlineStr">
+      <c r="B13" s="93" t="inlineStr">
         <is>
           <t>درصد ۱ (نزدیک خالی)</t>
         </is>
@@ -2523,38 +2595,38 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="98" t="inlineStr">
+      <c r="D13" s="93" t="inlineStr">
         <is>
           <t>دستگاه فقط روی باتری؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E13" s="98" t="inlineStr">
+      <c r="E13" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را طوری تنظیم کن که درصد روی ۱ بایستد (باتری تقریباً خالی ولی نه صفر).
 گام ۲: دو دقیقه چراغ سبز و بوق را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F13" s="101" t="inlineStr">
+      <c r="F13" s="95" t="inlineStr">
         <is>
           <t>درصد پایدار ۱</t>
         </is>
       </c>
-      <c r="G13" s="101" t="inlineStr">
+      <c r="G13" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H13" s="98" t="inlineStr">
+      <c r="H13" s="93" t="inlineStr">
         <is>
           <t>هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند</t>
         </is>
       </c>
-      <c r="I13" s="98" t="inlineStr">
+      <c r="I13" s="93" t="inlineStr">
         <is>
           <t>برق‌های کوتاه و کم</t>
         </is>
       </c>
-      <c r="J13" s="98" t="inlineStr">
+      <c r="J13" s="93" t="inlineStr">
         <is>
           <t>باید بشنوید و ببینید: هر از چندی سه بوق می‌آید و سبز تقریباً همیشه خاموش است و فقط گهگاه یک برق خیلی کوتاه می‌زند. اگر مثل باتریِ کاملاً خالی رفتار کرد (بوق بلند و خاموشی کامل)، قبول نیست.</t>
         </is>
@@ -2569,7 +2641,7 @@
       <c r="N13" s="98" t="n"/>
       <c r="O13" s="101" t="n"/>
       <c r="P13" s="101" t="n"/>
-      <c r="Q13" s="102">
+      <c r="Q13" s="97">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
@@ -2580,48 +2652,48 @@
           <t>UI-016</t>
         </is>
       </c>
-      <c r="B14" s="93" t="inlineStr">
+      <c r="B14" s="134" t="inlineStr">
         <is>
           <t>Full 100/95 stay</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="137" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="103" t="inlineStr">
+      <c r="D14" s="138" t="inlineStr">
         <is>
           <t>ادامهٔ UI-015؛ درصد روی ۱۰۰ و سبز ثابت است</t>
         </is>
       </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="E14" s="134" t="inlineStr">
         <is>
           <t>گام ۱: با یک مصرف کوچک درصد را بین ۹۵ و ۱۰۰ نگه دار و چند بار بالا پایینش کن.
 گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F14" s="95" t="inlineStr">
+      <c r="F14" s="135" t="inlineStr">
         <is>
           <t>درصد بین ۹۵ تا ۱۰۰</t>
         </is>
       </c>
-      <c r="G14" s="95" t="inlineStr">
+      <c r="G14" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H14" s="93" t="inlineStr">
+      <c r="H14" s="134" t="inlineStr">
         <is>
           <t>تا وقتی درصد بالای ۹۵ است همان ورودی خوب می‌ماند: سبز ثابت و زرد خاموش</t>
         </is>
       </c>
-      <c r="I14" s="93" t="inlineStr">
+      <c r="I14" s="134" t="inlineStr">
         <is>
           <t>سبز ثابت</t>
         </is>
       </c>
-      <c r="J14" s="93" t="inlineStr">
+      <c r="J14" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: تا وقتی باتری پر است سبز ثابت می‌ماند و زرد خاموش است. اگر بی‌دلیل به چشمک زرد شارژ برگشت، قبول نیست.</t>
         </is>
@@ -2636,7 +2708,7 @@
       <c r="N14" s="93" t="n"/>
       <c r="O14" s="95" t="n"/>
       <c r="P14" s="95" t="n"/>
-      <c r="Q14" s="97">
+      <c r="Q14" s="136">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
@@ -2647,7 +2719,7 @@
           <t>UI-017</t>
         </is>
       </c>
-      <c r="B15" s="98" t="inlineStr">
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>Full 95 exit</t>
         </is>
@@ -2657,38 +2729,38 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D15" s="100" t="inlineStr">
+      <c r="D15" s="103" t="inlineStr">
         <is>
           <t>ادامهٔ UI-016؛ درصد بالای ۹۵ و سبز ثابت است</t>
         </is>
       </c>
-      <c r="E15" s="98" t="inlineStr">
+      <c r="E15" s="93" t="inlineStr">
         <is>
           <t>گام ۱: یک بار واقعی روی باتری بکش تا درصد زیر ۹۵ بیاید.
 گام ۲: چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F15" s="101" t="inlineStr">
+      <c r="F15" s="95" t="inlineStr">
         <is>
           <t>افت درصد شارژ به زیر ۹۵</t>
         </is>
       </c>
-      <c r="G15" s="101" t="inlineStr">
+      <c r="G15" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H15" s="98" t="inlineStr">
+      <c r="H15" s="93" t="inlineStr">
         <is>
           <t>برمی‌گردد به وضعیت شارژ: سبز از ثابت درمی‌آید و زرد دوباره چشمک می‌زند</t>
         </is>
       </c>
-      <c r="I15" s="98" t="inlineStr">
+      <c r="I15" s="93" t="inlineStr">
         <is>
           <t>برگشت به چشمک زرد</t>
         </is>
       </c>
-      <c r="J15" s="98" t="inlineStr">
+      <c r="J15" s="93" t="inlineStr">
         <is>
           <t>باید ببینید: وقتی شارژ باتری پایین آمد، زرد دوباره چشمک می‌زند و سبز از ثابت درمی‌آید. اگر روی سبز ثابت ماند، قبول نیست.</t>
         </is>
@@ -2703,7 +2775,7 @@
       <c r="N15" s="98" t="n"/>
       <c r="O15" s="101" t="n"/>
       <c r="P15" s="101" t="n"/>
-      <c r="Q15" s="102">
+      <c r="Q15" s="97">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
@@ -2714,48 +2786,48 @@
           <t>UI-020</t>
         </is>
       </c>
-      <c r="B16" s="93" t="inlineStr">
+      <c r="B16" s="134" t="inlineStr">
         <is>
           <t>Charging non-blocking</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="137" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D16" s="93" t="inlineStr">
+      <c r="D16" s="134" t="inlineStr">
         <is>
           <t>برق شهر وصل و باتری در حال شارژ است (زرد چشمک‌زن)</t>
         </is>
       </c>
-      <c r="E16" s="93" t="inlineStr">
+      <c r="E16" s="134" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ با پنل کار کن و چند پارامتر بخوان.
 گام ۲: دو دقیقه دستگاه را زیر نظر بگیر.</t>
         </is>
       </c>
-      <c r="F16" s="95" t="inlineStr">
+      <c r="F16" s="135" t="inlineStr">
         <is>
           <t>کار با پنل حین شارژ</t>
         </is>
       </c>
-      <c r="G16" s="95" t="inlineStr">
+      <c r="G16" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H16" s="93" t="inlineStr">
+      <c r="H16" s="134" t="inlineStr">
         <is>
           <t>زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست</t>
         </is>
       </c>
-      <c r="I16" s="93" t="inlineStr">
+      <c r="I16" s="134" t="inlineStr">
         <is>
           <t>چشمک منظم زرد</t>
         </is>
       </c>
-      <c r="J16" s="93" t="inlineStr">
+      <c r="J16" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: زرد منظم چشمک می‌زند و هیچ هنگ، مکث یا ریستی در دستگاه و پنل نیست. اگر هنگ یا قطع ارتباط دیدید، قبول نیست.</t>
         </is>
@@ -2770,7 +2842,7 @@
       <c r="N16" s="93" t="n"/>
       <c r="O16" s="95" t="n"/>
       <c r="P16" s="95" t="n"/>
-      <c r="Q16" s="97">
+      <c r="Q16" s="136">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
@@ -2849,48 +2921,48 @@
           <t>UI-024</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
+      <c r="B18" s="134" t="inlineStr">
         <is>
           <t>Input switch 20/21</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="137" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D18" s="93" t="inlineStr">
+      <c r="D18" s="134" t="inlineStr">
         <is>
           <t>ورودی از منبع آزمایشگاهی می‌آید؛ باتری وصل است</t>
         </is>
       </c>
-      <c r="E18" s="93" t="inlineStr">
+      <c r="E18" s="134" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
 گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
         </is>
       </c>
-      <c r="F18" s="95" t="inlineStr">
+      <c r="F18" s="135" t="inlineStr">
         <is>
           <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
         </is>
       </c>
-      <c r="G18" s="95" t="inlineStr">
+      <c r="G18" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H18" s="93" t="inlineStr">
+      <c r="H18" s="134" t="inlineStr">
         <is>
           <t>وضعیت ورودی فقط وقتی واقعاً از مرز رد می‌شوی عوض می‌شود؛ وسط راه هیچ رفت‌وبرگشت بی‌دلیلی نیست</t>
         </is>
       </c>
-      <c r="I18" s="93" t="inlineStr">
+      <c r="I18" s="134" t="inlineStr">
         <is>
           <t>گذار تکی و تمیز</t>
         </is>
       </c>
-      <c r="J18" s="93" t="inlineStr">
+      <c r="J18" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: با رد شدن واقعی از مرز ورودی، چهره فقط یک‌بار و تمیز عوض می‌شود؛ وسط راه رفت‌وبرگشت بی‌دلیل نیست. اگر فلیکر دیدید، قبول نیست.</t>
         </is>
@@ -2905,7 +2977,7 @@
       <c r="N18" s="93" t="n"/>
       <c r="O18" s="95" t="n"/>
       <c r="P18" s="95" t="n"/>
-      <c r="Q18" s="97">
+      <c r="Q18" s="136">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
@@ -2916,22 +2988,22 @@
           <t>UI-031</t>
         </is>
       </c>
-      <c r="B19" s="98" t="inlineStr">
+      <c r="B19" s="93" t="inlineStr">
         <is>
           <t>عملکرد واقعی درصد</t>
         </is>
       </c>
-      <c r="C19" s="101" t="inlineStr">
+      <c r="C19" s="95" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D19" s="98" t="inlineStr">
+      <c r="D19" s="93" t="inlineStr">
         <is>
           <t>دستگاه روی باتری در حال کار، درصد شارژ معلوم</t>
         </is>
       </c>
-      <c r="E19" s="98" t="inlineStr">
+      <c r="E19" s="93" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روی باتری روشن کن تا درصد شارژ و چشمک سبز معلوم باشد.
 گام ۲: فقط ولتاژ ورودی را بالا و پایین کن (به باتری دست نزن).
@@ -2939,27 +3011,27 @@
 گام ۴: حالا فقط ولتاژ باتری را عوض کن؛ درصد باید عوض شود.</t>
         </is>
       </c>
-      <c r="F19" s="98" t="inlineStr">
+      <c r="F19" s="93" t="inlineStr">
         <is>
           <t>تغییر جدا جدا ورودی و باتری</t>
         </is>
       </c>
-      <c r="G19" s="101" t="inlineStr">
+      <c r="G19" s="95" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H19" s="98" t="inlineStr">
+      <c r="H19" s="93" t="inlineStr">
         <is>
           <t>درصد فقط از باتری می‌آید، نه از ورودی</t>
         </is>
       </c>
-      <c r="I19" s="98" t="inlineStr">
+      <c r="I19" s="93" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="98" t="inlineStr">
+      <c r="J19" s="93" t="inlineStr">
         <is>
           <t>باید ببینید: درصد نمایش با ولتاژ باتری عوض می‌شود و با تغییر ولتاژ ورودی ثابت می‌ماند. اگر درصد از ورودی اثر گرفت، قبول نیست.</t>
         </is>
@@ -2974,7 +3046,7 @@
       <c r="N19" s="98" t="n"/>
       <c r="O19" s="101" t="n"/>
       <c r="P19" s="101" t="n"/>
-      <c r="Q19" s="102">
+      <c r="Q19" s="97">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
@@ -2985,23 +3057,23 @@
           <t>UI-035</t>
         </is>
       </c>
-      <c r="B20" s="98" t="inlineStr">
+      <c r="B20" s="134" t="inlineStr">
         <is>
           <t>عدم‌توازن باتری: قرمز چشمک‌زن تنها</t>
         </is>
       </c>
-      <c r="C20" s="101" t="inlineStr">
+      <c r="C20" s="135" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D20" s="98" t="inlineStr">
+      <c r="D20" s="134" t="inlineStr">
         <is>
           <t>دو باتری ۱۲ ولت داری. یکی را با لامپ ۱۲ ولت کمی خالی کرده‌ای.
 برای زودتر دیدن نتیجه، از پنل حد رویداد مجاز را موقتاً کم کن.</t>
         </is>
       </c>
-      <c r="E20" s="98" t="inlineStr">
+      <c r="E20" s="134" t="inlineStr">
         <is>
           <t>گام ۱: باتری‌های نابرابر را وصل و دستگاه را مدتی به کار بگذار تا حکم عدم‌توازن قفل شود.
 گام ۲: چراغ‌ها را ببین: فقط قرمز چشمک می‌زند؛ سبز و زرد خاموش‌اند و هر از چندی یک بوق کوتاه می‌آید.
@@ -3009,27 +3081,27 @@
 گام ۴: چند دقیقه صبر کن تا قفل خودش پاک شود.</t>
         </is>
       </c>
-      <c r="F20" s="98" t="inlineStr">
+      <c r="F20" s="134" t="inlineStr">
         <is>
           <t>باتری‌های نابرابر و بعد تعویض با سالم</t>
         </is>
       </c>
-      <c r="G20" s="101" t="inlineStr">
+      <c r="G20" s="135" t="inlineStr">
         <is>
           <t>نیم ساعت</t>
         </is>
       </c>
-      <c r="H20" s="98" t="inlineStr">
+      <c r="H20" s="134" t="inlineStr">
         <is>
           <t>در قفل: قرمز چشمک‌زنِ تنها بدون سبز و زرد؛ با تعویض باتری قفل خودکار پاک می‌شود</t>
         </is>
       </c>
-      <c r="I20" s="98" t="inlineStr">
+      <c r="I20" s="134" t="inlineStr">
         <is>
           <t>قرمز چشمک‌زن، بقیه خاموش</t>
         </is>
       </c>
-      <c r="J20" s="98" t="inlineStr">
+      <c r="J20" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: فقط قرمز چشمک می‌زند و سبز و زرد خاموش‌اند؛ با تعویض باتری قفل خودش پاک می‌شود. اگر سبز یا زرد روشن بود یا قفل پاک نشد، قبول نیست.</t>
         </is>
@@ -3044,7 +3116,7 @@
       <c r="N20" s="98" t="n"/>
       <c r="O20" s="101" t="n"/>
       <c r="P20" s="101" t="n"/>
-      <c r="Q20" s="102">
+      <c r="Q20" s="136">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
@@ -3123,7 +3195,7 @@
           <t>UI-003</t>
         </is>
       </c>
-      <c r="B22" s="98" t="inlineStr">
+      <c r="B22" s="134" t="inlineStr">
         <is>
           <t>BatteryRun 57→55</t>
         </is>
@@ -3133,39 +3205,39 @@
           <t>پایین</t>
         </is>
       </c>
-      <c r="D22" s="100" t="inlineStr">
+      <c r="D22" s="138" t="inlineStr">
         <is>
           <t>ادامهٔ UI-002؛ درصد حدود ۵۷ و چشمک سبز جا افتاده</t>
         </is>
       </c>
-      <c r="E22" s="98" t="inlineStr">
+      <c r="E22" s="134" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را آرام پایین بیاور تا درصد به حدود ۵۵ برسد.
 گام ۲: دست نگه دار و چند ثانیه صبر کن تا درصد ثابت شود.
 گام ۳: ریتم تازهٔ سبز را با ریتم قبلی مقایسه کن.</t>
         </is>
       </c>
-      <c r="F22" s="101" t="inlineStr">
+      <c r="F22" s="135" t="inlineStr">
         <is>
           <t>کم‌کردن آرام ولتاژ باتری تا درصد ۵۵</t>
         </is>
       </c>
-      <c r="G22" s="101" t="inlineStr">
+      <c r="G22" s="135" t="inlineStr">
         <is>
           <t>نیم دقیقه</t>
         </is>
       </c>
-      <c r="H22" s="98" t="inlineStr">
+      <c r="H22" s="134" t="inlineStr">
         <is>
           <t>درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر می‌شود (خاموشی‌اش بیشتر از قبل)</t>
         </is>
       </c>
-      <c r="I22" s="100" t="inlineStr">
+      <c r="I22" s="138" t="inlineStr">
         <is>
           <t>تندتر از UI-002، بدون پرش ناگهانی</t>
         </is>
       </c>
-      <c r="J22" s="98" t="inlineStr">
+      <c r="J22" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: درصد روی ۵۵ می‌ایستد و چشمک سبز کمی تندتر از قبل می‌شود، بدون هیچ پرش ناگهانی. اگر روی ۵۷ ماند یا ریتم پرید، قبول نیست.</t>
         </is>
@@ -3180,7 +3252,7 @@
       <c r="N22" s="98" t="n"/>
       <c r="O22" s="101" t="n"/>
       <c r="P22" s="101" t="n"/>
-      <c r="Q22" s="102">
+      <c r="Q22" s="136">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
@@ -3259,48 +3331,48 @@
           <t>UI-006</t>
         </is>
       </c>
-      <c r="B24" s="93" t="inlineStr">
+      <c r="B24" s="134" t="inlineStr">
         <is>
           <t>0↔1 نویز</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="137" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D24" s="103" t="inlineStr">
+      <c r="D24" s="138" t="inlineStr">
         <is>
           <t>ادامهٔ UI-005؛ درصد روی صفر و بوق بحرانی تمام شده</t>
         </is>
       </c>
-      <c r="E24" s="93" t="inlineStr">
+      <c r="E24" s="134" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را خیلی کم بالا و پایین کن، دور مرز صفر و یک درصد.
 گام ۲: دو دقیقه به چراغ‌ها و بوق گوش بده.</t>
         </is>
       </c>
-      <c r="F24" s="95" t="inlineStr">
+      <c r="F24" s="135" t="inlineStr">
         <is>
           <t>بازی ولتاژ دور مرز ۰ و ۱ درصد</t>
         </is>
       </c>
-      <c r="G24" s="95" t="inlineStr">
+      <c r="G24" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H24" s="93" t="inlineStr">
+      <c r="H24" s="134" t="inlineStr">
         <is>
           <t>بوق بحرانی دوباره شروع نمی‌شود و چراغ‌ها بی‌دلیل روشن و خاموش نمی‌شوند</t>
         </is>
       </c>
-      <c r="I24" s="93" t="inlineStr">
+      <c r="I24" s="134" t="inlineStr">
         <is>
           <t>خاموش و آرام</t>
         </is>
       </c>
-      <c r="J24" s="93" t="inlineStr">
+      <c r="J24" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: چراغ‌ها خاموش و آرام می‌مانند و بوق بحرانی با نوسان کوچک دوباره شروع نمی‌شود. اگر بوق یا چراغی بی‌دلیل آمد، قبول نیست.</t>
         </is>
@@ -3315,7 +3387,7 @@
       <c r="N24" s="93" t="n"/>
       <c r="O24" s="95" t="n"/>
       <c r="P24" s="95" t="n"/>
-      <c r="Q24" s="97">
+      <c r="Q24" s="136">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
@@ -3393,7 +3465,7 @@
           <t>UI-009</t>
         </is>
       </c>
-      <c r="B26" s="98" t="inlineStr">
+      <c r="B26" s="134" t="inlineStr">
         <is>
           <t>1% →2 خروج با3</t>
         </is>
@@ -3403,38 +3475,38 @@
           <t>پایین</t>
         </is>
       </c>
-      <c r="D26" s="100" t="inlineStr">
+      <c r="D26" s="138" t="inlineStr">
         <is>
           <t>ادامهٔ UI-007؛ درصد روی ۱</t>
         </is>
       </c>
-      <c r="E26" s="98" t="inlineStr">
+      <c r="E26" s="134" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ را آرام بالا ببر تا درصد به ۲ برسد و ثابت شود.
 گام ۲: یک دقیقه به الگوی بوق گوش بده و با درصد ۱ مقایسه کن.</t>
         </is>
       </c>
-      <c r="F26" s="101" t="inlineStr">
+      <c r="F26" s="135" t="inlineStr">
         <is>
           <t>بالا بردن ولتاژ تا درصد ۲</t>
         </is>
       </c>
-      <c r="G26" s="101" t="inlineStr">
+      <c r="G26" s="135" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H26" s="98" t="inlineStr">
+      <c r="H26" s="134" t="inlineStr">
         <is>
           <t>الگوی بوق به الگوی ملایم‌ترِ درصد ۲ عوض می‌شود و سبز بیشتر از قبل روشن می‌ماند</t>
         </is>
       </c>
-      <c r="I26" s="98" t="inlineStr">
+      <c r="I26" s="134" t="inlineStr">
         <is>
           <t>روشن‌تر از درصد ۱</t>
         </is>
       </c>
-      <c r="J26" s="98" t="inlineStr">
+      <c r="J26" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: از درصد ۲ به بعد الگوی بوق ملایم‌تر می‌شود و سبز بیشتر از قبل روشن می‌ماند. اگر روی الگوی درصد ۱ ماند، قبول نیست.</t>
         </is>
@@ -3449,7 +3521,7 @@
       <c r="N26" s="98" t="n"/>
       <c r="O26" s="101" t="n"/>
       <c r="P26" s="101" t="n"/>
-      <c r="Q26" s="102">
+      <c r="Q26" s="136">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
@@ -3527,7 +3599,7 @@
           <t>UI-011</t>
         </is>
       </c>
-      <c r="B28" s="98" t="inlineStr">
+      <c r="B28" s="134" t="inlineStr">
         <is>
           <t>Charging 5% 56/57/58</t>
         </is>
@@ -3537,38 +3609,38 @@
           <t>پایین</t>
         </is>
       </c>
-      <c r="D28" s="98" t="inlineStr">
+      <c r="D28" s="134" t="inlineStr">
         <is>
           <t>برق شهر وصل و باتری واقعی در حال شارژ است؛ درصد حدود نصف</t>
         </is>
       </c>
-      <c r="E28" s="98" t="inlineStr">
+      <c r="E28" s="134" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را به شارژ بزن و صبر کن درصد دور ۵۷ ثابت شود.
 گام ۲: یک دقیقه فقط چراغ زرد را نگاه کن.</t>
         </is>
       </c>
-      <c r="F28" s="101" t="inlineStr">
+      <c r="F28" s="135" t="inlineStr">
         <is>
           <t>شارژ عادی با درصد میانی</t>
         </is>
       </c>
-      <c r="G28" s="101" t="inlineStr">
+      <c r="G28" s="135" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H28" s="98" t="inlineStr">
+      <c r="H28" s="134" t="inlineStr">
         <is>
           <t>زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند</t>
         </is>
       </c>
-      <c r="I28" s="98" t="inlineStr">
+      <c r="I28" s="134" t="inlineStr">
         <is>
           <t>ریتم ثابت</t>
         </is>
       </c>
-      <c r="J28" s="98" t="inlineStr">
+      <c r="J28" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: زرد منظم و با ریتم ثابت چشمک می‌زند؛ نه ریتمش می‌پرد نه خاموش می‌ماند. اگر ریتم پرید یا زرد ایستاد، قبول نیست.</t>
         </is>
@@ -3583,7 +3655,7 @@
       <c r="N28" s="98" t="n"/>
       <c r="O28" s="101" t="n"/>
       <c r="P28" s="101" t="n"/>
-      <c r="Q28" s="102">
+      <c r="Q28" s="136">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
@@ -3661,7 +3733,7 @@
           <t>UI-013</t>
         </is>
       </c>
-      <c r="B30" s="98" t="inlineStr">
+      <c r="B30" s="134" t="inlineStr">
         <is>
           <t>Charging 5% خروج</t>
         </is>
@@ -3671,39 +3743,39 @@
           <t>پایین</t>
         </is>
       </c>
-      <c r="D30" s="98" t="inlineStr">
+      <c r="D30" s="134" t="inlineStr">
         <is>
           <t>برق شهر وصل و دستگاه در حال شارژ؛ درصد حدود ۵۷</t>
         </is>
       </c>
-      <c r="E30" s="98" t="inlineStr">
+      <c r="E30" s="134" t="inlineStr">
         <is>
           <t>گام ۱: درصد شارژ را با منبع یا مصرف واقعی اول به حدود ۵۲ ببر و ثابت کن.
 گام ۲: بعد به حدود ۶۲ ببر و ثابت کن.
 گام ۳: موقع جابه‌جایی‌ها به زرد نگاه کن که قطع و وصل ناگهانی نکند.</t>
         </is>
       </c>
-      <c r="F30" s="101" t="inlineStr">
+      <c r="F30" s="135" t="inlineStr">
         <is>
           <t>درصد شارژ ۵۷ بعد ۵۲ بعد ۶۲</t>
         </is>
       </c>
-      <c r="G30" s="101" t="inlineStr">
+      <c r="G30" s="135" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H30" s="98" t="inlineStr">
+      <c r="H30" s="134" t="inlineStr">
         <is>
           <t>ریتم زرد با درصد عوض می‌شود ولی چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد</t>
         </is>
       </c>
-      <c r="I30" s="98" t="inlineStr">
+      <c r="I30" s="134" t="inlineStr">
         <is>
           <t>ریتم تازه، بدون راه‌اندازی از صفر</t>
         </is>
       </c>
-      <c r="J30" s="98" t="inlineStr">
+      <c r="J30" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: با بزرگ‌شدن تغییر درصد، ریتم زرد نرم عوض می‌شود؛ چشمک از اول شروع نمی‌شود و قطع‌ووصل ناگهانی ندارد. اگر روی ریتم قبلی ماند یا پرید، قبول نیست.</t>
         </is>
@@ -3718,7 +3790,7 @@
       <c r="N30" s="98" t="n"/>
       <c r="O30" s="101" t="n"/>
       <c r="P30" s="101" t="n"/>
-      <c r="Q30" s="102">
+      <c r="Q30" s="136">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
@@ -3729,7 +3801,7 @@
           <t>UI-023</t>
         </is>
       </c>
-      <c r="B31" s="98" t="inlineStr">
+      <c r="B31" s="93" t="inlineStr">
         <is>
           <t>Low Alarm 21/21.2</t>
         </is>
@@ -3739,38 +3811,38 @@
           <t>پایین</t>
         </is>
       </c>
-      <c r="D31" s="98" t="inlineStr">
+      <c r="D31" s="93" t="inlineStr">
         <is>
           <t>دستگاه روی باتری کار می‌کند؛ منبع آزمایشگاهی به‌جای باتری</t>
         </is>
       </c>
-      <c r="E31" s="98" t="inlineStr">
+      <c r="E31" s="93" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ باتری را آرام تا نزدیک مرز باتری کم (حدود ۲۱ ولت) پایین بیاور.
 گام ۲: کمی دور همان مرز بالا و پایینش کن و چراغ‌ها را نگاه کن.</t>
         </is>
       </c>
-      <c r="F31" s="101" t="inlineStr">
+      <c r="F31" s="95" t="inlineStr">
         <is>
           <t>باتری دور مرز ۲۱ ولت</t>
         </is>
       </c>
-      <c r="G31" s="101" t="inlineStr">
+      <c r="G31" s="95" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H31" s="98" t="inlineStr">
+      <c r="H31" s="93" t="inlineStr">
         <is>
           <t>چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود</t>
         </is>
       </c>
-      <c r="I31" s="98" t="inlineStr">
+      <c r="I31" s="93" t="inlineStr">
         <is>
           <t>پایدار، بدون فلیکر</t>
         </is>
       </c>
-      <c r="J31" s="98" t="inlineStr">
+      <c r="J31" s="93" t="inlineStr">
         <is>
           <t>باید ببینید: دور مرز باتریِ کم، چهرهٔ دستگاه پرپر نمی‌زند و با هر نوسان کوچک عوض نمی‌شود. اگر چراغ‌ها رفت‌وبرگشت تند کردند، قبول نیست.</t>
         </is>
@@ -3785,7 +3857,7 @@
       <c r="N31" s="98" t="n"/>
       <c r="O31" s="101" t="n"/>
       <c r="P31" s="101" t="n"/>
-      <c r="Q31" s="102">
+      <c r="Q31" s="97">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
@@ -3796,49 +3868,49 @@
           <t>UI-030</t>
         </is>
       </c>
-      <c r="B32" s="93" t="inlineStr">
+      <c r="B32" s="134" t="inlineStr">
         <is>
           <t>پنل دیالوگ مستقل</t>
         </is>
       </c>
-      <c r="C32" s="95" t="inlineStr">
+      <c r="C32" s="135" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D32" s="93" t="inlineStr">
+      <c r="D32" s="134" t="inlineStr">
         <is>
           <t>پنل به دستگاه وصل و دستگاه در حال کار عادی است</t>
         </is>
       </c>
-      <c r="E32" s="93" t="inlineStr">
+      <c r="E32" s="134" t="inlineStr">
         <is>
           <t>گام ۱: در پنل یک پیام یا دیالوگ باز کن.
 گام ۲: هم‌زمان چراغ‌های دستگاه را نگاه کن.
 گام ۳: دیالوگ را ببند.</t>
         </is>
       </c>
-      <c r="F32" s="95" t="inlineStr">
+      <c r="F32" s="135" t="inlineStr">
         <is>
           <t>باز و بسته‌کردن دیالوگ پنل</t>
         </is>
       </c>
-      <c r="G32" s="95" t="inlineStr">
+      <c r="G32" s="135" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H32" s="93" t="inlineStr">
+      <c r="H32" s="134" t="inlineStr">
         <is>
           <t>دیالوگ پنل چراغ‌ها و بوق دستگاه را به هم نمی‌ریزد؛ رفتار عادی ادامه دارد</t>
         </is>
       </c>
-      <c r="I32" s="93" t="inlineStr">
+      <c r="I32" s="134" t="inlineStr">
         <is>
           <t>بدون تغییر</t>
         </is>
       </c>
-      <c r="J32" s="93" t="inlineStr">
+      <c r="J32" s="134" t="inlineStr">
         <is>
           <t>باید ببینید: دیالوگ پنل باز و بسته می‌شود و چراغ‌ها و بوق دستگاه دقیقاً مثل قبل ادامه می‌دهند. اگر رفتار چراغ یا بوق به‌هم ریخت، قبول نیست.</t>
         </is>
@@ -3851,13 +3923,13 @@
       </c>
       <c r="M32" s="93" t="n"/>
       <c r="N32" s="93" t="n"/>
-      <c r="O32" s="95" t="inlineStr">
+      <c r="O32" s="135" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P32" s="95" t="n"/>
-      <c r="Q32" s="97">
+      <c r="Q32" s="136">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
@@ -4662,7 +4734,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="106" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>تست‌های آزمایشگاهی (پایه، اسیلوسکوپ و زمان‌بندی دقیق — جدا از تست عملی)</t>
         </is>
@@ -4727,87 +4799,87 @@
       <c r="Q3" s="80" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="132" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="82" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr">
+      <c r="D4" s="132" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="82" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="82" t="inlineStr">
+      <c r="F4" s="132" t="inlineStr">
         <is>
           <t>ورودی‌ها (v_bat/v_in/raw)</t>
         </is>
       </c>
-      <c r="G4" s="82" t="inlineStr">
+      <c r="G4" s="132" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="82" t="inlineStr">
+      <c r="H4" s="132" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="82" t="inlineStr">
+      <c r="I4" s="132" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="82" t="inlineStr">
+      <c r="J4" s="132" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="82" t="inlineStr">
+      <c r="K4" s="132" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="82" t="inlineStr">
+      <c r="L4" s="132" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="82" t="inlineStr">
+      <c r="M4" s="132" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="82" t="inlineStr">
+      <c r="N4" s="132" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="82" t="inlineStr">
+      <c r="O4" s="132" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="82" t="inlineStr">
+      <c r="P4" s="132" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="82" t="inlineStr">
+      <c r="Q4" s="132" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4819,7 +4891,7 @@
           <t>UI-001</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>Mapping PA3→v_bat</t>
         </is>
@@ -4829,12 +4901,12 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="98" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>برد روشن, valid</t>
         </is>
       </c>
-      <c r="E5" s="98" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>گام ۱: برد روشن و snapshot معتبر باشد؛ روی پایهٔ PA3 دقیقاً 2 ولت بده (counts 2482).
 گام ۲: ورودی را هم روی 24 ولت بگذار تا v_in مشکلی نداشته باشد.
@@ -4842,27 +4914,27 @@
 گام ۴: v_bat باید حدود 22352 میلی‌ولت باشد و درصد از روی همان حساب شود (21000 میلی‌ولت = صفر درصد، پس حدود 17 درصد). PA3 فقط v_bat است؛ اگر از v_in استفاده شد تست رد است.</t>
         </is>
       </c>
-      <c r="F5" s="101" t="inlineStr">
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>PA3 2.0V pin → v_bat≈22352mV, v_in 24V</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H5" s="98" t="inlineStr">
+      <c r="H5" s="93" t="inlineStr">
         <is>
           <t>v_bat≈22352, percent ~17% (21000=0). PA3 فقط v_bat</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="93" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="98" t="inlineStr">
+      <c r="J5" s="93" t="inlineStr">
         <is>
           <t>PASS: PA3/raw2/v_bat. FAIL: v_in استفاده</t>
         </is>
@@ -4877,7 +4949,7 @@
       <c r="N5" s="98" t="n"/>
       <c r="O5" s="101" t="n"/>
       <c r="P5" s="101" t="n"/>
-      <c r="Q5" s="102">
+      <c r="Q5" s="97">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -4888,22 +4960,22 @@
           <t>UI-014</t>
         </is>
       </c>
-      <c r="B6" s="93" t="inlineStr">
+      <c r="B6" s="134" t="inlineStr">
         <is>
           <t>Charging yellow phase</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="137" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="93" t="inlineStr">
+      <c r="D6" s="134" t="inlineStr">
         <is>
           <t>Charging 25V On430</t>
         </is>
       </c>
-      <c r="E6" s="93" t="inlineStr">
+      <c r="E6" s="134" t="inlineStr">
         <is>
           <t>گام ۱: وضعیت Charging با باتری 25 ولت باشد تا زرد در حال روشنی با زمان روشنی 430 میلی‌ثانیه باشد.
 گام ۲: وقتی 100 میلی‌ثانیه از روشنی گذشت، درصد خام را 56 کن (درصد پایدار همان 57 می‌ماند).
@@ -4911,27 +4983,27 @@
 گام ۴: اگر روشنی وسطش از نو شروع شد (restart) تست رد است.</t>
         </is>
       </c>
-      <c r="F6" s="95" t="inlineStr">
+      <c r="F6" s="135" t="inlineStr">
         <is>
           <t>On430 jitter56</t>
         </is>
       </c>
-      <c r="G6" s="95" t="inlineStr">
+      <c r="G6" s="135" t="inlineStr">
         <is>
           <t>600ms</t>
         </is>
       </c>
-      <c r="H6" s="93" t="inlineStr">
+      <c r="H6" s="134" t="inlineStr">
         <is>
           <t>ON تا 430 حفظ سپس OFF</t>
         </is>
       </c>
-      <c r="I6" s="93" t="inlineStr">
+      <c r="I6" s="134" t="inlineStr">
         <is>
           <t>ON حفظ</t>
         </is>
       </c>
-      <c r="J6" s="93" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>PASS: restart نشد. FAIL: restart</t>
         </is>
@@ -4946,7 +5018,7 @@
       <c r="N6" s="93" t="n"/>
       <c r="O6" s="95" t="n"/>
       <c r="P6" s="95" t="n"/>
-      <c r="Q6" s="97">
+      <c r="Q6" s="136">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -5026,7 +5098,7 @@
           <t>UI-025</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="134" t="inlineStr">
         <is>
           <t>Mapping PA3/PA2</t>
         </is>
@@ -5036,12 +5108,12 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="98" t="inlineStr">
+      <c r="D8" s="134" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="E8" s="98" t="inlineStr">
+      <c r="E8" s="134" t="inlineStr">
         <is>
           <t>گام ۱: از Measurement شروع کن: روی PA3 دقیقاً 1 ولت و روی PA2 هم دقیقاً 1 ولت بده.
 گام ۲: 100 میلی‌ثانیه صبر کن و این‌ها را بخوان: raw1 باید ولتاژ ورودی باشد و raw2 باید ولتاژ باتری. هر دو باید حدود 11176 میلی‌ولت خوانده شوند.
@@ -5049,27 +5121,27 @@
 گام ۴: BatteryRun فقط باید بر اساس v_bat کار کند. جابه‌جا بودن این دو یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F8" s="101" t="inlineStr">
+      <c r="F8" s="135" t="inlineStr">
         <is>
           <t>PA2/PA3 1V</t>
         </is>
       </c>
-      <c r="G8" s="101" t="inlineStr">
+      <c r="G8" s="135" t="inlineStr">
         <is>
           <t>100ms</t>
         </is>
       </c>
-      <c r="H8" s="98" t="inlineStr">
+      <c r="H8" s="134" t="inlineStr">
         <is>
           <t>v_bat PA3/raw2 v_in PA2/raw1 BatteryRun فقط v_bat</t>
         </is>
       </c>
-      <c r="I8" s="98" t="inlineStr">
+      <c r="I8" s="134" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="98" t="inlineStr">
+      <c r="J8" s="134" t="inlineStr">
         <is>
           <t>PASS: mapping. FAIL: جابجایی</t>
         </is>
@@ -5084,7 +5156,7 @@
       <c r="N8" s="98" t="n"/>
       <c r="O8" s="101" t="n"/>
       <c r="P8" s="101" t="n"/>
-      <c r="Q8" s="102">
+      <c r="Q8" s="136">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -5613,7 +5685,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5640,7 +5712,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="106" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -5705,87 +5777,87 @@
       <c r="Q3" s="80" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="132" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="82" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr">
+      <c r="D4" s="132" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="82" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="82" t="inlineStr">
+      <c r="F4" s="132" t="inlineStr">
         <is>
           <t>ورودی‌ها (v_bat/v_in/raw)</t>
         </is>
       </c>
-      <c r="G4" s="82" t="inlineStr">
+      <c r="G4" s="132" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="82" t="inlineStr">
+      <c r="H4" s="132" t="inlineStr">
         <is>
           <t>LED/بوق — انتظار</t>
         </is>
       </c>
-      <c r="I4" s="82" t="inlineStr">
+      <c r="I4" s="132" t="inlineStr">
         <is>
           <t>فاز چشمک — انتظار</t>
         </is>
       </c>
-      <c r="J4" s="82" t="inlineStr">
+      <c r="J4" s="132" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="82" t="inlineStr">
+      <c r="K4" s="132" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="L4" s="82" t="inlineStr">
+      <c r="L4" s="132" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="82" t="inlineStr">
+      <c r="M4" s="132" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="N4" s="82" t="inlineStr">
+      <c r="N4" s="132" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="82" t="inlineStr">
+      <c r="O4" s="132" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="82" t="inlineStr">
+      <c r="P4" s="132" t="inlineStr">
         <is>
           <t>تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="82" t="inlineStr">
+      <c r="Q4" s="132" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -5866,7 +5938,7 @@
           <t>UI-027</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="134" t="inlineStr">
         <is>
           <t>No extra RTOS</t>
         </is>
@@ -5876,39 +5948,39 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="D6" s="134" t="inlineStr">
         <is>
           <t>hysteresis UI</t>
         </is>
       </c>
-      <c r="E6" s="98" t="inlineStr">
+      <c r="E6" s="134" t="inlineStr">
         <is>
           <t>گام ۱: در کل کد محصول دنبال ساختن صف (queue)، تایمر نرم‌افزاری، موتکس یا heap تازه برای هیسترزیس UI بگرد (grep).
 گام ۲: هیسترزیس UI باید فقط با همان متغیرهای سادهٔ قبلی کار کند.
 گام ۳: هیچ شیء RTOS تازه‌ای نباید برای هیسترزیس ساخته شده باشد؛ پیدا شدن هر کدام یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F6" s="101" t="inlineStr">
+      <c r="F6" s="135" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="101" t="inlineStr">
+      <c r="G6" s="135" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="134" t="inlineStr">
         <is>
           <t>هیچ شئ جدید برای hysteresis</t>
         </is>
       </c>
-      <c r="I6" s="98" t="inlineStr">
+      <c r="I6" s="134" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="98" t="inlineStr">
+      <c r="J6" s="134" t="inlineStr">
         <is>
           <t>PASS: بدون شئ. FAIL: شئ جدید</t>
         </is>
@@ -5923,7 +5995,7 @@
       <c r="N6" s="98" t="n"/>
       <c r="O6" s="101" t="n"/>
       <c r="P6" s="101" t="n"/>
-      <c r="Q6" s="102">
+      <c r="Q6" s="136">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -5934,22 +6006,22 @@
           <t>UI-029</t>
         </is>
       </c>
-      <c r="B7" s="98" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C7" s="108" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="98" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E7" s="98" t="inlineStr">
+      <c r="E7" s="93" t="inlineStr">
         <is>
           <t>گام ۱: task_ui را با snapshot صفرشده صدا بزن: valid=false و هر 9 فیلد صفر.
 گام ۲: 2 ثانیه نگاه کن.
@@ -5957,27 +6029,27 @@
 گام ۴: روشن‌شدن LED یعنی رد تست.</t>
         </is>
       </c>
-      <c r="F7" s="101" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" s="101" t="inlineStr">
+      <c r="G7" s="95" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H7" s="98" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>UI باید safe-off بماند؛ چراغ‌ها خاموش؛ بدون خواندن v_bat24 زباله</t>
         </is>
       </c>
-      <c r="I7" s="98" t="inlineStr">
+      <c r="I7" s="93" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J7" s="98" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>LED خاموش بدون درصد کاذب</t>
         </is>
@@ -5990,13 +6062,13 @@
       </c>
       <c r="M7" s="98" t="n"/>
       <c r="N7" s="98" t="n"/>
-      <c r="O7" s="101" t="inlineStr">
+      <c r="O7" s="95" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P7" s="101" t="n"/>
-      <c r="Q7" s="102" t="inlineStr">
+      <c r="Q7" s="97" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -6473,7 +6545,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="131" t="inlineStr">
         <is>
           <t>مرجع سریع UI — هیسترزیس 2%/5%/100.95 و نگاشت</t>
         </is>
@@ -6487,64 +6559,64 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="140" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="140" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="109" t="inlineStr">
+      <c r="C3" s="140" t="inlineStr">
         <is>
           <t>رفتار</t>
         </is>
       </c>
-      <c r="D3" s="109" t="inlineStr">
+      <c r="D3" s="140" t="inlineStr">
         <is>
           <t>ثابت / محل</t>
         </is>
       </c>
-      <c r="E3" s="109" t="inlineStr">
+      <c r="E3" s="140" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="F3" s="109" t="inlineStr">
+      <c r="F3" s="140" t="inlineStr">
         <is>
           <t>وابستگی</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="110" t="inlineStr">
+      <c r="A4" s="141" t="inlineStr">
         <is>
           <t>PA3 mapping</t>
         </is>
       </c>
-      <c r="B4" s="110" t="inlineStr">
+      <c r="B4" s="141" t="inlineStr">
         <is>
           <t>PA3 pin13 ADC1_IN3 → raw2 → v_bat24_mv → BatteryRun/Charging</t>
         </is>
       </c>
-      <c r="C4" s="110" t="inlineStr">
+      <c r="C4" s="141" t="inlineStr">
         <is>
           <t>فقط v_bat</t>
         </is>
       </c>
-      <c r="D4" s="111" t="inlineStr">
+      <c r="D4" s="142" t="inlineStr">
         <is>
           <t>board_pins.h:PIN_ADC_24_BAT</t>
         </is>
       </c>
-      <c r="E4" s="110" t="inlineStr">
+      <c r="E4" s="141" t="inlineStr">
         <is>
           <t>PA3→BatteryRun</t>
         </is>
       </c>
-      <c r="F4" s="111" t="inlineStr">
+      <c r="F4" s="142" t="inlineStr">
         <is>
           <t>UI-001,025</t>
         </is>
@@ -6583,32 +6655,32 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="110" t="inlineStr">
+      <c r="A6" s="141" t="inlineStr">
         <is>
           <t>PB4</t>
         </is>
       </c>
-      <c r="B6" s="110" t="inlineStr">
+      <c r="B6" s="141" t="inlineStr">
         <is>
           <t>MCU_INT_24_IN EXTI دو لبه</t>
         </is>
       </c>
-      <c r="C6" s="110" t="inlineStr">
+      <c r="C6" s="141" t="inlineStr">
         <is>
           <t>فقط ورودی</t>
         </is>
       </c>
-      <c r="D6" s="111" t="inlineStr">
+      <c r="D6" s="142" t="inlineStr">
         <is>
           <t>board_pins.h</t>
         </is>
       </c>
-      <c r="E6" s="110" t="inlineStr">
+      <c r="E6" s="141" t="inlineStr">
         <is>
           <t>PB4→ورودی</t>
         </is>
       </c>
-      <c r="F6" s="111" t="inlineStr">
+      <c r="F6" s="142" t="inlineStr">
         <is>
           <t>UI-024</t>
         </is>
@@ -6647,32 +6719,32 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
+      <c r="A8" s="141" t="inlineStr">
         <is>
           <t>Battery 2%+0/1</t>
         </is>
       </c>
-      <c r="B8" s="110" t="inlineStr">
+      <c r="B8" s="141" t="inlineStr">
         <is>
           <t>stable0→raw&gt;=2→1, stable1:0→0 &gt;=3→2 else1</t>
         </is>
       </c>
-      <c r="C8" s="110" t="inlineStr">
+      <c r="C8" s="141" t="inlineStr">
         <is>
           <t>جلوگیری 0↔1</t>
         </is>
       </c>
-      <c r="D8" s="110" t="inlineStr">
+      <c r="D8" s="141" t="inlineStr">
         <is>
           <t>RUN_HYSTERESIS 2 ZERO2 ONE3</t>
         </is>
       </c>
-      <c r="E8" s="110" t="inlineStr">
+      <c r="E8" s="141" t="inlineStr">
         <is>
           <t>0/1 جدا</t>
         </is>
       </c>
-      <c r="F8" s="111" t="inlineStr">
+      <c r="F8" s="142" t="inlineStr">
         <is>
           <t>UI-002-010</t>
         </is>
@@ -6711,32 +6783,32 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
+      <c r="A10" s="141" t="inlineStr">
         <is>
           <t>Charging 5%</t>
         </is>
       </c>
-      <c r="B10" s="110" t="inlineStr">
+      <c r="B10" s="141" t="inlineStr">
         <is>
           <t>|raw-stable|&gt;=5 → update else keep, 53..61 حفظ</t>
         </is>
       </c>
-      <c r="C10" s="110" t="inlineStr">
+      <c r="C10" s="141" t="inlineStr">
         <is>
           <t>پایدار زرد</t>
         </is>
       </c>
-      <c r="D10" s="110" t="inlineStr">
+      <c r="D10" s="141" t="inlineStr">
         <is>
           <t>CHARGING_HYSTERESIS 5</t>
         </is>
       </c>
-      <c r="E10" s="110" t="inlineStr">
+      <c r="E10" s="141" t="inlineStr">
         <is>
           <t>فقط Charging</t>
         </is>
       </c>
-      <c r="F10" s="111" t="inlineStr">
+      <c r="F10" s="142" t="inlineStr">
         <is>
           <t>UI-011-013</t>
         </is>
@@ -6775,32 +6847,32 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
+      <c r="A12" s="141" t="inlineStr">
         <is>
           <t>Full 100/95</t>
         </is>
       </c>
-      <c r="B12" s="110" t="inlineStr">
+      <c r="B12" s="141" t="inlineStr">
         <is>
           <t>&gt;=100 InputOk, &lt;95 Charging, else hold</t>
         </is>
       </c>
-      <c r="C12" s="110" t="inlineStr">
+      <c r="C12" s="141" t="inlineStr">
         <is>
           <t>جلوگیری 28V پرش</t>
         </is>
       </c>
-      <c r="D12" s="110" t="inlineStr">
+      <c r="D12" s="141" t="inlineStr">
         <is>
           <t>FULL_ENTER 100 FULL_EXIT95</t>
         </is>
       </c>
-      <c r="E12" s="110" t="inlineStr">
+      <c r="E12" s="141" t="inlineStr">
         <is>
           <t>stateful</t>
         </is>
       </c>
-      <c r="F12" s="111" t="inlineStr">
+      <c r="F12" s="142" t="inlineStr">
         <is>
           <t>UI-015-017</t>
         </is>
@@ -6839,32 +6911,32 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
+      <c r="A14" s="141" t="inlineStr">
         <is>
           <t>Yellow phase</t>
         </is>
       </c>
-      <c r="B14" s="110" t="inlineStr">
+      <c r="B14" s="141" t="inlineStr">
         <is>
           <t>stable5 تغییر فاز reset نه</t>
         </is>
       </c>
-      <c r="C14" s="110" t="inlineStr">
+      <c r="C14" s="141" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="D14" s="110" t="inlineStr">
+      <c r="D14" s="141" t="inlineStr">
         <is>
           <t>UpdateChargingYellowBlink</t>
         </is>
       </c>
-      <c r="E14" s="110" t="inlineStr">
+      <c r="E14" s="141" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="F14" s="111" t="inlineStr">
+      <c r="F14" s="142" t="inlineStr">
         <is>
           <t>UI-011,014</t>
         </is>
@@ -6903,32 +6975,32 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="110" t="inlineStr">
+      <c r="A16" s="141" t="inlineStr">
         <is>
           <t>Overvoltage</t>
         </is>
       </c>
-      <c r="B16" s="110" t="inlineStr">
+      <c r="B16" s="141" t="inlineStr">
         <is>
           <t>&gt;28000 خطا &lt;=27000 پاک</t>
         </is>
       </c>
-      <c r="C16" s="110" t="inlineStr">
+      <c r="C16" s="141" t="inlineStr">
         <is>
           <t>قرمز50%+بوق10s</t>
         </is>
       </c>
-      <c r="D16" s="110" t="inlineStr">
+      <c r="D16" s="141" t="inlineStr">
         <is>
           <t>OVERVOLTAGE</t>
         </is>
       </c>
-      <c r="E16" s="110" t="inlineStr">
+      <c r="E16" s="141" t="inlineStr">
         <is>
           <t>27/28</t>
         </is>
       </c>
-      <c r="F16" s="111" t="inlineStr">
+      <c r="F16" s="142" t="inlineStr">
         <is>
           <t>UI-021</t>
         </is>
@@ -6967,32 +7039,32 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="110" t="inlineStr">
+      <c r="A18" s="141" t="inlineStr">
         <is>
           <t>0% critical</t>
         </is>
       </c>
-      <c r="B18" s="110" t="inlineStr">
+      <c r="B18" s="141" t="inlineStr">
         <is>
           <t>&lt;1% 10s یک بار سپس خاموش</t>
         </is>
       </c>
-      <c r="C18" s="110" t="inlineStr">
+      <c r="C18" s="141" t="inlineStr">
         <is>
           <t>تا خروج 0 تکرار نه</t>
         </is>
       </c>
-      <c r="D18" s="110" t="inlineStr">
+      <c r="D18" s="141" t="inlineStr">
         <is>
           <t>CRITICAL 1</t>
         </is>
       </c>
-      <c r="E18" s="110" t="inlineStr">
+      <c r="E18" s="141" t="inlineStr">
         <is>
           <t>stable0</t>
         </is>
       </c>
-      <c r="F18" s="111" t="inlineStr">
+      <c r="F18" s="142" t="inlineStr">
         <is>
           <t>UI-005,006</t>
         </is>
@@ -7031,32 +7103,32 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="110" t="inlineStr">
+      <c r="A20" s="141" t="inlineStr">
         <is>
           <t>RTOS static</t>
         </is>
       </c>
-      <c r="B20" s="110" t="inlineStr">
+      <c r="B20" s="141" t="inlineStr">
         <is>
           <t>DYNAMIC 0 cb/stack</t>
         </is>
       </c>
-      <c r="C20" s="110" t="inlineStr">
+      <c r="C20" s="141" t="inlineStr">
         <is>
           <t>همه static</t>
         </is>
       </c>
-      <c r="D20" s="110" t="inlineStr">
+      <c r="D20" s="141" t="inlineStr">
         <is>
           <t>FreeRTOSConfig</t>
         </is>
       </c>
-      <c r="E20" s="110" t="inlineStr">
+      <c r="E20" s="141" t="inlineStr">
         <is>
           <t>word/byte</t>
         </is>
       </c>
-      <c r="F20" s="111" t="inlineStr">
+      <c r="F20" s="142" t="inlineStr">
         <is>
           <t>UI-026</t>
         </is>
@@ -7152,7 +7224,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="131" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — UI هیسترزیس 2%/5%/100.95 و فاز</t>
         </is>
@@ -7166,86 +7238,86 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="82" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="82" t="inlineStr">
+      <c r="B3" s="132" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="82" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="82" t="inlineStr">
+      <c r="D3" s="132" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="82" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>شرح کوتاه</t>
         </is>
       </c>
-      <c r="F3" s="82" t="inlineStr">
+      <c r="F3" s="132" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="82" t="inlineStr">
+      <c r="G3" s="132" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="82" t="inlineStr">
+      <c r="H3" s="132" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="82" t="inlineStr">
+      <c r="I3" s="132" t="inlineStr">
         <is>
           <t>مدرک/عکس</t>
         </is>
       </c>
-      <c r="J3" s="82" t="inlineStr">
+      <c r="J3" s="132" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="K3" s="132" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="82" t="inlineStr">
+      <c r="L3" s="132" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M3" s="82" t="inlineStr">
+      <c r="M3" s="132" t="inlineStr">
         <is>
           <t>تأیید رفع</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="115" t="inlineStr"/>
-      <c r="B4" s="115" t="inlineStr"/>
-      <c r="C4" s="115" t="inlineStr"/>
-      <c r="D4" s="115" t="inlineStr"/>
-      <c r="E4" s="115" t="inlineStr"/>
-      <c r="F4" s="115" t="inlineStr"/>
-      <c r="G4" s="115" t="inlineStr"/>
-      <c r="H4" s="115" t="inlineStr"/>
-      <c r="I4" s="115" t="inlineStr"/>
-      <c r="J4" s="115" t="inlineStr"/>
-      <c r="K4" s="115" t="inlineStr"/>
-      <c r="L4" s="115" t="inlineStr"/>
-      <c r="M4" s="115" t="inlineStr"/>
+      <c r="A4" s="143" t="inlineStr"/>
+      <c r="B4" s="143" t="inlineStr"/>
+      <c r="C4" s="143" t="inlineStr"/>
+      <c r="D4" s="143" t="inlineStr"/>
+      <c r="E4" s="143" t="inlineStr"/>
+      <c r="F4" s="143" t="inlineStr"/>
+      <c r="G4" s="143" t="inlineStr"/>
+      <c r="H4" s="143" t="inlineStr"/>
+      <c r="I4" s="143" t="inlineStr"/>
+      <c r="J4" s="143" t="inlineStr"/>
+      <c r="K4" s="143" t="inlineStr"/>
+      <c r="L4" s="143" t="inlineStr"/>
+      <c r="M4" s="143" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="116" t="inlineStr"/>
@@ -7263,19 +7335,19 @@
       <c r="M5" s="116" t="inlineStr"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="115" t="inlineStr"/>
-      <c r="B6" s="115" t="inlineStr"/>
-      <c r="C6" s="115" t="inlineStr"/>
-      <c r="D6" s="115" t="inlineStr"/>
-      <c r="E6" s="115" t="inlineStr"/>
-      <c r="F6" s="115" t="inlineStr"/>
-      <c r="G6" s="115" t="inlineStr"/>
-      <c r="H6" s="115" t="inlineStr"/>
-      <c r="I6" s="115" t="inlineStr"/>
-      <c r="J6" s="115" t="inlineStr"/>
-      <c r="K6" s="115" t="inlineStr"/>
-      <c r="L6" s="115" t="inlineStr"/>
-      <c r="M6" s="115" t="inlineStr"/>
+      <c r="A6" s="143" t="inlineStr"/>
+      <c r="B6" s="143" t="inlineStr"/>
+      <c r="C6" s="143" t="inlineStr"/>
+      <c r="D6" s="143" t="inlineStr"/>
+      <c r="E6" s="143" t="inlineStr"/>
+      <c r="F6" s="143" t="inlineStr"/>
+      <c r="G6" s="143" t="inlineStr"/>
+      <c r="H6" s="143" t="inlineStr"/>
+      <c r="I6" s="143" t="inlineStr"/>
+      <c r="J6" s="143" t="inlineStr"/>
+      <c r="K6" s="143" t="inlineStr"/>
+      <c r="L6" s="143" t="inlineStr"/>
+      <c r="M6" s="143" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="116" t="inlineStr"/>
@@ -7293,19 +7365,19 @@
       <c r="M7" s="116" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="115" t="inlineStr"/>
-      <c r="B8" s="115" t="inlineStr"/>
-      <c r="C8" s="115" t="inlineStr"/>
-      <c r="D8" s="115" t="inlineStr"/>
-      <c r="E8" s="115" t="inlineStr"/>
-      <c r="F8" s="115" t="inlineStr"/>
-      <c r="G8" s="115" t="inlineStr"/>
-      <c r="H8" s="115" t="inlineStr"/>
-      <c r="I8" s="115" t="inlineStr"/>
-      <c r="J8" s="115" t="inlineStr"/>
-      <c r="K8" s="115" t="inlineStr"/>
-      <c r="L8" s="115" t="inlineStr"/>
-      <c r="M8" s="115" t="inlineStr"/>
+      <c r="A8" s="143" t="inlineStr"/>
+      <c r="B8" s="143" t="inlineStr"/>
+      <c r="C8" s="143" t="inlineStr"/>
+      <c r="D8" s="143" t="inlineStr"/>
+      <c r="E8" s="143" t="inlineStr"/>
+      <c r="F8" s="143" t="inlineStr"/>
+      <c r="G8" s="143" t="inlineStr"/>
+      <c r="H8" s="143" t="inlineStr"/>
+      <c r="I8" s="143" t="inlineStr"/>
+      <c r="J8" s="143" t="inlineStr"/>
+      <c r="K8" s="143" t="inlineStr"/>
+      <c r="L8" s="143" t="inlineStr"/>
+      <c r="M8" s="143" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="116" t="inlineStr"/>
@@ -7323,19 +7395,19 @@
       <c r="M9" s="116" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="115" t="inlineStr"/>
-      <c r="B10" s="115" t="inlineStr"/>
-      <c r="C10" s="115" t="inlineStr"/>
-      <c r="D10" s="115" t="inlineStr"/>
-      <c r="E10" s="115" t="inlineStr"/>
-      <c r="F10" s="115" t="inlineStr"/>
-      <c r="G10" s="115" t="inlineStr"/>
-      <c r="H10" s="115" t="inlineStr"/>
-      <c r="I10" s="115" t="inlineStr"/>
-      <c r="J10" s="115" t="inlineStr"/>
-      <c r="K10" s="115" t="inlineStr"/>
-      <c r="L10" s="115" t="inlineStr"/>
-      <c r="M10" s="115" t="inlineStr"/>
+      <c r="A10" s="143" t="inlineStr"/>
+      <c r="B10" s="143" t="inlineStr"/>
+      <c r="C10" s="143" t="inlineStr"/>
+      <c r="D10" s="143" t="inlineStr"/>
+      <c r="E10" s="143" t="inlineStr"/>
+      <c r="F10" s="143" t="inlineStr"/>
+      <c r="G10" s="143" t="inlineStr"/>
+      <c r="H10" s="143" t="inlineStr"/>
+      <c r="I10" s="143" t="inlineStr"/>
+      <c r="J10" s="143" t="inlineStr"/>
+      <c r="K10" s="143" t="inlineStr"/>
+      <c r="L10" s="143" t="inlineStr"/>
+      <c r="M10" s="143" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="116" t="inlineStr"/>
@@ -7353,19 +7425,19 @@
       <c r="M11" s="116" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="115" t="inlineStr"/>
-      <c r="B12" s="115" t="inlineStr"/>
-      <c r="C12" s="115" t="inlineStr"/>
-      <c r="D12" s="115" t="inlineStr"/>
-      <c r="E12" s="115" t="inlineStr"/>
-      <c r="F12" s="115" t="inlineStr"/>
-      <c r="G12" s="115" t="inlineStr"/>
-      <c r="H12" s="115" t="inlineStr"/>
-      <c r="I12" s="115" t="inlineStr"/>
-      <c r="J12" s="115" t="inlineStr"/>
-      <c r="K12" s="115" t="inlineStr"/>
-      <c r="L12" s="115" t="inlineStr"/>
-      <c r="M12" s="115" t="inlineStr"/>
+      <c r="A12" s="143" t="inlineStr"/>
+      <c r="B12" s="143" t="inlineStr"/>
+      <c r="C12" s="143" t="inlineStr"/>
+      <c r="D12" s="143" t="inlineStr"/>
+      <c r="E12" s="143" t="inlineStr"/>
+      <c r="F12" s="143" t="inlineStr"/>
+      <c r="G12" s="143" t="inlineStr"/>
+      <c r="H12" s="143" t="inlineStr"/>
+      <c r="I12" s="143" t="inlineStr"/>
+      <c r="J12" s="143" t="inlineStr"/>
+      <c r="K12" s="143" t="inlineStr"/>
+      <c r="L12" s="143" t="inlineStr"/>
+      <c r="M12" s="143" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="116" t="inlineStr"/>
@@ -7410,7 +7482,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="131" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی روی برد — UI — 2%/5%/100.95</t>
         </is>
@@ -7424,7 +7496,7 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="140" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
@@ -7504,14 +7576,14 @@
       <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="117" t="inlineStr">
+      <c r="A7" s="144" t="inlineStr">
         <is>
           <t>تست‌کننده اصلی</t>
         </is>
       </c>
       <c r="B7" s="112" t="inlineStr"/>
       <c r="C7" s="80" t="n"/>
-      <c r="D7" s="117" t="inlineStr">
+      <c r="D7" s="145" t="inlineStr">
         <is>
           <t>تاریخ شروع</t>
         </is>
@@ -7520,19 +7592,19 @@
       <c r="F7" s="80" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="117" t="inlineStr">
+      <c r="A8" s="144" t="inlineStr">
         <is>
           <t>تاریخ پایان</t>
         </is>
       </c>
       <c r="B8" s="112" t="inlineStr"/>
       <c r="C8" s="80" t="n"/>
-      <c r="D8" s="117" t="inlineStr">
+      <c r="D8" s="146" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="E8" s="112" t="inlineStr">
+      <c r="E8" s="147" t="inlineStr">
         <is>
           <t>منبع آزمایشگاهی + DMM + اسکوپ + تایمر10ms</t>
         </is>
@@ -7540,23 +7612,23 @@
       <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="117" t="inlineStr">
+      <c r="A9" s="144" t="inlineStr">
         <is>
           <t>فرکانس تیک</t>
         </is>
       </c>
-      <c r="B9" s="112" t="inlineStr">
+      <c r="B9" s="141" t="inlineStr">
         <is>
           <t>1000Hz (osKernelGetTickFreq)</t>
         </is>
       </c>
       <c r="C9" s="80" t="n"/>
-      <c r="D9" s="117" t="inlineStr">
+      <c r="D9" s="145" t="inlineStr">
         <is>
           <t>دوره UI</t>
         </is>
       </c>
-      <c r="E9" s="112" t="inlineStr">
+      <c r="E9" s="141" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
@@ -7564,23 +7636,23 @@
       <c r="F9" s="80" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="117" t="inlineStr">
+      <c r="A10" s="144" t="inlineStr">
         <is>
           <t>آستانه‌ها</t>
         </is>
       </c>
-      <c r="B10" s="112" t="inlineStr">
+      <c r="B10" s="147" t="inlineStr">
         <is>
           <t>BatteryRun2%+0/1, Charging5%, Full100/95, Low21/21.2</t>
         </is>
       </c>
       <c r="C10" s="80" t="n"/>
-      <c r="D10" s="117" t="inlineStr">
+      <c r="D10" s="146" t="inlineStr">
         <is>
           <t>فیلتر</t>
         </is>
       </c>
-      <c r="E10" s="112" t="inlineStr">
+      <c r="E10" s="147" t="inlineStr">
         <is>
           <t>سبزOff(100-stable)*10 زردOn(100-stable5)*10</t>
         </is>
@@ -7596,7 +7668,7 @@
       <c r="F11" s="80" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="140" t="inlineStr">
         <is>
           <t>خلاصه وضعیت تست‌ها</t>
         </is>
@@ -7608,18 +7680,18 @@
       <c r="F12" s="29" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="117" t="inlineStr">
+      <c r="A13" s="144" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B13" s="112" t="inlineStr">
+      <c r="B13" s="141" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
       <c r="C13" s="80" t="n"/>
-      <c r="D13" s="117" t="inlineStr">
+      <c r="D13" s="145" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
@@ -7628,18 +7700,18 @@
       <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="117" t="inlineStr">
+      <c r="A14" s="144" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B14" s="112" t="inlineStr">
+      <c r="B14" s="147" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
       <c r="C14" s="80" t="n"/>
-      <c r="D14" s="118" t="inlineStr">
+      <c r="D14" s="148" t="inlineStr">
         <is>
           <t>UI-001 تا UI-028</t>
         </is>
@@ -7648,18 +7720,18 @@
       <c r="F14" s="80" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="117" t="inlineStr">
+      <c r="A15" s="144" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B15" s="112" t="inlineStr">
+      <c r="B15" s="141" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="C15" s="80" t="n"/>
-      <c r="D15" s="117" t="inlineStr">
+      <c r="D15" s="145" t="inlineStr">
         <is>
           <t>COUNTIF</t>
         </is>
@@ -7668,12 +7740,12 @@
       <c r="F15" s="80" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="117" t="inlineStr">
+      <c r="A16" s="144" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B16" s="112" t="inlineStr">
+      <c r="B16" s="147" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7684,12 +7756,12 @@
       <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="117" t="inlineStr">
+      <c r="A17" s="144" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B17" s="112" t="inlineStr">
+      <c r="B17" s="141" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -7700,12 +7772,12 @@
       <c r="F17" s="80" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="117" t="inlineStr">
+      <c r="A18" s="144" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B18" s="112" t="inlineStr">
+      <c r="B18" s="147" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7724,7 +7796,7 @@
       <c r="F19" s="80" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="114" t="inlineStr">
+      <c r="A20" s="149" t="inlineStr">
         <is>
           <t>امضا: تست‌کننده ________________  سرپرست ________________  تاریخ ________________</t>
         </is>
@@ -7749,7 +7821,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7760,14 +7832,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="119" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="120" t="inlineStr">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
@@ -7809,7 +7881,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="119" t="inlineStr">
+      <c r="A8" s="150" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -7840,7 +7912,7 @@
       <c r="A12" s="80" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="119" t="inlineStr">
+      <c r="A13" s="150" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -7886,7 +7958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7900,11 +7972,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="80" t="n"/>
-      <c r="B2" s="80" t="n"/>
-      <c r="C2" s="80" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -7916,7 +7984,6 @@
           <t>Ui_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="80" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -7929,7 +7996,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="80" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
@@ -7942,7 +8008,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="80" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -7950,13 +8015,13 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="80" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -7964,7 +8029,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="68">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -382,8 +382,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -483,6 +499,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -629,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1045,6 +1066,27 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1831,7 +1873,6 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
@@ -1841,6 +1882,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="152" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B22" s="153" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1897,12 +1950,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="131" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — UI 2.2 (BatteryRun 2%+0/1, Charging 5%, Full 100/95, فاز preserve, non-blocking)</t>
+        </is>
+      </c>
+      <c r="T1" s="154" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1912,6 +1973,14 @@
           <t>ورودی mV، درصد 0-100، زمان ms. BatteryRun PA3 stable2%، Charging PA3 stable5% و زرد، Full 100/95 با raw.</t>
         </is>
       </c>
+      <c r="T2" s="155" t="inlineStr">
+        <is>
+          <t>درصد باتری (0 تا 100)</t>
+        </is>
+      </c>
+      <c r="U2" s="156" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="91" t="inlineStr">
@@ -1919,6 +1988,14 @@
           <t>هر ردیف: snapshot.valid, v_bat/v_in, raw/stable, ورودی present/overvoltage, فاز LED/بوق با اسکوپ 10ms. InputOk/Charging سریع برگردد.</t>
         </is>
       </c>
+      <c r="T3" s="155" t="inlineStr">
+        <is>
+          <t>ورودی حاضر است؟ (1=بله، 0=نه)</t>
+        </is>
+      </c>
+      <c r="U3" s="156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="132" t="inlineStr">
@@ -2005,6 +2082,19 @@
         <is>
           <t>تاریخ</t>
         </is>
+      </c>
+      <c r="R4" s="132" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="155" t="inlineStr">
+        <is>
+          <t>در حال شارژ؟ (1=بله، 0=نه)</t>
+        </is>
+      </c>
+      <c r="U4" s="156" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
@@ -2084,6 +2174,18 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="153">
+        <f>IF($U$5=7,"هر سه چراغ با هم چشمک می‌زنند، شارژ متوقف است و بوق خطای فنی می‌آید",IF($U$6=1,"سبز ثابت، زرد خاموش، قرمز چشمک‌زن و گهگاه بوق",IF($U$5=6,"سبز ثابت، زرد خاموش، قرمز چشمک تند (نیم‌ثانیه‌ای) و سه بوق دوره‌ای؛ شارژ صفر",IF($U$3=0,"روی باتری: سبز بر اساس درصد چشمک می‌زند؛ درصد فعلی "&amp;$U$2,IF($U$2&gt;=100,"شارژ کامل: سبز ثابت و زرد خاموش",IF($U$4=1,"در حال شارژ: سبز ثابت و زرد چشمک‌زن","با ورودی و بدون شارژ: سبز ثابت"))))))</f>
+        <v/>
+      </c>
+      <c r="T5" s="155" t="inlineStr">
+        <is>
+          <t>خطا (0=نداریم، 6=قطع باتری، 7=فنی)</t>
+        </is>
+      </c>
+      <c r="U5" s="156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="92" t="inlineStr">
@@ -2152,6 +2254,18 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="153">
+        <f>IF($U$2=0,"درصد صفر: بوق بحرانی و چشمک سریع سبز (باتری کاملاً خالی)",IF($U$2&lt;2,"درصد ۱: سه بوق دوره‌ای و برق کوتاه سبز","درصد بالاتر از ۱: رفتار عادی همان درصد"))</f>
+        <v/>
+      </c>
+      <c r="T6" s="155" t="inlineStr">
+        <is>
+          <t>اضافه‌ولتاژ ورودی؟ (1=بله، 0=نه)</t>
+        </is>
+      </c>
+      <c r="U6" s="156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="92" t="inlineStr">
@@ -2220,6 +2334,18 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="153">
+        <f>IF($U$2&gt;=100,"شارژ کامل: سبز ثابت و زرد خاموش",IF($U$2&gt;=95,"هنوز کامل نیست: زرد چشمک‌زن می‌ماند تا درصد به ۱۰۰ برسد","در حال شارژ عادی"))</f>
+        <v/>
+      </c>
+      <c r="T7" s="155" t="inlineStr">
+        <is>
+          <t>درصد خام (برای هیسترزیس)</t>
+        </is>
+      </c>
+      <c r="U7" s="156" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="92" t="inlineStr">
@@ -2297,6 +2423,18 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="153">
+        <f>IF($U$5=6,"خطای ۶ فعال: سبز ثابت، زرد خاموش، قرمز چشمک تند و سه بوق دوره‌ای؛ شارژ صفر",IF($U$5=0,"خطا را بساز: هنگام شارژ سیم باتری را بکش تا این چهره بیاید","خطای دیگری فعال است؛ اول خطا را ۶ کن"))</f>
+        <v/>
+      </c>
+      <c r="T8" s="155" t="inlineStr">
+        <is>
+          <t>درصد پایدار فعلی</t>
+        </is>
+      </c>
+      <c r="U8" s="156" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="92" t="inlineStr">
@@ -2369,6 +2507,18 @@
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
+      <c r="R9" s="153">
+        <f>IF($U$5=7,"خطای ۷ فعال: هر سه چراغ هم‌فاز چشمک می‌زنند و شارژ قفل است؛ فقط با خاموش و روشن‌کردن پاک می‌شود","خطای ۷ نیست: این چهره دیده نمی‌شود؛ خطا را ۷ کن")</f>
+        <v/>
+      </c>
+      <c r="T9" s="155" t="inlineStr">
+        <is>
+          <t>ولتاژ باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U9" s="156" t="n">
+        <v>24000</v>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="92" t="inlineStr">
@@ -2436,6 +2586,16 @@
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
+      <c r="R10" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="158" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="92" t="inlineStr">
@@ -2508,6 +2668,10 @@
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
+      <c r="R11" s="153">
+        <f>IF($U$6=1,"اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک‌زن و گهگاه بوق","ولتاژ عادی است: چهرهٔ اضافه‌ولتاژ نیست")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="92" t="inlineStr">
@@ -2578,6 +2742,10 @@
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
+      <c r="R12" s="153">
+        <f>IF($U$4=1,"در حال شارژ: شمارندهٔ باتری خراب جلو می‌رود؛ به حدش (پارامتر ۱۲۵) برسد قرمز ثابت و قفل شارژ","بدون شارژ فعال: شمارنده جلو نمی‌رود")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="92" t="inlineStr">
@@ -2645,6 +2813,10 @@
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
+      <c r="R13" s="153">
+        <f>IF($U$2&lt;=1,"درصد ۱ یا صفر: سه بوق دوره‌ای و برق کوتاه سبز",IF($U$2=2,"درصد ۲: الگوی درصد ۲","درصد بالاتر: الگوی همان درصد"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="92" t="inlineStr">
@@ -2712,6 +2884,10 @@
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
+      <c r="R14" s="153">
+        <f>IF($U$2&gt;=95,"کامل می‌ماند: سبز ثابت و زرد خاموش","زیر ۹۵: از کامل خارج می‌شود و شارژ از سر گرفته می‌شود")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="92" t="inlineStr">
@@ -2779,6 +2955,10 @@
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
+      <c r="R15" s="153">
+        <f>IF($U$2&lt;95,"خروج از کامل: زرد برمی‌گردد و شارژ ادامه می‌یابد","هنوز کامل است: سبز ثابت و زرد خاموش")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="92" t="inlineStr">
@@ -2846,6 +3026,11 @@
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
+      <c r="R16" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="92" t="inlineStr">
@@ -2914,6 +3099,11 @@
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
+      <c r="R17" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="92" t="inlineStr">
@@ -2981,6 +3171,10 @@
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
+      <c r="R18" s="153">
+        <f>IF($U$5=7,"هر سه چراغ با هم چشمک می‌زنند، شارژ متوقف است و بوق خطای فنی می‌آید",IF($U$6=1,"سبز ثابت، زرد خاموش، قرمز چشمک‌زن و گهگاه بوق",IF($U$5=6,"سبز ثابت، زرد خاموش، قرمز چشمک تند (نیم‌ثانیه‌ای) و سه بوق دوره‌ای؛ شارژ صفر",IF($U$3=0,"روی باتری: سبز بر اساس درصد چشمک می‌زند؛ درصد فعلی "&amp;$U$2,IF($U$2&gt;=100,"شارژ کامل: سبز ثابت و زرد خاموش",IF($U$4=1,"در حال شارژ: سبز ثابت و زرد چشمک‌زن","با ورودی و بدون شارژ: سبز ثابت"))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="92" t="inlineStr">
@@ -3050,6 +3244,10 @@
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
+      <c r="R19" s="153">
+        <f>IF($U$5=7,"هر سه چراغ با هم چشمک می‌زنند، شارژ متوقف است و بوق خطای فنی می‌آید",IF($U$6=1,"سبز ثابت، زرد خاموش، قرمز چشمک‌زن و گهگاه بوق",IF($U$5=6,"سبز ثابت، زرد خاموش، قرمز چشمک تند (نیم‌ثانیه‌ای) و سه بوق دوره‌ای؛ شارژ صفر",IF($U$3=0,"روی باتری: سبز بر اساس درصد چشمک می‌زند؛ درصد فعلی "&amp;$U$2,IF($U$2&gt;=100,"شارژ کامل: سبز ثابت و زرد خاموش",IF($U$4=1,"در حال شارژ: سبز ثابت و زرد چشمک‌زن","با ورودی و بدون شارژ: سبز ثابت"))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="92" t="inlineStr">
@@ -3120,6 +3318,10 @@
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
+      <c r="R20" s="153">
+        <f>IF($U$5=0,"قفل عدم‌توازن: فقط قرمز چشمک می‌زند و خروجی قطع است (ربطی به خطای ۶ و ۷ ندارد)","اول خطای فعال را صفر کن؛ قفل عدم‌توازن چهرهٔ خودش را دارد")</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="92" t="inlineStr">
@@ -3188,6 +3390,10 @@
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
+      <c r="R21" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="A22" s="92" t="inlineStr">
@@ -3256,6 +3462,10 @@
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
+      <c r="R22" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="54" customHeight="1">
       <c r="A23" s="92" t="inlineStr">
@@ -3324,6 +3534,10 @@
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
+      <c r="R23" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="54" customHeight="1">
       <c r="A24" s="92" t="inlineStr">
@@ -3391,6 +3605,10 @@
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
+      <c r="R24" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="54" customHeight="1">
       <c r="A25" s="92" t="inlineStr">
@@ -3458,6 +3676,10 @@
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
+      <c r="R25" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="40.5" customHeight="1">
       <c r="A26" s="92" t="inlineStr">
@@ -3525,6 +3747,10 @@
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
+      <c r="R26" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="54" customHeight="1">
       <c r="A27" s="92" t="inlineStr">
@@ -3592,6 +3818,10 @@
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
+      <c r="R27" s="153">
+        <f>"درصد پایدار می‌شود: "&amp;IF(AND($U$8=0,$U$7&lt;2),0,IF(AND($U$8=0,$U$7&gt;=2),1,IF(AND($U$8=1,$U$7=0),0,IF(AND($U$8=1,$U$7&gt;=3),2,IF(ABS($U$7-$U$8)&lt;2,$U$8,$U$7)))))&amp;" (خام "&amp;$U$7&amp;"، پایدار قبلی "&amp;$U$8&amp;")"</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="A28" s="92" t="inlineStr">
@@ -3659,6 +3889,10 @@
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
+      <c r="R28" s="153">
+        <f>"درصد پایدار شارژ می‌شود: "&amp;IF(ABS($U$7-$U$8)&lt;5,$U$8,$U$7)&amp;" (اختلاف کمتر از ۵ یعنی همان قبلی)"</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="54" customHeight="1">
       <c r="A29" s="92" t="inlineStr">
@@ -3726,6 +3960,10 @@
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
+      <c r="R29" s="153">
+        <f>"درصد پایدار شارژ می‌شود: "&amp;IF(ABS($U$7-$U$8)&lt;5,$U$8,$U$7)&amp;" (اختلاف کمتر از ۵ یعنی همان قبلی)"</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="40.5" customHeight="1">
       <c r="A30" s="92" t="inlineStr">
@@ -3794,6 +4032,10 @@
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
+      <c r="R30" s="153">
+        <f>"درصد پایدار شارژ می‌شود: "&amp;IF(ABS($U$7-$U$8)&lt;5,$U$8,$U$7)&amp;" (اختلاف کمتر از ۵ یعنی همان قبلی)"</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="54" customHeight="1">
       <c r="A31" s="92" t="inlineStr">
@@ -3861,6 +4103,10 @@
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
+      <c r="R31" s="153">
+        <f>IF($U$9&lt;21000,"آلارم باتری کم فعال می‌شود",IF($U$9&gt;21200,"آلارم باتری کم پاک می‌شود","بین ۲۱ تا ۲۱٫۲ ولت: آلارم همان قبلی می‌ماند (هیسترزیس)"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="54" customHeight="1">
       <c r="A32" s="92" t="inlineStr">
@@ -3932,6 +4178,11 @@
       <c r="Q32" s="136">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
+      </c>
+      <c r="R32" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -4677,8 +4928,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q67"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="T10:U10"/>
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -7958,7 +8211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7972,7 +8225,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -8021,7 +8273,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1873,6 +1873,7 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
@@ -1885,6 +1886,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="152" t="inlineStr">
         <is>
@@ -3128,13 +3130,13 @@
       </c>
       <c r="E18" s="134" t="inlineStr">
         <is>
-          <t>گام ۱: ولتاژ ورودی را آرام بین ۲۰ و ۲۱ ولت بالا و پایین کن.
+          <t>گام ۱: ولتاژ ورودی را آرام بین ۲۱ و ۲۱٫۵ ولت بالا و پایین کن.
 گام ۲: به چهرهٔ ورودی (سبز و رفتار شارژ) نگاه کن که تندتند عوض نشود.</t>
         </is>
       </c>
       <c r="F18" s="135" t="inlineStr">
         <is>
-          <t>ورودی بازی‌کنان دور ۲۰ تا ۲۱ ولت</t>
+          <t>ورودی بازی‌کنان دور ۲۱ تا ۲۱٫۵ ولت</t>
         </is>
       </c>
       <c r="G18" s="135" t="inlineStr">
@@ -6807,7 +6809,7 @@
     <row r="2">
       <c r="A2" s="90" t="inlineStr">
         <is>
-          <t>هیسترزیس: ورودی 20/21 (1000mV), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
+          <t>اشمیت مشترک ورودی: افتادن بیرون q33/q34، برگشت با q169/q170 (پیش‌فرض ۵۰۰/۵۰۰), BatteryRun 2%+0/1, Charging 5%, Full 100/95, Low 21/21.2, Overvoltage 27/28</t>
         </is>
       </c>
     </row>
@@ -8225,6 +8227,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1873,7 +1873,6 @@
       <c r="O18" s="28" t="n"/>
       <c r="P18" s="29" t="n"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="124" t="inlineStr">
         <is>
@@ -1886,7 +1885,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="152" t="inlineStr">
         <is>
@@ -7237,7 +7235,7 @@
       </c>
       <c r="B16" s="141" t="inlineStr">
         <is>
-          <t>&gt;28000 خطا &lt;=27000 پاک</t>
+          <t>&gt;q34 خطا &lt;=q34−q71 پاک</t>
         </is>
       </c>
       <c r="C16" s="141" t="inlineStr">
@@ -7252,7 +7250,7 @@
       </c>
       <c r="E16" s="141" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>q34/q71</t>
         </is>
       </c>
       <c r="F16" s="142" t="inlineStr">
@@ -8227,7 +8225,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
         <is>

--- a/Firmware/Modules/Ui/UI_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/UI_Board_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$67</definedName>
